--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A11138E-AABB-4335-9381-AB2B18E7B971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA0BF57-F3CF-412D-A657-300C4CB51917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4053,928 +4053,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="92">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0409\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0415\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5203D16-F0B5-429A-B727-136B1F5A377F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21F931-BB0C-473A-AE08-EE7A5E2C41E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="1305">
   <si>
     <t>替代规格2</t>
   </si>
@@ -3957,6 +3957,15 @@
   <si>
     <t>STC9A001G</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9902I</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-CI-X0NR-2434</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-CD-X0NR-2434</t>
   </si>
 </sst>
 </file>
@@ -9499,12 +9508,24 @@
       <c r="Q111" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="R111" s="1"/>
-      <c r="S111" s="1"/>
-      <c r="T111" s="1"/>
-      <c r="U111" s="1"/>
-      <c r="V111" s="1"/>
-      <c r="W111" s="1"/>
+      <c r="R111" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="S111" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="T111" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="U111" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="V111" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="W111" s="1" t="s">
+        <v>1304</v>
+      </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0415\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21F931-BB0C-473A-AE08-EE7A5E2C41E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88583AE0-43DA-4BEE-BF29-34283F43D524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="1323">
   <si>
     <t>替代规格2</t>
   </si>
@@ -2965,9 +2965,6 @@
     <t>SC243XSO-118113-TR-Q</t>
   </si>
   <si>
-    <t>SC1134UA-CI-00AY-44E</t>
-  </si>
-  <si>
     <t>SC4011DN-CB-90LR-4011</t>
   </si>
   <si>
@@ -3966,13 +3963,81 @@
   </si>
   <si>
     <t>SC2434SO-N-CD-X0NR-2434</t>
+  </si>
+  <si>
+    <t>SC1134UA-CF-90AK-1134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CF-90AK-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CF-90AK-44L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-90AY-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AY-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC69401DC-SPI3P3-Q-HD-4XAR-69401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2203SO-TR</t>
+  </si>
+  <si>
+    <t>SC2203SO-CH-10AR-2203</t>
+  </si>
+  <si>
+    <t>SC2203SO-CH-10NR-2203</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC2G201A</t>
+  </si>
+  <si>
+    <t>SC24023SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-N-GA-00NR-2403</t>
+  </si>
+  <si>
+    <t>SC24023SO-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-GA-00NR-2403</t>
+  </si>
+  <si>
+    <t>SC2403SO-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-DB-00NR-2403</t>
+  </si>
+  <si>
+    <t>SC2403SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-N-DB-00NR-2403</t>
+  </si>
+  <si>
+    <t>宁芯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3986,6 +4051,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4041,17 +4113,1619 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="160">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4327,7 +6001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}">
-  <dimension ref="A1:W341"/>
+  <dimension ref="A1:W344"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -4357,46 +6031,46 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>996</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>997</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>998</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>1004</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>2</v>
@@ -4434,7 +6108,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -4443,7 +6117,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>909</v>
@@ -4612,22 +6286,22 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B6" t="s">
         <v>1289</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>1290</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>1290</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1292</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -4694,7 +6368,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -4760,7 +6434,7 @@
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>909</v>
@@ -4797,7 +6471,7 @@
         <v>123</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>905</v>
+        <v>1305</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>909</v>
@@ -4809,12 +6483,18 @@
         <v>584</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>905</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -4836,7 +6516,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>903</v>
+        <v>1304</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>909</v>
@@ -4848,12 +6528,18 @@
         <v>584</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -4875,7 +6561,7 @@
         <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>904</v>
+        <v>1306</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>909</v>
@@ -4887,12 +6573,18 @@
         <v>584</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>904</v>
+      </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -4908,7 +6600,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>31</v>
@@ -4917,7 +6609,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>30</v>
@@ -4963,7 +6655,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>914</v>
@@ -5010,7 +6702,7 @@
         <v>40</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -5068,7 +6760,7 @@
         <v>36</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>32</v>
@@ -5097,7 +6789,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>909</v>
@@ -5269,7 +6961,7 @@
         <v>971</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>909</v>
@@ -5318,7 +7010,7 @@
         <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>845</v>
@@ -5347,7 +7039,7 @@
         <v>62</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>35</v>
@@ -5365,7 +7057,7 @@
         <v>62</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.2">
@@ -5416,7 +7108,7 @@
         <v>67</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>35</v>
@@ -5448,7 +7140,7 @@
         <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>909</v>
@@ -5470,7 +7162,7 @@
         <v>69</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -5562,7 +7254,7 @@
         <v>73</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>35</v>
@@ -5603,7 +7295,7 @@
         <v>76</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>909</v>
@@ -5623,7 +7315,7 @@
         <v>76</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -5646,7 +7338,7 @@
         <v>62</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>913</v>
@@ -5666,7 +7358,7 @@
         <v>62</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -5750,7 +7442,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>909</v>
@@ -5942,7 +7634,7 @@
         <v>615</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>916</v>
@@ -5987,7 +7679,7 @@
         <v>902</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>916</v>
@@ -6038,7 +7730,7 @@
         <v>100</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>913</v>
@@ -6204,7 +7896,7 @@
         <v>114</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -6405,7 +8097,7 @@
         <v>123</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>974</v>
+        <v>1308</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>909</v>
@@ -6420,9 +8112,15 @@
         <v>124</v>
       </c>
       <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
+      <c r="L43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>1307</v>
+      </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
@@ -6681,7 +8379,7 @@
         <v>583</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
@@ -6720,7 +8418,7 @@
         <v>148</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>917</v>
@@ -7095,10 +8793,10 @@
         <v>143</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>1294</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>1295</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>916</v>
@@ -7158,10 +8856,10 @@
         <v>143</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>1296</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>1297</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>916</v>
@@ -7192,7 +8890,7 @@
         <v>164</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
@@ -7986,7 +9684,7 @@
         <v>230</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>229</v>
@@ -8841,7 +10539,7 @@
         <v>270</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>911</v>
@@ -9047,7 +10745,7 @@
         <v>580</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -9080,7 +10778,7 @@
         <v>561</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>913</v>
@@ -9092,7 +10790,7 @@
         <v>580</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -9137,7 +10835,7 @@
         <v>580</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -9182,7 +10880,7 @@
         <v>580</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
@@ -9215,7 +10913,7 @@
         <v>719</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>845</v>
@@ -9227,7 +10925,7 @@
         <v>580</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -9266,7 +10964,7 @@
         <v>580</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -9342,7 +11040,7 @@
         <v>297</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>845</v>
@@ -9362,7 +11060,7 @@
         <v>297</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
@@ -9448,7 +11146,7 @@
         <v>937</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
@@ -9477,7 +11175,7 @@
         <v>303</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>914</v>
@@ -9509,13 +11207,13 @@
         <v>304</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>303</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="U111" s="1" t="s">
         <v>621</v>
@@ -9524,7 +11222,7 @@
         <v>303</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.2">
@@ -9589,7 +11287,7 @@
         <v>312</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>845</v>
@@ -9627,7 +11325,7 @@
         <v>312</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
@@ -9828,7 +11526,7 @@
         <v>331</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>914</v>
@@ -10143,7 +11841,7 @@
         <v>357</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>845</v>
@@ -10163,7 +11861,7 @@
         <v>357</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
@@ -10192,7 +11890,7 @@
         <v>361</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>909</v>
@@ -10284,7 +11982,7 @@
         <v>611</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>914</v>
@@ -10304,7 +12002,7 @@
         <v>611</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
@@ -10327,7 +12025,7 @@
         <v>611</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>914</v>
@@ -10503,7 +12201,7 @@
         <v>370</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
@@ -10532,7 +12230,7 @@
         <v>320</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>845</v>
@@ -10552,7 +12250,7 @@
         <v>320</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
@@ -10581,7 +12279,7 @@
         <v>755</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>914</v>
@@ -10601,7 +12299,7 @@
         <v>755</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
@@ -10630,7 +12328,7 @@
         <v>379</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>914</v>
@@ -10679,7 +12377,7 @@
         <v>62</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>913</v>
@@ -10708,7 +12406,7 @@
         <v>62</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
@@ -10777,7 +12475,7 @@
         <v>383</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>845</v>
@@ -10797,7 +12495,7 @@
         <v>383</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
@@ -10820,7 +12518,7 @@
         <v>392</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>845</v>
@@ -10849,7 +12547,7 @@
         <v>392</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
@@ -11010,7 +12708,7 @@
         <v>410</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>916</v>
@@ -11032,7 +12730,7 @@
         <v>410</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="O144" s="1" t="s">
         <v>35</v>
@@ -11050,7 +12748,7 @@
         <v>410</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="U144" s="1" t="s">
         <v>407</v>
@@ -11091,7 +12789,7 @@
         <v>594</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
@@ -11124,10 +12822,10 @@
         <v>415</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G146" s="1" t="s">
         <v>1299</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>1300</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>729</v>
@@ -11136,7 +12834,7 @@
         <v>594</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="K146" s="1"/>
       <c r="L146" s="1" t="s">
@@ -11226,7 +12924,7 @@
         <v>436</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>918</v>
@@ -11248,7 +12946,7 @@
         <v>436</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>433</v>
@@ -11277,7 +12975,7 @@
         <v>52</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>916</v>
@@ -11316,7 +13014,7 @@
         <v>159</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>916</v>
@@ -11338,7 +13036,7 @@
         <v>159</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
@@ -11352,25 +13050,25 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F151" s="1" t="s">
+      <c r="G151" s="1" t="s">
         <v>1068</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>1069</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>562</v>
@@ -11408,7 +13106,7 @@
         <v>438</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>918</v>
@@ -11433,7 +13131,7 @@
         <v>439</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>438</v>
@@ -11465,7 +13163,7 @@
         <v>448</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>920</v>
@@ -11477,7 +13175,7 @@
         <v>580</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
@@ -11487,7 +13185,7 @@
         <v>448</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="O153" s="1"/>
       <c r="P153" s="1"/>
@@ -11516,7 +13214,7 @@
         <v>451</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>920</v>
@@ -11528,7 +13226,7 @@
         <v>580</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
@@ -11538,7 +13236,7 @@
         <v>451</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
@@ -11567,7 +13265,7 @@
         <v>454</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>920</v>
@@ -11579,7 +13277,7 @@
         <v>580</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
@@ -11589,7 +13287,7 @@
         <v>454</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
@@ -11618,7 +13316,7 @@
         <v>654</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>920</v>
@@ -11630,7 +13328,7 @@
         <v>580</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K156" s="1"/>
       <c r="L156" s="1" t="s">
@@ -11640,7 +13338,7 @@
         <v>654</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
@@ -11669,7 +13367,7 @@
         <v>457</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>913</v>
@@ -11714,7 +13412,7 @@
         <v>458</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>920</v>
@@ -11726,7 +13424,7 @@
         <v>580</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1" t="s">
@@ -11736,7 +13434,7 @@
         <v>458</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
@@ -11765,10 +13463,10 @@
         <v>459</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>562</v>
@@ -11777,7 +13475,7 @@
         <v>580</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
@@ -11816,19 +13514,19 @@
         <v>467</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="J160" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
@@ -11861,7 +13559,7 @@
         <v>468</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>909</v>
@@ -11910,7 +13608,7 @@
         <v>469</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>909</v>
@@ -11959,19 +13657,19 @@
         <v>469</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H163" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I163" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="I163" s="1" t="s">
-        <v>1085</v>
-      </c>
       <c r="J163" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="K163" s="1"/>
       <c r="L163" s="1" t="s">
@@ -12010,19 +13708,19 @@
         <v>475</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H164" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I164" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="I164" s="1" t="s">
-        <v>1085</v>
-      </c>
       <c r="J164" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="1" t="s">
@@ -12061,7 +13759,7 @@
         <v>479</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>909</v>
@@ -12070,7 +13768,7 @@
         <v>54</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
@@ -12110,7 +13808,7 @@
         <v>482</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>831</v>
@@ -12119,10 +13817,10 @@
         <v>54</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="K166" s="1"/>
       <c r="L166" s="1" t="s">
@@ -12161,7 +13859,7 @@
         <v>482</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>913</v>
@@ -12170,7 +13868,7 @@
         <v>563</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
@@ -12204,7 +13902,7 @@
         <v>488</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>909</v>
@@ -12213,7 +13911,7 @@
         <v>54</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
@@ -12238,7 +13936,7 @@
         <v>489</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>969</v>
@@ -12247,7 +13945,7 @@
         <v>489</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>913</v>
@@ -12256,7 +13954,7 @@
         <v>563</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
@@ -12284,19 +13982,19 @@
         <v>491</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
@@ -12329,19 +14027,19 @@
         <v>491</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
@@ -12374,19 +14072,19 @@
         <v>494</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I172" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J172" s="1" t="s">
         <v>1104</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>1105</v>
       </c>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
@@ -12410,7 +14108,7 @@
         <v>495</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>476</v>
@@ -12419,7 +14117,7 @@
         <v>495</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>913</v>
@@ -12428,7 +14126,7 @@
         <v>563</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -12456,19 +14154,19 @@
         <v>756</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
@@ -12501,19 +14199,19 @@
         <v>497</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K175" s="1"/>
       <c r="L175" s="1" t="s">
@@ -12541,7 +14239,7 @@
         <v>497</v>
       </c>
       <c r="T175" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="U175" s="1" t="s">
         <v>476</v>
@@ -12550,7 +14248,7 @@
         <v>497</v>
       </c>
       <c r="W175" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.2">
@@ -12561,7 +14259,7 @@
         <v>499</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>476</v>
@@ -12570,7 +14268,7 @@
         <v>499</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>913</v>
@@ -12579,7 +14277,7 @@
         <v>563</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
@@ -12613,19 +14311,19 @@
         <v>499</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -12658,19 +14356,19 @@
         <v>500</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K178" s="1"/>
       <c r="L178" s="1" t="s">
@@ -12709,19 +14407,19 @@
         <v>499</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1" t="s">
@@ -12740,7 +14438,7 @@
         <v>499</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>476</v>
@@ -12749,7 +14447,7 @@
         <v>499</v>
       </c>
       <c r="T179" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="U179" s="1" t="s">
         <v>969</v>
@@ -12758,7 +14456,7 @@
         <v>499</v>
       </c>
       <c r="W179" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.2">
@@ -12778,7 +14476,7 @@
         <v>610</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>913</v>
@@ -12835,7 +14533,7 @@
         <v>524</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>909</v>
@@ -12878,13 +14576,13 @@
         <v>525</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>879</v>
@@ -12923,7 +14621,7 @@
         <v>526</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>909</v>
@@ -12966,19 +14664,19 @@
         <v>526</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I184" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="J184" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
@@ -13011,19 +14709,19 @@
         <v>529</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
@@ -13056,7 +14754,7 @@
         <v>533</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>909</v>
@@ -13099,7 +14797,7 @@
         <v>536</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>911</v>
@@ -13142,7 +14840,7 @@
         <v>540</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>911</v>
@@ -13185,13 +14883,13 @@
         <v>270</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>912</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>578</v>
@@ -13260,7 +14958,7 @@
         <v>965</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
@@ -13289,7 +14987,7 @@
         <v>278</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>909</v>
@@ -13301,7 +14999,7 @@
         <v>584</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
@@ -13328,7 +15026,7 @@
         <v>278</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>909</v>
@@ -13340,7 +15038,7 @@
         <v>584</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
@@ -13373,7 +15071,7 @@
         <v>278</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>909</v>
@@ -13416,7 +15114,7 @@
         <v>278</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>909</v>
@@ -13428,7 +15126,7 @@
         <v>581</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
@@ -13461,7 +15159,7 @@
         <v>278</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>909</v>
@@ -13473,7 +15171,7 @@
         <v>581</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
@@ -13497,7 +15195,7 @@
         <v>273</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>545</v>
@@ -13535,7 +15233,7 @@
         <v>270</v>
       </c>
       <c r="Q196" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
@@ -13561,7 +15259,7 @@
         <v>443</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>909</v>
@@ -13636,7 +15334,7 @@
         <v>553</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
@@ -13665,7 +15363,7 @@
         <v>557</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>909</v>
@@ -13685,7 +15383,7 @@
         <v>557</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -13708,19 +15406,19 @@
         <v>561</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
@@ -13747,19 +15445,19 @@
         <v>561</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
@@ -13789,10 +15487,10 @@
         <v>571</v>
       </c>
       <c r="G202" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H202" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H202" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>590</v>
@@ -13826,10 +15524,10 @@
         <v>574</v>
       </c>
       <c r="G203" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H203" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H203" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>590</v>
@@ -13863,10 +15561,10 @@
         <v>577</v>
       </c>
       <c r="G204" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H204" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -13895,7 +15593,7 @@
         <v>323</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>909</v>
@@ -13944,7 +15642,7 @@
         <v>620</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>911</v>
@@ -13987,7 +15685,7 @@
         <v>624</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>911</v>
@@ -14036,7 +15734,7 @@
         <v>626</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>921</v>
@@ -14099,7 +15797,7 @@
         <v>631</v>
       </c>
       <c r="N209" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
@@ -14142,7 +15840,7 @@
         <v>936</v>
       </c>
       <c r="N210" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
@@ -14171,7 +15869,7 @@
         <v>637</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>909</v>
@@ -14209,7 +15907,7 @@
         <v>637</v>
       </c>
       <c r="T211" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -14246,7 +15944,7 @@
         <v>638</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O212" s="1"/>
       <c r="P212" s="1"/>
@@ -14269,7 +15967,7 @@
         <v>641</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>916</v>
@@ -14281,7 +15979,7 @@
         <v>579</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K213" s="1"/>
       <c r="L213" s="1"/>
@@ -14308,7 +16006,7 @@
         <v>642</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>916</v>
@@ -14320,7 +16018,7 @@
         <v>579</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
@@ -14347,7 +16045,7 @@
         <v>773</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>916</v>
@@ -14359,7 +16057,7 @@
         <v>579</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K215" s="1"/>
       <c r="L215" s="1"/>
@@ -14392,19 +16090,19 @@
         <v>646</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K216" s="1"/>
       <c r="L216" s="1"/>
@@ -14431,7 +16129,7 @@
         <v>651</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>910</v>
@@ -14451,7 +16149,7 @@
         <v>651</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
@@ -14480,7 +16178,7 @@
         <v>658</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>909</v>
@@ -14523,7 +16221,7 @@
         <v>662</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>909</v>
@@ -14560,19 +16258,19 @@
         <v>505</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I220" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J220" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
@@ -14605,13 +16303,13 @@
         <v>845</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I221" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J221" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
@@ -14644,13 +16342,13 @@
         <v>845</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I222" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J222" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J222" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
@@ -14683,13 +16381,13 @@
         <v>845</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I223" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J223" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J223" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -14722,13 +16420,13 @@
         <v>845</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I224" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J224" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J224" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
@@ -14761,13 +16459,13 @@
         <v>845</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I225" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J225" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J225" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
@@ -14800,13 +16498,13 @@
         <v>845</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I226" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J226" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J226" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K226" s="1"/>
       <c r="L226" s="1"/>
@@ -14833,19 +16531,19 @@
         <v>506</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I227" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J227" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J227" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K227" s="1"/>
       <c r="L227" s="1"/>
@@ -14878,13 +16576,13 @@
         <v>845</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I228" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J228" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J228" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K228" s="1"/>
       <c r="L228" s="1"/>
@@ -14917,13 +16615,13 @@
         <v>845</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I229" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J229" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J229" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -14956,13 +16654,13 @@
         <v>845</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I230" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J230" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J230" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
@@ -14995,13 +16693,13 @@
         <v>845</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I231" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J231" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J231" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
@@ -15034,13 +16732,13 @@
         <v>845</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I232" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J232" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J232" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -15073,13 +16771,13 @@
         <v>845</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I233" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J233" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J233" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
@@ -15112,13 +16810,13 @@
         <v>845</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I234" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J234" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J234" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
@@ -15151,13 +16849,13 @@
         <v>845</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I235" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J235" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J235" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -15190,13 +16888,13 @@
         <v>845</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I236" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J236" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J236" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K236" s="1"/>
       <c r="L236" s="1"/>
@@ -15229,13 +16927,13 @@
         <v>845</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I237" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J237" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J237" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
@@ -15268,19 +16966,19 @@
         <v>720</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I238" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J238" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J238" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
@@ -15313,7 +17011,7 @@
         <v>509</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>909</v>
@@ -15333,7 +17031,7 @@
         <v>509</v>
       </c>
       <c r="N239" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
@@ -15362,7 +17060,7 @@
         <v>509</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>909</v>
@@ -15382,7 +17080,7 @@
         <v>509</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
@@ -15405,7 +17103,7 @@
         <v>673</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>909</v>
@@ -15450,10 +17148,10 @@
         <v>960</v>
       </c>
       <c r="H242" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I242" s="1" t="s">
         <v>1179</v>
-      </c>
-      <c r="I242" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>959</v>
@@ -15489,13 +17187,13 @@
         <v>845</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>589</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -15512,53 +17210,39 @@
       <c r="W243" s="1"/>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A244" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>678</v>
-      </c>
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
       <c r="D244" s="1" t="s">
-        <v>607</v>
+        <v>35</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>843</v>
+        <v>1318</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>842</v>
+        <v>1319</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H244" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="I244" s="1"/>
-      <c r="J244" s="1" t="s">
-        <v>841</v>
-      </c>
+        <v>1322</v>
+      </c>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="J244" s="1"/>
       <c r="K244" s="1"/>
       <c r="L244" s="1" t="s">
-        <v>607</v>
+        <v>1313</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>677</v>
+        <v>1314</v>
       </c>
       <c r="N244" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="O244" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="P244" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="Q244" s="1" t="s">
-        <v>1183</v>
-      </c>
+        <v>1315</v>
+      </c>
+      <c r="O244" s="1"/>
+      <c r="P244" s="1"/>
+      <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
       <c r="T244" s="1"/>
@@ -15567,38 +17251,36 @@
       <c r="W244" s="1"/>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A245" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>765</v>
-      </c>
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
       <c r="D245" s="1" t="s">
-        <v>625</v>
+        <v>35</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>681</v>
+        <v>1320</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>682</v>
+        <v>1321</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="H245" s="1" t="s">
-        <v>562</v>
-      </c>
+        <v>1322</v>
+      </c>
+      <c r="H245" s="1"/>
       <c r="I245" s="1" t="s">
-        <v>1184</v>
+        <v>578</v>
       </c>
       <c r="J245" s="1"/>
       <c r="K245" s="1"/>
-      <c r="L245" s="1"/>
-      <c r="M245" s="1"/>
-      <c r="N245" s="1"/>
+      <c r="L245" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="M245" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="N245" s="1" t="s">
+        <v>1317</v>
+      </c>
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
@@ -15611,34 +17293,52 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>545</v>
+        <v>676</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="D246" s="1"/>
-      <c r="E246" s="1"/>
-      <c r="F246" s="1"/>
+        <v>678</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>842</v>
+      </c>
       <c r="G246" s="1" t="s">
-        <v>921</v>
+        <v>1181</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="I246" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="J246" s="1"/>
+        <v>729</v>
+      </c>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1" t="s">
+        <v>841</v>
+      </c>
       <c r="K246" s="1"/>
-      <c r="L246" s="1"/>
-      <c r="M246" s="1"/>
-      <c r="N246" s="1"/>
-      <c r="O246" s="1"/>
-      <c r="P246" s="1"/>
-      <c r="Q246" s="1"/>
+      <c r="L246" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M246" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="N246" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="O246" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="P246" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q246" s="1" t="s">
+        <v>1182</v>
+      </c>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
       <c r="T246" s="1"/>
@@ -15647,26 +17347,32 @@
       <c r="W246" s="1"/>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A247" s="1"/>
-      <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
+      <c r="A247" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>765</v>
+      </c>
       <c r="D247" s="1" t="s">
-        <v>35</v>
+        <v>625</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1186</v>
+        <v>682</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>578</v>
+        <v>1183</v>
       </c>
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
@@ -15684,26 +17390,26 @@
       <c r="W247" s="1"/>
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A248" s="1"/>
-      <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-      <c r="D248" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>1187</v>
-      </c>
+      <c r="A248" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
       <c r="G248" s="1" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>580</v>
+        <v>1184</v>
       </c>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -15725,13 +17431,13 @@
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1" t="s">
-        <v>688</v>
+        <v>35</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>909</v>
@@ -15740,7 +17446,7 @@
         <v>54</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -15758,23 +17464,23 @@
       <c r="W249" s="1"/>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A250" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="D250" s="1"/>
-      <c r="E250" s="1"/>
-      <c r="F250" s="1"/>
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>1186</v>
+      </c>
       <c r="G250" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>580</v>
@@ -15799,36 +17505,28 @@
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1" t="s">
-        <v>433</v>
+        <v>688</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>436</v>
+        <v>689</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J251" s="1" t="s">
-        <v>848</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J251" s="1"/>
       <c r="K251" s="1"/>
-      <c r="L251" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="M251" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="N251" s="1" t="s">
-        <v>1190</v>
-      </c>
+      <c r="L251" s="1"/>
+      <c r="M251" s="1"/>
+      <c r="N251" s="1"/>
       <c r="O251" s="1"/>
       <c r="P251" s="1"/>
       <c r="Q251" s="1"/>
@@ -15840,26 +17538,26 @@
       <c r="W251" s="1"/>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A252" s="1"/>
-      <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-      <c r="D252" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>1191</v>
-      </c>
+      <c r="A252" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -15877,38 +17575,40 @@
       <c r="W252" s="1"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A253" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>697</v>
-      </c>
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
       <c r="D253" s="1" t="s">
-        <v>695</v>
+        <v>433</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>696</v>
+        <v>436</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="J253" s="1"/>
+        <v>594</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>848</v>
+      </c>
       <c r="K253" s="1"/>
-      <c r="L253" s="1"/>
-      <c r="M253" s="1"/>
-      <c r="N253" s="1"/>
+      <c r="L253" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="M253" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N253" s="1" t="s">
+        <v>1189</v>
+      </c>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
@@ -15920,26 +17620,26 @@
       <c r="W253" s="1"/>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A254" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="D254" s="1"/>
-      <c r="E254" s="1"/>
-      <c r="F254" s="1"/>
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>1190</v>
+      </c>
       <c r="G254" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>1104</v>
+        <v>594</v>
       </c>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
@@ -15958,22 +17658,22 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>791</v>
+        <v>696</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>792</v>
+        <v>697</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>909</v>
@@ -15982,7 +17682,7 @@
         <v>54</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>586</v>
+        <v>1192</v>
       </c>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
@@ -16000,26 +17700,26 @@
       <c r="W255" s="1"/>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A256" s="1"/>
-      <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-      <c r="D256" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E256" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F256" s="1" t="s">
-        <v>1195</v>
-      </c>
+      <c r="A256" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>581</v>
+        <v>1103</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -16037,17 +17737,23 @@
       <c r="W256" s="1"/>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A257" s="1"/>
-      <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
+      <c r="A257" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>792</v>
+      </c>
       <c r="D257" s="1" t="s">
-        <v>259</v>
+        <v>701</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>909</v>
@@ -16056,7 +17762,7 @@
         <v>54</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -16078,22 +17784,22 @@
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1" t="s">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -16115,13 +17821,13 @@
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>316</v>
+        <v>704</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>909</v>
@@ -16148,29 +17854,23 @@
       <c r="W259" s="1"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A260" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>801</v>
-      </c>
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
       <c r="D260" s="1" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>388</v>
+        <v>705</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>578</v>
@@ -16195,22 +17895,22 @@
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>706</v>
+        <v>316</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="J261" s="1"/>
       <c r="K261" s="1"/>
@@ -16228,23 +17928,29 @@
       <c r="W261" s="1"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A262" s="1"/>
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
+      <c r="A262" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>801</v>
+      </c>
       <c r="D262" s="1" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>707</v>
+        <v>388</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>578</v>
@@ -16272,19 +17978,19 @@
         <v>35</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>398</v>
+        <v>706</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
@@ -16306,13 +18012,13 @@
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1" t="s">
-        <v>686</v>
+        <v>35</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>913</v>
@@ -16321,7 +18027,7 @@
         <v>563</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -16343,22 +18049,22 @@
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1" t="s">
-        <v>601</v>
+        <v>35</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>709</v>
+        <v>398</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -16380,13 +18086,13 @@
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1" t="s">
-        <v>601</v>
+        <v>686</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>913</v>
@@ -16395,7 +18101,7 @@
         <v>563</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>586</v>
+        <v>928</v>
       </c>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -16413,23 +18119,17 @@
       <c r="W266" s="1"/>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A267" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>712</v>
-      </c>
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
       <c r="D267" s="1" t="s">
-        <v>212</v>
+        <v>601</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>976</v>
+        <v>709</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>913</v>
@@ -16438,19 +18138,13 @@
         <v>563</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>1185</v>
+        <v>586</v>
       </c>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
-      <c r="L267" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M267" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="N267" s="1" t="s">
-        <v>975</v>
-      </c>
+      <c r="L267" s="1"/>
+      <c r="M267" s="1"/>
+      <c r="N267" s="1"/>
       <c r="O267" s="1"/>
       <c r="P267" s="1"/>
       <c r="Q267" s="1"/>
@@ -16462,18 +18156,18 @@
       <c r="W267" s="1"/>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A268" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="D268" s="1"/>
-      <c r="E268" s="1"/>
-      <c r="F268" s="1"/>
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>1204</v>
+      </c>
       <c r="G268" s="1" t="s">
         <v>913</v>
       </c>
@@ -16481,7 +18175,7 @@
         <v>563</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
@@ -16499,32 +18193,44 @@
       <c r="W268" s="1"/>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A269" s="1"/>
-      <c r="B269" s="1"/>
-      <c r="C269" s="1"/>
+      <c r="A269" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>712</v>
+      </c>
       <c r="D269" s="1" t="s">
-        <v>464</v>
+        <v>212</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>469</v>
+        <v>975</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>589</v>
+        <v>1184</v>
       </c>
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
-      <c r="L269" s="1"/>
-      <c r="M269" s="1"/>
-      <c r="N269" s="1"/>
+      <c r="L269" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M269" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="N269" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="O269" s="1"/>
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
@@ -16537,23 +18243,17 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>676</v>
+        <v>640</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>814</v>
+        <v>713</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="F270" s="1" t="s">
-        <v>1208</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
       <c r="G270" s="1" t="s">
         <v>913</v>
       </c>
@@ -16561,11 +18261,9 @@
         <v>563</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J270" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="J270" s="1"/>
       <c r="K270" s="1"/>
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
@@ -16585,19 +18283,19 @@
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1" t="s">
-        <v>607</v>
+        <v>464</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>716</v>
+        <v>469</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1210</v>
+        <v>909</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>589</v>
@@ -16618,28 +18316,36 @@
       <c r="W271" s="1"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A272" s="1"/>
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
+      <c r="A272" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>815</v>
+      </c>
       <c r="D272" s="1" t="s">
         <v>607</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1210</v>
+        <v>913</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="J272" s="1"/>
+      <c r="J272" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K272" s="1"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
@@ -16659,22 +18365,22 @@
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1" t="s">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>913</v>
+        <v>1209</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="J273" s="1"/>
       <c r="K273" s="1"/>
@@ -16696,22 +18402,22 @@
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1" t="s">
-        <v>724</v>
+        <v>607</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>909</v>
+        <v>1209</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="J274" s="1"/>
       <c r="K274" s="1"/>
@@ -16733,26 +18439,24 @@
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1" t="s">
-        <v>693</v>
+        <v>648</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>845</v>
+        <v>913</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>1084</v>
+        <v>563</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J275" s="1" t="s">
-        <v>1215</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="J275" s="1"/>
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
@@ -16772,36 +18476,28 @@
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="J276" s="1" t="s">
-        <v>854</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="J276" s="1"/>
       <c r="K276" s="1"/>
-      <c r="L276" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="M276" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="N276" s="1" t="s">
-        <v>865</v>
-      </c>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+      <c r="N276" s="1"/>
       <c r="O276" s="1"/>
       <c r="P276" s="1"/>
       <c r="Q276" s="1"/>
@@ -16817,24 +18513,26 @@
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1" t="s">
-        <v>572</v>
+        <v>693</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>746</v>
+        <v>694</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1148</v>
+        <v>845</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>1149</v>
+        <v>1083</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J277" s="1"/>
+        <v>1169</v>
+      </c>
+      <c r="J277" s="1" t="s">
+        <v>1214</v>
+      </c>
       <c r="K277" s="1"/>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
@@ -16854,30 +18552,36 @@
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>763</v>
+        <v>727</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>932</v>
+        <v>1215</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>916</v>
+        <v>845</v>
       </c>
       <c r="H278" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>583</v>
+        <v>1192</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>933</v>
+        <v>854</v>
       </c>
       <c r="K278" s="1"/>
-      <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-      <c r="N278" s="1"/>
+      <c r="L278" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="M278" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="N278" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="O278" s="1"/>
       <c r="P278" s="1"/>
       <c r="Q278" s="1"/>
@@ -16893,26 +18597,24 @@
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1" t="s">
-        <v>747</v>
+        <v>572</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>916</v>
+        <v>1147</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>54</v>
+        <v>1148</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J279" s="1" t="s">
-        <v>1220</v>
-      </c>
+        <v>1217</v>
+      </c>
+      <c r="J279" s="1"/>
       <c r="K279" s="1"/>
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
@@ -16932,36 +18634,30 @@
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1" t="s">
-        <v>179</v>
+        <v>747</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>851</v>
+        <v>932</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H280" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>832</v>
+        <v>933</v>
       </c>
       <c r="K280" s="1"/>
-      <c r="L280" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M280" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="N280" s="1" t="s">
-        <v>850</v>
-      </c>
+      <c r="L280" s="1"/>
+      <c r="M280" s="1"/>
+      <c r="N280" s="1"/>
       <c r="O280" s="1"/>
       <c r="P280" s="1"/>
       <c r="Q280" s="1"/>
@@ -16977,34 +18673,30 @@
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1" t="s">
-        <v>49</v>
+        <v>747</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>985</v>
+        <v>748</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>987</v>
+        <v>1218</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H281" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J281" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="J281" s="1" t="s">
+        <v>1219</v>
+      </c>
       <c r="K281" s="1"/>
-      <c r="L281" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M281" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="N281" s="1" t="s">
-        <v>986</v>
-      </c>
+      <c r="L281" s="1"/>
+      <c r="M281" s="1"/>
+      <c r="N281" s="1"/>
       <c r="O281" s="1"/>
       <c r="P281" s="1"/>
       <c r="Q281" s="1"/>
@@ -17020,33 +18712,35 @@
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1" t="s">
-        <v>858</v>
+        <v>179</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>270</v>
+        <v>751</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>990</v>
+        <v>851</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J282" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>832</v>
+      </c>
       <c r="K282" s="1"/>
       <c r="L282" s="1" t="s">
-        <v>858</v>
+        <v>179</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>270</v>
+        <v>751</v>
       </c>
       <c r="N282" s="1" t="s">
-        <v>1221</v>
+        <v>850</v>
       </c>
       <c r="O282" s="1"/>
       <c r="P282" s="1"/>
@@ -17059,64 +18753,44 @@
       <c r="W282" s="1"/>
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A283" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B283" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
       <c r="D283" s="1" t="s">
-        <v>291</v>
+        <v>49</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>294</v>
+        <v>984</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>757</v>
+        <v>986</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>1084</v>
+        <v>54</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J283" s="1" t="s">
-        <v>1222</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J283" s="1"/>
       <c r="K283" s="1"/>
       <c r="L283" s="1" t="s">
-        <v>686</v>
+        <v>49</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>294</v>
+        <v>984</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="O283" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="P283" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q283" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="R283" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="S283" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T283" s="1" t="s">
-        <v>908</v>
-      </c>
+        <v>985</v>
+      </c>
+      <c r="O283" s="1"/>
+      <c r="P283" s="1"/>
+      <c r="Q283" s="1"/>
+      <c r="R283" s="1"/>
+      <c r="S283" s="1"/>
+      <c r="T283" s="1"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -17126,28 +18800,34 @@
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1" t="s">
-        <v>269</v>
+        <v>858</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>754</v>
+        <v>270</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1224</v>
+        <v>989</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>578</v>
       </c>
       <c r="J284" s="1"/>
       <c r="K284" s="1"/>
-      <c r="L284" s="1"/>
-      <c r="M284" s="1"/>
-      <c r="N284" s="1"/>
+      <c r="L284" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="M284" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="N284" s="1" t="s">
+        <v>1220</v>
+      </c>
       <c r="O284" s="1"/>
       <c r="P284" s="1"/>
       <c r="Q284" s="1"/>
@@ -17159,44 +18839,64 @@
       <c r="W284" s="1"/>
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A285" s="1"/>
-      <c r="B285" s="1"/>
-      <c r="C285" s="1"/>
+      <c r="A285" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="D285" s="1" t="s">
-        <v>363</v>
+        <v>291</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1225</v>
+        <v>757</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>914</v>
+        <v>845</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>924</v>
+        <v>1083</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J285" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>1221</v>
+      </c>
       <c r="K285" s="1"/>
       <c r="L285" s="1" t="s">
-        <v>363</v>
+        <v>686</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O285" s="1"/>
-      <c r="P285" s="1"/>
-      <c r="Q285" s="1"/>
-      <c r="R285" s="1"/>
-      <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
+        <v>1222</v>
+      </c>
+      <c r="O285" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="P285" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q285" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="R285" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S285" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T285" s="1" t="s">
+        <v>908</v>
+      </c>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -17206,22 +18906,22 @@
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
       <c r="D286" s="1" t="s">
-        <v>476</v>
+        <v>269</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1084</v>
+        <v>54</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J286" s="1"/>
       <c r="K286" s="1"/>
@@ -17243,28 +18943,34 @@
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1" t="s">
-        <v>442</v>
+        <v>363</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>443</v>
+        <v>331</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="J287" s="1"/>
       <c r="K287" s="1"/>
-      <c r="L287" s="1"/>
-      <c r="M287" s="1"/>
-      <c r="N287" s="1"/>
+      <c r="L287" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M287" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="N287" s="1" t="s">
+        <v>1225</v>
+      </c>
       <c r="O287" s="1"/>
       <c r="P287" s="1"/>
       <c r="Q287" s="1"/>
@@ -17280,34 +18986,28 @@
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>924</v>
+        <v>1083</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
-      <c r="L288" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="M288" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="N288" s="1" t="s">
-        <v>1230</v>
-      </c>
+      <c r="L288" s="1"/>
+      <c r="M288" s="1"/>
+      <c r="N288" s="1"/>
       <c r="O288" s="1"/>
       <c r="P288" s="1"/>
       <c r="Q288" s="1"/>
@@ -17323,13 +19023,13 @@
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1" t="s">
-        <v>35</v>
+        <v>442</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>761</v>
+        <v>443</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>909</v>
@@ -17338,19 +19038,13 @@
         <v>54</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="J289" s="1"/>
       <c r="K289" s="1"/>
-      <c r="L289" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M289" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="N289" s="1" t="s">
-        <v>1232</v>
-      </c>
+      <c r="L289" s="1"/>
+      <c r="M289" s="1"/>
+      <c r="N289" s="1"/>
       <c r="O289" s="1"/>
       <c r="P289" s="1"/>
       <c r="Q289" s="1"/>
@@ -17366,30 +19060,34 @@
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1234</v>
+        <v>845</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="J290" s="1" t="s">
-        <v>977</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J290" s="1"/>
       <c r="K290" s="1"/>
-      <c r="L290" s="1"/>
-      <c r="M290" s="1"/>
-      <c r="N290" s="1"/>
+      <c r="L290" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="M290" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="N290" s="1" t="s">
+        <v>1229</v>
+      </c>
       <c r="O290" s="1"/>
       <c r="P290" s="1"/>
       <c r="Q290" s="1"/>
@@ -17405,13 +19103,13 @@
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1" t="s">
-        <v>747</v>
+        <v>35</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>909</v>
@@ -17424,9 +19122,15 @@
       </c>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
-      <c r="L291" s="1"/>
-      <c r="M291" s="1"/>
-      <c r="N291" s="1"/>
+      <c r="L291" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M291" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="N291" s="1" t="s">
+        <v>1231</v>
+      </c>
       <c r="O291" s="1"/>
       <c r="P291" s="1"/>
       <c r="Q291" s="1"/>
@@ -17442,25 +19146,25 @@
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1" t="s">
-        <v>747</v>
+        <v>476</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>916</v>
+        <v>1233</v>
       </c>
       <c r="H292" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>579</v>
+        <v>1103</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>1237</v>
+        <v>976</v>
       </c>
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
@@ -17481,22 +19185,22 @@
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
-        <v>98</v>
+        <v>747</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J293" s="1"/>
       <c r="K293" s="1"/>
@@ -17514,38 +19218,34 @@
       <c r="W293" s="1"/>
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A294" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>989</v>
-      </c>
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
       <c r="D294" s="1" t="s">
-        <v>43</v>
+        <v>747</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>988</v>
+        <v>764</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-      <c r="I294" s="1"/>
-      <c r="J294" s="1"/>
+        <v>1235</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="J294" s="1" t="s">
+        <v>1236</v>
+      </c>
       <c r="K294" s="1"/>
-      <c r="L294" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M294" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="N294" s="1" t="s">
-        <v>1240</v>
-      </c>
+      <c r="L294" s="1"/>
+      <c r="M294" s="1"/>
+      <c r="N294" s="1"/>
       <c r="O294" s="1"/>
       <c r="P294" s="1"/>
       <c r="Q294" s="1"/>
@@ -17557,36 +19257,28 @@
       <c r="W294" s="1"/>
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A295" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="B295" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>1241</v>
-      </c>
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
       <c r="D295" s="1" t="s">
-        <v>747</v>
+        <v>98</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>934</v>
+        <v>768</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="J295" s="1" t="s">
-        <v>1243</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="J295" s="1"/>
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
@@ -17602,32 +19294,38 @@
       <c r="W295" s="1"/>
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A296" s="1"/>
-      <c r="B296" s="1"/>
-      <c r="C296" s="1"/>
+      <c r="A296" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>988</v>
+      </c>
       <c r="D296" s="1" t="s">
-        <v>698</v>
+        <v>43</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>770</v>
+        <v>987</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="H296" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I296" s="1" t="s">
-        <v>1104</v>
-      </c>
+        <v>1238</v>
+      </c>
+      <c r="G296" s="1"/>
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
-      <c r="L296" s="1"/>
-      <c r="M296" s="1"/>
-      <c r="N296" s="1"/>
+      <c r="L296" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M296" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="N296" s="1" t="s">
+        <v>1239</v>
+      </c>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
       <c r="Q296" s="1"/>
@@ -17639,28 +19337,36 @@
       <c r="W296" s="1"/>
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A297" s="1"/>
-      <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
+      <c r="A297" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>1240</v>
+      </c>
       <c r="D297" s="1" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>772</v>
+        <v>934</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H297" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J297" s="1"/>
+        <v>586</v>
+      </c>
+      <c r="J297" s="1" t="s">
+        <v>1242</v>
+      </c>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
@@ -17680,21 +19386,23 @@
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1" t="s">
-        <v>212</v>
+        <v>698</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>774</v>
+        <v>1243</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="I298" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>1103</v>
+      </c>
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
@@ -17711,23 +19419,17 @@
       <c r="W298" s="1"/>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A299" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>776</v>
-      </c>
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
       <c r="D299" s="1" t="s">
-        <v>300</v>
+        <v>771</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>335</v>
+        <v>772</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>909</v>
@@ -17738,9 +19440,7 @@
       <c r="I299" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="J299" s="1" t="s">
-        <v>338</v>
-      </c>
+      <c r="J299" s="1"/>
       <c r="K299" s="1"/>
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
@@ -17756,44 +19456,30 @@
       <c r="W299" s="1"/>
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A300" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>391</v>
-      </c>
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
       <c r="D300" s="1" t="s">
-        <v>390</v>
+        <v>212</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>67</v>
+        <v>774</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1247</v>
+        <v>774</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>845</v>
+        <v>911</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>924</v>
-      </c>
-      <c r="I300" s="1" t="s">
-        <v>578</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="I300" s="1"/>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
-      <c r="L300" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="M300" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N300" s="1" t="s">
-        <v>943</v>
-      </c>
+      <c r="L300" s="1"/>
+      <c r="M300" s="1"/>
+      <c r="N300" s="1"/>
       <c r="O300" s="1"/>
       <c r="P300" s="1"/>
       <c r="Q300" s="1"/>
@@ -17806,34 +19492,34 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>786</v>
+        <v>335</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>767</v>
+        <v>335</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>1249</v>
+        <v>338</v>
       </c>
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
@@ -17851,42 +19537,42 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>788</v>
+        <v>65</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>789</v>
+        <v>391</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>790</v>
+        <v>67</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
       <c r="L302" s="1" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="M302" s="1" t="s">
-        <v>790</v>
+        <v>67</v>
       </c>
       <c r="N302" s="1" t="s">
-        <v>1251</v>
+        <v>943</v>
       </c>
       <c r="O302" s="1"/>
       <c r="P302" s="1"/>
@@ -17899,28 +19585,36 @@
       <c r="W302" s="1"/>
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A303" s="1"/>
-      <c r="B303" s="1"/>
-      <c r="C303" s="1"/>
+      <c r="A303" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>787</v>
+      </c>
       <c r="D303" s="1" t="s">
-        <v>504</v>
+        <v>49</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>819</v>
+        <v>767</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>819</v>
+        <v>1247</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>845</v>
+        <v>916</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>1084</v>
+        <v>54</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J303" s="1"/>
+        <v>583</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>1248</v>
+      </c>
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
@@ -17936,34 +19630,44 @@
       <c r="W303" s="1"/>
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A304" s="1"/>
-      <c r="B304" s="1"/>
-      <c r="C304" s="1"/>
+      <c r="A304" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>789</v>
+      </c>
       <c r="D304" s="1" t="s">
-        <v>607</v>
+        <v>57</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>899</v>
+        <v>790</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>900</v>
+        <v>1249</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J304" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J304" s="1"/>
       <c r="K304" s="1"/>
-      <c r="L304" s="1"/>
-      <c r="M304" s="1"/>
-      <c r="N304" s="1"/>
+      <c r="L304" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M304" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="N304" s="1" t="s">
+        <v>1250</v>
+      </c>
       <c r="O304" s="1"/>
       <c r="P304" s="1"/>
       <c r="Q304" s="1"/>
@@ -17979,36 +19683,28 @@
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1298</v>
+        <v>819</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>913</v>
+        <v>845</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>563</v>
+        <v>1083</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J305" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>1169</v>
+      </c>
+      <c r="J305" s="1"/>
       <c r="K305" s="1"/>
-      <c r="L305" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="M305" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="N305" s="1" t="s">
-        <v>1252</v>
-      </c>
+      <c r="L305" s="1"/>
+      <c r="M305" s="1"/>
+      <c r="N305" s="1"/>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
@@ -18024,26 +19720,36 @@
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1" t="s">
-        <v>821</v>
+        <v>607</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>822</v>
+        <v>899</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1253</v>
+        <v>1309</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1148</v>
+        <v>913</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I306" s="1"/>
-      <c r="J306" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I306" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="J306" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K306" s="1"/>
-      <c r="L306" s="1"/>
-      <c r="M306" s="1"/>
-      <c r="N306" s="1"/>
+      <c r="L306" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M306" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="N306" s="1" t="s">
+        <v>900</v>
+      </c>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
@@ -18059,26 +19765,36 @@
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1" t="s">
-        <v>821</v>
+        <v>607</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1254</v>
+        <v>1297</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1148</v>
+        <v>913</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I307" s="1"/>
-      <c r="J307" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I307" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="J307" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K307" s="1"/>
-      <c r="L307" s="1"/>
-      <c r="M307" s="1"/>
-      <c r="N307" s="1"/>
+      <c r="L307" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M307" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="N307" s="1" t="s">
+        <v>1251</v>
+      </c>
       <c r="O307" s="1"/>
       <c r="P307" s="1"/>
       <c r="Q307" s="1"/>
@@ -18094,19 +19810,19 @@
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1" t="s">
-        <v>1255</v>
+        <v>821</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="G308" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H308" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H308" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -18129,26 +19845,22 @@
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1" t="s">
-        <v>517</v>
+        <v>821</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>845</v>
+        <v>1147</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="I309" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="J309" s="1" t="s">
-        <v>1258</v>
-      </c>
+        <v>1148</v>
+      </c>
+      <c r="I309" s="1"/>
+      <c r="J309" s="1"/>
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
@@ -18163,33 +19875,37 @@
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
-      <c r="D310" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E310" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F310" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G310" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="H310" s="1" t="s">
-        <v>563</v>
-      </c>
+      <c r="D310" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E310" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G310" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="H310" s="1"/>
       <c r="I310" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
-      <c r="L310" s="1"/>
-      <c r="M310" s="1"/>
-      <c r="N310" s="1"/>
+      <c r="L310" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="M310" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="N310" s="5" t="s">
+        <v>1312</v>
+      </c>
       <c r="O310" s="1"/>
       <c r="P310" s="1"/>
       <c r="Q310" s="1"/>
@@ -18205,34 +19921,26 @@
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
       <c r="D311" s="1" t="s">
-        <v>106</v>
+        <v>1254</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>114</v>
+        <v>824</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>913</v>
+        <v>1147</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I311" s="1" t="s">
-        <v>588</v>
-      </c>
+        <v>1148</v>
+      </c>
+      <c r="I311" s="1"/>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
-      <c r="L311" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M311" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N311" s="1" t="s">
-        <v>1262</v>
-      </c>
+      <c r="L311" s="1"/>
+      <c r="M311" s="1"/>
+      <c r="N311" s="1"/>
       <c r="O311" s="1"/>
       <c r="P311" s="1"/>
       <c r="Q311" s="1"/>
@@ -18248,25 +19956,25 @@
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1" t="s">
-        <v>98</v>
+        <v>517</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>917</v>
+        <v>845</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>54</v>
+        <v>1083</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>579</v>
+        <v>879</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
@@ -18287,26 +19995,24 @@
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1" t="s">
-        <v>179</v>
+        <v>686</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>180</v>
+        <v>1258</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J313" s="1" t="s">
-        <v>1266</v>
-      </c>
+        <v>928</v>
+      </c>
+      <c r="J313" s="1"/>
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
@@ -18326,33 +20032,33 @@
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1" t="s">
-        <v>833</v>
+        <v>106</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>834</v>
+        <v>114</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
       <c r="L314" s="1" t="s">
-        <v>1268</v>
+        <v>106</v>
       </c>
       <c r="M314" s="1" t="s">
-        <v>834</v>
+        <v>114</v>
       </c>
       <c r="N314" s="1" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="O314" s="1"/>
       <c r="P314" s="1"/>
@@ -18369,24 +20075,26 @@
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1" t="s">
-        <v>836</v>
+        <v>98</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J315" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>1263</v>
+      </c>
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
@@ -18406,25 +20114,25 @@
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1" t="s">
-        <v>421</v>
+        <v>179</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>844</v>
+        <v>1264</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>845</v>
+        <v>916</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>846</v>
+        <v>1265</v>
       </c>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
@@ -18441,38 +20149,38 @@
       <c r="W316" s="1"/>
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A317" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>827</v>
-      </c>
+      <c r="A317" s="1"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
       <c r="D317" s="1" t="s">
-        <v>433</v>
+        <v>833</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>848</v>
+        <v>1266</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>729</v>
+        <v>562</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="J317" s="1"/>
       <c r="K317" s="1"/>
-      <c r="L317" s="1"/>
-      <c r="M317" s="1"/>
-      <c r="N317" s="1"/>
+      <c r="L317" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M317" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="N317" s="1" t="s">
+        <v>1268</v>
+      </c>
       <c r="O317" s="1"/>
       <c r="P317" s="1"/>
       <c r="Q317" s="1"/>
@@ -18484,32 +20192,26 @@
       <c r="W317" s="1"/>
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A318" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>852</v>
-      </c>
+      <c r="A318" s="1"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
       <c r="D318" s="1" t="s">
-        <v>407</v>
+        <v>836</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>410</v>
+        <v>837</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>411</v>
+        <v>1269</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
@@ -18531,24 +20233,26 @@
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1" t="s">
-        <v>143</v>
+        <v>421</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>566</v>
+        <v>424</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>794</v>
+        <v>844</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H319" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J319" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J319" s="1" t="s">
+        <v>846</v>
+      </c>
       <c r="K319" s="1"/>
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
@@ -18565,35 +20269,33 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>49</v>
+        <v>433</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>856</v>
+        <v>827</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>49</v>
+        <v>433</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1271</v>
+        <v>848</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J320" s="1" t="s">
-        <v>1272</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="J320" s="1"/>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
@@ -18609,30 +20311,34 @@
       <c r="W320" s="1"/>
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A321" s="1"/>
-      <c r="B321" s="1"/>
-      <c r="C321" s="1"/>
+      <c r="A321" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="D321" s="1" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>866</v>
+        <v>410</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>867</v>
+        <v>411</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H321" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J321" s="1" t="s">
-        <v>869</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J321" s="1"/>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
@@ -18652,26 +20358,24 @@
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
       <c r="D322" s="1" t="s">
-        <v>381</v>
+        <v>143</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>69</v>
+        <v>566</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>926</v>
+        <v>794</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="H322" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J322" s="1" t="s">
-        <v>907</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="J322" s="1"/>
       <c r="K322" s="1"/>
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
@@ -18687,28 +20391,36 @@
       <c r="W322" s="1"/>
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A323" s="1"/>
-      <c r="B323" s="1"/>
-      <c r="C323" s="1"/>
+      <c r="A323" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>856</v>
+      </c>
       <c r="D323" s="1" t="s">
-        <v>381</v>
+        <v>49</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>69</v>
+        <v>857</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J323" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J323" s="1" t="s">
+        <v>1271</v>
+      </c>
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
@@ -18728,24 +20440,26 @@
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
       <c r="D324" s="1" t="s">
-        <v>625</v>
+        <v>143</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="J324" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>869</v>
+      </c>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
@@ -18765,25 +20479,25 @@
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1" t="s">
-        <v>517</v>
+        <v>381</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>877</v>
+        <v>69</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>878</v>
+        <v>926</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>879</v>
+        <v>584</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -18800,46 +20514,32 @@
       <c r="W325" s="1"/>
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A326" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>952</v>
-      </c>
+      <c r="A326" s="1"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
       <c r="D326" s="1" t="s">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>881</v>
+        <v>69</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1275</v>
+        <v>909</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J326" s="1" t="s">
-        <v>882</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J326" s="1"/>
       <c r="K326" s="1"/>
-      <c r="L326" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M326" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="N326" s="1" t="s">
-        <v>1276</v>
-      </c>
+      <c r="L326" s="1"/>
+      <c r="M326" s="1"/>
+      <c r="N326" s="1"/>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
       <c r="Q326" s="1"/>
@@ -18855,34 +20555,28 @@
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1" t="s">
-        <v>363</v>
+        <v>625</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>925</v>
+        <v>874</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1277</v>
+        <v>875</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>845</v>
+        <v>921</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>924</v>
+        <v>562</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>578</v>
+        <v>876</v>
       </c>
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
-      <c r="L327" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M327" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="N327" s="1" t="s">
-        <v>1278</v>
-      </c>
+      <c r="L327" s="1"/>
+      <c r="M327" s="1"/>
+      <c r="N327" s="1"/>
       <c r="O327" s="1"/>
       <c r="P327" s="1"/>
       <c r="Q327" s="1"/>
@@ -18894,35 +20588,34 @@
       <c r="W327" s="1"/>
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A328" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>1280</v>
-      </c>
+      <c r="A328" s="1"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
       <c r="D328" s="1" t="s">
-        <v>381</v>
+        <v>517</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>62</v>
+        <v>877</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1279</v>
+        <v>878</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="H328" s="1" t="s">
         <v>563</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J328" s="1"/>
+        <v>879</v>
+      </c>
+      <c r="J328" s="1" t="s">
+        <v>880</v>
+      </c>
       <c r="K328" s="1"/>
+      <c r="L328" s="1"/>
+      <c r="M328" s="1"/>
+      <c r="N328" s="1"/>
       <c r="O328" s="1"/>
       <c r="P328" s="1"/>
       <c r="Q328" s="1"/>
@@ -18934,49 +20627,49 @@
       <c r="W328" s="1"/>
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
-      <c r="C329" s="1"/>
+      <c r="A329" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>952</v>
+      </c>
       <c r="D329" s="1" t="s">
-        <v>35</v>
+        <v>464</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>410</v>
+        <v>881</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>929</v>
+        <v>1273</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>916</v>
+        <v>1274</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>852</v>
+        <v>882</v>
       </c>
       <c r="K329" s="1"/>
       <c r="L329" s="1" t="s">
-        <v>35</v>
+        <v>464</v>
       </c>
       <c r="M329" s="1" t="s">
-        <v>410</v>
+        <v>881</v>
       </c>
       <c r="N329" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="O329" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P329" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q329" s="1" t="s">
-        <v>596</v>
-      </c>
+        <v>1275</v>
+      </c>
+      <c r="O329" s="1"/>
+      <c r="P329" s="1"/>
+      <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
       <c r="T329" s="1"/>
@@ -18985,38 +20678,38 @@
       <c r="W329" s="1"/>
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A330" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>883</v>
-      </c>
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
       <c r="D330" s="1" t="s">
-        <v>464</v>
+        <v>363</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>882</v>
+        <v>1276</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1275</v>
+        <v>845</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>729</v>
+        <v>924</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
-      <c r="L330" s="1"/>
-      <c r="M330" s="1"/>
-      <c r="N330" s="1"/>
+      <c r="L330" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M330" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="N330" s="1" t="s">
+        <v>1277</v>
+      </c>
       <c r="O330" s="1"/>
       <c r="P330" s="1"/>
       <c r="Q330" s="1"/>
@@ -19028,17 +20721,23 @@
       <c r="W330" s="1"/>
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A331" s="1"/>
-      <c r="B331" s="1"/>
-      <c r="C331" s="1"/>
+      <c r="A331" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>1279</v>
+      </c>
       <c r="D331" s="1" t="s">
-        <v>686</v>
+        <v>381</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>708</v>
+        <v>62</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>927</v>
+        <v>1278</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>913</v>
@@ -19047,13 +20746,10 @@
         <v>563</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
-      <c r="L331" s="1"/>
-      <c r="M331" s="1"/>
-      <c r="N331" s="1"/>
       <c r="O331" s="1"/>
       <c r="P331" s="1"/>
       <c r="Q331" s="1"/>
@@ -19065,51 +20761,83 @@
       <c r="W331" s="1"/>
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
       <c r="D332" s="1" t="s">
-        <v>476</v>
+        <v>35</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>853</v>
+        <v>929</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1286</v>
+        <v>916</v>
       </c>
       <c r="H332" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>1085</v>
+        <v>584</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>1095</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="K332" s="1"/>
+      <c r="L332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M332" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N332" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="O332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P332" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q332" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="R332" s="1"/>
+      <c r="S332" s="1"/>
+      <c r="T332" s="1"/>
+      <c r="U332" s="1"/>
+      <c r="V332" s="1"/>
+      <c r="W332" s="1"/>
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A333" s="1"/>
-      <c r="B333" s="1"/>
-      <c r="C333" s="1"/>
+      <c r="A333" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>883</v>
+      </c>
       <c r="D333" s="1" t="s">
-        <v>836</v>
+        <v>464</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>922</v>
+        <v>882</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>912</v>
+        <v>1274</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>1132</v>
+        <v>729</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
@@ -19131,22 +20859,22 @@
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
       <c r="D334" s="1" t="s">
-        <v>885</v>
+        <v>686</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>887</v>
+        <v>708</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>888</v>
+        <v>927</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>578</v>
+        <v>928</v>
       </c>
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
@@ -19164,63 +20892,51 @@
       <c r="W334" s="1"/>
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1" t="s">
-        <v>724</v>
+        <v>476</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>889</v>
+        <v>482</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>890</v>
+        <v>853</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>909</v>
+        <v>1285</v>
       </c>
       <c r="H335" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J335" s="1"/>
-      <c r="K335" s="1"/>
-      <c r="L335" s="1"/>
-      <c r="M335" s="1"/>
-      <c r="N335" s="1"/>
-      <c r="O335" s="1"/>
-      <c r="P335" s="1"/>
-      <c r="Q335" s="1"/>
-      <c r="R335" s="1"/>
-      <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
-      <c r="U335" s="1"/>
-      <c r="V335" s="1"/>
-      <c r="W335" s="1"/>
+        <v>1084</v>
+      </c>
+      <c r="J335" s="1" t="s">
+        <v>1094</v>
+      </c>
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1" t="s">
-        <v>892</v>
+        <v>836</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>54</v>
+        <v>1131</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
@@ -19242,22 +20958,22 @@
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -19279,32 +20995,28 @@
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1" t="s">
-        <v>569</v>
+        <v>724</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>569</v>
+        <v>889</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>569</v>
+        <v>890</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1148</v>
+        <v>909</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I338" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>594</v>
+      </c>
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
-      <c r="L338" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="M338" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="N338" s="1" t="s">
-        <v>896</v>
-      </c>
+      <c r="L338" s="1"/>
+      <c r="M338" s="1"/>
+      <c r="N338" s="1"/>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
       <c r="Q338" s="1"/>
@@ -19320,32 +21032,28 @@
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>1148</v>
+        <v>909</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I339" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>589</v>
+      </c>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
-      <c r="L339" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="M339" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="N339" s="1" t="s">
-        <v>897</v>
-      </c>
+      <c r="L339" s="1"/>
+      <c r="M339" s="1"/>
+      <c r="N339" s="1"/>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
       <c r="Q339" s="1"/>
@@ -19361,32 +21069,28 @@
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1" t="s">
-        <v>572</v>
+        <v>892</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>572</v>
+        <v>893</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>572</v>
+        <v>894</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>1148</v>
+        <v>909</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I340" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>589</v>
+      </c>
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
-      <c r="L340" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="M340" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="N340" s="1" t="s">
-        <v>898</v>
-      </c>
+      <c r="L340" s="1"/>
+      <c r="M340" s="1"/>
+      <c r="N340" s="1"/>
       <c r="O340" s="1"/>
       <c r="P340" s="1"/>
       <c r="Q340" s="1"/>
@@ -19402,31 +21106,31 @@
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1281</v>
+        <v>1147</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
       <c r="L341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="M341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="N341" s="1" t="s">
-        <v>577</v>
+        <v>896</v>
       </c>
       <c r="O341" s="1"/>
       <c r="P341" s="1"/>
@@ -19438,9 +21142,254 @@
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
     </row>
+    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H342" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I342" s="1"/>
+      <c r="J342" s="1"/>
+      <c r="K342" s="1"/>
+      <c r="L342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="M342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="N342" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="O342" s="1"/>
+      <c r="P342" s="1"/>
+      <c r="Q342" s="1"/>
+      <c r="R342" s="1"/>
+      <c r="S342" s="1"/>
+      <c r="T342" s="1"/>
+      <c r="U342" s="1"/>
+      <c r="V342" s="1"/>
+      <c r="W342" s="1"/>
+    </row>
+    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G343" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H343" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I343" s="1"/>
+      <c r="J343" s="1"/>
+      <c r="K343" s="1"/>
+      <c r="L343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="M343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N343" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="O343" s="1"/>
+      <c r="P343" s="1"/>
+      <c r="Q343" s="1"/>
+      <c r="R343" s="1"/>
+      <c r="S343" s="1"/>
+      <c r="T343" s="1"/>
+      <c r="U343" s="1"/>
+      <c r="V343" s="1"/>
+      <c r="W343" s="1"/>
+    </row>
+    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G344" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H344" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I344" s="1"/>
+      <c r="J344" s="1"/>
+      <c r="K344" s="1"/>
+      <c r="L344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="M344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="N344" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="O344" s="1"/>
+      <c r="P344" s="1"/>
+      <c r="Q344" s="1"/>
+      <c r="R344" s="1"/>
+      <c r="S344" s="1"/>
+      <c r="T344" s="1"/>
+      <c r="U344" s="1"/>
+      <c r="V344" s="1"/>
+      <c r="W344" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="F310">
+    <cfRule type="duplicateValues" dxfId="159" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F310">
+    <cfRule type="duplicateValues" dxfId="155" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="160"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F310">
+    <cfRule type="duplicateValues" dxfId="113" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F310">
+    <cfRule type="duplicateValues" dxfId="110" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N310">
+    <cfRule type="duplicateValues" dxfId="106" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N310">
+    <cfRule type="duplicateValues" dxfId="102" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N310">
+    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N310">
+    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0415\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88583AE0-43DA-4BEE-BF29-34283F43D524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFAA402-CB2C-4C98-9B7C-068E01F45A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="1323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1325">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4028,6 +4028,13 @@
   <si>
     <t>宁芯</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9642TS-EC-Q-AH-4XAR-9642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9642TS-EC-Q-AH-43LR-9642</t>
   </si>
 </sst>
 </file>
@@ -4124,7 +4131,17 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="160">
+  <dxfs count="161">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13089,7 +13106,7 @@
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>433</v>
       </c>
@@ -13137,11 +13154,17 @@
         <v>438</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="R152" s="1"/>
-      <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+        <v>1323</v>
+      </c>
+      <c r="R152" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="S152" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="T152" s="5" t="s">
+        <v>1324</v>
+      </c>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -21269,126 +21292,179 @@
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="159" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="115"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="155" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="160"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="113" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="118"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="110" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="106" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="102" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="107"/>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="65"/>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0415\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFAA402-CB2C-4C98-9B7C-068E01F45A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21F931-BB0C-473A-AE08-EE7A5E2C41E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="1305">
   <si>
     <t>替代规格2</t>
   </si>
@@ -2965,6 +2965,9 @@
     <t>SC243XSO-118113-TR-Q</t>
   </si>
   <si>
+    <t>SC1134UA-CI-00AY-44E</t>
+  </si>
+  <si>
     <t>SC4011DN-CB-90LR-4011</t>
   </si>
   <si>
@@ -3963,88 +3966,13 @@
   </si>
   <si>
     <t>SC2434SO-N-CD-X0NR-2434</t>
-  </si>
-  <si>
-    <t>SC1134UA-CF-90AK-1134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134UA-CF-90AK-44E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134UA-CF-90AK-44L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134UA-CI-90AY-44E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AY-44E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC69401DC-SPI3P3-Q-HD-4XAR-69401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2203SO-TR</t>
-  </si>
-  <si>
-    <t>SC2203SO-CH-10AR-2203</t>
-  </si>
-  <si>
-    <t>SC2203SO-CH-10NR-2203</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC2G201A</t>
-  </si>
-  <si>
-    <t>SC24023SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2403SO-N-GA-00NR-2403</t>
-  </si>
-  <si>
-    <t>SC24023SO-TR</t>
-  </si>
-  <si>
-    <t>SC2403SO-GA-00NR-2403</t>
-  </si>
-  <si>
-    <t>SC2403SO-TR</t>
-  </si>
-  <si>
-    <t>SC2403SO-DB-00NR-2403</t>
-  </si>
-  <si>
-    <t>SC2403SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2403SO-N-DB-00NR-2403</t>
-  </si>
-  <si>
-    <t>宁芯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9642TS-EC-Q-AH-4XAR-9642</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9642TS-EC-Q-AH-43LR-9642</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4058,13 +3986,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4120,1629 +4041,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="161">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6018,7 +4327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}">
-  <dimension ref="A1:W344"/>
+  <dimension ref="A1:W341"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -6048,46 +4357,46 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>2</v>
@@ -6125,7 +4434,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -6134,7 +4443,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>909</v>
@@ -6303,22 +4612,22 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B6" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C6" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>1292</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1291</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -6385,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -6451,7 +4760,7 @@
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>909</v>
@@ -6488,7 +4797,7 @@
         <v>123</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1305</v>
+        <v>905</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>909</v>
@@ -6500,18 +4809,12 @@
         <v>584</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>905</v>
-      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -6533,7 +4836,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1304</v>
+        <v>903</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>909</v>
@@ -6545,18 +4848,12 @@
         <v>584</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>903</v>
-      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -6578,7 +4875,7 @@
         <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1306</v>
+        <v>904</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>909</v>
@@ -6590,18 +4887,12 @@
         <v>584</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>904</v>
-      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -6617,7 +4908,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>31</v>
@@ -6626,7 +4917,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>30</v>
@@ -6672,7 +4963,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>914</v>
@@ -6719,7 +5010,7 @@
         <v>40</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -6777,7 +5068,7 @@
         <v>36</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>32</v>
@@ -6806,7 +5097,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>909</v>
@@ -6978,7 +5269,7 @@
         <v>971</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>909</v>
@@ -7027,7 +5318,7 @@
         <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>845</v>
@@ -7056,7 +5347,7 @@
         <v>62</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>35</v>
@@ -7074,7 +5365,7 @@
         <v>62</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.2">
@@ -7125,7 +5416,7 @@
         <v>67</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>35</v>
@@ -7157,7 +5448,7 @@
         <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>909</v>
@@ -7179,7 +5470,7 @@
         <v>69</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -7271,7 +5562,7 @@
         <v>73</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>35</v>
@@ -7312,7 +5603,7 @@
         <v>76</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>909</v>
@@ -7332,7 +5623,7 @@
         <v>76</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -7355,7 +5646,7 @@
         <v>62</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>913</v>
@@ -7375,7 +5666,7 @@
         <v>62</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -7459,7 +5750,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>909</v>
@@ -7651,7 +5942,7 @@
         <v>615</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>916</v>
@@ -7696,7 +5987,7 @@
         <v>902</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>916</v>
@@ -7747,7 +6038,7 @@
         <v>100</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>913</v>
@@ -7913,7 +6204,7 @@
         <v>114</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -8114,7 +6405,7 @@
         <v>123</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1308</v>
+        <v>974</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>909</v>
@@ -8129,15 +6420,9 @@
         <v>124</v>
       </c>
       <c r="K43" s="1"/>
-      <c r="L43" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>1307</v>
-      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
@@ -8396,7 +6681,7 @@
         <v>583</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
@@ -8435,7 +6720,7 @@
         <v>148</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>917</v>
@@ -8810,10 +7095,10 @@
         <v>143</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>916</v>
@@ -8873,10 +7158,10 @@
         <v>143</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>916</v>
@@ -8907,7 +7192,7 @@
         <v>164</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
@@ -9701,7 +7986,7 @@
         <v>230</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>229</v>
@@ -10556,7 +8841,7 @@
         <v>270</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>911</v>
@@ -10762,7 +9047,7 @@
         <v>580</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -10795,7 +9080,7 @@
         <v>561</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>913</v>
@@ -10807,7 +9092,7 @@
         <v>580</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -10852,7 +9137,7 @@
         <v>580</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -10897,7 +9182,7 @@
         <v>580</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
@@ -10930,7 +9215,7 @@
         <v>719</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>845</v>
@@ -10942,7 +9227,7 @@
         <v>580</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -10981,7 +9266,7 @@
         <v>580</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -11057,7 +9342,7 @@
         <v>297</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>845</v>
@@ -11077,7 +9362,7 @@
         <v>297</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
@@ -11163,7 +9448,7 @@
         <v>937</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
@@ -11192,7 +9477,7 @@
         <v>303</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>914</v>
@@ -11224,13 +9509,13 @@
         <v>304</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>303</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="U111" s="1" t="s">
         <v>621</v>
@@ -11239,7 +9524,7 @@
         <v>303</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.2">
@@ -11304,7 +9589,7 @@
         <v>312</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>845</v>
@@ -11342,7 +9627,7 @@
         <v>312</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
@@ -11543,7 +9828,7 @@
         <v>331</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>914</v>
@@ -11858,7 +10143,7 @@
         <v>357</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>845</v>
@@ -11878,7 +10163,7 @@
         <v>357</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
@@ -11907,7 +10192,7 @@
         <v>361</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>909</v>
@@ -11999,7 +10284,7 @@
         <v>611</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>914</v>
@@ -12019,7 +10304,7 @@
         <v>611</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
@@ -12042,7 +10327,7 @@
         <v>611</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>914</v>
@@ -12218,7 +10503,7 @@
         <v>370</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
@@ -12247,7 +10532,7 @@
         <v>320</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>845</v>
@@ -12267,7 +10552,7 @@
         <v>320</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
@@ -12296,7 +10581,7 @@
         <v>755</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>914</v>
@@ -12316,7 +10601,7 @@
         <v>755</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
@@ -12345,7 +10630,7 @@
         <v>379</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>914</v>
@@ -12394,7 +10679,7 @@
         <v>62</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>913</v>
@@ -12423,7 +10708,7 @@
         <v>62</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
@@ -12492,7 +10777,7 @@
         <v>383</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>845</v>
@@ -12512,7 +10797,7 @@
         <v>383</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
@@ -12535,7 +10820,7 @@
         <v>392</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>845</v>
@@ -12564,7 +10849,7 @@
         <v>392</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
@@ -12725,7 +11010,7 @@
         <v>410</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>916</v>
@@ -12747,7 +11032,7 @@
         <v>410</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="O144" s="1" t="s">
         <v>35</v>
@@ -12765,7 +11050,7 @@
         <v>410</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="U144" s="1" t="s">
         <v>407</v>
@@ -12806,7 +11091,7 @@
         <v>594</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
@@ -12839,10 +11124,10 @@
         <v>415</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>729</v>
@@ -12851,7 +11136,7 @@
         <v>594</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K146" s="1"/>
       <c r="L146" s="1" t="s">
@@ -12941,7 +11226,7 @@
         <v>436</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>918</v>
@@ -12963,7 +11248,7 @@
         <v>436</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>433</v>
@@ -12992,7 +11277,7 @@
         <v>52</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>916</v>
@@ -13031,7 +11316,7 @@
         <v>159</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>916</v>
@@ -13053,7 +11338,7 @@
         <v>159</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
@@ -13067,25 +11352,25 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="E151" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>1065</v>
-      </c>
       <c r="F151" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>562</v>
@@ -13106,7 +11391,7 @@
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>433</v>
       </c>
@@ -13123,7 +11408,7 @@
         <v>438</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>918</v>
@@ -13148,23 +11433,17 @@
         <v>439</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>438</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>1323</v>
-      </c>
-      <c r="R152" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="S152" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="T152" s="5" t="s">
-        <v>1324</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="R152" s="1"/>
+      <c r="S152" s="1"/>
+      <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -13186,7 +11465,7 @@
         <v>448</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>920</v>
@@ -13198,7 +11477,7 @@
         <v>580</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
@@ -13208,7 +11487,7 @@
         <v>448</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="O153" s="1"/>
       <c r="P153" s="1"/>
@@ -13237,7 +11516,7 @@
         <v>451</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>920</v>
@@ -13249,7 +11528,7 @@
         <v>580</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
@@ -13259,7 +11538,7 @@
         <v>451</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
@@ -13288,7 +11567,7 @@
         <v>454</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>920</v>
@@ -13300,7 +11579,7 @@
         <v>580</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
@@ -13310,7 +11589,7 @@
         <v>454</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
@@ -13339,7 +11618,7 @@
         <v>654</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>920</v>
@@ -13351,7 +11630,7 @@
         <v>580</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K156" s="1"/>
       <c r="L156" s="1" t="s">
@@ -13361,7 +11640,7 @@
         <v>654</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
@@ -13390,7 +11669,7 @@
         <v>457</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>913</v>
@@ -13435,7 +11714,7 @@
         <v>458</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>920</v>
@@ -13447,7 +11726,7 @@
         <v>580</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1" t="s">
@@ -13457,7 +11736,7 @@
         <v>458</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
@@ -13486,10 +11765,10 @@
         <v>459</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>562</v>
@@ -13498,7 +11777,7 @@
         <v>580</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
@@ -13537,19 +11816,19 @@
         <v>467</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
@@ -13582,7 +11861,7 @@
         <v>468</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>909</v>
@@ -13631,7 +11910,7 @@
         <v>469</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>909</v>
@@ -13680,19 +11959,19 @@
         <v>469</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="K163" s="1"/>
       <c r="L163" s="1" t="s">
@@ -13731,19 +12010,19 @@
         <v>475</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="1" t="s">
@@ -13782,7 +12061,7 @@
         <v>479</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>909</v>
@@ -13791,7 +12070,7 @@
         <v>54</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
@@ -13831,7 +12110,7 @@
         <v>482</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>831</v>
@@ -13840,10 +12119,10 @@
         <v>54</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="K166" s="1"/>
       <c r="L166" s="1" t="s">
@@ -13882,7 +12161,7 @@
         <v>482</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>913</v>
@@ -13891,7 +12170,7 @@
         <v>563</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
@@ -13925,7 +12204,7 @@
         <v>488</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>909</v>
@@ -13934,7 +12213,7 @@
         <v>54</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
@@ -13959,7 +12238,7 @@
         <v>489</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>969</v>
@@ -13968,7 +12247,7 @@
         <v>489</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>913</v>
@@ -13977,7 +12256,7 @@
         <v>563</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
@@ -14005,19 +12284,19 @@
         <v>491</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I170" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J170" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>1098</v>
       </c>
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
@@ -14050,19 +12329,19 @@
         <v>491</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I171" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="J171" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>1098</v>
       </c>
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
@@ -14095,19 +12374,19 @@
         <v>494</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
@@ -14131,7 +12410,7 @@
         <v>495</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>476</v>
@@ -14140,7 +12419,7 @@
         <v>495</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>913</v>
@@ -14149,7 +12428,7 @@
         <v>563</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -14177,19 +12456,19 @@
         <v>756</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
@@ -14222,19 +12501,19 @@
         <v>497</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="K175" s="1"/>
       <c r="L175" s="1" t="s">
@@ -14262,7 +12541,7 @@
         <v>497</v>
       </c>
       <c r="T175" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="U175" s="1" t="s">
         <v>476</v>
@@ -14271,7 +12550,7 @@
         <v>497</v>
       </c>
       <c r="W175" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.2">
@@ -14282,7 +12561,7 @@
         <v>499</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>476</v>
@@ -14291,7 +12570,7 @@
         <v>499</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>913</v>
@@ -14300,7 +12579,7 @@
         <v>563</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
@@ -14334,19 +12613,19 @@
         <v>499</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -14379,19 +12658,19 @@
         <v>500</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K178" s="1"/>
       <c r="L178" s="1" t="s">
@@ -14430,19 +12709,19 @@
         <v>499</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1" t="s">
@@ -14461,7 +12740,7 @@
         <v>499</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>476</v>
@@ -14470,7 +12749,7 @@
         <v>499</v>
       </c>
       <c r="T179" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="U179" s="1" t="s">
         <v>969</v>
@@ -14479,7 +12758,7 @@
         <v>499</v>
       </c>
       <c r="W179" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.2">
@@ -14499,7 +12778,7 @@
         <v>610</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>913</v>
@@ -14556,7 +12835,7 @@
         <v>524</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>909</v>
@@ -14599,13 +12878,13 @@
         <v>525</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>879</v>
@@ -14644,7 +12923,7 @@
         <v>526</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>909</v>
@@ -14687,19 +12966,19 @@
         <v>526</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
@@ -14732,19 +13011,19 @@
         <v>529</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
@@ -14777,7 +13056,7 @@
         <v>533</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>909</v>
@@ -14820,7 +13099,7 @@
         <v>536</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>911</v>
@@ -14863,7 +13142,7 @@
         <v>540</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>911</v>
@@ -14906,13 +13185,13 @@
         <v>270</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>912</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>578</v>
@@ -14981,7 +13260,7 @@
         <v>965</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
@@ -15010,7 +13289,7 @@
         <v>278</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>909</v>
@@ -15022,7 +13301,7 @@
         <v>584</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
@@ -15049,7 +13328,7 @@
         <v>278</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>909</v>
@@ -15061,7 +13340,7 @@
         <v>584</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
@@ -15094,7 +13373,7 @@
         <v>278</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>909</v>
@@ -15137,7 +13416,7 @@
         <v>278</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>909</v>
@@ -15149,7 +13428,7 @@
         <v>581</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
@@ -15182,7 +13461,7 @@
         <v>278</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>909</v>
@@ -15194,7 +13473,7 @@
         <v>581</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
@@ -15218,7 +13497,7 @@
         <v>273</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>545</v>
@@ -15256,7 +13535,7 @@
         <v>270</v>
       </c>
       <c r="Q196" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
@@ -15282,7 +13561,7 @@
         <v>443</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>909</v>
@@ -15357,7 +13636,7 @@
         <v>553</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
@@ -15386,7 +13665,7 @@
         <v>557</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>909</v>
@@ -15406,7 +13685,7 @@
         <v>557</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -15429,19 +13708,19 @@
         <v>561</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
@@ -15468,19 +13747,19 @@
         <v>561</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
@@ -15510,10 +13789,10 @@
         <v>571</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>590</v>
@@ -15547,10 +13826,10 @@
         <v>574</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>590</v>
@@ -15584,10 +13863,10 @@
         <v>577</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -15616,7 +13895,7 @@
         <v>323</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>909</v>
@@ -15665,7 +13944,7 @@
         <v>620</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>911</v>
@@ -15708,7 +13987,7 @@
         <v>624</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>911</v>
@@ -15757,7 +14036,7 @@
         <v>626</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>921</v>
@@ -15820,7 +14099,7 @@
         <v>631</v>
       </c>
       <c r="N209" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
@@ -15863,7 +14142,7 @@
         <v>936</v>
       </c>
       <c r="N210" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
@@ -15892,7 +14171,7 @@
         <v>637</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>909</v>
@@ -15930,7 +14209,7 @@
         <v>637</v>
       </c>
       <c r="T211" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -15967,7 +14246,7 @@
         <v>638</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="O212" s="1"/>
       <c r="P212" s="1"/>
@@ -15990,7 +14269,7 @@
         <v>641</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>916</v>
@@ -16002,7 +14281,7 @@
         <v>579</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="K213" s="1"/>
       <c r="L213" s="1"/>
@@ -16029,7 +14308,7 @@
         <v>642</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>916</v>
@@ -16041,7 +14320,7 @@
         <v>579</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
@@ -16068,7 +14347,7 @@
         <v>773</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>916</v>
@@ -16080,7 +14359,7 @@
         <v>579</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="K215" s="1"/>
       <c r="L215" s="1"/>
@@ -16113,19 +14392,19 @@
         <v>646</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="K216" s="1"/>
       <c r="L216" s="1"/>
@@ -16152,7 +14431,7 @@
         <v>651</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>910</v>
@@ -16172,7 +14451,7 @@
         <v>651</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
@@ -16201,7 +14480,7 @@
         <v>658</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>909</v>
@@ -16244,7 +14523,7 @@
         <v>662</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>909</v>
@@ -16281,19 +14560,19 @@
         <v>505</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
@@ -16326,13 +14605,13 @@
         <v>845</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
@@ -16365,13 +14644,13 @@
         <v>845</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
@@ -16404,13 +14683,13 @@
         <v>845</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -16443,13 +14722,13 @@
         <v>845</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
@@ -16482,13 +14761,13 @@
         <v>845</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
@@ -16521,13 +14800,13 @@
         <v>845</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K226" s="1"/>
       <c r="L226" s="1"/>
@@ -16554,19 +14833,19 @@
         <v>506</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K227" s="1"/>
       <c r="L227" s="1"/>
@@ -16599,13 +14878,13 @@
         <v>845</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K228" s="1"/>
       <c r="L228" s="1"/>
@@ -16638,13 +14917,13 @@
         <v>845</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -16677,13 +14956,13 @@
         <v>845</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
@@ -16716,13 +14995,13 @@
         <v>845</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
@@ -16755,13 +15034,13 @@
         <v>845</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -16794,13 +15073,13 @@
         <v>845</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
@@ -16833,13 +15112,13 @@
         <v>845</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
@@ -16872,13 +15151,13 @@
         <v>845</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -16911,13 +15190,13 @@
         <v>845</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K236" s="1"/>
       <c r="L236" s="1"/>
@@ -16950,13 +15229,13 @@
         <v>845</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
@@ -16989,19 +15268,19 @@
         <v>720</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
@@ -17034,7 +15313,7 @@
         <v>509</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>909</v>
@@ -17054,7 +15333,7 @@
         <v>509</v>
       </c>
       <c r="N239" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
@@ -17083,7 +15362,7 @@
         <v>509</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>909</v>
@@ -17103,7 +15382,7 @@
         <v>509</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
@@ -17126,7 +15405,7 @@
         <v>673</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>909</v>
@@ -17171,10 +15450,10 @@
         <v>960</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>959</v>
@@ -17210,13 +15489,13 @@
         <v>845</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>589</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -17233,39 +15512,53 @@
       <c r="W243" s="1"/>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A244" s="1"/>
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
+      <c r="A244" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>678</v>
+      </c>
       <c r="D244" s="1" t="s">
-        <v>35</v>
+        <v>607</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>1318</v>
+        <v>843</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>1319</v>
+        <v>842</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1322</v>
-      </c>
-      <c r="H244" s="1"/>
-      <c r="I244" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J244" s="1"/>
+        <v>1182</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1" t="s">
+        <v>841</v>
+      </c>
       <c r="K244" s="1"/>
       <c r="L244" s="1" t="s">
-        <v>1313</v>
+        <v>607</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>1314</v>
+        <v>677</v>
       </c>
       <c r="N244" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="O244" s="1"/>
-      <c r="P244" s="1"/>
-      <c r="Q244" s="1"/>
+        <v>679</v>
+      </c>
+      <c r="O244" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="P244" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q244" s="1" t="s">
+        <v>1183</v>
+      </c>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
       <c r="T244" s="1"/>
@@ -17274,36 +15567,38 @@
       <c r="W244" s="1"/>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A245" s="1"/>
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
+      <c r="A245" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>765</v>
+      </c>
       <c r="D245" s="1" t="s">
-        <v>35</v>
+        <v>625</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1320</v>
+        <v>681</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>1321</v>
+        <v>682</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1322</v>
-      </c>
-      <c r="H245" s="1"/>
+        <v>921</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>562</v>
+      </c>
       <c r="I245" s="1" t="s">
-        <v>578</v>
+        <v>1184</v>
       </c>
       <c r="J245" s="1"/>
       <c r="K245" s="1"/>
-      <c r="L245" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="M245" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="N245" s="1" t="s">
-        <v>1317</v>
-      </c>
+      <c r="L245" s="1"/>
+      <c r="M245" s="1"/>
+      <c r="N245" s="1"/>
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
@@ -17316,52 +15611,34 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>676</v>
+        <v>545</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E246" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="F246" s="1" t="s">
-        <v>842</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
       <c r="G246" s="1" t="s">
-        <v>1181</v>
+        <v>921</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="I246" s="1"/>
-      <c r="J246" s="1" t="s">
-        <v>841</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J246" s="1"/>
       <c r="K246" s="1"/>
-      <c r="L246" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="M246" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="N246" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="O246" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="P246" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="Q246" s="1" t="s">
-        <v>1182</v>
-      </c>
+      <c r="L246" s="1"/>
+      <c r="M246" s="1"/>
+      <c r="N246" s="1"/>
+      <c r="O246" s="1"/>
+      <c r="P246" s="1"/>
+      <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
       <c r="T246" s="1"/>
@@ -17370,32 +15647,26 @@
       <c r="W246" s="1"/>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A247" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>765</v>
-      </c>
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
       <c r="D247" s="1" t="s">
-        <v>625</v>
+        <v>35</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>682</v>
+        <v>1186</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>1183</v>
+        <v>578</v>
       </c>
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
@@ -17413,26 +15684,26 @@
       <c r="W247" s="1"/>
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A248" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="D248" s="1"/>
-      <c r="E248" s="1"/>
-      <c r="F248" s="1"/>
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>1187</v>
+      </c>
       <c r="G248" s="1" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>1184</v>
+        <v>580</v>
       </c>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -17454,13 +15725,13 @@
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>909</v>
@@ -17469,7 +15740,7 @@
         <v>54</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -17487,23 +15758,23 @@
       <c r="W249" s="1"/>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A250" s="1"/>
-      <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-      <c r="D250" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>1186</v>
-      </c>
+      <c r="A250" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
       <c r="G250" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>580</v>
@@ -17528,28 +15799,36 @@
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1" t="s">
-        <v>688</v>
+        <v>433</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>689</v>
+        <v>436</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J251" s="1"/>
+        <v>594</v>
+      </c>
+      <c r="J251" s="1" t="s">
+        <v>848</v>
+      </c>
       <c r="K251" s="1"/>
-      <c r="L251" s="1"/>
-      <c r="M251" s="1"/>
-      <c r="N251" s="1"/>
+      <c r="L251" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="M251" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N251" s="1" t="s">
+        <v>1190</v>
+      </c>
       <c r="O251" s="1"/>
       <c r="P251" s="1"/>
       <c r="Q251" s="1"/>
@@ -17561,26 +15840,26 @@
       <c r="W251" s="1"/>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A252" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="D252" s="1"/>
-      <c r="E252" s="1"/>
-      <c r="F252" s="1"/>
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>1191</v>
+      </c>
       <c r="G252" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -17598,40 +15877,38 @@
       <c r="W252" s="1"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A253" s="1"/>
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
+      <c r="A253" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>697</v>
+      </c>
       <c r="D253" s="1" t="s">
-        <v>433</v>
+        <v>695</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>436</v>
+        <v>696</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J253" s="1" t="s">
-        <v>848</v>
-      </c>
+        <v>1193</v>
+      </c>
+      <c r="J253" s="1"/>
       <c r="K253" s="1"/>
-      <c r="L253" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="M253" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="N253" s="1" t="s">
-        <v>1189</v>
-      </c>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+      <c r="N253" s="1"/>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
@@ -17643,26 +15920,26 @@
       <c r="W253" s="1"/>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A254" s="1"/>
-      <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-      <c r="D254" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E254" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="F254" s="1" t="s">
-        <v>1190</v>
-      </c>
+      <c r="A254" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>594</v>
+        <v>1104</v>
       </c>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
@@ -17681,22 +15958,22 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>696</v>
+        <v>791</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>697</v>
+        <v>792</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>909</v>
@@ -17705,7 +15982,7 @@
         <v>54</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>1192</v>
+        <v>586</v>
       </c>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
@@ -17723,26 +16000,26 @@
       <c r="W255" s="1"/>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A256" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="D256" s="1"/>
-      <c r="E256" s="1"/>
-      <c r="F256" s="1"/>
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>1195</v>
+      </c>
       <c r="G256" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1103</v>
+        <v>581</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -17760,23 +16037,17 @@
       <c r="W256" s="1"/>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A257" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>792</v>
-      </c>
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
       <c r="D257" s="1" t="s">
-        <v>701</v>
+        <v>259</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>909</v>
@@ -17785,7 +16056,7 @@
         <v>54</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -17807,22 +16078,22 @@
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1" t="s">
-        <v>143</v>
+        <v>300</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -17844,13 +16115,13 @@
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>704</v>
+        <v>316</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>909</v>
@@ -17877,23 +16148,29 @@
       <c r="W259" s="1"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A260" s="1"/>
-      <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
+      <c r="A260" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>801</v>
+      </c>
       <c r="D260" s="1" t="s">
-        <v>300</v>
+        <v>381</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>705</v>
+        <v>388</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>578</v>
@@ -17918,22 +16195,22 @@
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>316</v>
+        <v>706</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="J261" s="1"/>
       <c r="K261" s="1"/>
@@ -17951,29 +16228,23 @@
       <c r="W261" s="1"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A262" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>801</v>
-      </c>
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
       <c r="D262" s="1" t="s">
-        <v>381</v>
+        <v>35</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>388</v>
+        <v>707</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>578</v>
@@ -18001,19 +16272,19 @@
         <v>35</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>706</v>
+        <v>398</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
@@ -18035,13 +16306,13 @@
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1" t="s">
-        <v>35</v>
+        <v>686</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>913</v>
@@ -18050,7 +16321,7 @@
         <v>563</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>578</v>
+        <v>928</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -18072,22 +16343,22 @@
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1" t="s">
-        <v>35</v>
+        <v>601</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>398</v>
+        <v>709</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -18109,13 +16380,13 @@
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1" t="s">
-        <v>686</v>
+        <v>601</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>913</v>
@@ -18124,7 +16395,7 @@
         <v>563</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>928</v>
+        <v>586</v>
       </c>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -18142,17 +16413,23 @@
       <c r="W266" s="1"/>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A267" s="1"/>
-      <c r="B267" s="1"/>
-      <c r="C267" s="1"/>
+      <c r="A267" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>712</v>
+      </c>
       <c r="D267" s="1" t="s">
-        <v>601</v>
+        <v>212</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>709</v>
+        <v>976</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>913</v>
@@ -18161,13 +16438,19 @@
         <v>563</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>586</v>
+        <v>1185</v>
       </c>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
-      <c r="L267" s="1"/>
-      <c r="M267" s="1"/>
-      <c r="N267" s="1"/>
+      <c r="L267" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M267" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="N267" s="1" t="s">
+        <v>975</v>
+      </c>
       <c r="O267" s="1"/>
       <c r="P267" s="1"/>
       <c r="Q267" s="1"/>
@@ -18179,18 +16462,18 @@
       <c r="W267" s="1"/>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A268" s="1"/>
-      <c r="B268" s="1"/>
-      <c r="C268" s="1"/>
-      <c r="D268" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="F268" s="1" t="s">
-        <v>1204</v>
-      </c>
+      <c r="A268" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D268" s="1"/>
+      <c r="E268" s="1"/>
+      <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
         <v>913</v>
       </c>
@@ -18198,7 +16481,7 @@
         <v>563</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
@@ -18216,44 +16499,32 @@
       <c r="W268" s="1"/>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A269" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>712</v>
-      </c>
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
       <c r="D269" s="1" t="s">
-        <v>212</v>
+        <v>464</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>975</v>
+        <v>469</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>1184</v>
+        <v>589</v>
       </c>
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
-      <c r="L269" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M269" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="N269" s="1" t="s">
-        <v>974</v>
-      </c>
+      <c r="L269" s="1"/>
+      <c r="M269" s="1"/>
+      <c r="N269" s="1"/>
       <c r="O269" s="1"/>
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
@@ -18266,17 +16537,23 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>713</v>
+        <v>814</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="D270" s="1"/>
-      <c r="E270" s="1"/>
-      <c r="F270" s="1"/>
+        <v>815</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>1208</v>
+      </c>
       <c r="G270" s="1" t="s">
         <v>913</v>
       </c>
@@ -18284,9 +16561,11 @@
         <v>563</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J270" s="1"/>
+        <v>589</v>
+      </c>
+      <c r="J270" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K270" s="1"/>
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
@@ -18306,19 +16585,19 @@
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1" t="s">
-        <v>464</v>
+        <v>607</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>469</v>
+        <v>716</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>909</v>
+        <v>1210</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>589</v>
@@ -18339,36 +16618,28 @@
       <c r="W271" s="1"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A272" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>815</v>
-      </c>
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
       <c r="D272" s="1" t="s">
         <v>607</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>913</v>
+        <v>1210</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="J272" s="1" t="s">
-        <v>840</v>
-      </c>
+      <c r="J272" s="1"/>
       <c r="K272" s="1"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
@@ -18388,22 +16659,22 @@
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1" t="s">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1209</v>
+        <v>913</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="J273" s="1"/>
       <c r="K273" s="1"/>
@@ -18425,22 +16696,22 @@
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1" t="s">
-        <v>607</v>
+        <v>724</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1209</v>
+        <v>909</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="J274" s="1"/>
       <c r="K274" s="1"/>
@@ -18462,24 +16733,26 @@
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>913</v>
+        <v>845</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>563</v>
+        <v>1084</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J275" s="1"/>
+        <v>1170</v>
+      </c>
+      <c r="J275" s="1" t="s">
+        <v>1215</v>
+      </c>
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
@@ -18499,28 +16772,36 @@
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J276" s="1"/>
+        <v>1193</v>
+      </c>
+      <c r="J276" s="1" t="s">
+        <v>854</v>
+      </c>
       <c r="K276" s="1"/>
-      <c r="L276" s="1"/>
-      <c r="M276" s="1"/>
-      <c r="N276" s="1"/>
+      <c r="L276" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="M276" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="N276" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="O276" s="1"/>
       <c r="P276" s="1"/>
       <c r="Q276" s="1"/>
@@ -18536,26 +16817,24 @@
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1" t="s">
-        <v>693</v>
+        <v>572</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>694</v>
+        <v>746</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>845</v>
+        <v>1148</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>1083</v>
+        <v>1149</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="J277" s="1" t="s">
-        <v>1214</v>
-      </c>
+        <v>1218</v>
+      </c>
+      <c r="J277" s="1"/>
       <c r="K277" s="1"/>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
@@ -18575,36 +16854,30 @@
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>727</v>
+        <v>763</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1215</v>
+        <v>932</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>845</v>
+        <v>916</v>
       </c>
       <c r="H278" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1192</v>
+        <v>583</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>854</v>
+        <v>933</v>
       </c>
       <c r="K278" s="1"/>
-      <c r="L278" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="M278" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="N278" s="1" t="s">
-        <v>865</v>
-      </c>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+      <c r="N278" s="1"/>
       <c r="O278" s="1"/>
       <c r="P278" s="1"/>
       <c r="Q278" s="1"/>
@@ -18620,24 +16893,26 @@
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1" t="s">
-        <v>572</v>
+        <v>747</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1147</v>
+        <v>916</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>1148</v>
+        <v>54</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="J279" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="J279" s="1" t="s">
+        <v>1220</v>
+      </c>
       <c r="K279" s="1"/>
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
@@ -18657,30 +16932,36 @@
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1" t="s">
-        <v>747</v>
+        <v>179</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>932</v>
+        <v>851</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H280" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>933</v>
+        <v>832</v>
       </c>
       <c r="K280" s="1"/>
-      <c r="L280" s="1"/>
-      <c r="M280" s="1"/>
-      <c r="N280" s="1"/>
+      <c r="L280" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M280" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="N280" s="1" t="s">
+        <v>850</v>
+      </c>
       <c r="O280" s="1"/>
       <c r="P280" s="1"/>
       <c r="Q280" s="1"/>
@@ -18696,30 +16977,34 @@
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1" t="s">
-        <v>747</v>
+        <v>49</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>748</v>
+        <v>985</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1218</v>
+        <v>987</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H281" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J281" s="1" t="s">
-        <v>1219</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J281" s="1"/>
       <c r="K281" s="1"/>
-      <c r="L281" s="1"/>
-      <c r="M281" s="1"/>
-      <c r="N281" s="1"/>
+      <c r="L281" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M281" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="N281" s="1" t="s">
+        <v>986</v>
+      </c>
       <c r="O281" s="1"/>
       <c r="P281" s="1"/>
       <c r="Q281" s="1"/>
@@ -18735,35 +17020,33 @@
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1" t="s">
-        <v>179</v>
+        <v>858</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>751</v>
+        <v>270</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>851</v>
+        <v>990</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J282" s="1" t="s">
-        <v>832</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J282" s="1"/>
       <c r="K282" s="1"/>
       <c r="L282" s="1" t="s">
-        <v>179</v>
+        <v>858</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>751</v>
+        <v>270</v>
       </c>
       <c r="N282" s="1" t="s">
-        <v>850</v>
+        <v>1221</v>
       </c>
       <c r="O282" s="1"/>
       <c r="P282" s="1"/>
@@ -18776,44 +17059,64 @@
       <c r="W282" s="1"/>
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A283" s="1"/>
-      <c r="B283" s="1"/>
-      <c r="C283" s="1"/>
+      <c r="A283" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="D283" s="1" t="s">
-        <v>49</v>
+        <v>291</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>984</v>
+        <v>294</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>986</v>
+        <v>757</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>54</v>
+        <v>1084</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J283" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J283" s="1" t="s">
+        <v>1222</v>
+      </c>
       <c r="K283" s="1"/>
       <c r="L283" s="1" t="s">
-        <v>49</v>
+        <v>686</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>984</v>
+        <v>294</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="O283" s="1"/>
-      <c r="P283" s="1"/>
-      <c r="Q283" s="1"/>
-      <c r="R283" s="1"/>
-      <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
+        <v>1223</v>
+      </c>
+      <c r="O283" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="P283" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q283" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="R283" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S283" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T283" s="1" t="s">
+        <v>908</v>
+      </c>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -18823,34 +17126,28 @@
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1" t="s">
-        <v>858</v>
+        <v>269</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>270</v>
+        <v>754</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>989</v>
+        <v>1224</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>578</v>
       </c>
       <c r="J284" s="1"/>
       <c r="K284" s="1"/>
-      <c r="L284" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="M284" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="N284" s="1" t="s">
-        <v>1220</v>
-      </c>
+      <c r="L284" s="1"/>
+      <c r="M284" s="1"/>
+      <c r="N284" s="1"/>
       <c r="O284" s="1"/>
       <c r="P284" s="1"/>
       <c r="Q284" s="1"/>
@@ -18862,64 +17159,44 @@
       <c r="W284" s="1"/>
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A285" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
       <c r="D285" s="1" t="s">
-        <v>291</v>
+        <v>363</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>757</v>
+        <v>1225</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>845</v>
+        <v>914</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>1083</v>
+        <v>924</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J285" s="1" t="s">
-        <v>1221</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J285" s="1"/>
       <c r="K285" s="1"/>
       <c r="L285" s="1" t="s">
-        <v>686</v>
+        <v>363</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="O285" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="P285" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q285" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="R285" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="S285" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T285" s="1" t="s">
-        <v>908</v>
-      </c>
+        <v>1226</v>
+      </c>
+      <c r="O285" s="1"/>
+      <c r="P285" s="1"/>
+      <c r="Q285" s="1"/>
+      <c r="R285" s="1"/>
+      <c r="S285" s="1"/>
+      <c r="T285" s="1"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -18929,22 +17206,22 @@
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
       <c r="D286" s="1" t="s">
-        <v>269</v>
+        <v>476</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>54</v>
+        <v>1084</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J286" s="1"/>
       <c r="K286" s="1"/>
@@ -18966,34 +17243,28 @@
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1" t="s">
-        <v>363</v>
+        <v>442</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>331</v>
+        <v>443</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>924</v>
+        <v>54</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="J287" s="1"/>
       <c r="K287" s="1"/>
-      <c r="L287" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M287" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="N287" s="1" t="s">
-        <v>1225</v>
-      </c>
+      <c r="L287" s="1"/>
+      <c r="M287" s="1"/>
+      <c r="N287" s="1"/>
       <c r="O287" s="1"/>
       <c r="P287" s="1"/>
       <c r="Q287" s="1"/>
@@ -19009,28 +17280,34 @@
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>1083</v>
+        <v>924</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
-      <c r="L288" s="1"/>
-      <c r="M288" s="1"/>
-      <c r="N288" s="1"/>
+      <c r="L288" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="M288" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="N288" s="1" t="s">
+        <v>1230</v>
+      </c>
       <c r="O288" s="1"/>
       <c r="P288" s="1"/>
       <c r="Q288" s="1"/>
@@ -19046,13 +17323,13 @@
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1" t="s">
-        <v>442</v>
+        <v>35</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>443</v>
+        <v>761</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>909</v>
@@ -19061,13 +17338,19 @@
         <v>54</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="J289" s="1"/>
       <c r="K289" s="1"/>
-      <c r="L289" s="1"/>
-      <c r="M289" s="1"/>
-      <c r="N289" s="1"/>
+      <c r="L289" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M289" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="N289" s="1" t="s">
+        <v>1232</v>
+      </c>
       <c r="O289" s="1"/>
       <c r="P289" s="1"/>
       <c r="Q289" s="1"/>
@@ -19083,34 +17366,30 @@
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>845</v>
+        <v>1234</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>924</v>
+        <v>54</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J290" s="1"/>
+        <v>1104</v>
+      </c>
+      <c r="J290" s="1" t="s">
+        <v>977</v>
+      </c>
       <c r="K290" s="1"/>
-      <c r="L290" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="M290" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="N290" s="1" t="s">
-        <v>1229</v>
-      </c>
+      <c r="L290" s="1"/>
+      <c r="M290" s="1"/>
+      <c r="N290" s="1"/>
       <c r="O290" s="1"/>
       <c r="P290" s="1"/>
       <c r="Q290" s="1"/>
@@ -19126,13 +17405,13 @@
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1" t="s">
-        <v>35</v>
+        <v>747</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>909</v>
@@ -19145,15 +17424,9 @@
       </c>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
-      <c r="L291" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M291" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="N291" s="1" t="s">
-        <v>1231</v>
-      </c>
+      <c r="L291" s="1"/>
+      <c r="M291" s="1"/>
+      <c r="N291" s="1"/>
       <c r="O291" s="1"/>
       <c r="P291" s="1"/>
       <c r="Q291" s="1"/>
@@ -19169,25 +17442,25 @@
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1" t="s">
-        <v>476</v>
+        <v>747</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1233</v>
+        <v>916</v>
       </c>
       <c r="H292" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>1103</v>
+        <v>579</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>976</v>
+        <v>1237</v>
       </c>
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
@@ -19208,22 +17481,22 @@
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
-        <v>747</v>
+        <v>98</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J293" s="1"/>
       <c r="K293" s="1"/>
@@ -19241,34 +17514,38 @@
       <c r="W293" s="1"/>
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A294" s="1"/>
-      <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
+      <c r="A294" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>989</v>
+      </c>
       <c r="D294" s="1" t="s">
-        <v>747</v>
+        <v>43</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>764</v>
+        <v>988</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="H294" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I294" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J294" s="1" t="s">
-        <v>1236</v>
-      </c>
+        <v>1239</v>
+      </c>
+      <c r="G294" s="1"/>
+      <c r="H294" s="1"/>
+      <c r="I294" s="1"/>
+      <c r="J294" s="1"/>
       <c r="K294" s="1"/>
-      <c r="L294" s="1"/>
-      <c r="M294" s="1"/>
-      <c r="N294" s="1"/>
+      <c r="L294" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M294" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="N294" s="1" t="s">
+        <v>1240</v>
+      </c>
       <c r="O294" s="1"/>
       <c r="P294" s="1"/>
       <c r="Q294" s="1"/>
@@ -19280,28 +17557,36 @@
       <c r="W294" s="1"/>
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A295" s="1"/>
-      <c r="B295" s="1"/>
-      <c r="C295" s="1"/>
+      <c r="A295" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>1241</v>
+      </c>
       <c r="D295" s="1" t="s">
-        <v>98</v>
+        <v>747</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>768</v>
+        <v>934</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J295" s="1"/>
+        <v>586</v>
+      </c>
+      <c r="J295" s="1" t="s">
+        <v>1243</v>
+      </c>
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
@@ -19317,38 +17602,32 @@
       <c r="W295" s="1"/>
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A296" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>988</v>
-      </c>
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
       <c r="D296" s="1" t="s">
-        <v>43</v>
+        <v>698</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>987</v>
+        <v>770</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G296" s="1"/>
-      <c r="H296" s="1"/>
-      <c r="I296" s="1"/>
+        <v>1244</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="H296" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>1104</v>
+      </c>
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
-      <c r="L296" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M296" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="N296" s="1" t="s">
-        <v>1239</v>
-      </c>
+      <c r="L296" s="1"/>
+      <c r="M296" s="1"/>
+      <c r="N296" s="1"/>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
       <c r="Q296" s="1"/>
@@ -19360,36 +17639,28 @@
       <c r="W296" s="1"/>
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A297" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>1240</v>
-      </c>
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
       <c r="D297" s="1" t="s">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>934</v>
+        <v>772</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H297" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="J297" s="1" t="s">
-        <v>1242</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J297" s="1"/>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
@@ -19409,23 +17680,21 @@
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1" t="s">
-        <v>698</v>
+        <v>212</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1243</v>
+        <v>774</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I298" s="1" t="s">
-        <v>1103</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="I298" s="1"/>
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
@@ -19442,17 +17711,23 @@
       <c r="W298" s="1"/>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A299" s="1"/>
-      <c r="B299" s="1"/>
-      <c r="C299" s="1"/>
+      <c r="A299" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>776</v>
+      </c>
       <c r="D299" s="1" t="s">
-        <v>771</v>
+        <v>300</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>772</v>
+        <v>335</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>909</v>
@@ -19463,7 +17738,9 @@
       <c r="I299" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="J299" s="1"/>
+      <c r="J299" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="K299" s="1"/>
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
@@ -19479,30 +17756,44 @@
       <c r="W299" s="1"/>
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A300" s="1"/>
-      <c r="B300" s="1"/>
-      <c r="C300" s="1"/>
+      <c r="A300" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="D300" s="1" t="s">
-        <v>212</v>
+        <v>390</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>774</v>
+        <v>67</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>774</v>
+        <v>1247</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>911</v>
+        <v>845</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="I300" s="1"/>
+        <v>924</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>578</v>
+      </c>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
-      <c r="L300" s="1"/>
-      <c r="M300" s="1"/>
-      <c r="N300" s="1"/>
+      <c r="L300" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="M300" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N300" s="1" t="s">
+        <v>943</v>
+      </c>
       <c r="O300" s="1"/>
       <c r="P300" s="1"/>
       <c r="Q300" s="1"/>
@@ -19515,34 +17806,34 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>300</v>
+        <v>49</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>335</v>
+        <v>786</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>300</v>
+        <v>49</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>335</v>
+        <v>767</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>338</v>
+        <v>1249</v>
       </c>
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
@@ -19560,42 +17851,42 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>390</v>
+        <v>57</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>65</v>
+        <v>788</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>391</v>
+        <v>789</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>390</v>
+        <v>57</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>67</v>
+        <v>790</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>924</v>
+        <v>54</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
       <c r="L302" s="1" t="s">
-        <v>390</v>
+        <v>57</v>
       </c>
       <c r="M302" s="1" t="s">
-        <v>67</v>
+        <v>790</v>
       </c>
       <c r="N302" s="1" t="s">
-        <v>943</v>
+        <v>1251</v>
       </c>
       <c r="O302" s="1"/>
       <c r="P302" s="1"/>
@@ -19608,36 +17899,28 @@
       <c r="W302" s="1"/>
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A303" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>787</v>
-      </c>
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
       <c r="D303" s="1" t="s">
-        <v>49</v>
+        <v>504</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>767</v>
+        <v>819</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1247</v>
+        <v>819</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>916</v>
+        <v>845</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>54</v>
+        <v>1084</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J303" s="1" t="s">
-        <v>1248</v>
-      </c>
+        <v>1170</v>
+      </c>
+      <c r="J303" s="1"/>
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
@@ -19653,44 +17936,34 @@
       <c r="W303" s="1"/>
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A304" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>789</v>
-      </c>
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
       <c r="D304" s="1" t="s">
-        <v>57</v>
+        <v>607</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>790</v>
+        <v>899</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1249</v>
+        <v>900</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J304" s="1"/>
+        <v>589</v>
+      </c>
+      <c r="J304" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K304" s="1"/>
-      <c r="L304" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M304" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="N304" s="1" t="s">
-        <v>1250</v>
-      </c>
+      <c r="L304" s="1"/>
+      <c r="M304" s="1"/>
+      <c r="N304" s="1"/>
       <c r="O304" s="1"/>
       <c r="P304" s="1"/>
       <c r="Q304" s="1"/>
@@ -19706,28 +17979,36 @@
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1" t="s">
-        <v>504</v>
+        <v>607</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>819</v>
+        <v>1298</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>845</v>
+        <v>913</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>1083</v>
+        <v>563</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="J305" s="1"/>
+        <v>589</v>
+      </c>
+      <c r="J305" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K305" s="1"/>
-      <c r="L305" s="1"/>
-      <c r="M305" s="1"/>
-      <c r="N305" s="1"/>
+      <c r="L305" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M305" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="N305" s="1" t="s">
+        <v>1252</v>
+      </c>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
@@ -19743,36 +18024,26 @@
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1" t="s">
-        <v>607</v>
+        <v>821</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>899</v>
+        <v>822</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1309</v>
+        <v>1253</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>913</v>
+        <v>1148</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I306" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J306" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>1149</v>
+      </c>
+      <c r="I306" s="1"/>
+      <c r="J306" s="1"/>
       <c r="K306" s="1"/>
-      <c r="L306" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="M306" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="N306" s="1" t="s">
-        <v>900</v>
-      </c>
+      <c r="L306" s="1"/>
+      <c r="M306" s="1"/>
+      <c r="N306" s="1"/>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
@@ -19788,36 +18059,26 @@
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1" t="s">
-        <v>607</v>
+        <v>821</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1297</v>
+        <v>1254</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>913</v>
+        <v>1148</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I307" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J307" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>1149</v>
+      </c>
+      <c r="I307" s="1"/>
+      <c r="J307" s="1"/>
       <c r="K307" s="1"/>
-      <c r="L307" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="M307" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="N307" s="1" t="s">
-        <v>1251</v>
-      </c>
+      <c r="L307" s="1"/>
+      <c r="M307" s="1"/>
+      <c r="N307" s="1"/>
       <c r="O307" s="1"/>
       <c r="P307" s="1"/>
       <c r="Q307" s="1"/>
@@ -19833,19 +18094,19 @@
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1" t="s">
-        <v>821</v>
+        <v>1255</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -19868,22 +18129,26 @@
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1" t="s">
-        <v>821</v>
+        <v>517</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1147</v>
+        <v>845</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I309" s="1"/>
-      <c r="J309" s="1"/>
+        <v>1084</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="J309" s="1" t="s">
+        <v>1258</v>
+      </c>
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
@@ -19898,37 +18163,33 @@
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
     </row>
-    <row r="310" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
-      <c r="D310" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E310" s="5" t="s">
-        <v>1310</v>
-      </c>
-      <c r="F310" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G310" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="H310" s="1"/>
+      <c r="D310" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="H310" s="1" t="s">
+        <v>563</v>
+      </c>
       <c r="I310" s="1" t="s">
-        <v>578</v>
+        <v>928</v>
       </c>
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
-      <c r="L310" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="M310" s="5" t="s">
-        <v>1310</v>
-      </c>
-      <c r="N310" s="5" t="s">
-        <v>1312</v>
-      </c>
+      <c r="L310" s="1"/>
+      <c r="M310" s="1"/>
+      <c r="N310" s="1"/>
       <c r="O310" s="1"/>
       <c r="P310" s="1"/>
       <c r="Q310" s="1"/>
@@ -19944,26 +18205,34 @@
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
       <c r="D311" s="1" t="s">
-        <v>1254</v>
+        <v>106</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>824</v>
+        <v>114</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1147</v>
+        <v>913</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I311" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I311" s="1" t="s">
+        <v>588</v>
+      </c>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
-      <c r="L311" s="1"/>
-      <c r="M311" s="1"/>
-      <c r="N311" s="1"/>
+      <c r="L311" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M311" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N311" s="1" t="s">
+        <v>1262</v>
+      </c>
       <c r="O311" s="1"/>
       <c r="P311" s="1"/>
       <c r="Q311" s="1"/>
@@ -19979,25 +18248,25 @@
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1" t="s">
-        <v>517</v>
+        <v>98</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>845</v>
+        <v>917</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>1083</v>
+        <v>54</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>879</v>
+        <v>579</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
@@ -20018,24 +18287,26 @@
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1" t="s">
-        <v>686</v>
+        <v>179</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1258</v>
+        <v>180</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="J313" s="1"/>
+        <v>583</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>1266</v>
+      </c>
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
@@ -20055,33 +18326,33 @@
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1" t="s">
-        <v>106</v>
+        <v>833</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>114</v>
+        <v>834</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
       <c r="L314" s="1" t="s">
-        <v>106</v>
+        <v>1268</v>
       </c>
       <c r="M314" s="1" t="s">
-        <v>114</v>
+        <v>834</v>
       </c>
       <c r="N314" s="1" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="O314" s="1"/>
       <c r="P314" s="1"/>
@@ -20098,26 +18369,24 @@
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1" t="s">
-        <v>98</v>
+        <v>836</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>828</v>
+        <v>837</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J315" s="1" t="s">
-        <v>1263</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J315" s="1"/>
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
@@ -20137,25 +18406,25 @@
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1" t="s">
-        <v>179</v>
+        <v>421</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>180</v>
+        <v>424</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1264</v>
+        <v>844</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>916</v>
+        <v>845</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>1265</v>
+        <v>846</v>
       </c>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
@@ -20172,38 +18441,38 @@
       <c r="W316" s="1"/>
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A317" s="1"/>
-      <c r="B317" s="1"/>
-      <c r="C317" s="1"/>
+      <c r="A317" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>827</v>
+      </c>
       <c r="D317" s="1" t="s">
-        <v>833</v>
+        <v>433</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1266</v>
+        <v>848</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>562</v>
+        <v>729</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="J317" s="1"/>
       <c r="K317" s="1"/>
-      <c r="L317" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="M317" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="N317" s="1" t="s">
-        <v>1268</v>
-      </c>
+      <c r="L317" s="1"/>
+      <c r="M317" s="1"/>
+      <c r="N317" s="1"/>
       <c r="O317" s="1"/>
       <c r="P317" s="1"/>
       <c r="Q317" s="1"/>
@@ -20215,26 +18484,32 @@
       <c r="W317" s="1"/>
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A318" s="1"/>
-      <c r="B318" s="1"/>
-      <c r="C318" s="1"/>
+      <c r="A318" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="D318" s="1" t="s">
-        <v>836</v>
+        <v>407</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>837</v>
+        <v>410</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1269</v>
+        <v>411</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
@@ -20256,26 +18531,24 @@
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1" t="s">
-        <v>421</v>
+        <v>143</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>424</v>
+        <v>566</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>844</v>
+        <v>794</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H319" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J319" s="1" t="s">
-        <v>846</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="J319" s="1"/>
       <c r="K319" s="1"/>
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
@@ -20292,33 +18565,35 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>433</v>
+        <v>49</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>433</v>
+        <v>49</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>848</v>
+        <v>1271</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J320" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J320" s="1" t="s">
+        <v>1272</v>
+      </c>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
@@ -20334,34 +18609,30 @@
       <c r="W320" s="1"/>
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A321" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>852</v>
-      </c>
+      <c r="A321" s="1"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
       <c r="D321" s="1" t="s">
-        <v>407</v>
+        <v>143</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>410</v>
+        <v>866</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>411</v>
+        <v>867</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H321" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J321" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>869</v>
+      </c>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
@@ -20381,24 +18652,26 @@
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
       <c r="D322" s="1" t="s">
-        <v>143</v>
+        <v>381</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>566</v>
+        <v>69</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>794</v>
+        <v>926</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="H322" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J322" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="J322" s="1" t="s">
+        <v>907</v>
+      </c>
       <c r="K322" s="1"/>
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
@@ -20414,36 +18687,28 @@
       <c r="W322" s="1"/>
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A323" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>856</v>
-      </c>
+      <c r="A323" s="1"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
       <c r="D323" s="1" t="s">
-        <v>49</v>
+        <v>381</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>857</v>
+        <v>69</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J323" s="1" t="s">
-        <v>1271</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J323" s="1"/>
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
@@ -20463,26 +18728,24 @@
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
       <c r="D324" s="1" t="s">
-        <v>143</v>
+        <v>625</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J324" s="1" t="s">
-        <v>869</v>
-      </c>
+        <v>876</v>
+      </c>
+      <c r="J324" s="1"/>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
@@ -20502,25 +18765,25 @@
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1" t="s">
-        <v>381</v>
+        <v>517</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>69</v>
+        <v>877</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>926</v>
+        <v>878</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>584</v>
+        <v>879</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>907</v>
+        <v>880</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -20537,32 +18800,46 @@
       <c r="W325" s="1"/>
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A326" s="1"/>
-      <c r="B326" s="1"/>
-      <c r="C326" s="1"/>
+      <c r="A326" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>952</v>
+      </c>
       <c r="D326" s="1" t="s">
-        <v>381</v>
+        <v>464</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>69</v>
+        <v>881</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>909</v>
+        <v>1275</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J326" s="1"/>
+        <v>589</v>
+      </c>
+      <c r="J326" s="1" t="s">
+        <v>882</v>
+      </c>
       <c r="K326" s="1"/>
-      <c r="L326" s="1"/>
-      <c r="M326" s="1"/>
-      <c r="N326" s="1"/>
+      <c r="L326" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="M326" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="N326" s="1" t="s">
+        <v>1276</v>
+      </c>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
       <c r="Q326" s="1"/>
@@ -20578,28 +18855,34 @@
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1" t="s">
-        <v>625</v>
+        <v>363</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>874</v>
+        <v>925</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>875</v>
+        <v>1277</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>921</v>
+        <v>845</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>562</v>
+        <v>924</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>876</v>
+        <v>578</v>
       </c>
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
-      <c r="L327" s="1"/>
-      <c r="M327" s="1"/>
-      <c r="N327" s="1"/>
+      <c r="L327" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M327" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="N327" s="1" t="s">
+        <v>1278</v>
+      </c>
       <c r="O327" s="1"/>
       <c r="P327" s="1"/>
       <c r="Q327" s="1"/>
@@ -20611,34 +18894,35 @@
       <c r="W327" s="1"/>
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A328" s="1"/>
-      <c r="B328" s="1"/>
-      <c r="C328" s="1"/>
+      <c r="A328" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>1280</v>
+      </c>
       <c r="D328" s="1" t="s">
-        <v>517</v>
+        <v>381</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>877</v>
+        <v>62</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>878</v>
+        <v>1279</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="H328" s="1" t="s">
         <v>563</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="J328" s="1" t="s">
-        <v>880</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J328" s="1"/>
       <c r="K328" s="1"/>
-      <c r="L328" s="1"/>
-      <c r="M328" s="1"/>
-      <c r="N328" s="1"/>
       <c r="O328" s="1"/>
       <c r="P328" s="1"/>
       <c r="Q328" s="1"/>
@@ -20650,49 +18934,49 @@
       <c r="W328" s="1"/>
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A329" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>952</v>
-      </c>
+      <c r="A329" s="1"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
       <c r="D329" s="1" t="s">
-        <v>464</v>
+        <v>35</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>881</v>
+        <v>410</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1273</v>
+        <v>929</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1274</v>
+        <v>916</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>882</v>
+        <v>852</v>
       </c>
       <c r="K329" s="1"/>
       <c r="L329" s="1" t="s">
-        <v>464</v>
+        <v>35</v>
       </c>
       <c r="M329" s="1" t="s">
-        <v>881</v>
+        <v>410</v>
       </c>
       <c r="N329" s="1" t="s">
-        <v>1275</v>
-      </c>
-      <c r="O329" s="1"/>
-      <c r="P329" s="1"/>
-      <c r="Q329" s="1"/>
+        <v>941</v>
+      </c>
+      <c r="O329" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P329" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q329" s="1" t="s">
+        <v>596</v>
+      </c>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
       <c r="T329" s="1"/>
@@ -20701,38 +18985,38 @@
       <c r="W329" s="1"/>
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A330" s="1"/>
-      <c r="B330" s="1"/>
-      <c r="C330" s="1"/>
+      <c r="A330" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>883</v>
+      </c>
       <c r="D330" s="1" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>925</v>
+        <v>884</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1276</v>
+        <v>882</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>845</v>
+        <v>1275</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>924</v>
+        <v>729</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
-      <c r="L330" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M330" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="N330" s="1" t="s">
-        <v>1277</v>
-      </c>
+      <c r="L330" s="1"/>
+      <c r="M330" s="1"/>
+      <c r="N330" s="1"/>
       <c r="O330" s="1"/>
       <c r="P330" s="1"/>
       <c r="Q330" s="1"/>
@@ -20744,23 +19028,17 @@
       <c r="W330" s="1"/>
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A331" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>1279</v>
-      </c>
+      <c r="A331" s="1"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
       <c r="D331" s="1" t="s">
-        <v>381</v>
+        <v>686</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>62</v>
+        <v>708</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1278</v>
+        <v>927</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>913</v>
@@ -20769,10 +19047,13 @@
         <v>563</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>578</v>
+        <v>928</v>
       </c>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
+      <c r="L331" s="1"/>
+      <c r="M331" s="1"/>
+      <c r="N331" s="1"/>
       <c r="O331" s="1"/>
       <c r="P331" s="1"/>
       <c r="Q331" s="1"/>
@@ -20784,83 +19065,51 @@
       <c r="W331" s="1"/>
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
       <c r="D332" s="1" t="s">
-        <v>35</v>
+        <v>476</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>410</v>
+        <v>482</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>929</v>
+        <v>853</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>916</v>
+        <v>1286</v>
       </c>
       <c r="H332" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>584</v>
+        <v>1085</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="K332" s="1"/>
-      <c r="L332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M332" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="N332" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="O332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P332" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q332" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="R332" s="1"/>
-      <c r="S332" s="1"/>
-      <c r="T332" s="1"/>
-      <c r="U332" s="1"/>
-      <c r="V332" s="1"/>
-      <c r="W332" s="1"/>
+        <v>1095</v>
+      </c>
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A333" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>883</v>
-      </c>
+      <c r="A333" s="1"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
       <c r="D333" s="1" t="s">
-        <v>464</v>
+        <v>836</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>882</v>
+        <v>922</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>1274</v>
+        <v>912</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>729</v>
+        <v>1132</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
@@ -20882,22 +19131,22 @@
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
       <c r="D334" s="1" t="s">
-        <v>686</v>
+        <v>885</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>708</v>
+        <v>887</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
@@ -20915,51 +19164,63 @@
       <c r="W334" s="1"/>
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1" t="s">
-        <v>476</v>
+        <v>724</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>482</v>
+        <v>889</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>853</v>
+        <v>890</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>1285</v>
+        <v>909</v>
       </c>
       <c r="H335" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J335" s="1" t="s">
-        <v>1094</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="J335" s="1"/>
+      <c r="K335" s="1"/>
+      <c r="L335" s="1"/>
+      <c r="M335" s="1"/>
+      <c r="N335" s="1"/>
+      <c r="O335" s="1"/>
+      <c r="P335" s="1"/>
+      <c r="Q335" s="1"/>
+      <c r="R335" s="1"/>
+      <c r="S335" s="1"/>
+      <c r="T335" s="1"/>
+      <c r="U335" s="1"/>
+      <c r="V335" s="1"/>
+      <c r="W335" s="1"/>
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1" t="s">
-        <v>836</v>
+        <v>892</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>1131</v>
+        <v>54</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
@@ -20981,22 +19242,22 @@
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -21018,28 +19279,32 @@
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1" t="s">
-        <v>724</v>
+        <v>569</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>889</v>
+        <v>569</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>890</v>
+        <v>569</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>909</v>
+        <v>1148</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I338" s="1" t="s">
-        <v>594</v>
-      </c>
+        <v>1149</v>
+      </c>
+      <c r="I338" s="1"/>
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
-      <c r="L338" s="1"/>
-      <c r="M338" s="1"/>
-      <c r="N338" s="1"/>
+      <c r="L338" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="M338" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="N338" s="1" t="s">
+        <v>896</v>
+      </c>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
       <c r="Q338" s="1"/>
@@ -21055,28 +19320,32 @@
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>909</v>
+        <v>1148</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I339" s="1" t="s">
-        <v>589</v>
-      </c>
+        <v>1149</v>
+      </c>
+      <c r="I339" s="1"/>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
-      <c r="L339" s="1"/>
-      <c r="M339" s="1"/>
-      <c r="N339" s="1"/>
+      <c r="L339" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="M339" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="N339" s="1" t="s">
+        <v>897</v>
+      </c>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
       <c r="Q339" s="1"/>
@@ -21092,28 +19361,32 @@
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1" t="s">
-        <v>892</v>
+        <v>572</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>893</v>
+        <v>572</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>894</v>
+        <v>572</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>909</v>
+        <v>1148</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I340" s="1" t="s">
-        <v>589</v>
-      </c>
+        <v>1149</v>
+      </c>
+      <c r="I340" s="1"/>
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
-      <c r="L340" s="1"/>
-      <c r="M340" s="1"/>
-      <c r="N340" s="1"/>
+      <c r="L340" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="M340" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N340" s="1" t="s">
+        <v>898</v>
+      </c>
       <c r="O340" s="1"/>
       <c r="P340" s="1"/>
       <c r="Q340" s="1"/>
@@ -21129,31 +19402,31 @@
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1147</v>
+        <v>1281</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
       <c r="L341" s="1" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="M341" s="1" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="N341" s="1" t="s">
-        <v>896</v>
+        <v>577</v>
       </c>
       <c r="O341" s="1"/>
       <c r="P341" s="1"/>
@@ -21165,307 +19438,9 @@
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A342" s="1"/>
-      <c r="B342" s="1"/>
-      <c r="C342" s="1"/>
-      <c r="D342" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="E342" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="F342" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="G342" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="H342" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I342" s="1"/>
-      <c r="J342" s="1"/>
-      <c r="K342" s="1"/>
-      <c r="L342" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="M342" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="N342" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="O342" s="1"/>
-      <c r="P342" s="1"/>
-      <c r="Q342" s="1"/>
-      <c r="R342" s="1"/>
-      <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
-      <c r="U342" s="1"/>
-      <c r="V342" s="1"/>
-      <c r="W342" s="1"/>
-    </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A343" s="1"/>
-      <c r="B343" s="1"/>
-      <c r="C343" s="1"/>
-      <c r="D343" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="E343" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="F343" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="G343" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="H343" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I343" s="1"/>
-      <c r="J343" s="1"/>
-      <c r="K343" s="1"/>
-      <c r="L343" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="M343" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="N343" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="O343" s="1"/>
-      <c r="P343" s="1"/>
-      <c r="Q343" s="1"/>
-      <c r="R343" s="1"/>
-      <c r="S343" s="1"/>
-      <c r="T343" s="1"/>
-      <c r="U343" s="1"/>
-      <c r="V343" s="1"/>
-      <c r="W343" s="1"/>
-    </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A344" s="1"/>
-      <c r="B344" s="1"/>
-      <c r="C344" s="1"/>
-      <c r="D344" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E344" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="F344" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="G344" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="H344" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="I344" s="1"/>
-      <c r="J344" s="1"/>
-      <c r="K344" s="1"/>
-      <c r="L344" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="M344" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="N344" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="O344" s="1"/>
-      <c r="P344" s="1"/>
-      <c r="Q344" s="1"/>
-      <c r="R344" s="1"/>
-      <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
-      <c r="U344" s="1"/>
-      <c r="V344" s="1"/>
-      <c r="W344" s="1"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="160" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="215"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="150"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0415\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21F931-BB0C-473A-AE08-EE7A5E2C41E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFAA402-CB2C-4C98-9B7C-068E01F45A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1325">
   <si>
     <t>替代规格2</t>
   </si>
@@ -2965,9 +2965,6 @@
     <t>SC243XSO-118113-TR-Q</t>
   </si>
   <si>
-    <t>SC1134UA-CI-00AY-44E</t>
-  </si>
-  <si>
     <t>SC4011DN-CB-90LR-4011</t>
   </si>
   <si>
@@ -3966,13 +3963,88 @@
   </si>
   <si>
     <t>SC2434SO-N-CD-X0NR-2434</t>
+  </si>
+  <si>
+    <t>SC1134UA-CF-90AK-1134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CF-90AK-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CF-90AK-44L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-90AY-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AY-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC69401DC-SPI3P3-Q-HD-4XAR-69401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2203SO-TR</t>
+  </si>
+  <si>
+    <t>SC2203SO-CH-10AR-2203</t>
+  </si>
+  <si>
+    <t>SC2203SO-CH-10NR-2203</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC2G201A</t>
+  </si>
+  <si>
+    <t>SC24023SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-N-GA-00NR-2403</t>
+  </si>
+  <si>
+    <t>SC24023SO-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-GA-00NR-2403</t>
+  </si>
+  <si>
+    <t>SC2403SO-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-DB-00NR-2403</t>
+  </si>
+  <si>
+    <t>SC2403SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2403SO-N-DB-00NR-2403</t>
+  </si>
+  <si>
+    <t>宁芯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9642TS-EC-Q-AH-4XAR-9642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9642TS-EC-Q-AH-43LR-9642</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3986,6 +4058,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4041,17 +4120,1629 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="161">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4327,7 +6018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}">
-  <dimension ref="A1:W341"/>
+  <dimension ref="A1:W344"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -4357,46 +6048,46 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>996</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>997</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>998</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>1004</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>2</v>
@@ -4434,7 +6125,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -4443,7 +6134,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>909</v>
@@ -4612,22 +6303,22 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B6" t="s">
         <v>1289</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>1290</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>1290</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1292</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -4694,7 +6385,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -4760,7 +6451,7 @@
         <v>123</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>909</v>
@@ -4797,7 +6488,7 @@
         <v>123</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>905</v>
+        <v>1305</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>909</v>
@@ -4809,12 +6500,18 @@
         <v>584</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>905</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -4836,7 +6533,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>903</v>
+        <v>1304</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>909</v>
@@ -4848,12 +6545,18 @@
         <v>584</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -4875,7 +6578,7 @@
         <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>904</v>
+        <v>1306</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>909</v>
@@ -4887,12 +6590,18 @@
         <v>584</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>904</v>
+      </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -4908,7 +6617,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>31</v>
@@ -4917,7 +6626,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>30</v>
@@ -4963,7 +6672,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>914</v>
@@ -5010,7 +6719,7 @@
         <v>40</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -5068,7 +6777,7 @@
         <v>36</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>32</v>
@@ -5097,7 +6806,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>909</v>
@@ -5269,7 +6978,7 @@
         <v>971</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>909</v>
@@ -5318,7 +7027,7 @@
         <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>845</v>
@@ -5347,7 +7056,7 @@
         <v>62</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>35</v>
@@ -5365,7 +7074,7 @@
         <v>62</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.2">
@@ -5416,7 +7125,7 @@
         <v>67</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>35</v>
@@ -5448,7 +7157,7 @@
         <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>909</v>
@@ -5470,7 +7179,7 @@
         <v>69</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -5562,7 +7271,7 @@
         <v>73</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>35</v>
@@ -5603,7 +7312,7 @@
         <v>76</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>909</v>
@@ -5623,7 +7332,7 @@
         <v>76</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -5646,7 +7355,7 @@
         <v>62</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>913</v>
@@ -5666,7 +7375,7 @@
         <v>62</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -5750,7 +7459,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>909</v>
@@ -5942,7 +7651,7 @@
         <v>615</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>916</v>
@@ -5987,7 +7696,7 @@
         <v>902</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>916</v>
@@ -6038,7 +7747,7 @@
         <v>100</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>913</v>
@@ -6204,7 +7913,7 @@
         <v>114</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -6405,7 +8114,7 @@
         <v>123</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>974</v>
+        <v>1308</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>909</v>
@@ -6420,9 +8129,15 @@
         <v>124</v>
       </c>
       <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
+      <c r="L43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>1307</v>
+      </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
@@ -6681,7 +8396,7 @@
         <v>583</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
@@ -6720,7 +8435,7 @@
         <v>148</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>917</v>
@@ -7095,10 +8810,10 @@
         <v>143</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>1294</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>1295</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>916</v>
@@ -7158,10 +8873,10 @@
         <v>143</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>1296</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>1297</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>916</v>
@@ -7192,7 +8907,7 @@
         <v>164</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
@@ -7986,7 +9701,7 @@
         <v>230</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>229</v>
@@ -8841,7 +10556,7 @@
         <v>270</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>911</v>
@@ -9047,7 +10762,7 @@
         <v>580</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -9080,7 +10795,7 @@
         <v>561</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>913</v>
@@ -9092,7 +10807,7 @@
         <v>580</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -9137,7 +10852,7 @@
         <v>580</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -9182,7 +10897,7 @@
         <v>580</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="1" t="s">
@@ -9215,7 +10930,7 @@
         <v>719</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>845</v>
@@ -9227,7 +10942,7 @@
         <v>580</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -9266,7 +10981,7 @@
         <v>580</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -9342,7 +11057,7 @@
         <v>297</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>845</v>
@@ -9362,7 +11077,7 @@
         <v>297</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
@@ -9448,7 +11163,7 @@
         <v>937</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
@@ -9477,7 +11192,7 @@
         <v>303</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>914</v>
@@ -9509,13 +11224,13 @@
         <v>304</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>303</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="U111" s="1" t="s">
         <v>621</v>
@@ -9524,7 +11239,7 @@
         <v>303</v>
       </c>
       <c r="W111" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.2">
@@ -9589,7 +11304,7 @@
         <v>312</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>845</v>
@@ -9627,7 +11342,7 @@
         <v>312</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
@@ -9828,7 +11543,7 @@
         <v>331</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>914</v>
@@ -10143,7 +11858,7 @@
         <v>357</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>845</v>
@@ -10163,7 +11878,7 @@
         <v>357</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
@@ -10192,7 +11907,7 @@
         <v>361</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>909</v>
@@ -10284,7 +11999,7 @@
         <v>611</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>914</v>
@@ -10304,7 +12019,7 @@
         <v>611</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
@@ -10327,7 +12042,7 @@
         <v>611</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>914</v>
@@ -10503,7 +12218,7 @@
         <v>370</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
@@ -10532,7 +12247,7 @@
         <v>320</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>845</v>
@@ -10552,7 +12267,7 @@
         <v>320</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
@@ -10581,7 +12296,7 @@
         <v>755</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>914</v>
@@ -10601,7 +12316,7 @@
         <v>755</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
@@ -10630,7 +12345,7 @@
         <v>379</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>914</v>
@@ -10679,7 +12394,7 @@
         <v>62</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>913</v>
@@ -10708,7 +12423,7 @@
         <v>62</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
@@ -10777,7 +12492,7 @@
         <v>383</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>845</v>
@@ -10797,7 +12512,7 @@
         <v>383</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
@@ -10820,7 +12535,7 @@
         <v>392</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>845</v>
@@ -10849,7 +12564,7 @@
         <v>392</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
@@ -11010,7 +12725,7 @@
         <v>410</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>916</v>
@@ -11032,7 +12747,7 @@
         <v>410</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="O144" s="1" t="s">
         <v>35</v>
@@ -11050,7 +12765,7 @@
         <v>410</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="U144" s="1" t="s">
         <v>407</v>
@@ -11091,7 +12806,7 @@
         <v>594</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
@@ -11124,10 +12839,10 @@
         <v>415</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G146" s="1" t="s">
         <v>1299</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>1300</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>729</v>
@@ -11136,7 +12851,7 @@
         <v>594</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="K146" s="1"/>
       <c r="L146" s="1" t="s">
@@ -11226,7 +12941,7 @@
         <v>436</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>918</v>
@@ -11248,7 +12963,7 @@
         <v>436</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>433</v>
@@ -11277,7 +12992,7 @@
         <v>52</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>916</v>
@@ -11316,7 +13031,7 @@
         <v>159</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>916</v>
@@ -11338,7 +13053,7 @@
         <v>159</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
@@ -11352,25 +13067,25 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F151" s="1" t="s">
+      <c r="G151" s="1" t="s">
         <v>1068</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>1069</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>562</v>
@@ -11391,7 +13106,7 @@
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>433</v>
       </c>
@@ -11408,7 +13123,7 @@
         <v>438</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>918</v>
@@ -11433,17 +13148,23 @@
         <v>439</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>438</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="R152" s="1"/>
-      <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+        <v>1323</v>
+      </c>
+      <c r="R152" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="S152" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="T152" s="5" t="s">
+        <v>1324</v>
+      </c>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -11465,7 +13186,7 @@
         <v>448</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>920</v>
@@ -11477,7 +13198,7 @@
         <v>580</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
@@ -11487,7 +13208,7 @@
         <v>448</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="O153" s="1"/>
       <c r="P153" s="1"/>
@@ -11516,7 +13237,7 @@
         <v>451</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>920</v>
@@ -11528,7 +13249,7 @@
         <v>580</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="1" t="s">
@@ -11538,7 +13259,7 @@
         <v>451</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
@@ -11567,7 +13288,7 @@
         <v>454</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>920</v>
@@ -11579,7 +13300,7 @@
         <v>580</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1" t="s">
@@ -11589,7 +13310,7 @@
         <v>454</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
@@ -11618,7 +13339,7 @@
         <v>654</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>920</v>
@@ -11630,7 +13351,7 @@
         <v>580</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K156" s="1"/>
       <c r="L156" s="1" t="s">
@@ -11640,7 +13361,7 @@
         <v>654</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
@@ -11669,7 +13390,7 @@
         <v>457</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>913</v>
@@ -11714,7 +13435,7 @@
         <v>458</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>920</v>
@@ -11726,7 +13447,7 @@
         <v>580</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1" t="s">
@@ -11736,7 +13457,7 @@
         <v>458</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
@@ -11765,10 +13486,10 @@
         <v>459</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>562</v>
@@ -11777,7 +13498,7 @@
         <v>580</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
@@ -11816,19 +13537,19 @@
         <v>467</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="J160" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
@@ -11861,7 +13582,7 @@
         <v>468</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>909</v>
@@ -11910,7 +13631,7 @@
         <v>469</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>909</v>
@@ -11959,19 +13680,19 @@
         <v>469</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H163" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I163" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="I163" s="1" t="s">
-        <v>1085</v>
-      </c>
       <c r="J163" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="K163" s="1"/>
       <c r="L163" s="1" t="s">
@@ -12010,19 +13731,19 @@
         <v>475</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H164" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I164" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="I164" s="1" t="s">
-        <v>1085</v>
-      </c>
       <c r="J164" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="1" t="s">
@@ -12061,7 +13782,7 @@
         <v>479</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>909</v>
@@ -12070,7 +13791,7 @@
         <v>54</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
@@ -12110,7 +13831,7 @@
         <v>482</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>831</v>
@@ -12119,10 +13840,10 @@
         <v>54</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="K166" s="1"/>
       <c r="L166" s="1" t="s">
@@ -12161,7 +13882,7 @@
         <v>482</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>913</v>
@@ -12170,7 +13891,7 @@
         <v>563</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
@@ -12204,7 +13925,7 @@
         <v>488</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>909</v>
@@ -12213,7 +13934,7 @@
         <v>54</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
@@ -12238,7 +13959,7 @@
         <v>489</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>969</v>
@@ -12247,7 +13968,7 @@
         <v>489</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>913</v>
@@ -12256,7 +13977,7 @@
         <v>563</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
@@ -12284,19 +14005,19 @@
         <v>491</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
@@ -12329,19 +14050,19 @@
         <v>491</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
@@ -12374,19 +14095,19 @@
         <v>494</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I172" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J172" s="1" t="s">
         <v>1104</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>1105</v>
       </c>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
@@ -12410,7 +14131,7 @@
         <v>495</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>476</v>
@@ -12419,7 +14140,7 @@
         <v>495</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>913</v>
@@ -12428,7 +14149,7 @@
         <v>563</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -12456,19 +14177,19 @@
         <v>756</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
@@ -12501,19 +14222,19 @@
         <v>497</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="K175" s="1"/>
       <c r="L175" s="1" t="s">
@@ -12541,7 +14262,7 @@
         <v>497</v>
       </c>
       <c r="T175" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="U175" s="1" t="s">
         <v>476</v>
@@ -12550,7 +14271,7 @@
         <v>497</v>
       </c>
       <c r="W175" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.2">
@@ -12561,7 +14282,7 @@
         <v>499</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>476</v>
@@ -12570,7 +14291,7 @@
         <v>499</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>913</v>
@@ -12579,7 +14300,7 @@
         <v>563</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
@@ -12613,19 +14334,19 @@
         <v>499</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -12658,19 +14379,19 @@
         <v>500</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K178" s="1"/>
       <c r="L178" s="1" t="s">
@@ -12709,19 +14430,19 @@
         <v>499</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1" t="s">
@@ -12740,7 +14461,7 @@
         <v>499</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>476</v>
@@ -12749,7 +14470,7 @@
         <v>499</v>
       </c>
       <c r="T179" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="U179" s="1" t="s">
         <v>969</v>
@@ -12758,7 +14479,7 @@
         <v>499</v>
       </c>
       <c r="W179" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.2">
@@ -12778,7 +14499,7 @@
         <v>610</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>913</v>
@@ -12835,7 +14556,7 @@
         <v>524</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>909</v>
@@ -12878,13 +14599,13 @@
         <v>525</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>879</v>
@@ -12923,7 +14644,7 @@
         <v>526</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>909</v>
@@ -12966,19 +14687,19 @@
         <v>526</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I184" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="J184" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
@@ -13011,19 +14732,19 @@
         <v>529</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
@@ -13056,7 +14777,7 @@
         <v>533</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>909</v>
@@ -13099,7 +14820,7 @@
         <v>536</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>911</v>
@@ -13142,7 +14863,7 @@
         <v>540</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>911</v>
@@ -13185,13 +14906,13 @@
         <v>270</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>912</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>578</v>
@@ -13260,7 +14981,7 @@
         <v>965</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
@@ -13289,7 +15010,7 @@
         <v>278</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>909</v>
@@ -13301,7 +15022,7 @@
         <v>584</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
@@ -13328,7 +15049,7 @@
         <v>278</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>909</v>
@@ -13340,7 +15061,7 @@
         <v>584</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
@@ -13373,7 +15094,7 @@
         <v>278</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>909</v>
@@ -13416,7 +15137,7 @@
         <v>278</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>909</v>
@@ -13428,7 +15149,7 @@
         <v>581</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
@@ -13461,7 +15182,7 @@
         <v>278</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>909</v>
@@ -13473,7 +15194,7 @@
         <v>581</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
@@ -13497,7 +15218,7 @@
         <v>273</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>545</v>
@@ -13535,7 +15256,7 @@
         <v>270</v>
       </c>
       <c r="Q196" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
@@ -13561,7 +15282,7 @@
         <v>443</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>909</v>
@@ -13636,7 +15357,7 @@
         <v>553</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
@@ -13665,7 +15386,7 @@
         <v>557</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>909</v>
@@ -13685,7 +15406,7 @@
         <v>557</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -13708,19 +15429,19 @@
         <v>561</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
@@ -13747,19 +15468,19 @@
         <v>561</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
@@ -13789,10 +15510,10 @@
         <v>571</v>
       </c>
       <c r="G202" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H202" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H202" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>590</v>
@@ -13826,10 +15547,10 @@
         <v>574</v>
       </c>
       <c r="G203" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H203" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H203" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>590</v>
@@ -13863,10 +15584,10 @@
         <v>577</v>
       </c>
       <c r="G204" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H204" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -13895,7 +15616,7 @@
         <v>323</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>909</v>
@@ -13944,7 +15665,7 @@
         <v>620</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>911</v>
@@ -13987,7 +15708,7 @@
         <v>624</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>911</v>
@@ -14036,7 +15757,7 @@
         <v>626</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>921</v>
@@ -14099,7 +15820,7 @@
         <v>631</v>
       </c>
       <c r="N209" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
@@ -14142,7 +15863,7 @@
         <v>936</v>
       </c>
       <c r="N210" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
@@ -14171,7 +15892,7 @@
         <v>637</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>909</v>
@@ -14209,7 +15930,7 @@
         <v>637</v>
       </c>
       <c r="T211" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
@@ -14246,7 +15967,7 @@
         <v>638</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="O212" s="1"/>
       <c r="P212" s="1"/>
@@ -14269,7 +15990,7 @@
         <v>641</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>916</v>
@@ -14281,7 +16002,7 @@
         <v>579</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K213" s="1"/>
       <c r="L213" s="1"/>
@@ -14308,7 +16029,7 @@
         <v>642</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>916</v>
@@ -14320,7 +16041,7 @@
         <v>579</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K214" s="1"/>
       <c r="L214" s="1"/>
@@ -14347,7 +16068,7 @@
         <v>773</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>916</v>
@@ -14359,7 +16080,7 @@
         <v>579</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K215" s="1"/>
       <c r="L215" s="1"/>
@@ -14392,19 +16113,19 @@
         <v>646</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>580</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K216" s="1"/>
       <c r="L216" s="1"/>
@@ -14431,7 +16152,7 @@
         <v>651</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>910</v>
@@ -14451,7 +16172,7 @@
         <v>651</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
@@ -14480,7 +16201,7 @@
         <v>658</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>909</v>
@@ -14523,7 +16244,7 @@
         <v>662</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>909</v>
@@ -14560,19 +16281,19 @@
         <v>505</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I220" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J220" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
@@ -14605,13 +16326,13 @@
         <v>845</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I221" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J221" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
@@ -14644,13 +16365,13 @@
         <v>845</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I222" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J222" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J222" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
@@ -14683,13 +16404,13 @@
         <v>845</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I223" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J223" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J223" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -14722,13 +16443,13 @@
         <v>845</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I224" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J224" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J224" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
@@ -14761,13 +16482,13 @@
         <v>845</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I225" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J225" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J225" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
@@ -14800,13 +16521,13 @@
         <v>845</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I226" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J226" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J226" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K226" s="1"/>
       <c r="L226" s="1"/>
@@ -14833,19 +16554,19 @@
         <v>506</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I227" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J227" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J227" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K227" s="1"/>
       <c r="L227" s="1"/>
@@ -14878,13 +16599,13 @@
         <v>845</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I228" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J228" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J228" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K228" s="1"/>
       <c r="L228" s="1"/>
@@ -14917,13 +16638,13 @@
         <v>845</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I229" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J229" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J229" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -14956,13 +16677,13 @@
         <v>845</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I230" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J230" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J230" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
@@ -14995,13 +16716,13 @@
         <v>845</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I231" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J231" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J231" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
@@ -15034,13 +16755,13 @@
         <v>845</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I232" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J232" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J232" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -15073,13 +16794,13 @@
         <v>845</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I233" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J233" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J233" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
@@ -15112,13 +16833,13 @@
         <v>845</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I234" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J234" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J234" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
@@ -15151,13 +16872,13 @@
         <v>845</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I235" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J235" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J235" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -15190,13 +16911,13 @@
         <v>845</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I236" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J236" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J236" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K236" s="1"/>
       <c r="L236" s="1"/>
@@ -15229,13 +16950,13 @@
         <v>845</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I237" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J237" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J237" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
@@ -15268,19 +16989,19 @@
         <v>720</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I238" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J238" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="J238" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
@@ -15313,7 +17034,7 @@
         <v>509</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>909</v>
@@ -15333,7 +17054,7 @@
         <v>509</v>
       </c>
       <c r="N239" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
@@ -15362,7 +17083,7 @@
         <v>509</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>909</v>
@@ -15382,7 +17103,7 @@
         <v>509</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
@@ -15405,7 +17126,7 @@
         <v>673</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>909</v>
@@ -15450,10 +17171,10 @@
         <v>960</v>
       </c>
       <c r="H242" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I242" s="1" t="s">
         <v>1179</v>
-      </c>
-      <c r="I242" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>959</v>
@@ -15489,13 +17210,13 @@
         <v>845</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>589</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -15512,53 +17233,39 @@
       <c r="W243" s="1"/>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A244" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>678</v>
-      </c>
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
       <c r="D244" s="1" t="s">
-        <v>607</v>
+        <v>35</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>843</v>
+        <v>1318</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>842</v>
+        <v>1319</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H244" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="I244" s="1"/>
-      <c r="J244" s="1" t="s">
-        <v>841</v>
-      </c>
+        <v>1322</v>
+      </c>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="J244" s="1"/>
       <c r="K244" s="1"/>
       <c r="L244" s="1" t="s">
-        <v>607</v>
+        <v>1313</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>677</v>
+        <v>1314</v>
       </c>
       <c r="N244" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="O244" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="P244" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="Q244" s="1" t="s">
-        <v>1183</v>
-      </c>
+        <v>1315</v>
+      </c>
+      <c r="O244" s="1"/>
+      <c r="P244" s="1"/>
+      <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
       <c r="T244" s="1"/>
@@ -15567,38 +17274,36 @@
       <c r="W244" s="1"/>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A245" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>765</v>
-      </c>
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
       <c r="D245" s="1" t="s">
-        <v>625</v>
+        <v>35</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>681</v>
+        <v>1320</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>682</v>
+        <v>1321</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="H245" s="1" t="s">
-        <v>562</v>
-      </c>
+        <v>1322</v>
+      </c>
+      <c r="H245" s="1"/>
       <c r="I245" s="1" t="s">
-        <v>1184</v>
+        <v>578</v>
       </c>
       <c r="J245" s="1"/>
       <c r="K245" s="1"/>
-      <c r="L245" s="1"/>
-      <c r="M245" s="1"/>
-      <c r="N245" s="1"/>
+      <c r="L245" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="M245" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="N245" s="1" t="s">
+        <v>1317</v>
+      </c>
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
@@ -15611,34 +17316,52 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>545</v>
+        <v>676</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="D246" s="1"/>
-      <c r="E246" s="1"/>
-      <c r="F246" s="1"/>
+        <v>678</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>842</v>
+      </c>
       <c r="G246" s="1" t="s">
-        <v>921</v>
+        <v>1181</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="I246" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="J246" s="1"/>
+        <v>729</v>
+      </c>
+      <c r="I246" s="1"/>
+      <c r="J246" s="1" t="s">
+        <v>841</v>
+      </c>
       <c r="K246" s="1"/>
-      <c r="L246" s="1"/>
-      <c r="M246" s="1"/>
-      <c r="N246" s="1"/>
-      <c r="O246" s="1"/>
-      <c r="P246" s="1"/>
-      <c r="Q246" s="1"/>
+      <c r="L246" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M246" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="N246" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="O246" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="P246" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="Q246" s="1" t="s">
+        <v>1182</v>
+      </c>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
       <c r="T246" s="1"/>
@@ -15647,26 +17370,32 @@
       <c r="W246" s="1"/>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A247" s="1"/>
-      <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
+      <c r="A247" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>765</v>
+      </c>
       <c r="D247" s="1" t="s">
-        <v>35</v>
+        <v>625</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1186</v>
+        <v>682</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>578</v>
+        <v>1183</v>
       </c>
       <c r="J247" s="1"/>
       <c r="K247" s="1"/>
@@ -15684,26 +17413,26 @@
       <c r="W247" s="1"/>
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A248" s="1"/>
-      <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-      <c r="D248" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>1187</v>
-      </c>
+      <c r="A248" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
       <c r="G248" s="1" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>580</v>
+        <v>1184</v>
       </c>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -15725,13 +17454,13 @@
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1" t="s">
-        <v>688</v>
+        <v>35</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>909</v>
@@ -15740,7 +17469,7 @@
         <v>54</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -15758,23 +17487,23 @@
       <c r="W249" s="1"/>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A250" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="D250" s="1"/>
-      <c r="E250" s="1"/>
-      <c r="F250" s="1"/>
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>1186</v>
+      </c>
       <c r="G250" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>580</v>
@@ -15799,36 +17528,28 @@
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1" t="s">
-        <v>433</v>
+        <v>688</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>436</v>
+        <v>689</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J251" s="1" t="s">
-        <v>848</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J251" s="1"/>
       <c r="K251" s="1"/>
-      <c r="L251" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="M251" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="N251" s="1" t="s">
-        <v>1190</v>
-      </c>
+      <c r="L251" s="1"/>
+      <c r="M251" s="1"/>
+      <c r="N251" s="1"/>
       <c r="O251" s="1"/>
       <c r="P251" s="1"/>
       <c r="Q251" s="1"/>
@@ -15840,26 +17561,26 @@
       <c r="W251" s="1"/>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A252" s="1"/>
-      <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-      <c r="D252" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>1191</v>
-      </c>
+      <c r="A252" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -15877,38 +17598,40 @@
       <c r="W252" s="1"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A253" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>697</v>
-      </c>
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
       <c r="D253" s="1" t="s">
-        <v>695</v>
+        <v>433</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>696</v>
+        <v>436</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="J253" s="1"/>
+        <v>594</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>848</v>
+      </c>
       <c r="K253" s="1"/>
-      <c r="L253" s="1"/>
-      <c r="M253" s="1"/>
-      <c r="N253" s="1"/>
+      <c r="L253" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="M253" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N253" s="1" t="s">
+        <v>1189</v>
+      </c>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
@@ -15920,26 +17643,26 @@
       <c r="W253" s="1"/>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A254" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="D254" s="1"/>
-      <c r="E254" s="1"/>
-      <c r="F254" s="1"/>
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>1190</v>
+      </c>
       <c r="G254" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>1104</v>
+        <v>594</v>
       </c>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
@@ -15958,22 +17681,22 @@
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>791</v>
+        <v>696</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>792</v>
+        <v>697</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>909</v>
@@ -15982,7 +17705,7 @@
         <v>54</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>586</v>
+        <v>1192</v>
       </c>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
@@ -16000,26 +17723,26 @@
       <c r="W255" s="1"/>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A256" s="1"/>
-      <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-      <c r="D256" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E256" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="F256" s="1" t="s">
-        <v>1195</v>
-      </c>
+      <c r="A256" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D256" s="1"/>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>581</v>
+        <v>1103</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -16037,17 +17760,23 @@
       <c r="W256" s="1"/>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A257" s="1"/>
-      <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
+      <c r="A257" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>792</v>
+      </c>
       <c r="D257" s="1" t="s">
-        <v>259</v>
+        <v>701</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>909</v>
@@ -16056,7 +17785,7 @@
         <v>54</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -16078,22 +17807,22 @@
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1" t="s">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -16115,13 +17844,13 @@
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>316</v>
+        <v>704</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>909</v>
@@ -16148,29 +17877,23 @@
       <c r="W259" s="1"/>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A260" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>801</v>
-      </c>
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
       <c r="D260" s="1" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>388</v>
+        <v>705</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>578</v>
@@ -16195,22 +17918,22 @@
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>706</v>
+        <v>316</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="J261" s="1"/>
       <c r="K261" s="1"/>
@@ -16228,23 +17951,29 @@
       <c r="W261" s="1"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A262" s="1"/>
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
+      <c r="A262" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>801</v>
+      </c>
       <c r="D262" s="1" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>707</v>
+        <v>388</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>578</v>
@@ -16272,19 +18001,19 @@
         <v>35</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>398</v>
+        <v>706</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
@@ -16306,13 +18035,13 @@
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1" t="s">
-        <v>686</v>
+        <v>35</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>913</v>
@@ -16321,7 +18050,7 @@
         <v>563</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -16343,22 +18072,22 @@
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1" t="s">
-        <v>601</v>
+        <v>35</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>709</v>
+        <v>398</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -16380,13 +18109,13 @@
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1" t="s">
-        <v>601</v>
+        <v>686</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>913</v>
@@ -16395,7 +18124,7 @@
         <v>563</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>586</v>
+        <v>928</v>
       </c>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -16413,23 +18142,17 @@
       <c r="W266" s="1"/>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A267" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>712</v>
-      </c>
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
       <c r="D267" s="1" t="s">
-        <v>212</v>
+        <v>601</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>976</v>
+        <v>709</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>913</v>
@@ -16438,19 +18161,13 @@
         <v>563</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>1185</v>
+        <v>586</v>
       </c>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
-      <c r="L267" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M267" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="N267" s="1" t="s">
-        <v>975</v>
-      </c>
+      <c r="L267" s="1"/>
+      <c r="M267" s="1"/>
+      <c r="N267" s="1"/>
       <c r="O267" s="1"/>
       <c r="P267" s="1"/>
       <c r="Q267" s="1"/>
@@ -16462,18 +18179,18 @@
       <c r="W267" s="1"/>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A268" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="D268" s="1"/>
-      <c r="E268" s="1"/>
-      <c r="F268" s="1"/>
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>1204</v>
+      </c>
       <c r="G268" s="1" t="s">
         <v>913</v>
       </c>
@@ -16481,7 +18198,7 @@
         <v>563</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
@@ -16499,32 +18216,44 @@
       <c r="W268" s="1"/>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A269" s="1"/>
-      <c r="B269" s="1"/>
-      <c r="C269" s="1"/>
+      <c r="A269" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>712</v>
+      </c>
       <c r="D269" s="1" t="s">
-        <v>464</v>
+        <v>212</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>469</v>
+        <v>975</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>589</v>
+        <v>1184</v>
       </c>
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
-      <c r="L269" s="1"/>
-      <c r="M269" s="1"/>
-      <c r="N269" s="1"/>
+      <c r="L269" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M269" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="N269" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="O269" s="1"/>
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
@@ -16537,23 +18266,17 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>676</v>
+        <v>640</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>814</v>
+        <v>713</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="F270" s="1" t="s">
-        <v>1208</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
       <c r="G270" s="1" t="s">
         <v>913</v>
       </c>
@@ -16561,11 +18284,9 @@
         <v>563</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J270" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="J270" s="1"/>
       <c r="K270" s="1"/>
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
@@ -16585,19 +18306,19 @@
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1" t="s">
-        <v>607</v>
+        <v>464</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>716</v>
+        <v>469</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1210</v>
+        <v>909</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>589</v>
@@ -16618,28 +18339,36 @@
       <c r="W271" s="1"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A272" s="1"/>
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
+      <c r="A272" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>815</v>
+      </c>
       <c r="D272" s="1" t="s">
         <v>607</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1210</v>
+        <v>913</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="J272" s="1"/>
+      <c r="J272" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K272" s="1"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
@@ -16659,22 +18388,22 @@
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1" t="s">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>913</v>
+        <v>1209</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="J273" s="1"/>
       <c r="K273" s="1"/>
@@ -16696,22 +18425,22 @@
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1" t="s">
-        <v>724</v>
+        <v>607</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>909</v>
+        <v>1209</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="J274" s="1"/>
       <c r="K274" s="1"/>
@@ -16733,26 +18462,24 @@
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1" t="s">
-        <v>693</v>
+        <v>648</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>845</v>
+        <v>913</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>1084</v>
+        <v>563</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J275" s="1" t="s">
-        <v>1215</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="J275" s="1"/>
       <c r="K275" s="1"/>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
@@ -16772,36 +18499,28 @@
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="J276" s="1" t="s">
-        <v>854</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="J276" s="1"/>
       <c r="K276" s="1"/>
-      <c r="L276" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="M276" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="N276" s="1" t="s">
-        <v>865</v>
-      </c>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+      <c r="N276" s="1"/>
       <c r="O276" s="1"/>
       <c r="P276" s="1"/>
       <c r="Q276" s="1"/>
@@ -16817,24 +18536,26 @@
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1" t="s">
-        <v>572</v>
+        <v>693</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>746</v>
+        <v>694</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1148</v>
+        <v>845</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>1149</v>
+        <v>1083</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J277" s="1"/>
+        <v>1169</v>
+      </c>
+      <c r="J277" s="1" t="s">
+        <v>1214</v>
+      </c>
       <c r="K277" s="1"/>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
@@ -16854,30 +18575,36 @@
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>763</v>
+        <v>727</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>932</v>
+        <v>1215</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>916</v>
+        <v>845</v>
       </c>
       <c r="H278" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>583</v>
+        <v>1192</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>933</v>
+        <v>854</v>
       </c>
       <c r="K278" s="1"/>
-      <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-      <c r="N278" s="1"/>
+      <c r="L278" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="M278" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="N278" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="O278" s="1"/>
       <c r="P278" s="1"/>
       <c r="Q278" s="1"/>
@@ -16893,26 +18620,24 @@
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1" t="s">
-        <v>747</v>
+        <v>572</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>916</v>
+        <v>1147</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>54</v>
+        <v>1148</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J279" s="1" t="s">
-        <v>1220</v>
-      </c>
+        <v>1217</v>
+      </c>
+      <c r="J279" s="1"/>
       <c r="K279" s="1"/>
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
@@ -16932,36 +18657,30 @@
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1" t="s">
-        <v>179</v>
+        <v>747</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>851</v>
+        <v>932</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H280" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>832</v>
+        <v>933</v>
       </c>
       <c r="K280" s="1"/>
-      <c r="L280" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M280" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="N280" s="1" t="s">
-        <v>850</v>
-      </c>
+      <c r="L280" s="1"/>
+      <c r="M280" s="1"/>
+      <c r="N280" s="1"/>
       <c r="O280" s="1"/>
       <c r="P280" s="1"/>
       <c r="Q280" s="1"/>
@@ -16977,34 +18696,30 @@
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1" t="s">
-        <v>49</v>
+        <v>747</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>985</v>
+        <v>748</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>987</v>
+        <v>1218</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H281" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J281" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="J281" s="1" t="s">
+        <v>1219</v>
+      </c>
       <c r="K281" s="1"/>
-      <c r="L281" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M281" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="N281" s="1" t="s">
-        <v>986</v>
-      </c>
+      <c r="L281" s="1"/>
+      <c r="M281" s="1"/>
+      <c r="N281" s="1"/>
       <c r="O281" s="1"/>
       <c r="P281" s="1"/>
       <c r="Q281" s="1"/>
@@ -17020,33 +18735,35 @@
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1" t="s">
-        <v>858</v>
+        <v>179</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>270</v>
+        <v>751</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>990</v>
+        <v>851</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J282" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>832</v>
+      </c>
       <c r="K282" s="1"/>
       <c r="L282" s="1" t="s">
-        <v>858</v>
+        <v>179</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>270</v>
+        <v>751</v>
       </c>
       <c r="N282" s="1" t="s">
-        <v>1221</v>
+        <v>850</v>
       </c>
       <c r="O282" s="1"/>
       <c r="P282" s="1"/>
@@ -17059,64 +18776,44 @@
       <c r="W282" s="1"/>
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A283" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B283" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
       <c r="D283" s="1" t="s">
-        <v>291</v>
+        <v>49</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>294</v>
+        <v>984</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>757</v>
+        <v>986</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>1084</v>
+        <v>54</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J283" s="1" t="s">
-        <v>1222</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J283" s="1"/>
       <c r="K283" s="1"/>
       <c r="L283" s="1" t="s">
-        <v>686</v>
+        <v>49</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>294</v>
+        <v>984</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="O283" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="P283" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q283" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="R283" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="S283" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T283" s="1" t="s">
-        <v>908</v>
-      </c>
+        <v>985</v>
+      </c>
+      <c r="O283" s="1"/>
+      <c r="P283" s="1"/>
+      <c r="Q283" s="1"/>
+      <c r="R283" s="1"/>
+      <c r="S283" s="1"/>
+      <c r="T283" s="1"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -17126,28 +18823,34 @@
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1" t="s">
-        <v>269</v>
+        <v>858</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>754</v>
+        <v>270</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1224</v>
+        <v>989</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>578</v>
       </c>
       <c r="J284" s="1"/>
       <c r="K284" s="1"/>
-      <c r="L284" s="1"/>
-      <c r="M284" s="1"/>
-      <c r="N284" s="1"/>
+      <c r="L284" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="M284" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="N284" s="1" t="s">
+        <v>1220</v>
+      </c>
       <c r="O284" s="1"/>
       <c r="P284" s="1"/>
       <c r="Q284" s="1"/>
@@ -17159,44 +18862,64 @@
       <c r="W284" s="1"/>
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A285" s="1"/>
-      <c r="B285" s="1"/>
-      <c r="C285" s="1"/>
+      <c r="A285" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="D285" s="1" t="s">
-        <v>363</v>
+        <v>291</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1225</v>
+        <v>757</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>914</v>
+        <v>845</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>924</v>
+        <v>1083</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J285" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>1221</v>
+      </c>
       <c r="K285" s="1"/>
       <c r="L285" s="1" t="s">
-        <v>363</v>
+        <v>686</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="O285" s="1"/>
-      <c r="P285" s="1"/>
-      <c r="Q285" s="1"/>
-      <c r="R285" s="1"/>
-      <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
+        <v>1222</v>
+      </c>
+      <c r="O285" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="P285" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q285" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="R285" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S285" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T285" s="1" t="s">
+        <v>908</v>
+      </c>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -17206,22 +18929,22 @@
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
       <c r="D286" s="1" t="s">
-        <v>476</v>
+        <v>269</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1084</v>
+        <v>54</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J286" s="1"/>
       <c r="K286" s="1"/>
@@ -17243,28 +18966,34 @@
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1" t="s">
-        <v>442</v>
+        <v>363</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>443</v>
+        <v>331</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="J287" s="1"/>
       <c r="K287" s="1"/>
-      <c r="L287" s="1"/>
-      <c r="M287" s="1"/>
-      <c r="N287" s="1"/>
+      <c r="L287" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M287" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="N287" s="1" t="s">
+        <v>1225</v>
+      </c>
       <c r="O287" s="1"/>
       <c r="P287" s="1"/>
       <c r="Q287" s="1"/>
@@ -17280,34 +19009,28 @@
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>845</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>924</v>
+        <v>1083</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
-      <c r="L288" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="M288" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="N288" s="1" t="s">
-        <v>1230</v>
-      </c>
+      <c r="L288" s="1"/>
+      <c r="M288" s="1"/>
+      <c r="N288" s="1"/>
       <c r="O288" s="1"/>
       <c r="P288" s="1"/>
       <c r="Q288" s="1"/>
@@ -17323,13 +19046,13 @@
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1" t="s">
-        <v>35</v>
+        <v>442</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>761</v>
+        <v>443</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>909</v>
@@ -17338,19 +19061,13 @@
         <v>54</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="J289" s="1"/>
       <c r="K289" s="1"/>
-      <c r="L289" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M289" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="N289" s="1" t="s">
-        <v>1232</v>
-      </c>
+      <c r="L289" s="1"/>
+      <c r="M289" s="1"/>
+      <c r="N289" s="1"/>
       <c r="O289" s="1"/>
       <c r="P289" s="1"/>
       <c r="Q289" s="1"/>
@@ -17366,30 +19083,34 @@
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1234</v>
+        <v>845</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="J290" s="1" t="s">
-        <v>977</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J290" s="1"/>
       <c r="K290" s="1"/>
-      <c r="L290" s="1"/>
-      <c r="M290" s="1"/>
-      <c r="N290" s="1"/>
+      <c r="L290" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="M290" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="N290" s="1" t="s">
+        <v>1229</v>
+      </c>
       <c r="O290" s="1"/>
       <c r="P290" s="1"/>
       <c r="Q290" s="1"/>
@@ -17405,13 +19126,13 @@
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1" t="s">
-        <v>747</v>
+        <v>35</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>909</v>
@@ -17424,9 +19145,15 @@
       </c>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
-      <c r="L291" s="1"/>
-      <c r="M291" s="1"/>
-      <c r="N291" s="1"/>
+      <c r="L291" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M291" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="N291" s="1" t="s">
+        <v>1231</v>
+      </c>
       <c r="O291" s="1"/>
       <c r="P291" s="1"/>
       <c r="Q291" s="1"/>
@@ -17442,25 +19169,25 @@
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1" t="s">
-        <v>747</v>
+        <v>476</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>916</v>
+        <v>1233</v>
       </c>
       <c r="H292" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>579</v>
+        <v>1103</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>1237</v>
+        <v>976</v>
       </c>
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
@@ -17481,22 +19208,22 @@
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
-        <v>98</v>
+        <v>747</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J293" s="1"/>
       <c r="K293" s="1"/>
@@ -17514,38 +19241,34 @@
       <c r="W293" s="1"/>
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A294" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>989</v>
-      </c>
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
       <c r="D294" s="1" t="s">
-        <v>43</v>
+        <v>747</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>988</v>
+        <v>764</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-      <c r="I294" s="1"/>
-      <c r="J294" s="1"/>
+        <v>1235</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="J294" s="1" t="s">
+        <v>1236</v>
+      </c>
       <c r="K294" s="1"/>
-      <c r="L294" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M294" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="N294" s="1" t="s">
-        <v>1240</v>
-      </c>
+      <c r="L294" s="1"/>
+      <c r="M294" s="1"/>
+      <c r="N294" s="1"/>
       <c r="O294" s="1"/>
       <c r="P294" s="1"/>
       <c r="Q294" s="1"/>
@@ -17557,36 +19280,28 @@
       <c r="W294" s="1"/>
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A295" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="B295" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>1241</v>
-      </c>
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
       <c r="D295" s="1" t="s">
-        <v>747</v>
+        <v>98</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>934</v>
+        <v>768</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="J295" s="1" t="s">
-        <v>1243</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="J295" s="1"/>
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
@@ -17602,32 +19317,38 @@
       <c r="W295" s="1"/>
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A296" s="1"/>
-      <c r="B296" s="1"/>
-      <c r="C296" s="1"/>
+      <c r="A296" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>988</v>
+      </c>
       <c r="D296" s="1" t="s">
-        <v>698</v>
+        <v>43</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>770</v>
+        <v>987</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="H296" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I296" s="1" t="s">
-        <v>1104</v>
-      </c>
+        <v>1238</v>
+      </c>
+      <c r="G296" s="1"/>
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
-      <c r="L296" s="1"/>
-      <c r="M296" s="1"/>
-      <c r="N296" s="1"/>
+      <c r="L296" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M296" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="N296" s="1" t="s">
+        <v>1239</v>
+      </c>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
       <c r="Q296" s="1"/>
@@ -17639,28 +19360,36 @@
       <c r="W296" s="1"/>
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A297" s="1"/>
-      <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
+      <c r="A297" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>1240</v>
+      </c>
       <c r="D297" s="1" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>772</v>
+        <v>934</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H297" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J297" s="1"/>
+        <v>586</v>
+      </c>
+      <c r="J297" s="1" t="s">
+        <v>1242</v>
+      </c>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
@@ -17680,21 +19409,23 @@
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1" t="s">
-        <v>212</v>
+        <v>698</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>774</v>
+        <v>1243</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="I298" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>1103</v>
+      </c>
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
@@ -17711,23 +19442,17 @@
       <c r="W298" s="1"/>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A299" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>776</v>
-      </c>
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
       <c r="D299" s="1" t="s">
-        <v>300</v>
+        <v>771</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>335</v>
+        <v>772</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>909</v>
@@ -17738,9 +19463,7 @@
       <c r="I299" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="J299" s="1" t="s">
-        <v>338</v>
-      </c>
+      <c r="J299" s="1"/>
       <c r="K299" s="1"/>
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
@@ -17756,44 +19479,30 @@
       <c r="W299" s="1"/>
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A300" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>391</v>
-      </c>
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
       <c r="D300" s="1" t="s">
-        <v>390</v>
+        <v>212</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>67</v>
+        <v>774</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1247</v>
+        <v>774</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>845</v>
+        <v>911</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>924</v>
-      </c>
-      <c r="I300" s="1" t="s">
-        <v>578</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="I300" s="1"/>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
-      <c r="L300" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="M300" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N300" s="1" t="s">
-        <v>943</v>
-      </c>
+      <c r="L300" s="1"/>
+      <c r="M300" s="1"/>
+      <c r="N300" s="1"/>
       <c r="O300" s="1"/>
       <c r="P300" s="1"/>
       <c r="Q300" s="1"/>
@@ -17806,34 +19515,34 @@
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>786</v>
+        <v>335</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>767</v>
+        <v>335</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>1249</v>
+        <v>338</v>
       </c>
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
@@ -17851,42 +19560,42 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>788</v>
+        <v>65</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>789</v>
+        <v>391</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>790</v>
+        <v>67</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
       <c r="L302" s="1" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="M302" s="1" t="s">
-        <v>790</v>
+        <v>67</v>
       </c>
       <c r="N302" s="1" t="s">
-        <v>1251</v>
+        <v>943</v>
       </c>
       <c r="O302" s="1"/>
       <c r="P302" s="1"/>
@@ -17899,28 +19608,36 @@
       <c r="W302" s="1"/>
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A303" s="1"/>
-      <c r="B303" s="1"/>
-      <c r="C303" s="1"/>
+      <c r="A303" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>787</v>
+      </c>
       <c r="D303" s="1" t="s">
-        <v>504</v>
+        <v>49</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>819</v>
+        <v>767</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>819</v>
+        <v>1247</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>845</v>
+        <v>916</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>1084</v>
+        <v>54</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="J303" s="1"/>
+        <v>583</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>1248</v>
+      </c>
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
@@ -17936,34 +19653,44 @@
       <c r="W303" s="1"/>
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A304" s="1"/>
-      <c r="B304" s="1"/>
-      <c r="C304" s="1"/>
+      <c r="A304" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>789</v>
+      </c>
       <c r="D304" s="1" t="s">
-        <v>607</v>
+        <v>57</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>899</v>
+        <v>790</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>900</v>
+        <v>1249</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J304" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J304" s="1"/>
       <c r="K304" s="1"/>
-      <c r="L304" s="1"/>
-      <c r="M304" s="1"/>
-      <c r="N304" s="1"/>
+      <c r="L304" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M304" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="N304" s="1" t="s">
+        <v>1250</v>
+      </c>
       <c r="O304" s="1"/>
       <c r="P304" s="1"/>
       <c r="Q304" s="1"/>
@@ -17979,36 +19706,28 @@
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1298</v>
+        <v>819</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>913</v>
+        <v>845</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>563</v>
+        <v>1083</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J305" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>1169</v>
+      </c>
+      <c r="J305" s="1"/>
       <c r="K305" s="1"/>
-      <c r="L305" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="M305" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="N305" s="1" t="s">
-        <v>1252</v>
-      </c>
+      <c r="L305" s="1"/>
+      <c r="M305" s="1"/>
+      <c r="N305" s="1"/>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
@@ -18024,26 +19743,36 @@
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1" t="s">
-        <v>821</v>
+        <v>607</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>822</v>
+        <v>899</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1253</v>
+        <v>1309</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1148</v>
+        <v>913</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I306" s="1"/>
-      <c r="J306" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I306" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="J306" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K306" s="1"/>
-      <c r="L306" s="1"/>
-      <c r="M306" s="1"/>
-      <c r="N306" s="1"/>
+      <c r="L306" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M306" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="N306" s="1" t="s">
+        <v>900</v>
+      </c>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
@@ -18059,26 +19788,36 @@
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1" t="s">
-        <v>821</v>
+        <v>607</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1254</v>
+        <v>1297</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1148</v>
+        <v>913</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I307" s="1"/>
-      <c r="J307" s="1"/>
+        <v>563</v>
+      </c>
+      <c r="I307" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="J307" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K307" s="1"/>
-      <c r="L307" s="1"/>
-      <c r="M307" s="1"/>
-      <c r="N307" s="1"/>
+      <c r="L307" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M307" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="N307" s="1" t="s">
+        <v>1251</v>
+      </c>
       <c r="O307" s="1"/>
       <c r="P307" s="1"/>
       <c r="Q307" s="1"/>
@@ -18094,19 +19833,19 @@
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1" t="s">
-        <v>1255</v>
+        <v>821</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="G308" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H308" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H308" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -18129,26 +19868,22 @@
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1" t="s">
-        <v>517</v>
+        <v>821</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>845</v>
+        <v>1147</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="I309" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="J309" s="1" t="s">
-        <v>1258</v>
-      </c>
+        <v>1148</v>
+      </c>
+      <c r="I309" s="1"/>
+      <c r="J309" s="1"/>
       <c r="K309" s="1"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
@@ -18163,33 +19898,37 @@
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
-      <c r="D310" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E310" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F310" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G310" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="H310" s="1" t="s">
-        <v>563</v>
-      </c>
+      <c r="D310" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E310" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G310" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="H310" s="1"/>
       <c r="I310" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
-      <c r="L310" s="1"/>
-      <c r="M310" s="1"/>
-      <c r="N310" s="1"/>
+      <c r="L310" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="M310" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="N310" s="5" t="s">
+        <v>1312</v>
+      </c>
       <c r="O310" s="1"/>
       <c r="P310" s="1"/>
       <c r="Q310" s="1"/>
@@ -18205,34 +19944,26 @@
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
       <c r="D311" s="1" t="s">
-        <v>106</v>
+        <v>1254</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>114</v>
+        <v>824</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>913</v>
+        <v>1147</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="I311" s="1" t="s">
-        <v>588</v>
-      </c>
+        <v>1148</v>
+      </c>
+      <c r="I311" s="1"/>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
-      <c r="L311" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M311" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N311" s="1" t="s">
-        <v>1262</v>
-      </c>
+      <c r="L311" s="1"/>
+      <c r="M311" s="1"/>
+      <c r="N311" s="1"/>
       <c r="O311" s="1"/>
       <c r="P311" s="1"/>
       <c r="Q311" s="1"/>
@@ -18248,25 +19979,25 @@
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1" t="s">
-        <v>98</v>
+        <v>517</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>917</v>
+        <v>845</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>54</v>
+        <v>1083</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>579</v>
+        <v>879</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
@@ -18287,26 +20018,24 @@
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1" t="s">
-        <v>179</v>
+        <v>686</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>180</v>
+        <v>1258</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>54</v>
+        <v>563</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J313" s="1" t="s">
-        <v>1266</v>
-      </c>
+        <v>928</v>
+      </c>
+      <c r="J313" s="1"/>
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
@@ -18326,33 +20055,33 @@
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1" t="s">
-        <v>833</v>
+        <v>106</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>834</v>
+        <v>114</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
       <c r="L314" s="1" t="s">
-        <v>1268</v>
+        <v>106</v>
       </c>
       <c r="M314" s="1" t="s">
-        <v>834</v>
+        <v>114</v>
       </c>
       <c r="N314" s="1" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="O314" s="1"/>
       <c r="P314" s="1"/>
@@ -18369,24 +20098,26 @@
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1" t="s">
-        <v>836</v>
+        <v>98</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J315" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>1263</v>
+      </c>
       <c r="K315" s="1"/>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
@@ -18406,25 +20137,25 @@
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1" t="s">
-        <v>421</v>
+        <v>179</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>844</v>
+        <v>1264</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>845</v>
+        <v>916</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>846</v>
+        <v>1265</v>
       </c>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
@@ -18441,38 +20172,38 @@
       <c r="W316" s="1"/>
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A317" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>827</v>
-      </c>
+      <c r="A317" s="1"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
       <c r="D317" s="1" t="s">
-        <v>433</v>
+        <v>833</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>848</v>
+        <v>1266</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>729</v>
+        <v>562</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="J317" s="1"/>
       <c r="K317" s="1"/>
-      <c r="L317" s="1"/>
-      <c r="M317" s="1"/>
-      <c r="N317" s="1"/>
+      <c r="L317" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M317" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="N317" s="1" t="s">
+        <v>1268</v>
+      </c>
       <c r="O317" s="1"/>
       <c r="P317" s="1"/>
       <c r="Q317" s="1"/>
@@ -18484,32 +20215,26 @@
       <c r="W317" s="1"/>
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A318" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>852</v>
-      </c>
+      <c r="A318" s="1"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
       <c r="D318" s="1" t="s">
-        <v>407</v>
+        <v>836</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>410</v>
+        <v>837</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>411</v>
+        <v>1269</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
@@ -18531,24 +20256,26 @@
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1" t="s">
-        <v>143</v>
+        <v>421</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>566</v>
+        <v>424</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>794</v>
+        <v>844</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="H319" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J319" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J319" s="1" t="s">
+        <v>846</v>
+      </c>
       <c r="K319" s="1"/>
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
@@ -18565,35 +20292,33 @@
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>49</v>
+        <v>433</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>856</v>
+        <v>827</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>49</v>
+        <v>433</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1271</v>
+        <v>848</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J320" s="1" t="s">
-        <v>1272</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="J320" s="1"/>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
@@ -18609,30 +20334,34 @@
       <c r="W320" s="1"/>
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A321" s="1"/>
-      <c r="B321" s="1"/>
-      <c r="C321" s="1"/>
+      <c r="A321" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="D321" s="1" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>866</v>
+        <v>410</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>867</v>
+        <v>411</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H321" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J321" s="1" t="s">
-        <v>869</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J321" s="1"/>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
@@ -18652,26 +20381,24 @@
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
       <c r="D322" s="1" t="s">
-        <v>381</v>
+        <v>143</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>69</v>
+        <v>566</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>926</v>
+        <v>794</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="H322" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J322" s="1" t="s">
-        <v>907</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="J322" s="1"/>
       <c r="K322" s="1"/>
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
@@ -18687,28 +20414,36 @@
       <c r="W322" s="1"/>
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A323" s="1"/>
-      <c r="B323" s="1"/>
-      <c r="C323" s="1"/>
+      <c r="A323" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>856</v>
+      </c>
       <c r="D323" s="1" t="s">
-        <v>381</v>
+        <v>49</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>69</v>
+        <v>857</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J323" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J323" s="1" t="s">
+        <v>1271</v>
+      </c>
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
@@ -18728,24 +20463,26 @@
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
       <c r="D324" s="1" t="s">
-        <v>625</v>
+        <v>143</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="J324" s="1"/>
+        <v>868</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>869</v>
+      </c>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
@@ -18765,25 +20502,25 @@
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1" t="s">
-        <v>517</v>
+        <v>381</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>877</v>
+        <v>69</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>878</v>
+        <v>926</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>563</v>
+        <v>54</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>879</v>
+        <v>584</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -18800,46 +20537,32 @@
       <c r="W325" s="1"/>
     </row>
     <row r="326" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A326" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>952</v>
-      </c>
+      <c r="A326" s="1"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
       <c r="D326" s="1" t="s">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>881</v>
+        <v>69</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1275</v>
+        <v>909</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>729</v>
+        <v>54</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J326" s="1" t="s">
-        <v>882</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J326" s="1"/>
       <c r="K326" s="1"/>
-      <c r="L326" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M326" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="N326" s="1" t="s">
-        <v>1276</v>
-      </c>
+      <c r="L326" s="1"/>
+      <c r="M326" s="1"/>
+      <c r="N326" s="1"/>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
       <c r="Q326" s="1"/>
@@ -18855,34 +20578,28 @@
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1" t="s">
-        <v>363</v>
+        <v>625</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>925</v>
+        <v>874</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1277</v>
+        <v>875</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>845</v>
+        <v>921</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>924</v>
+        <v>562</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>578</v>
+        <v>876</v>
       </c>
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
-      <c r="L327" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M327" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="N327" s="1" t="s">
-        <v>1278</v>
-      </c>
+      <c r="L327" s="1"/>
+      <c r="M327" s="1"/>
+      <c r="N327" s="1"/>
       <c r="O327" s="1"/>
       <c r="P327" s="1"/>
       <c r="Q327" s="1"/>
@@ -18894,35 +20611,34 @@
       <c r="W327" s="1"/>
     </row>
     <row r="328" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A328" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>1280</v>
-      </c>
+      <c r="A328" s="1"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
       <c r="D328" s="1" t="s">
-        <v>381</v>
+        <v>517</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>62</v>
+        <v>877</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1279</v>
+        <v>878</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="H328" s="1" t="s">
         <v>563</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J328" s="1"/>
+        <v>879</v>
+      </c>
+      <c r="J328" s="1" t="s">
+        <v>880</v>
+      </c>
       <c r="K328" s="1"/>
+      <c r="L328" s="1"/>
+      <c r="M328" s="1"/>
+      <c r="N328" s="1"/>
       <c r="O328" s="1"/>
       <c r="P328" s="1"/>
       <c r="Q328" s="1"/>
@@ -18934,49 +20650,49 @@
       <c r="W328" s="1"/>
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
-      <c r="C329" s="1"/>
+      <c r="A329" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>952</v>
+      </c>
       <c r="D329" s="1" t="s">
-        <v>35</v>
+        <v>464</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>410</v>
+        <v>881</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>929</v>
+        <v>1273</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>916</v>
+        <v>1274</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>54</v>
+        <v>729</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>852</v>
+        <v>882</v>
       </c>
       <c r="K329" s="1"/>
       <c r="L329" s="1" t="s">
-        <v>35</v>
+        <v>464</v>
       </c>
       <c r="M329" s="1" t="s">
-        <v>410</v>
+        <v>881</v>
       </c>
       <c r="N329" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="O329" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P329" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q329" s="1" t="s">
-        <v>596</v>
-      </c>
+        <v>1275</v>
+      </c>
+      <c r="O329" s="1"/>
+      <c r="P329" s="1"/>
+      <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
       <c r="T329" s="1"/>
@@ -18985,38 +20701,38 @@
       <c r="W329" s="1"/>
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A330" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>883</v>
-      </c>
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
       <c r="D330" s="1" t="s">
-        <v>464</v>
+        <v>363</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>882</v>
+        <v>1276</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1275</v>
+        <v>845</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>729</v>
+        <v>924</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
-      <c r="L330" s="1"/>
-      <c r="M330" s="1"/>
-      <c r="N330" s="1"/>
+      <c r="L330" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M330" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="N330" s="1" t="s">
+        <v>1277</v>
+      </c>
       <c r="O330" s="1"/>
       <c r="P330" s="1"/>
       <c r="Q330" s="1"/>
@@ -19028,17 +20744,23 @@
       <c r="W330" s="1"/>
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A331" s="1"/>
-      <c r="B331" s="1"/>
-      <c r="C331" s="1"/>
+      <c r="A331" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>1279</v>
+      </c>
       <c r="D331" s="1" t="s">
-        <v>686</v>
+        <v>381</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>708</v>
+        <v>62</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>927</v>
+        <v>1278</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>913</v>
@@ -19047,13 +20769,10 @@
         <v>563</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>928</v>
+        <v>578</v>
       </c>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
-      <c r="L331" s="1"/>
-      <c r="M331" s="1"/>
-      <c r="N331" s="1"/>
       <c r="O331" s="1"/>
       <c r="P331" s="1"/>
       <c r="Q331" s="1"/>
@@ -19065,51 +20784,83 @@
       <c r="W331" s="1"/>
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
       <c r="D332" s="1" t="s">
-        <v>476</v>
+        <v>35</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>853</v>
+        <v>929</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1286</v>
+        <v>916</v>
       </c>
       <c r="H332" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>1085</v>
+        <v>584</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>1095</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="K332" s="1"/>
+      <c r="L332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M332" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N332" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="O332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P332" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q332" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="R332" s="1"/>
+      <c r="S332" s="1"/>
+      <c r="T332" s="1"/>
+      <c r="U332" s="1"/>
+      <c r="V332" s="1"/>
+      <c r="W332" s="1"/>
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A333" s="1"/>
-      <c r="B333" s="1"/>
-      <c r="C333" s="1"/>
+      <c r="A333" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>883</v>
+      </c>
       <c r="D333" s="1" t="s">
-        <v>836</v>
+        <v>464</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>922</v>
+        <v>882</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>912</v>
+        <v>1274</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>1132</v>
+        <v>729</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
@@ -19131,22 +20882,22 @@
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
       <c r="D334" s="1" t="s">
-        <v>885</v>
+        <v>686</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>887</v>
+        <v>708</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>888</v>
+        <v>927</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>578</v>
+        <v>928</v>
       </c>
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
@@ -19164,63 +20915,51 @@
       <c r="W334" s="1"/>
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1" t="s">
-        <v>724</v>
+        <v>476</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>889</v>
+        <v>482</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>890</v>
+        <v>853</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>909</v>
+        <v>1285</v>
       </c>
       <c r="H335" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="J335" s="1"/>
-      <c r="K335" s="1"/>
-      <c r="L335" s="1"/>
-      <c r="M335" s="1"/>
-      <c r="N335" s="1"/>
-      <c r="O335" s="1"/>
-      <c r="P335" s="1"/>
-      <c r="Q335" s="1"/>
-      <c r="R335" s="1"/>
-      <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
-      <c r="U335" s="1"/>
-      <c r="V335" s="1"/>
-      <c r="W335" s="1"/>
+        <v>1084</v>
+      </c>
+      <c r="J335" s="1" t="s">
+        <v>1094</v>
+      </c>
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1" t="s">
-        <v>892</v>
+        <v>836</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>54</v>
+        <v>1131</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
@@ -19242,22 +20981,22 @@
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -19279,32 +21018,28 @@
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1" t="s">
-        <v>569</v>
+        <v>724</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>569</v>
+        <v>889</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>569</v>
+        <v>890</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1148</v>
+        <v>909</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I338" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>594</v>
+      </c>
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
-      <c r="L338" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="M338" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="N338" s="1" t="s">
-        <v>896</v>
-      </c>
+      <c r="L338" s="1"/>
+      <c r="M338" s="1"/>
+      <c r="N338" s="1"/>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
       <c r="Q338" s="1"/>
@@ -19320,32 +21055,28 @@
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>1148</v>
+        <v>909</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I339" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>589</v>
+      </c>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
-      <c r="L339" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="M339" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="N339" s="1" t="s">
-        <v>897</v>
-      </c>
+      <c r="L339" s="1"/>
+      <c r="M339" s="1"/>
+      <c r="N339" s="1"/>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
       <c r="Q339" s="1"/>
@@ -19361,32 +21092,28 @@
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1" t="s">
-        <v>572</v>
+        <v>892</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>572</v>
+        <v>893</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>572</v>
+        <v>894</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>1148</v>
+        <v>909</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I340" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>589</v>
+      </c>
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
-      <c r="L340" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="M340" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="N340" s="1" t="s">
-        <v>898</v>
-      </c>
+      <c r="L340" s="1"/>
+      <c r="M340" s="1"/>
+      <c r="N340" s="1"/>
       <c r="O340" s="1"/>
       <c r="P340" s="1"/>
       <c r="Q340" s="1"/>
@@ -19402,31 +21129,31 @@
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1281</v>
+        <v>1147</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
       <c r="L341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="M341" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="N341" s="1" t="s">
-        <v>577</v>
+        <v>896</v>
       </c>
       <c r="O341" s="1"/>
       <c r="P341" s="1"/>
@@ -19438,9 +21165,307 @@
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
     </row>
+    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H342" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I342" s="1"/>
+      <c r="J342" s="1"/>
+      <c r="K342" s="1"/>
+      <c r="L342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="M342" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="N342" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="O342" s="1"/>
+      <c r="P342" s="1"/>
+      <c r="Q342" s="1"/>
+      <c r="R342" s="1"/>
+      <c r="S342" s="1"/>
+      <c r="T342" s="1"/>
+      <c r="U342" s="1"/>
+      <c r="V342" s="1"/>
+      <c r="W342" s="1"/>
+    </row>
+    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G343" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H343" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I343" s="1"/>
+      <c r="J343" s="1"/>
+      <c r="K343" s="1"/>
+      <c r="L343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="M343" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="N343" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="O343" s="1"/>
+      <c r="P343" s="1"/>
+      <c r="Q343" s="1"/>
+      <c r="R343" s="1"/>
+      <c r="S343" s="1"/>
+      <c r="T343" s="1"/>
+      <c r="U343" s="1"/>
+      <c r="V343" s="1"/>
+      <c r="W343" s="1"/>
+    </row>
+    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G344" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H344" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I344" s="1"/>
+      <c r="J344" s="1"/>
+      <c r="K344" s="1"/>
+      <c r="L344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="M344" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="N344" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="O344" s="1"/>
+      <c r="P344" s="1"/>
+      <c r="Q344" s="1"/>
+      <c r="R344" s="1"/>
+      <c r="S344" s="1"/>
+      <c r="T344" s="1"/>
+      <c r="U344" s="1"/>
+      <c r="V344" s="1"/>
+      <c r="W344" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="F310">
+    <cfRule type="duplicateValues" dxfId="160" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="215"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N310">
+    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0415\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0420\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFAA402-CB2C-4C98-9B7C-068E01F45A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4E1FCF-FD34-429C-AC7F-A1C708467542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3346" uniqueCount="1330">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4035,6 +4035,26 @@
   </si>
   <si>
     <t>SC9642TS-EC-Q-AH-43LR-9642</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-90AK-1134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-90AK-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-90AK-44L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-90AK-43F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC1134UA-CI-90AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8003,9 +8023,15 @@
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
+      <c r="L40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>1329</v>
+      </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -8048,9 +8074,15 @@
         <v>124</v>
       </c>
       <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
+      <c r="L41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>1325</v>
+      </c>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
@@ -8093,6 +8125,15 @@
         <v>124</v>
       </c>
       <c r="K42" s="1"/>
+      <c r="L42" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>1326</v>
+      </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
@@ -8180,9 +8221,15 @@
         <v>124</v>
       </c>
       <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
+      <c r="L44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>1327</v>
+      </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
@@ -8225,9 +8272,15 @@
         <v>124</v>
       </c>
       <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
+      <c r="L45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>1328</v>
+      </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
@@ -21292,179 +21345,171 @@
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="160" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="191"/>
     <cfRule type="duplicateValues" dxfId="133" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="54" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
     <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0420\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4E1FCF-FD34-429C-AC7F-A1C708467542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF2E121-E76D-4CB0-9FD1-506B8EA8A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3346" uniqueCount="1330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="1332">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4055,6 +4055,13 @@
   <si>
     <t>NM.SC1134UA-CI-90AK</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC60220SS-DC-90CB-60220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NF.SC60220SS-DC-60220</t>
   </si>
 </sst>
 </file>
@@ -16607,7 +16614,7 @@
         <v>506</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1171</v>
+        <v>1330</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>845</v>
@@ -16619,12 +16626,18 @@
         <v>1169</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>1170</v>
+        <v>1331</v>
       </c>
       <c r="K227" s="1"/>
-      <c r="L227" s="1"/>
-      <c r="M227" s="1"/>
-      <c r="N227" s="1"/>
+      <c r="L227" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="M227" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="N227" s="1" t="s">
+        <v>1171</v>
+      </c>
       <c r="O227" s="1"/>
       <c r="P227" s="1"/>
       <c r="Q227" s="1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0424\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D03E639-0250-4398-AA75-6C2FD25CC2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81A40CD-596D-4A85-8400-10A02C9760C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="1333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3357" uniqueCount="1336">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4065,6 +4065,17 @@
   </si>
   <si>
     <t>STC9D03F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VE8600EC-Q-DB-9XCR-8600</t>
+  </si>
+  <si>
+    <t>长电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSSOP20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6049,7 +6060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}">
-  <dimension ref="A1:W344"/>
+  <dimension ref="A1:W345"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -15025,27 +15036,31 @@
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1" t="s">
-        <v>963</v>
+        <v>1063</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>964</v>
+        <v>1064</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="G190" s="1"/>
+        <v>1333</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>1334</v>
+      </c>
       <c r="H190" s="1"/>
-      <c r="I190" s="1"/>
+      <c r="I190" s="1" t="s">
+        <v>1335</v>
+      </c>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
       <c r="L190" s="1" t="s">
-        <v>963</v>
+        <v>1063</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>964</v>
+        <v>1064</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>1131</v>
+        <v>1066</v>
       </c>
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
@@ -15058,40 +15073,32 @@
       <c r="W190" s="1"/>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A191" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
       <c r="D191" s="1" t="s">
-        <v>544</v>
+        <v>963</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>278</v>
+        <v>964</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="H191" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J191" s="1" t="s">
-        <v>1133</v>
-      </c>
+        <v>965</v>
+      </c>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
       <c r="K191" s="1"/>
-      <c r="L191" s="1"/>
-      <c r="M191" s="1"/>
-      <c r="N191" s="1"/>
+      <c r="L191" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="M191" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="N191" s="1" t="s">
+        <v>1131</v>
+      </c>
       <c r="O191" s="1"/>
       <c r="P191" s="1"/>
       <c r="Q191" s="1"/>
@@ -15103,9 +15110,15 @@
       <c r="W191" s="1"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
+      <c r="A192" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>546</v>
+      </c>
       <c r="D192" s="1" t="s">
         <v>544</v>
       </c>
@@ -15113,7 +15126,7 @@
         <v>278</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>908</v>
@@ -15142,15 +15155,9 @@
       <c r="W192" s="1"/>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A193" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>548</v>
-      </c>
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
       <c r="D193" s="1" t="s">
         <v>544</v>
       </c>
@@ -15158,7 +15165,7 @@
         <v>278</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>908</v>
@@ -15167,9 +15174,11 @@
         <v>54</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J193" s="1"/>
+        <v>583</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>1133</v>
+      </c>
       <c r="K193" s="1"/>
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
@@ -15186,13 +15195,13 @@
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>269</v>
+        <v>544</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>632</v>
+        <v>548</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>544</v>
@@ -15201,7 +15210,7 @@
         <v>278</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>908</v>
@@ -15212,9 +15221,7 @@
       <c r="I194" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="J194" s="1" t="s">
-        <v>1133</v>
-      </c>
+      <c r="J194" s="1"/>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
@@ -15231,13 +15238,13 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>544</v>
+        <v>269</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>547</v>
+        <v>632</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>544</v>
@@ -15246,7 +15253,7 @@
         <v>278</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>908</v>
@@ -15279,19 +15286,19 @@
         <v>544</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>1137</v>
+        <v>547</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>544</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>872</v>
+        <v>1136</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>908</v>
@@ -15300,28 +15307,18 @@
         <v>54</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J196" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>1133</v>
+      </c>
       <c r="K196" s="1"/>
-      <c r="L196" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M196" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="N196" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="O196" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="P196" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q196" s="1" t="s">
-        <v>1138</v>
-      </c>
+      <c r="L196" s="1"/>
+      <c r="M196" s="1"/>
+      <c r="N196" s="1"/>
+      <c r="O196" s="1"/>
+      <c r="P196" s="1"/>
+      <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
       <c r="T196" s="1"/>
@@ -15331,22 +15328,22 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>550</v>
+        <v>273</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>551</v>
+        <v>1137</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1139</v>
+        <v>872</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>908</v>
@@ -15355,27 +15352,27 @@
         <v>54</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="J197" s="1"/>
       <c r="K197" s="1"/>
       <c r="L197" s="1" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="N197" s="1" t="s">
-        <v>444</v>
+        <v>549</v>
       </c>
       <c r="O197" s="1" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
       <c r="P197" s="1" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="Q197" s="1" t="s">
-        <v>744</v>
+        <v>1138</v>
       </c>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
@@ -15389,25 +15386,25 @@
         <v>442</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>817</v>
+        <v>551</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>442</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>552</v>
+        <v>443</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>553</v>
+        <v>1139</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>593</v>
@@ -15418,14 +15415,20 @@
         <v>442</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>552</v>
+        <v>443</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="O198" s="1"/>
-      <c r="P198" s="1"/>
-      <c r="Q198" s="1"/>
+        <v>444</v>
+      </c>
+      <c r="O198" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="P198" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q198" s="1" t="s">
+        <v>744</v>
+      </c>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
       <c r="T198" s="1"/>
@@ -15441,22 +15444,22 @@
         <v>554</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>555</v>
+        <v>817</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>442</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>1141</v>
+        <v>553</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>593</v>
@@ -15467,10 +15470,10 @@
         <v>442</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -15483,34 +15486,44 @@
       <c r="W199" s="1"/>
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A200" s="1"/>
-      <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
+      <c r="A200" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>555</v>
+      </c>
       <c r="D200" s="1" t="s">
-        <v>558</v>
+        <v>442</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1082</v>
+        <v>54</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J200" s="1" t="s">
-        <v>1144</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="J200" s="1"/>
       <c r="K200" s="1"/>
-      <c r="L200" s="1"/>
-      <c r="M200" s="1"/>
-      <c r="N200" s="1"/>
+      <c r="L200" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="N200" s="1" t="s">
+        <v>1142</v>
+      </c>
       <c r="O200" s="1"/>
       <c r="P200" s="1"/>
       <c r="Q200" s="1"/>
@@ -15532,7 +15545,7 @@
         <v>560</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>844</v>
@@ -15565,24 +15578,26 @@
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>570</v>
+        <v>1145</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>1146</v>
+        <v>844</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1147</v>
+        <v>1082</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="J202" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>1144</v>
+      </c>
       <c r="K202" s="1"/>
       <c r="L202" s="1"/>
       <c r="M202" s="1"/>
@@ -15602,13 +15617,13 @@
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>1146</v>
@@ -15639,13 +15654,13 @@
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>1146</v>
@@ -15653,7 +15668,9 @@
       <c r="H204" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="I204" s="1"/>
+      <c r="I204" s="1" t="s">
+        <v>589</v>
+      </c>
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
@@ -15674,34 +15691,26 @@
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1" t="s">
-        <v>300</v>
+        <v>574</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>323</v>
+        <v>575</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>1148</v>
+        <v>576</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>908</v>
+        <v>1146</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>594</v>
-      </c>
+        <v>1147</v>
+      </c>
+      <c r="I205" s="1"/>
       <c r="J205" s="1"/>
       <c r="K205" s="1"/>
-      <c r="L205" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="M205" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="N205" s="1" t="s">
-        <v>599</v>
-      </c>
+      <c r="L205" s="1"/>
+      <c r="M205" s="1"/>
+      <c r="N205" s="1"/>
       <c r="O205" s="1"/>
       <c r="P205" s="1"/>
       <c r="Q205" s="1"/>
@@ -15713,38 +15722,38 @@
       <c r="W205" s="1"/>
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A206" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>618</v>
-      </c>
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
       <c r="D206" s="1" t="s">
-        <v>529</v>
+        <v>300</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>619</v>
+        <v>323</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="J206" s="1"/>
       <c r="K206" s="1"/>
-      <c r="L206" s="1"/>
-      <c r="M206" s="1"/>
-      <c r="N206" s="1"/>
+      <c r="L206" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="M206" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="N206" s="1" t="s">
+        <v>599</v>
+      </c>
       <c r="O206" s="1"/>
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
@@ -15757,22 +15766,22 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>620</v>
+        <v>529</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>620</v>
+        <v>529</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>910</v>
@@ -15785,15 +15794,9 @@
       </c>
       <c r="J207" s="1"/>
       <c r="K207" s="1"/>
-      <c r="L207" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="M207" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="N207" s="1" t="s">
-        <v>727</v>
-      </c>
+      <c r="L207" s="1"/>
+      <c r="M207" s="1"/>
+      <c r="N207" s="1"/>
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
       <c r="Q207" s="1"/>
@@ -15806,25 +15809,25 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>561</v>
@@ -15834,9 +15837,15 @@
       </c>
       <c r="J208" s="1"/>
       <c r="K208" s="1"/>
-      <c r="L208" s="1"/>
-      <c r="M208" s="1"/>
-      <c r="N208" s="1"/>
+      <c r="L208" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="M208" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="N208" s="1" t="s">
+        <v>727</v>
+      </c>
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
@@ -15849,43 +15858,37 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>627</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>860</v>
+        <v>1151</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>561</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="J209" s="1"/>
       <c r="K209" s="1"/>
-      <c r="L209" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="M209" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="N209" s="1" t="s">
-        <v>1152</v>
-      </c>
+      <c r="L209" s="1"/>
+      <c r="M209" s="1"/>
+      <c r="N209" s="1"/>
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
       <c r="Q209" s="1"/>
@@ -15897,37 +15900,43 @@
       <c r="W209" s="1"/>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A210" s="1"/>
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
+      <c r="A210" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>629</v>
+      </c>
       <c r="D210" s="1" t="s">
-        <v>35</v>
+        <v>627</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>935</v>
+        <v>630</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>934</v>
+        <v>860</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="J210" s="1"/>
       <c r="K210" s="1"/>
       <c r="L210" s="1" t="s">
-        <v>35</v>
+        <v>627</v>
       </c>
       <c r="M210" s="1" t="s">
-        <v>935</v>
+        <v>630</v>
       </c>
       <c r="N210" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
@@ -15940,23 +15949,17 @@
       <c r="W210" s="1"/>
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A211" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>635</v>
-      </c>
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
       <c r="D211" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>636</v>
+        <v>935</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>1154</v>
+        <v>934</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>908</v>
@@ -15973,72 +15976,78 @@
         <v>35</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>634</v>
+        <v>935</v>
       </c>
       <c r="N211" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="O211" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P211" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="Q211" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="R211" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S211" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="T211" s="1" t="s">
-        <v>1155</v>
-      </c>
+        <v>1153</v>
+      </c>
+      <c r="O211" s="1"/>
+      <c r="P211" s="1"/>
+      <c r="Q211" s="1"/>
+      <c r="R211" s="1"/>
+      <c r="S211" s="1"/>
+      <c r="T211" s="1"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A212" s="1"/>
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
+      <c r="A212" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>635</v>
+      </c>
       <c r="D212" s="1" t="s">
-        <v>846</v>
+        <v>35</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>638</v>
+        <v>1154</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>927</v>
+        <v>577</v>
       </c>
       <c r="J212" s="1"/>
       <c r="K212" s="1"/>
       <c r="L212" s="1" t="s">
-        <v>846</v>
+        <v>35</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="O212" s="1"/>
-      <c r="P212" s="1"/>
-      <c r="Q212" s="1"/>
-      <c r="R212" s="1"/>
-      <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
+        <v>768</v>
+      </c>
+      <c r="O212" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P212" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q212" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="R212" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S212" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="T212" s="1" t="s">
+        <v>1155</v>
+      </c>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
@@ -16048,30 +16057,34 @@
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1" t="s">
-        <v>639</v>
+        <v>846</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1157</v>
+        <v>638</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J213" s="1" t="s">
-        <v>1158</v>
-      </c>
+        <v>927</v>
+      </c>
+      <c r="J213" s="1"/>
       <c r="K213" s="1"/>
-      <c r="L213" s="1"/>
-      <c r="M213" s="1"/>
-      <c r="N213" s="1"/>
+      <c r="L213" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="M213" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="N213" s="1" t="s">
+        <v>1156</v>
+      </c>
       <c r="O213" s="1"/>
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
@@ -16090,10 +16103,10 @@
         <v>639</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>915</v>
@@ -16129,10 +16142,10 @@
         <v>639</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>772</v>
+        <v>641</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>915</v>
@@ -16161,35 +16174,29 @@
       <c r="W215" s="1"/>
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A216" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>644</v>
-      </c>
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
       <c r="D216" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>645</v>
+        <v>772</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>844</v>
+        <v>915</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>1082</v>
+        <v>54</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="K216" s="1"/>
       <c r="L216" s="1"/>
@@ -16206,38 +16213,40 @@
       <c r="W216" s="1"/>
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A217" s="1"/>
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
+      <c r="A217" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>644</v>
+      </c>
       <c r="D217" s="1" t="s">
-        <v>442</v>
+        <v>642</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>909</v>
+        <v>844</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>728</v>
+        <v>1082</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="J217" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>1162</v>
+      </c>
       <c r="K217" s="1"/>
-      <c r="L217" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="M217" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="N217" s="1" t="s">
-        <v>1164</v>
-      </c>
+      <c r="L217" s="1"/>
+      <c r="M217" s="1"/>
+      <c r="N217" s="1"/>
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
       <c r="Q217" s="1"/>
@@ -16249,38 +16258,38 @@
       <c r="W217" s="1"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A218" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>656</v>
-      </c>
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
       <c r="D218" s="1" t="s">
-        <v>658</v>
+        <v>442</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>54</v>
+        <v>728</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="J218" s="1"/>
       <c r="K218" s="1"/>
-      <c r="L218" s="1"/>
-      <c r="M218" s="1"/>
-      <c r="N218" s="1"/>
+      <c r="L218" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="M218" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="N218" s="1" t="s">
+        <v>1164</v>
+      </c>
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
       <c r="Q218" s="1"/>
@@ -16293,22 +16302,22 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>658</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>908</v>
@@ -16335,30 +16344,34 @@
       <c r="W219" s="1"/>
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A220" s="1"/>
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
+      <c r="A220" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>660</v>
+      </c>
       <c r="D220" s="1" t="s">
-        <v>503</v>
+        <v>658</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>504</v>
+        <v>661</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1082</v>
+        <v>54</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>1169</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="J220" s="1"/>
       <c r="K220" s="1"/>
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
@@ -16381,10 +16394,10 @@
         <v>503</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>509</v>
+        <v>1167</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>844</v>
@@ -16420,10 +16433,10 @@
         <v>503</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>663</v>
+        <v>509</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>663</v>
+        <v>509</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>844</v>
@@ -16459,10 +16472,10 @@
         <v>503</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>844</v>
@@ -16498,10 +16511,10 @@
         <v>503</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>844</v>
@@ -16537,10 +16550,10 @@
         <v>503</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>844</v>
@@ -16576,10 +16589,10 @@
         <v>503</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>844</v>
@@ -16615,10 +16628,10 @@
         <v>503</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>505</v>
+        <v>667</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1329</v>
+        <v>667</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>844</v>
@@ -16630,18 +16643,12 @@
         <v>1168</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>1330</v>
+        <v>1169</v>
       </c>
       <c r="K227" s="1"/>
-      <c r="L227" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M227" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="N227" s="1" t="s">
-        <v>1170</v>
-      </c>
+      <c r="L227" s="1"/>
+      <c r="M227" s="1"/>
+      <c r="N227" s="1"/>
       <c r="O227" s="1"/>
       <c r="P227" s="1"/>
       <c r="Q227" s="1"/>
@@ -16660,10 +16667,10 @@
         <v>503</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>668</v>
+        <v>505</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>668</v>
+        <v>1329</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>844</v>
@@ -16675,12 +16682,18 @@
         <v>1168</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>1169</v>
+        <v>1330</v>
       </c>
       <c r="K228" s="1"/>
-      <c r="L228" s="1"/>
-      <c r="M228" s="1"/>
-      <c r="N228" s="1"/>
+      <c r="L228" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="M228" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="N228" s="1" t="s">
+        <v>1170</v>
+      </c>
       <c r="O228" s="1"/>
       <c r="P228" s="1"/>
       <c r="Q228" s="1"/>
@@ -16699,10 +16712,10 @@
         <v>503</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>510</v>
+        <v>668</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>510</v>
+        <v>668</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>844</v>
@@ -16738,10 +16751,10 @@
         <v>503</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>844</v>
@@ -16777,10 +16790,10 @@
         <v>503</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>844</v>
@@ -16816,10 +16829,10 @@
         <v>503</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>669</v>
+        <v>512</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>669</v>
+        <v>512</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>844</v>
@@ -16855,10 +16868,10 @@
         <v>503</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>844</v>
@@ -16894,10 +16907,10 @@
         <v>503</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>844</v>
@@ -16933,10 +16946,10 @@
         <v>503</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>844</v>
@@ -16972,10 +16985,10 @@
         <v>503</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>513</v>
+        <v>662</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>513</v>
+        <v>662</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>844</v>
@@ -17011,10 +17024,10 @@
         <v>503</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>844</v>
@@ -17043,23 +17056,17 @@
       <c r="W237" s="1"/>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A238" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>691</v>
-      </c>
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
       <c r="D238" s="1" t="s">
         <v>503</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>719</v>
+        <v>514</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1171</v>
+        <v>514</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>844</v>
@@ -17092,40 +17099,36 @@
         <v>503</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>506</v>
+        <v>690</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>507</v>
+        <v>691</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>503</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>508</v>
+        <v>719</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>908</v>
+        <v>844</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>54</v>
+        <v>1082</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J239" s="1"/>
+        <v>1168</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>1169</v>
+      </c>
       <c r="K239" s="1"/>
-      <c r="L239" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M239" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="N239" s="1" t="s">
-        <v>1173</v>
-      </c>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+      <c r="N239" s="1"/>
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
       <c r="Q239" s="1"/>
@@ -17144,7 +17147,7 @@
         <v>506</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>503</v>
@@ -17153,7 +17156,7 @@
         <v>508</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>908</v>
@@ -17173,7 +17176,7 @@
         <v>508</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
@@ -17186,17 +17189,23 @@
       <c r="W240" s="1"/>
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A241" s="1"/>
-      <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
+      <c r="A241" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>515</v>
+      </c>
       <c r="D241" s="1" t="s">
-        <v>106</v>
+        <v>503</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>672</v>
+        <v>508</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>908</v>
@@ -17205,15 +17214,19 @@
         <v>54</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J241" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="J241" s="1"/>
       <c r="K241" s="1"/>
-      <c r="L241" s="1"/>
-      <c r="M241" s="1"/>
-      <c r="N241" s="1"/>
+      <c r="L241" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="M241" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="N241" s="1" t="s">
+        <v>1175</v>
+      </c>
       <c r="O241" s="1"/>
       <c r="P241" s="1"/>
       <c r="Q241" s="1"/>
@@ -17229,25 +17242,25 @@
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1" t="s">
-        <v>960</v>
+        <v>106</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>961</v>
+        <v>672</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>962</v>
+        <v>1176</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>959</v>
+        <v>908</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1177</v>
+        <v>54</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>1178</v>
+        <v>580</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>958</v>
+        <v>124</v>
       </c>
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
@@ -17264,29 +17277,29 @@
       <c r="W242" s="1"/>
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A243" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="D243" s="1"/>
-      <c r="E243" s="1"/>
-      <c r="F243" s="1"/>
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>962</v>
+      </c>
       <c r="G243" s="1" t="s">
-        <v>844</v>
+        <v>959</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1082</v>
+        <v>1177</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>588</v>
+        <v>1178</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1179</v>
+        <v>958</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -17303,36 +17316,34 @@
       <c r="W243" s="1"/>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A244" s="1"/>
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
-      <c r="D244" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>1317</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>1318</v>
-      </c>
+      <c r="A244" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H244" s="1"/>
+        <v>844</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>1082</v>
+      </c>
       <c r="I244" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J244" s="1"/>
+        <v>588</v>
+      </c>
+      <c r="J244" s="1" t="s">
+        <v>1179</v>
+      </c>
       <c r="K244" s="1"/>
-      <c r="L244" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="M244" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="N244" s="1" t="s">
-        <v>1314</v>
-      </c>
+      <c r="L244" s="1"/>
+      <c r="M244" s="1"/>
+      <c r="N244" s="1"/>
       <c r="O244" s="1"/>
       <c r="P244" s="1"/>
       <c r="Q244" s="1"/>
@@ -17351,10 +17362,10 @@
         <v>35</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>1321</v>
@@ -17369,10 +17380,10 @@
         <v>1312</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="N245" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
@@ -17385,53 +17396,39 @@
       <c r="W245" s="1"/>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A246" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>677</v>
-      </c>
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
       <c r="D246" s="1" t="s">
-        <v>606</v>
+        <v>35</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>842</v>
+        <v>1319</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>841</v>
+        <v>1320</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="I246" s="1"/>
-      <c r="J246" s="1" t="s">
-        <v>840</v>
-      </c>
+        <v>1321</v>
+      </c>
+      <c r="H246" s="1"/>
+      <c r="I246" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="J246" s="1"/>
       <c r="K246" s="1"/>
       <c r="L246" s="1" t="s">
-        <v>606</v>
+        <v>1312</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>676</v>
+        <v>1315</v>
       </c>
       <c r="N246" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="O246" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="P246" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="Q246" s="1" t="s">
-        <v>1181</v>
-      </c>
+        <v>1316</v>
+      </c>
+      <c r="O246" s="1"/>
+      <c r="P246" s="1"/>
+      <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
       <c r="T246" s="1"/>
@@ -17441,40 +17438,52 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>627</v>
+        <v>676</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>764</v>
+        <v>677</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>680</v>
+        <v>842</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>681</v>
+        <v>841</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>920</v>
+        <v>1180</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="I247" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="J247" s="1"/>
+        <v>728</v>
+      </c>
+      <c r="I247" s="1"/>
+      <c r="J247" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="K247" s="1"/>
-      <c r="L247" s="1"/>
-      <c r="M247" s="1"/>
-      <c r="N247" s="1"/>
-      <c r="O247" s="1"/>
-      <c r="P247" s="1"/>
-      <c r="Q247" s="1"/>
+      <c r="L247" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="M247" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="N247" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="O247" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="P247" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="Q247" s="1" t="s">
+        <v>1181</v>
+      </c>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
       <c r="T247" s="1"/>
@@ -17484,17 +17493,23 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>544</v>
+        <v>680</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>682</v>
+        <v>627</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="D248" s="1"/>
-      <c r="E248" s="1"/>
-      <c r="F248" s="1"/>
+        <v>764</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>681</v>
+      </c>
       <c r="G248" s="1" t="s">
         <v>920</v>
       </c>
@@ -17502,7 +17517,7 @@
         <v>561</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -17520,26 +17535,26 @@
       <c r="W248" s="1"/>
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A249" s="1"/>
-      <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
-      <c r="D249" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E249" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="F249" s="1" t="s">
-        <v>1184</v>
-      </c>
+      <c r="A249" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
       <c r="G249" s="1" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>577</v>
+        <v>1183</v>
       </c>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -17561,13 +17576,13 @@
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1" t="s">
-        <v>685</v>
+        <v>35</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>908</v>
@@ -17576,7 +17591,7 @@
         <v>54</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
@@ -17598,13 +17613,13 @@
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>908</v>
@@ -17613,7 +17628,7 @@
         <v>54</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J251" s="1"/>
       <c r="K251" s="1"/>
@@ -17631,26 +17646,26 @@
       <c r="W251" s="1"/>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A252" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="D252" s="1"/>
-      <c r="E252" s="1"/>
-      <c r="F252" s="1"/>
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>1186</v>
+      </c>
       <c r="G252" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -17668,40 +17683,32 @@
       <c r="W252" s="1"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A253" s="1"/>
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-      <c r="D253" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E253" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="F253" s="1" t="s">
-        <v>1187</v>
-      </c>
+      <c r="A253" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
       <c r="G253" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>728</v>
+        <v>562</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="J253" s="1" t="s">
-        <v>847</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="J253" s="1"/>
       <c r="K253" s="1"/>
-      <c r="L253" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="M253" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="N253" s="1" t="s">
-        <v>1188</v>
-      </c>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+      <c r="N253" s="1"/>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
@@ -17717,28 +17724,36 @@
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>54</v>
+        <v>728</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="J254" s="1"/>
+      <c r="J254" s="1" t="s">
+        <v>847</v>
+      </c>
       <c r="K254" s="1"/>
-      <c r="L254" s="1"/>
-      <c r="M254" s="1"/>
-      <c r="N254" s="1"/>
+      <c r="L254" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="M254" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N254" s="1" t="s">
+        <v>1188</v>
+      </c>
       <c r="O254" s="1"/>
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
@@ -17750,23 +17765,17 @@
       <c r="W254" s="1"/>
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A255" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>696</v>
-      </c>
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
       <c r="D255" s="1" t="s">
-        <v>694</v>
+        <v>426</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>695</v>
+        <v>429</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>908</v>
@@ -17775,7 +17784,7 @@
         <v>54</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>1191</v>
+        <v>593</v>
       </c>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
@@ -17794,25 +17803,31 @@
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="D256" s="1"/>
-      <c r="E256" s="1"/>
-      <c r="F256" s="1"/>
+        <v>696</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>1190</v>
+      </c>
       <c r="G256" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1102</v>
+        <v>1191</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -17831,31 +17846,25 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>790</v>
+        <v>698</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="E257" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="F257" s="1" t="s">
-        <v>1192</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="D257" s="1"/>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>585</v>
+        <v>1102</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -17873,17 +17882,23 @@
       <c r="W257" s="1"/>
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A258" s="1"/>
-      <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
+      <c r="A258" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>791</v>
+      </c>
       <c r="D258" s="1" t="s">
-        <v>143</v>
+        <v>700</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>908</v>
@@ -17892,7 +17907,7 @@
         <v>54</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -17914,13 +17929,13 @@
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1" t="s">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>908</v>
@@ -17929,7 +17944,7 @@
         <v>54</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
@@ -17951,19 +17966,19 @@
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>577</v>
@@ -17991,16 +18006,16 @@
         <v>300</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>316</v>
+        <v>704</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>577</v>
@@ -18021,23 +18036,17 @@
       <c r="W261" s="1"/>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A262" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>800</v>
-      </c>
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
       <c r="D262" s="1" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>908</v>
@@ -18064,26 +18073,32 @@
       <c r="W262" s="1"/>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A263" s="1"/>
-      <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
+      <c r="A263" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>800</v>
+      </c>
       <c r="D263" s="1" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>705</v>
+        <v>388</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
@@ -18108,10 +18123,10 @@
         <v>35</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>912</v>
@@ -18120,7 +18135,7 @@
         <v>562</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -18145,19 +18160,19 @@
         <v>35</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>398</v>
+        <v>706</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -18179,22 +18194,22 @@
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1" t="s">
-        <v>685</v>
+        <v>35</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>707</v>
+        <v>398</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>927</v>
+        <v>580</v>
       </c>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -18216,13 +18231,13 @@
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
       <c r="D267" s="1" t="s">
-        <v>600</v>
+        <v>685</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>912</v>
@@ -18231,7 +18246,7 @@
         <v>562</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>585</v>
+        <v>927</v>
       </c>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
@@ -18256,10 +18271,10 @@
         <v>600</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>912</v>
@@ -18286,23 +18301,17 @@
       <c r="W268" s="1"/>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A269" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>711</v>
-      </c>
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
       <c r="D269" s="1" t="s">
-        <v>212</v>
+        <v>600</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>974</v>
+        <v>709</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>912</v>
@@ -18311,19 +18320,13 @@
         <v>562</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>1183</v>
+        <v>585</v>
       </c>
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
-      <c r="L269" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M269" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="N269" s="1" t="s">
-        <v>973</v>
-      </c>
+      <c r="L269" s="1"/>
+      <c r="M269" s="1"/>
+      <c r="N269" s="1"/>
       <c r="O269" s="1"/>
       <c r="P269" s="1"/>
       <c r="Q269" s="1"/>
@@ -18336,17 +18339,23 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>639</v>
+        <v>212</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="D270" s="1"/>
-      <c r="E270" s="1"/>
-      <c r="F270" s="1"/>
+        <v>711</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>1204</v>
+      </c>
       <c r="G270" s="1" t="s">
         <v>912</v>
       </c>
@@ -18354,13 +18363,19 @@
         <v>562</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>587</v>
+        <v>1183</v>
       </c>
       <c r="J270" s="1"/>
       <c r="K270" s="1"/>
-      <c r="L270" s="1"/>
-      <c r="M270" s="1"/>
-      <c r="N270" s="1"/>
+      <c r="L270" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M270" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="N270" s="1" t="s">
+        <v>973</v>
+      </c>
       <c r="O270" s="1"/>
       <c r="P270" s="1"/>
       <c r="Q270" s="1"/>
@@ -18372,26 +18387,26 @@
       <c r="W270" s="1"/>
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A271" s="1"/>
-      <c r="B271" s="1"/>
-      <c r="C271" s="1"/>
-      <c r="D271" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="F271" s="1" t="s">
-        <v>1205</v>
-      </c>
+      <c r="A271" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
       <c r="G271" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J271" s="1"/>
       <c r="K271" s="1"/>
@@ -18409,36 +18424,28 @@
       <c r="W271" s="1"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A272" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>814</v>
-      </c>
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
       <c r="D272" s="1" t="s">
-        <v>606</v>
+        <v>464</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>714</v>
+        <v>469</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="J272" s="1" t="s">
-        <v>839</v>
-      </c>
+      <c r="J272" s="1"/>
       <c r="K272" s="1"/>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
@@ -18454,28 +18461,36 @@
       <c r="W272" s="1"/>
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A273" s="1"/>
-      <c r="B273" s="1"/>
-      <c r="C273" s="1"/>
+      <c r="A273" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>814</v>
+      </c>
       <c r="D273" s="1" t="s">
         <v>606</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1208</v>
+        <v>912</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="J273" s="1"/>
+      <c r="J273" s="1" t="s">
+        <v>839</v>
+      </c>
       <c r="K273" s="1"/>
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
@@ -18498,10 +18513,10 @@
         <v>606</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>1208</v>
@@ -18532,22 +18547,22 @@
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1" t="s">
-        <v>647</v>
+        <v>606</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>912</v>
+        <v>1208</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="J275" s="1"/>
       <c r="K275" s="1"/>
@@ -18569,22 +18584,22 @@
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1" t="s">
-        <v>723</v>
+        <v>647</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
@@ -18606,26 +18621,24 @@
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>693</v>
+        <v>724</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>1082</v>
+        <v>54</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="J277" s="1" t="s">
-        <v>1213</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="J277" s="1"/>
       <c r="K277" s="1"/>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
@@ -18645,36 +18658,30 @@
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1" t="s">
-        <v>725</v>
+        <v>692</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>844</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>54</v>
+        <v>1082</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1191</v>
+        <v>1168</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>853</v>
+        <v>1213</v>
       </c>
       <c r="K278" s="1"/>
-      <c r="L278" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="M278" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="N278" s="1" t="s">
-        <v>864</v>
-      </c>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+      <c r="N278" s="1"/>
       <c r="O278" s="1"/>
       <c r="P278" s="1"/>
       <c r="Q278" s="1"/>
@@ -18690,28 +18697,36 @@
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1" t="s">
-        <v>571</v>
+        <v>725</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1146</v>
+        <v>844</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>1147</v>
+        <v>54</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1216</v>
-      </c>
-      <c r="J279" s="1"/>
+        <v>1191</v>
+      </c>
+      <c r="J279" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="K279" s="1"/>
-      <c r="L279" s="1"/>
-      <c r="M279" s="1"/>
-      <c r="N279" s="1"/>
+      <c r="L279" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="M279" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="N279" s="1" t="s">
+        <v>864</v>
+      </c>
       <c r="O279" s="1"/>
       <c r="P279" s="1"/>
       <c r="Q279" s="1"/>
@@ -18727,26 +18742,24 @@
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1" t="s">
-        <v>746</v>
+        <v>571</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>931</v>
+        <v>1215</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>915</v>
+        <v>1146</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>54</v>
+        <v>1147</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J280" s="1" t="s">
-        <v>932</v>
-      </c>
+        <v>1216</v>
+      </c>
+      <c r="J280" s="1"/>
       <c r="K280" s="1"/>
       <c r="L280" s="1"/>
       <c r="M280" s="1"/>
@@ -18769,10 +18782,10 @@
         <v>746</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1217</v>
+        <v>931</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>915</v>
@@ -18781,10 +18794,10 @@
         <v>54</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>867</v>
+        <v>582</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>1218</v>
+        <v>932</v>
       </c>
       <c r="K281" s="1"/>
       <c r="L281" s="1"/>
@@ -18805,36 +18818,30 @@
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1" t="s">
-        <v>179</v>
+        <v>746</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>850</v>
+        <v>1217</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="H282" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>583</v>
+        <v>867</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>831</v>
+        <v>1218</v>
       </c>
       <c r="K282" s="1"/>
-      <c r="L282" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M282" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="N282" s="1" t="s">
-        <v>849</v>
-      </c>
+      <c r="L282" s="1"/>
+      <c r="M282" s="1"/>
+      <c r="N282" s="1"/>
       <c r="O282" s="1"/>
       <c r="P282" s="1"/>
       <c r="Q282" s="1"/>
@@ -18850,13 +18857,13 @@
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>983</v>
+        <v>750</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>985</v>
+        <v>850</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>908</v>
@@ -18867,16 +18874,18 @@
       <c r="I283" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="J283" s="1"/>
+      <c r="J283" s="1" t="s">
+        <v>831</v>
+      </c>
       <c r="K283" s="1"/>
       <c r="L283" s="1" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>983</v>
+        <v>750</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>984</v>
+        <v>849</v>
       </c>
       <c r="O283" s="1"/>
       <c r="P283" s="1"/>
@@ -18893,33 +18902,33 @@
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1" t="s">
-        <v>857</v>
+        <v>49</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>270</v>
+        <v>983</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="J284" s="1"/>
       <c r="K284" s="1"/>
       <c r="L284" s="1" t="s">
-        <v>857</v>
+        <v>49</v>
       </c>
       <c r="M284" s="1" t="s">
-        <v>270</v>
+        <v>983</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>1219</v>
+        <v>984</v>
       </c>
       <c r="O284" s="1"/>
       <c r="P284" s="1"/>
@@ -18932,101 +18941,107 @@
       <c r="W284" s="1"/>
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A285" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
       <c r="D285" s="1" t="s">
-        <v>291</v>
+        <v>857</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>756</v>
+        <v>988</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>844</v>
+        <v>910</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>1082</v>
+        <v>561</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J285" s="1" t="s">
-        <v>1220</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="J285" s="1"/>
       <c r="K285" s="1"/>
       <c r="L285" s="1" t="s">
-        <v>685</v>
+        <v>857</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="O285" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="P285" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q285" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="R285" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="S285" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T285" s="1" t="s">
-        <v>907</v>
-      </c>
+        <v>1219</v>
+      </c>
+      <c r="O285" s="1"/>
+      <c r="P285" s="1"/>
+      <c r="Q285" s="1"/>
+      <c r="R285" s="1"/>
+      <c r="S285" s="1"/>
+      <c r="T285" s="1"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A286" s="1"/>
-      <c r="B286" s="1"/>
-      <c r="C286" s="1"/>
+      <c r="A286" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="D286" s="1" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>753</v>
+        <v>294</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1222</v>
+        <v>756</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>908</v>
+        <v>844</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>54</v>
+        <v>1082</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J286" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J286" s="1" t="s">
+        <v>1220</v>
+      </c>
       <c r="K286" s="1"/>
-      <c r="L286" s="1"/>
-      <c r="M286" s="1"/>
-      <c r="N286" s="1"/>
-      <c r="O286" s="1"/>
-      <c r="P286" s="1"/>
-      <c r="Q286" s="1"/>
-      <c r="R286" s="1"/>
-      <c r="S286" s="1"/>
-      <c r="T286" s="1"/>
+      <c r="L286" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M286" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N286" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="O286" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="P286" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q286" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="R286" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S286" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T286" s="1" t="s">
+        <v>907</v>
+      </c>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
@@ -19036,34 +19051,28 @@
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>331</v>
+        <v>753</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>923</v>
+        <v>54</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>577</v>
       </c>
       <c r="J287" s="1"/>
       <c r="K287" s="1"/>
-      <c r="L287" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M287" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="N287" s="1" t="s">
-        <v>1224</v>
-      </c>
+      <c r="L287" s="1"/>
+      <c r="M287" s="1"/>
+      <c r="N287" s="1"/>
       <c r="O287" s="1"/>
       <c r="P287" s="1"/>
       <c r="Q287" s="1"/>
@@ -19079,28 +19088,34 @@
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>476</v>
+        <v>363</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>755</v>
+        <v>331</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>844</v>
+        <v>913</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>1082</v>
+        <v>923</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
-      <c r="L288" s="1"/>
-      <c r="M288" s="1"/>
-      <c r="N288" s="1"/>
+      <c r="L288" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M288" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="N288" s="1" t="s">
+        <v>1224</v>
+      </c>
       <c r="O288" s="1"/>
       <c r="P288" s="1"/>
       <c r="Q288" s="1"/>
@@ -19116,22 +19131,22 @@
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>443</v>
+        <v>755</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>908</v>
+        <v>844</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>54</v>
+        <v>1082</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="J289" s="1"/>
       <c r="K289" s="1"/>
@@ -19153,34 +19168,28 @@
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
-        <v>339</v>
+        <v>442</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>759</v>
+        <v>443</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>923</v>
+        <v>54</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="J290" s="1"/>
       <c r="K290" s="1"/>
-      <c r="L290" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="M290" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="N290" s="1" t="s">
-        <v>1228</v>
-      </c>
+      <c r="L290" s="1"/>
+      <c r="M290" s="1"/>
+      <c r="N290" s="1"/>
       <c r="O290" s="1"/>
       <c r="P290" s="1"/>
       <c r="Q290" s="1"/>
@@ -19196,33 +19205,33 @@
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>908</v>
+        <v>844</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>54</v>
+        <v>923</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
       <c r="L291" s="1" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="M291" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N291" s="1" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="O291" s="1"/>
       <c r="P291" s="1"/>
@@ -19239,30 +19248,34 @@
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1" t="s">
-        <v>476</v>
+        <v>35</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1232</v>
+        <v>908</v>
       </c>
       <c r="H292" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J292" s="1" t="s">
-        <v>975</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="J292" s="1"/>
       <c r="K292" s="1"/>
-      <c r="L292" s="1"/>
-      <c r="M292" s="1"/>
-      <c r="N292" s="1"/>
+      <c r="L292" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M292" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="N292" s="1" t="s">
+        <v>1230</v>
+      </c>
       <c r="O292" s="1"/>
       <c r="P292" s="1"/>
       <c r="Q292" s="1"/>
@@ -19278,24 +19291,26 @@
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
-        <v>746</v>
+        <v>476</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>908</v>
+        <v>1232</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="J293" s="1"/>
+        <v>1102</v>
+      </c>
+      <c r="J293" s="1" t="s">
+        <v>975</v>
+      </c>
       <c r="K293" s="1"/>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
@@ -19318,23 +19333,21 @@
         <v>746</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="H294" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J294" s="1" t="s">
-        <v>1235</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="J294" s="1"/>
       <c r="K294" s="1"/>
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
@@ -19354,24 +19367,26 @@
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
       <c r="D295" s="1" t="s">
-        <v>98</v>
+        <v>746</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J295" s="1"/>
+        <v>578</v>
+      </c>
+      <c r="J295" s="1" t="s">
+        <v>1235</v>
+      </c>
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
@@ -19387,38 +19402,32 @@
       <c r="W295" s="1"/>
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A296" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>987</v>
-      </c>
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
       <c r="D296" s="1" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>986</v>
+        <v>767</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G296" s="1"/>
-      <c r="H296" s="1"/>
-      <c r="I296" s="1"/>
+        <v>1236</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="H296" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>582</v>
+      </c>
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
-      <c r="L296" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M296" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="N296" s="1" t="s">
-        <v>1238</v>
-      </c>
+      <c r="L296" s="1"/>
+      <c r="M296" s="1"/>
+      <c r="N296" s="1"/>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
       <c r="Q296" s="1"/>
@@ -19431,39 +19440,37 @@
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>746</v>
+        <v>43</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>762</v>
+        <v>986</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1239</v>
+        <v>987</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>746</v>
+        <v>43</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>933</v>
+        <v>986</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="H297" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I297" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="J297" s="1" t="s">
-        <v>1241</v>
-      </c>
+        <v>1237</v>
+      </c>
+      <c r="G297" s="1"/>
+      <c r="H297" s="1"/>
+      <c r="I297" s="1"/>
+      <c r="J297" s="1"/>
       <c r="K297" s="1"/>
-      <c r="L297" s="1"/>
-      <c r="M297" s="1"/>
-      <c r="N297" s="1"/>
+      <c r="L297" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M297" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="N297" s="1" t="s">
+        <v>1238</v>
+      </c>
       <c r="O297" s="1"/>
       <c r="P297" s="1"/>
       <c r="Q297" s="1"/>
@@ -19475,28 +19482,36 @@
       <c r="W297" s="1"/>
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A298" s="1"/>
-      <c r="B298" s="1"/>
-      <c r="C298" s="1"/>
+      <c r="A298" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>1239</v>
+      </c>
       <c r="D298" s="1" t="s">
-        <v>697</v>
+        <v>746</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>769</v>
+        <v>933</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>562</v>
+        <v>54</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J298" s="1"/>
+        <v>585</v>
+      </c>
+      <c r="J298" s="1" t="s">
+        <v>1241</v>
+      </c>
       <c r="K298" s="1"/>
       <c r="L298" s="1"/>
       <c r="M298" s="1"/>
@@ -19516,22 +19531,22 @@
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
       <c r="D299" s="1" t="s">
-        <v>770</v>
+        <v>697</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>577</v>
+        <v>1102</v>
       </c>
       <c r="J299" s="1"/>
       <c r="K299" s="1"/>
@@ -19553,21 +19568,23 @@
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
       <c r="D300" s="1" t="s">
-        <v>212</v>
+        <v>770</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>773</v>
+        <v>1243</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="I300" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>577</v>
+      </c>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
       <c r="L300" s="1"/>
@@ -19584,36 +19601,26 @@
       <c r="W300" s="1"/>
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A301" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>775</v>
-      </c>
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
       <c r="D301" s="1" t="s">
-        <v>300</v>
+        <v>212</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>335</v>
+        <v>773</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1244</v>
+        <v>773</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I301" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J301" s="1" t="s">
-        <v>338</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="I301" s="1"/>
+      <c r="J301" s="1"/>
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
       <c r="M301" s="1"/>
@@ -19630,43 +19637,39 @@
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>391</v>
+        <v>775</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>67</v>
+        <v>335</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>923</v>
+        <v>54</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="J302" s="1"/>
+      <c r="J302" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="K302" s="1"/>
-      <c r="L302" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="M302" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N302" s="1" t="s">
-        <v>942</v>
-      </c>
+      <c r="L302" s="1"/>
+      <c r="M302" s="1"/>
+      <c r="N302" s="1"/>
       <c r="O302" s="1"/>
       <c r="P302" s="1"/>
       <c r="Q302" s="1"/>
@@ -19679,39 +19682,43 @@
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>49</v>
+        <v>390</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>785</v>
+        <v>65</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>786</v>
+        <v>391</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>49</v>
+        <v>390</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>766</v>
+        <v>67</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>915</v>
+        <v>844</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>54</v>
+        <v>923</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J303" s="1" t="s">
-        <v>1247</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="J303" s="1"/>
       <c r="K303" s="1"/>
-      <c r="L303" s="1"/>
-      <c r="M303" s="1"/>
-      <c r="N303" s="1"/>
+      <c r="L303" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="M303" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N303" s="1" t="s">
+        <v>942</v>
+      </c>
       <c r="O303" s="1"/>
       <c r="P303" s="1"/>
       <c r="Q303" s="1"/>
@@ -19724,43 +19731,39 @@
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>789</v>
+        <v>766</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="H304" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J304" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="J304" s="1" t="s">
+        <v>1247</v>
+      </c>
       <c r="K304" s="1"/>
-      <c r="L304" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M304" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="N304" s="1" t="s">
-        <v>1249</v>
-      </c>
+      <c r="L304" s="1"/>
+      <c r="M304" s="1"/>
+      <c r="N304" s="1"/>
       <c r="O304" s="1"/>
       <c r="P304" s="1"/>
       <c r="Q304" s="1"/>
@@ -19772,32 +19775,44 @@
       <c r="W304" s="1"/>
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A305" s="1"/>
-      <c r="B305" s="1"/>
-      <c r="C305" s="1"/>
+      <c r="A305" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>788</v>
+      </c>
       <c r="D305" s="1" t="s">
-        <v>503</v>
+        <v>57</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>818</v>
+        <v>789</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>818</v>
+        <v>1248</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>1082</v>
+        <v>54</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>1168</v>
+        <v>583</v>
       </c>
       <c r="J305" s="1"/>
       <c r="K305" s="1"/>
-      <c r="L305" s="1"/>
-      <c r="M305" s="1"/>
-      <c r="N305" s="1"/>
+      <c r="L305" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M305" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="N305" s="1" t="s">
+        <v>1249</v>
+      </c>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
@@ -19813,36 +19828,28 @@
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>898</v>
+        <v>818</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1308</v>
+        <v>818</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>912</v>
+        <v>844</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>562</v>
+        <v>1082</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J306" s="1" t="s">
-        <v>839</v>
-      </c>
+        <v>1168</v>
+      </c>
+      <c r="J306" s="1"/>
       <c r="K306" s="1"/>
-      <c r="L306" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="M306" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="N306" s="1" t="s">
-        <v>899</v>
-      </c>
+      <c r="L306" s="1"/>
+      <c r="M306" s="1"/>
+      <c r="N306" s="1"/>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
@@ -19861,10 +19868,10 @@
         <v>606</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>819</v>
+        <v>898</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1296</v>
+        <v>1308</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>912</v>
@@ -19883,10 +19890,10 @@
         <v>606</v>
       </c>
       <c r="M307" s="1" t="s">
-        <v>819</v>
+        <v>898</v>
       </c>
       <c r="N307" s="1" t="s">
-        <v>1250</v>
+        <v>899</v>
       </c>
       <c r="O307" s="1"/>
       <c r="P307" s="1"/>
@@ -19903,26 +19910,36 @@
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1" t="s">
-        <v>820</v>
+        <v>606</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1251</v>
+        <v>1296</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1146</v>
+        <v>912</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I308" s="1"/>
-      <c r="J308" s="1"/>
+        <v>562</v>
+      </c>
+      <c r="I308" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="J308" s="1" t="s">
+        <v>839</v>
+      </c>
       <c r="K308" s="1"/>
-      <c r="L308" s="1"/>
-      <c r="M308" s="1"/>
-      <c r="N308" s="1"/>
+      <c r="L308" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="M308" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="N308" s="1" t="s">
+        <v>1250</v>
+      </c>
       <c r="O308" s="1"/>
       <c r="P308" s="1"/>
       <c r="Q308" s="1"/>
@@ -19941,10 +19958,10 @@
         <v>820</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>1146</v>
@@ -19968,37 +19985,31 @@
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
     </row>
-    <row r="310" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
-      <c r="D310" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E310" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F310" s="5" t="s">
-        <v>1310</v>
-      </c>
-      <c r="G310" s="5" t="s">
-        <v>908</v>
-      </c>
-      <c r="H310" s="1"/>
-      <c r="I310" s="1" t="s">
-        <v>577</v>
-      </c>
+      <c r="D310" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H310" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I310" s="1"/>
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
-      <c r="L310" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="M310" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="N310" s="5" t="s">
-        <v>1311</v>
-      </c>
+      <c r="L310" s="1"/>
+      <c r="M310" s="1"/>
+      <c r="N310" s="1"/>
       <c r="O310" s="1"/>
       <c r="P310" s="1"/>
       <c r="Q310" s="1"/>
@@ -20009,31 +20020,37 @@
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
-      <c r="D311" s="1" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E311" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="F311" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="G311" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H311" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I311" s="1"/>
+      <c r="D311" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E311" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G311" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="H311" s="1"/>
+      <c r="I311" s="1" t="s">
+        <v>577</v>
+      </c>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
-      <c r="L311" s="1"/>
-      <c r="M311" s="1"/>
-      <c r="N311" s="1"/>
+      <c r="L311" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="M311" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="N311" s="5" t="s">
+        <v>1311</v>
+      </c>
       <c r="O311" s="1"/>
       <c r="P311" s="1"/>
       <c r="Q311" s="1"/>
@@ -20049,26 +20066,22 @@
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1" t="s">
-        <v>516</v>
+        <v>1253</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>844</v>
+        <v>1146</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="I312" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="J312" s="1" t="s">
-        <v>1256</v>
-      </c>
+        <v>1147</v>
+      </c>
+      <c r="I312" s="1"/>
+      <c r="J312" s="1"/>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
       <c r="M312" s="1"/>
@@ -20088,24 +20101,26 @@
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1" t="s">
-        <v>685</v>
+        <v>516</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1257</v>
+        <v>824</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>912</v>
+        <v>844</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>562</v>
+        <v>1082</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="J313" s="1"/>
+        <v>878</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>1256</v>
+      </c>
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
@@ -20125,13 +20140,13 @@
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1" t="s">
-        <v>106</v>
+        <v>685</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>114</v>
+        <v>1257</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>912</v>
@@ -20140,19 +20155,13 @@
         <v>562</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>587</v>
+        <v>927</v>
       </c>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
-      <c r="L314" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M314" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N314" s="1" t="s">
-        <v>1260</v>
-      </c>
+      <c r="L314" s="1"/>
+      <c r="M314" s="1"/>
+      <c r="N314" s="1"/>
       <c r="O314" s="1"/>
       <c r="P314" s="1"/>
       <c r="Q314" s="1"/>
@@ -20168,30 +20177,34 @@
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>827</v>
+        <v>114</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J315" s="1" t="s">
-        <v>1262</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="J315" s="1"/>
       <c r="K315" s="1"/>
-      <c r="L315" s="1"/>
-      <c r="M315" s="1"/>
-      <c r="N315" s="1"/>
+      <c r="L315" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M315" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N315" s="1" t="s">
+        <v>1260</v>
+      </c>
       <c r="O315" s="1"/>
       <c r="P315" s="1"/>
       <c r="Q315" s="1"/>
@@ -20207,25 +20220,25 @@
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>180</v>
+        <v>827</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
@@ -20246,34 +20259,30 @@
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
       <c r="D317" s="1" t="s">
-        <v>832</v>
+        <v>179</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>833</v>
+        <v>180</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J317" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="J317" s="1" t="s">
+        <v>1264</v>
+      </c>
       <c r="K317" s="1"/>
-      <c r="L317" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="M317" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="N317" s="1" t="s">
-        <v>1267</v>
-      </c>
+      <c r="L317" s="1"/>
+      <c r="M317" s="1"/>
+      <c r="N317" s="1"/>
       <c r="O317" s="1"/>
       <c r="P317" s="1"/>
       <c r="Q317" s="1"/>
@@ -20289,13 +20298,13 @@
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
       <c r="D318" s="1" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>910</v>
@@ -20308,9 +20317,15 @@
       </c>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
-      <c r="L318" s="1"/>
-      <c r="M318" s="1"/>
-      <c r="N318" s="1"/>
+      <c r="L318" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M318" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="N318" s="1" t="s">
+        <v>1267</v>
+      </c>
       <c r="O318" s="1"/>
       <c r="P318" s="1"/>
       <c r="Q318" s="1"/>
@@ -20326,26 +20341,24 @@
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1" t="s">
-        <v>421</v>
+        <v>835</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>424</v>
+        <v>836</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>843</v>
+        <v>1268</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>844</v>
+        <v>910</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J319" s="1" t="s">
-        <v>845</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="J319" s="1"/>
       <c r="K319" s="1"/>
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
@@ -20361,34 +20374,30 @@
       <c r="W319" s="1"/>
     </row>
     <row r="320" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A320" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>826</v>
-      </c>
+      <c r="A320" s="1"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
       <c r="D320" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>848</v>
+        <v>424</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>909</v>
+        <v>844</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>728</v>
+        <v>54</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="J320" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J320" s="1" t="s">
+        <v>845</v>
+      </c>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
@@ -20405,31 +20414,31 @@
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>35</v>
+        <v>433</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>410</v>
+        <v>848</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>851</v>
+        <v>826</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>410</v>
+        <v>848</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>411</v>
+        <v>847</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>54</v>
+        <v>728</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="J321" s="1"/>
       <c r="K321" s="1"/>
@@ -20447,26 +20456,32 @@
       <c r="W321" s="1"/>
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A322" s="1"/>
-      <c r="B322" s="1"/>
-      <c r="C322" s="1"/>
+      <c r="A322" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>851</v>
+      </c>
       <c r="D322" s="1" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>565</v>
+        <v>410</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>793</v>
+        <v>411</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="H322" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J322" s="1"/>
       <c r="K322" s="1"/>
@@ -20484,36 +20499,28 @@
       <c r="W322" s="1"/>
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A323" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B323" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>855</v>
-      </c>
+      <c r="A323" s="1"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
       <c r="D323" s="1" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>856</v>
+        <v>565</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1269</v>
+        <v>793</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J323" s="1" t="s">
-        <v>1270</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="J323" s="1"/>
       <c r="K323" s="1"/>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
@@ -20529,17 +20536,23 @@
       <c r="W323" s="1"/>
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A324" s="1"/>
-      <c r="B324" s="1"/>
-      <c r="C324" s="1"/>
+      <c r="A324" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="D324" s="1" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>866</v>
+        <v>1269</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>915</v>
@@ -20548,10 +20561,10 @@
         <v>54</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>867</v>
+        <v>578</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>868</v>
+        <v>1270</v>
       </c>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
@@ -20572,25 +20585,25 @@
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1" t="s">
-        <v>381</v>
+        <v>143</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>69</v>
+        <v>865</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>925</v>
+        <v>866</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H325" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>583</v>
+        <v>867</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>906</v>
+        <v>868</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -20617,10 +20630,10 @@
         <v>69</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1271</v>
+        <v>925</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="H326" s="1" t="s">
         <v>54</v>
@@ -20628,7 +20641,9 @@
       <c r="I326" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="J326" s="1"/>
+      <c r="J326" s="1" t="s">
+        <v>906</v>
+      </c>
       <c r="K326" s="1"/>
       <c r="L326" s="1"/>
       <c r="M326" s="1"/>
@@ -20648,22 +20663,22 @@
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1" t="s">
-        <v>624</v>
+        <v>381</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>873</v>
+        <v>69</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>874</v>
+        <v>1271</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>875</v>
+        <v>583</v>
       </c>
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
@@ -20685,26 +20700,24 @@
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
       <c r="D328" s="1" t="s">
-        <v>516</v>
+        <v>624</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="J328" s="1" t="s">
-        <v>879</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="J328" s="1"/>
       <c r="K328" s="1"/>
       <c r="L328" s="1"/>
       <c r="M328" s="1"/>
@@ -20720,46 +20733,34 @@
       <c r="W328" s="1"/>
     </row>
     <row r="329" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A329" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>951</v>
-      </c>
+      <c r="A329" s="1"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
       <c r="D329" s="1" t="s">
-        <v>464</v>
+        <v>516</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1272</v>
+        <v>877</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1273</v>
+        <v>914</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>728</v>
+        <v>562</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>588</v>
+        <v>878</v>
       </c>
       <c r="J329" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="K329" s="1"/>
-      <c r="L329" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M329" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="N329" s="1" t="s">
-        <v>1274</v>
-      </c>
+      <c r="L329" s="1"/>
+      <c r="M329" s="1"/>
+      <c r="N329" s="1"/>
       <c r="O329" s="1"/>
       <c r="P329" s="1"/>
       <c r="Q329" s="1"/>
@@ -20771,37 +20772,45 @@
       <c r="W329" s="1"/>
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A330" s="1"/>
-      <c r="B330" s="1"/>
-      <c r="C330" s="1"/>
+      <c r="A330" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>951</v>
+      </c>
       <c r="D330" s="1" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>924</v>
+        <v>880</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>844</v>
+        <v>1273</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>923</v>
+        <v>728</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J330" s="1"/>
+        <v>588</v>
+      </c>
+      <c r="J330" s="1" t="s">
+        <v>881</v>
+      </c>
       <c r="K330" s="1"/>
       <c r="L330" s="1" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="M330" s="1" t="s">
-        <v>924</v>
+        <v>880</v>
       </c>
       <c r="N330" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="O330" s="1"/>
       <c r="P330" s="1"/>
@@ -20814,35 +20823,38 @@
       <c r="W330" s="1"/>
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A331" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>1278</v>
-      </c>
+      <c r="A331" s="1"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
       <c r="D331" s="1" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>62</v>
+        <v>924</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>912</v>
+        <v>844</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>562</v>
+        <v>923</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>577</v>
       </c>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
+      <c r="L331" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M331" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="N331" s="1" t="s">
+        <v>1276</v>
+      </c>
       <c r="O331" s="1"/>
       <c r="P331" s="1"/>
       <c r="Q331" s="1"/>
@@ -20854,49 +20866,38 @@
       <c r="W331" s="1"/>
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A332" s="1"/>
-      <c r="B332" s="1"/>
-      <c r="C332" s="1"/>
+      <c r="A332" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>1278</v>
+      </c>
       <c r="D332" s="1" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>410</v>
+        <v>62</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>928</v>
+        <v>1277</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J332" s="1" t="s">
-        <v>851</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="J332" s="1"/>
       <c r="K332" s="1"/>
-      <c r="L332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M332" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="N332" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="O332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P332" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q332" s="1" t="s">
-        <v>595</v>
-      </c>
+      <c r="O332" s="1"/>
+      <c r="P332" s="1"/>
+      <c r="Q332" s="1"/>
       <c r="R332" s="1"/>
       <c r="S332" s="1"/>
       <c r="T332" s="1"/>
@@ -20905,41 +20906,49 @@
       <c r="W332" s="1"/>
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A333" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>882</v>
-      </c>
+      <c r="A333" s="1"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
       <c r="D333" s="1" t="s">
-        <v>464</v>
+        <v>35</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>883</v>
+        <v>410</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>881</v>
+        <v>928</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>1273</v>
+        <v>915</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>728</v>
+        <v>54</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J333" s="1"/>
+        <v>583</v>
+      </c>
+      <c r="J333" s="1" t="s">
+        <v>851</v>
+      </c>
       <c r="K333" s="1"/>
-      <c r="L333" s="1"/>
-      <c r="M333" s="1"/>
-      <c r="N333" s="1"/>
-      <c r="O333" s="1"/>
-      <c r="P333" s="1"/>
-      <c r="Q333" s="1"/>
+      <c r="L333" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M333" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N333" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="O333" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P333" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q333" s="1" t="s">
+        <v>595</v>
+      </c>
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
       <c r="T333" s="1"/>
@@ -20948,26 +20957,32 @@
       <c r="W333" s="1"/>
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A334" s="1"/>
-      <c r="B334" s="1"/>
-      <c r="C334" s="1"/>
+      <c r="A334" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>882</v>
+      </c>
       <c r="D334" s="1" t="s">
-        <v>685</v>
+        <v>464</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>707</v>
+        <v>883</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>926</v>
+        <v>881</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>912</v>
+        <v>1273</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>562</v>
+        <v>728</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>927</v>
+        <v>588</v>
       </c>
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
@@ -20985,85 +21000,85 @@
       <c r="W334" s="1"/>
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1" t="s">
-        <v>476</v>
+        <v>685</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>482</v>
+        <v>707</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>852</v>
+        <v>926</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>1284</v>
+        <v>912</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>54</v>
+        <v>562</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="J335" s="1" t="s">
-        <v>1093</v>
-      </c>
+        <v>927</v>
+      </c>
+      <c r="J335" s="1"/>
+      <c r="K335" s="1"/>
+      <c r="L335" s="1"/>
+      <c r="M335" s="1"/>
+      <c r="N335" s="1"/>
+      <c r="O335" s="1"/>
+      <c r="P335" s="1"/>
+      <c r="Q335" s="1"/>
+      <c r="R335" s="1"/>
+      <c r="S335" s="1"/>
+      <c r="T335" s="1"/>
+      <c r="U335" s="1"/>
+      <c r="V335" s="1"/>
+      <c r="W335" s="1"/>
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1" t="s">
-        <v>835</v>
+        <v>476</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>885</v>
+        <v>482</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>921</v>
+        <v>852</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>911</v>
+        <v>1284</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>1130</v>
+        <v>54</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J336" s="1"/>
-      <c r="K336" s="1"/>
-      <c r="L336" s="1"/>
-      <c r="M336" s="1"/>
-      <c r="N336" s="1"/>
-      <c r="O336" s="1"/>
-      <c r="P336" s="1"/>
-      <c r="Q336" s="1"/>
-      <c r="R336" s="1"/>
-      <c r="S336" s="1"/>
-      <c r="T336" s="1"/>
-      <c r="U336" s="1"/>
-      <c r="V336" s="1"/>
-      <c r="W336" s="1"/>
+        <v>1083</v>
+      </c>
+      <c r="J336" s="1" t="s">
+        <v>1093</v>
+      </c>
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1" t="s">
-        <v>884</v>
+        <v>835</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>887</v>
+        <v>921</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>561</v>
+        <v>1130</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>577</v>
@@ -21088,22 +21103,22 @@
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1" t="s">
-        <v>723</v>
+        <v>884</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
@@ -21125,13 +21140,13 @@
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1" t="s">
-        <v>891</v>
+        <v>723</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>908</v>
@@ -21140,7 +21155,7 @@
         <v>54</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
@@ -21168,7 +21183,7 @@
         <v>892</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>908</v>
@@ -21199,32 +21214,28 @@
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1" t="s">
-        <v>568</v>
+        <v>891</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>568</v>
+        <v>892</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>568</v>
+        <v>893</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>1146</v>
+        <v>908</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I341" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>588</v>
+      </c>
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
-      <c r="L341" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="M341" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="N341" s="1" t="s">
-        <v>895</v>
-      </c>
+      <c r="L341" s="1"/>
+      <c r="M341" s="1"/>
+      <c r="N341" s="1"/>
       <c r="O341" s="1"/>
       <c r="P341" s="1"/>
       <c r="Q341" s="1"/>
@@ -21240,13 +21251,13 @@
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
       <c r="D342" s="1" t="s">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>1146</v>
@@ -21258,13 +21269,13 @@
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
       <c r="L342" s="1" t="s">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="M342" s="1" t="s">
-        <v>894</v>
+        <v>568</v>
       </c>
       <c r="N342" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="O342" s="1"/>
       <c r="P342" s="1"/>
@@ -21281,13 +21292,13 @@
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
       <c r="D343" s="1" t="s">
-        <v>571</v>
+        <v>894</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>571</v>
+        <v>894</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>571</v>
+        <v>894</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>1146</v>
@@ -21299,13 +21310,13 @@
       <c r="J343" s="1"/>
       <c r="K343" s="1"/>
       <c r="L343" s="1" t="s">
-        <v>571</v>
+        <v>894</v>
       </c>
       <c r="M343" s="1" t="s">
-        <v>571</v>
+        <v>894</v>
       </c>
       <c r="N343" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="O343" s="1"/>
       <c r="P343" s="1"/>
@@ -21322,16 +21333,16 @@
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
       <c r="D344" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1279</v>
+        <v>1146</v>
       </c>
       <c r="H344" s="1" t="s">
         <v>1147</v>
@@ -21340,13 +21351,13 @@
       <c r="J344" s="1"/>
       <c r="K344" s="1"/>
       <c r="L344" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M344" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N344" s="1" t="s">
-        <v>576</v>
+        <v>897</v>
       </c>
       <c r="O344" s="1"/>
       <c r="P344" s="1"/>
@@ -21358,175 +21369,216 @@
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
     </row>
+    <row r="345" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A345" s="1"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G345" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H345" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I345" s="1"/>
+      <c r="J345" s="1"/>
+      <c r="K345" s="1"/>
+      <c r="L345" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="M345" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="N345" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="O345" s="1"/>
+      <c r="P345" s="1"/>
+      <c r="Q345" s="1"/>
+      <c r="R345" s="1"/>
+      <c r="S345" s="1"/>
+      <c r="T345" s="1"/>
+      <c r="U345" s="1"/>
+      <c r="V345" s="1"/>
+      <c r="W345" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F310">
-    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="191"/>
+  <conditionalFormatting sqref="F311">
+    <cfRule type="duplicateValues" dxfId="160" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="189"/>
     <cfRule type="duplicateValues" dxfId="133" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="215"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="107" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="160"/>
+  <conditionalFormatting sqref="N311">
+    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T152">
     <cfRule type="duplicateValues" dxfId="54" priority="1"/>
     <cfRule type="duplicateValues" dxfId="53" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
     <cfRule type="duplicateValues" dxfId="26" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0424\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F28C96-FCC8-4F4E-A71D-7C9C4F1EF78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8392933-69F4-4A33-92DA-8A7927D06CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3360" uniqueCount="1338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3368" uniqueCount="1341">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4084,6 +4084,16 @@
   </si>
   <si>
     <t>SC4643VB-Q-DF-40AR-FFH-L43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4933SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4933SO-N-CD-00AR-4933</t>
+  </si>
+  <si>
+    <t>SC4933SO-N-CD-00NR-4933</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6068,7 +6078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}">
-  <dimension ref="A1:W345"/>
+  <dimension ref="A1:W346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
@@ -12265,43 +12275,35 @@
       <c r="W132" s="1"/>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A133" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
       <c r="D133" s="1" t="s">
-        <v>363</v>
+        <v>28</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>370</v>
+        <v>1338</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>371</v>
+        <v>1339</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>561</v>
-      </c>
+        <v>907</v>
+      </c>
+      <c r="H133" s="1"/>
       <c r="I133" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
       <c r="L133" s="1" t="s">
-        <v>363</v>
+        <v>28</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>370</v>
+        <v>1338</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1041</v>
+        <v>1340</v>
       </c>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
@@ -12318,25 +12320,25 @@
         <v>363</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1042</v>
+        <v>371</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>843</v>
+        <v>911</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>922</v>
+        <v>561</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>576</v>
@@ -12347,10 +12349,10 @@
         <v>363</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
@@ -12367,22 +12369,22 @@
         <v>363</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>753</v>
+        <v>320</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>912</v>
+        <v>843</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>922</v>
@@ -12396,10 +12398,10 @@
         <v>363</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>753</v>
+        <v>320</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
@@ -12413,22 +12415,22 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>379</v>
+        <v>753</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>912</v>
@@ -12442,13 +12444,13 @@
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
       <c r="L136" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>379</v>
+        <v>753</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>380</v>
+        <v>1045</v>
       </c>
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
@@ -12462,28 +12464,28 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>60</v>
+        <v>377</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>561</v>
+        <v>922</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>576</v>
@@ -12491,23 +12493,17 @@
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>60</v>
+        <v>379</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="O137" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="P137" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q137" s="1" t="s">
-        <v>1048</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="O137" s="1"/>
+      <c r="P137" s="1"/>
+      <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
@@ -12520,37 +12516,49 @@
         <v>381</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>386</v>
+        <v>60</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>388</v>
+        <v>62</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>389</v>
+        <v>1047</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
-      <c r="L138" s="1"/>
-      <c r="M138" s="1"/>
-      <c r="N138" s="1"/>
-      <c r="O138" s="1"/>
-      <c r="P138" s="1"/>
-      <c r="Q138" s="1"/>
+      <c r="L138" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N138" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="P138" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q138" s="1" t="s">
+        <v>1048</v>
+      </c>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
@@ -12563,40 +12571,34 @@
         <v>381</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1049</v>
+        <v>389</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>922</v>
+        <v>54</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
-      <c r="L139" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="N139" s="1" t="s">
-        <v>1050</v>
-      </c>
+      <c r="L139" s="1"/>
+      <c r="M139" s="1"/>
+      <c r="N139" s="1"/>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
@@ -12608,17 +12610,23 @@
       <c r="W139" s="1"/>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
+      <c r="A140" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="D140" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>843</v>
@@ -12632,23 +12640,17 @@
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="O140" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="P140" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q140" s="1" t="s">
-        <v>1052</v>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="O140" s="1"/>
+      <c r="P140" s="1"/>
+      <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
@@ -12657,52 +12659,46 @@
       <c r="W140" s="1"/>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A141" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>397</v>
-      </c>
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
       <c r="D141" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>399</v>
+        <v>1051</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>561</v>
+        <v>922</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>400</v>
+        <v>776</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="P141" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>401</v>
+        <v>1052</v>
       </c>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
@@ -12712,17 +12708,23 @@
       <c r="W141" s="1"/>
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
+      <c r="A142" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="D142" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>911</v>
@@ -12731,16 +12733,28 @@
         <v>561</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
-      <c r="L142" s="1"/>
-      <c r="M142" s="1"/>
-      <c r="N142" s="1"/>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1"/>
-      <c r="Q142" s="1"/>
+      <c r="L142" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M142" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="P142" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q142" s="1" t="s">
+        <v>401</v>
+      </c>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
@@ -12756,10 +12770,10 @@
         <v>402</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>911</v>
@@ -12772,15 +12786,9 @@
       </c>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
-      <c r="L143" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M143" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="N143" s="1" t="s">
-        <v>595</v>
-      </c>
+      <c r="L143" s="1"/>
+      <c r="M143" s="1"/>
+      <c r="N143" s="1"/>
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
@@ -12792,129 +12800,127 @@
       <c r="W143" s="1"/>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A144" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>409</v>
-      </c>
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
       <c r="D144" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>1053</v>
+        <v>405</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>411</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>407</v>
+        <v>35</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="O144" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P144" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q144" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="R144" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S144" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="T144" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="U144" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="V144" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="W144" s="1" t="s">
-        <v>940</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="O144" s="1"/>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+      <c r="S144" s="1"/>
+      <c r="T144" s="1"/>
+      <c r="U144" s="1"/>
+      <c r="V144" s="1"/>
+      <c r="W144" s="1"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>417</v>
+        <v>410</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>1053</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1056</v>
+        <v>411</v>
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="O145" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P145" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q145" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="R145" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S145" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="T145" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="U145" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="V145" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="W145" s="1" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="M145" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="N145" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="O145" s="1"/>
-      <c r="P145" s="1"/>
-      <c r="Q145" s="1"/>
-      <c r="R145" s="1"/>
-      <c r="S145" s="1"/>
-      <c r="T145" s="1"/>
-      <c r="U145" s="1"/>
-      <c r="V145" s="1"/>
-      <c r="W145" s="1"/>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
+      <c r="B146" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>414</v>
+      </c>
       <c r="D146" s="1" t="s">
         <v>412</v>
       </c>
@@ -12922,13 +12928,13 @@
         <v>415</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1296</v>
+        <v>417</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1297</v>
+        <v>907</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>727</v>
+        <v>54</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>592</v>
@@ -12944,7 +12950,7 @@
         <v>415</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>742</v>
+        <v>416</v>
       </c>
       <c r="O146" s="1"/>
       <c r="P146" s="1"/>
@@ -12957,45 +12963,39 @@
       <c r="W146" s="1"/>
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A147" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>428</v>
-      </c>
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
       <c r="D147" s="1" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>430</v>
+        <v>1296</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>914</v>
+        <v>1297</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>54</v>
+        <v>727</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>592</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>432</v>
+        <v>1056</v>
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="1" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>431</v>
+        <v>742</v>
       </c>
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
@@ -13009,54 +13009,48 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>426</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>977</v>
+        <v>430</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>592</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>825</v>
+        <v>432</v>
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="O148" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="P148" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q148" s="1" t="s">
-        <v>437</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O148" s="1"/>
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
       <c r="T148" s="1"/>
@@ -13065,37 +13059,55 @@
       <c r="W148" s="1"/>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
+      <c r="A149" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>435</v>
+      </c>
       <c r="D149" s="1" t="s">
-        <v>57</v>
+        <v>426</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>52</v>
+        <v>436</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1059</v>
+        <v>977</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>968</v>
+        <v>825</v>
       </c>
       <c r="K149" s="1"/>
-      <c r="L149" s="1"/>
-      <c r="M149" s="1"/>
-      <c r="N149" s="1"/>
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
-      <c r="Q149" s="1"/>
+      <c r="L149" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q149" s="1" t="s">
+        <v>437</v>
+      </c>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
@@ -13108,13 +13120,13 @@
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>914</v>
@@ -13123,21 +13135,15 @@
         <v>54</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>161</v>
+        <v>968</v>
       </c>
       <c r="K150" s="1"/>
-      <c r="L150" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="M150" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N150" s="1" t="s">
-        <v>1061</v>
-      </c>
+      <c r="L150" s="1"/>
+      <c r="M150" s="1"/>
+      <c r="N150" s="1"/>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
@@ -13149,36 +13155,40 @@
       <c r="W150" s="1"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>1064</v>
-      </c>
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
       <c r="D151" s="1" t="s">
-        <v>1062</v>
+        <v>143</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>1063</v>
+        <v>159</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1066</v>
+        <v>914</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="I151" s="1"/>
-      <c r="J151" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="K151" s="1"/>
-      <c r="L151" s="1"/>
-      <c r="M151" s="1"/>
-      <c r="N151" s="1"/>
+      <c r="L151" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>1061</v>
+      </c>
       <c r="O151" s="1"/>
       <c r="P151" s="1"/>
       <c r="Q151" s="1"/>
@@ -13189,116 +13199,106 @@
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>433</v>
+        <v>1062</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>440</v>
+        <v>1063</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>441</v>
+        <v>1064</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>426</v>
+        <v>1062</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>438</v>
+        <v>1063</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>916</v>
+        <v>1066</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="I152" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>824</v>
-      </c>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
       <c r="K152" s="1"/>
-      <c r="L152" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="M152" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="N152" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="O152" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="P152" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="Q152" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="R152" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="S152" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="T152" s="5" t="s">
-        <v>1322</v>
-      </c>
+      <c r="L152" s="1"/>
+      <c r="M152" s="1"/>
+      <c r="N152" s="1"/>
+      <c r="O152" s="1"/>
+      <c r="P152" s="1"/>
+      <c r="Q152" s="1"/>
+      <c r="R152" s="1"/>
+      <c r="S152" s="1"/>
+      <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>727</v>
+        <v>560</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1068</v>
+        <v>824</v>
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="1" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="O153" s="1"/>
-      <c r="P153" s="1"/>
-      <c r="Q153" s="1"/>
-      <c r="R153" s="1"/>
-      <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
+        <v>439</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="P153" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q153" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="R153" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="S153" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="T153" s="5" t="s">
+        <v>1322</v>
+      </c>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
@@ -13308,19 +13308,19 @@
         <v>445</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>918</v>
@@ -13339,10 +13339,10 @@
         <v>445</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
@@ -13359,19 +13359,19 @@
         <v>445</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>918</v>
@@ -13390,10 +13390,10 @@
         <v>445</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
@@ -13410,19 +13410,19 @@
         <v>445</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>651</v>
+        <v>452</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>650</v>
+        <v>453</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>652</v>
+        <v>454</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>918</v>
@@ -13441,10 +13441,10 @@
         <v>445</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>652</v>
+        <v>454</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
@@ -13461,36 +13461,42 @@
         <v>445</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>455</v>
+        <v>651</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>456</v>
+        <v>650</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>457</v>
+        <v>652</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>561</v>
+        <v>727</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>578</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>929</v>
+        <v>1068</v>
       </c>
       <c r="K157" s="1"/>
-      <c r="L157" s="1"/>
-      <c r="M157" s="1"/>
-      <c r="N157" s="1"/>
+      <c r="L157" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="M157" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="N157" s="1" t="s">
+        <v>1075</v>
+      </c>
       <c r="O157" s="1"/>
       <c r="P157" s="1"/>
       <c r="Q157" s="1"/>
@@ -13506,42 +13512,36 @@
         <v>445</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>727</v>
+        <v>561</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>578</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1068</v>
+        <v>929</v>
       </c>
       <c r="K158" s="1"/>
-      <c r="L158" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="M158" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="N158" s="1" t="s">
-        <v>1078</v>
-      </c>
+      <c r="L158" s="1"/>
+      <c r="M158" s="1"/>
+      <c r="N158" s="1"/>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
       <c r="Q158" s="1"/>
@@ -13557,41 +13557,41 @@
         <v>445</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>1079</v>
+        <v>918</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>560</v>
+        <v>727</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>578</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
         <v>445</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>928</v>
+        <v>1078</v>
       </c>
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
@@ -13605,39 +13605,45 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>843</v>
+        <v>1079</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>1081</v>
+        <v>560</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>1082</v>
+        <v>578</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="K160" s="1"/>
-      <c r="L160" s="1"/>
-      <c r="M160" s="1"/>
-      <c r="N160" s="1"/>
+      <c r="L160" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="N160" s="1" t="s">
+        <v>928</v>
+      </c>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
@@ -13653,40 +13659,36 @@
         <v>464</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>807</v>
+        <v>465</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>808</v>
+        <v>466</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>464</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J161" s="1"/>
+        <v>1082</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>1083</v>
+      </c>
       <c r="K161" s="1"/>
-      <c r="L161" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M161" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="N161" s="1" t="s">
-        <v>470</v>
-      </c>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+      <c r="N161" s="1"/>
       <c r="O161" s="1"/>
       <c r="P161" s="1"/>
       <c r="Q161" s="1"/>
@@ -13702,19 +13704,19 @@
         <v>464</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>464</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>907</v>
@@ -13734,7 +13736,7 @@
         <v>469</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="O162" s="1"/>
       <c r="P162" s="1"/>
@@ -13751,10 +13753,10 @@
         <v>464</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>809</v>
+        <v>777</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>810</v>
+        <v>778</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>464</v>
@@ -13763,29 +13765,27 @@
         <v>469</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>1087</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="J163" s="1"/>
       <c r="K163" s="1"/>
       <c r="L163" s="1" t="s">
         <v>464</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>811</v>
+        <v>471</v>
       </c>
       <c r="O163" s="1"/>
       <c r="P163" s="1"/>
@@ -13799,22 +13799,22 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>473</v>
+        <v>809</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>474</v>
+        <v>810</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>843</v>
@@ -13826,17 +13826,17 @@
         <v>1082</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="1" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>756</v>
+        <v>465</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>757</v>
+        <v>811</v>
       </c>
       <c r="O164" s="1"/>
       <c r="P164" s="1"/>
@@ -13850,42 +13850,44 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="J165" s="1"/>
+      <c r="J165" s="1" t="s">
+        <v>1089</v>
+      </c>
       <c r="K165" s="1"/>
       <c r="L165" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>480</v>
+        <v>756</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>487</v>
+        <v>757</v>
       </c>
       <c r="O165" s="1"/>
       <c r="P165" s="1"/>
@@ -13902,22 +13904,22 @@
         <v>476</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>829</v>
+        <v>907</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>54</v>
@@ -13925,18 +13927,16 @@
       <c r="I166" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="J166" s="1" t="s">
-        <v>1284</v>
-      </c>
+      <c r="J166" s="1"/>
       <c r="K166" s="1"/>
       <c r="L166" s="1" t="s">
         <v>476</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>851</v>
+        <v>487</v>
       </c>
       <c r="O166" s="1"/>
       <c r="P166" s="1"/>
@@ -13953,10 +13953,10 @@
         <v>476</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>476</v>
@@ -13965,22 +13965,30 @@
         <v>482</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>911</v>
+        <v>829</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J167" s="1"/>
+        <v>1082</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>1284</v>
+      </c>
       <c r="K167" s="1"/>
-      <c r="L167" s="1"/>
-      <c r="M167" s="1"/>
-      <c r="N167" s="1"/>
+      <c r="L167" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="M167" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="N167" s="1" t="s">
+        <v>851</v>
+      </c>
       <c r="O167" s="1"/>
       <c r="P167" s="1"/>
       <c r="Q167" s="1"/>
@@ -13996,25 +14004,25 @@
         <v>476</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>1093</v>
@@ -14039,28 +14047,28 @@
         <v>476</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1095</v>
+        <v>478</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>967</v>
+        <v>476</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
@@ -14078,30 +14086,34 @@
       <c r="W169" s="1"/>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A170" s="1"/>
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
+      <c r="A170" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>1095</v>
+      </c>
       <c r="D170" s="1" t="s">
-        <v>476</v>
+        <v>967</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>843</v>
+        <v>911</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>1081</v>
+        <v>561</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="J170" s="1" t="s">
-        <v>1096</v>
-      </c>
+      <c r="J170" s="1"/>
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="1"/>
@@ -14117,15 +14129,9 @@
       <c r="W170" s="1"/>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A171" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>490</v>
-      </c>
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
       <c r="D171" s="1" t="s">
         <v>476</v>
       </c>
@@ -14133,7 +14139,7 @@
         <v>491</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>843</v>
@@ -14166,19 +14172,19 @@
         <v>476</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>843</v>
@@ -14187,10 +14193,10 @@
         <v>1081</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
@@ -14211,30 +14217,32 @@
         <v>476</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1103</v>
+        <v>493</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>561</v>
+        <v>1081</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="J173" s="1"/>
+        <v>1101</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>1102</v>
+      </c>
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
@@ -14250,30 +14258,34 @@
       <c r="W173" s="1"/>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
+      <c r="A174" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>1103</v>
+      </c>
       <c r="D174" s="1" t="s">
-        <v>967</v>
+        <v>476</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>754</v>
+        <v>495</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>843</v>
+        <v>911</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>1081</v>
+        <v>561</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>1104</v>
-      </c>
+        <v>1097</v>
+      </c>
+      <c r="J174" s="1"/>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
@@ -14289,23 +14301,17 @@
       <c r="W174" s="1"/>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A175" s="1" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>1330</v>
-      </c>
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
       <c r="D175" s="1" t="s">
         <v>967</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>496</v>
+        <v>754</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>843</v>
@@ -14320,95 +14326,97 @@
         <v>1104</v>
       </c>
       <c r="K175" s="1"/>
-      <c r="L175" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="M175" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="N175" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="O175" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="P175" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q175" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="R175" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="S175" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="T175" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="U175" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="V175" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="W175" s="1" t="s">
-        <v>975</v>
-      </c>
+      <c r="L175" s="1"/>
+      <c r="M175" s="1"/>
+      <c r="N175" s="1"/>
+      <c r="O175" s="1"/>
+      <c r="P175" s="1"/>
+      <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+      <c r="S175" s="1"/>
+      <c r="T175" s="1"/>
+      <c r="U175" s="1"/>
+      <c r="V175" s="1"/>
+      <c r="W175" s="1"/>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D176" s="1" t="s">
+      <c r="M176" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="N176" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="O176" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="E176" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="H176" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
-      <c r="L176" s="1"/>
-      <c r="M176" s="1"/>
-      <c r="N176" s="1"/>
-      <c r="O176" s="1"/>
-      <c r="P176" s="1"/>
-      <c r="Q176" s="1"/>
-      <c r="R176" s="1"/>
-      <c r="S176" s="1"/>
-      <c r="T176" s="1"/>
-      <c r="U176" s="1"/>
-      <c r="V176" s="1"/>
-      <c r="W176" s="1"/>
+      <c r="P176" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q176" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="R176" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="S176" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="T176" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="U176" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="V176" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="W176" s="1" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>476</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>802</v>
+        <v>498</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>804</v>
+        <v>1108</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>476</v>
@@ -14417,20 +14425,18 @@
         <v>498</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>843</v>
+        <v>911</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>1081</v>
+        <v>561</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>1109</v>
-      </c>
+        <v>1097</v>
+      </c>
+      <c r="J177" s="1"/>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
@@ -14453,16 +14459,16 @@
         <v>802</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>843</v>
@@ -14477,24 +14483,12 @@
         <v>1109</v>
       </c>
       <c r="K178" s="1"/>
-      <c r="L178" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="M178" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="N178" s="1" t="s">
-        <v>966</v>
-      </c>
-      <c r="O178" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="P178" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q178" s="1" t="s">
-        <v>1337</v>
-      </c>
+      <c r="L178" s="1"/>
+      <c r="M178" s="1"/>
+      <c r="N178" s="1"/>
+      <c r="O178" s="1"/>
+      <c r="P178" s="1"/>
+      <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
       <c r="T178" s="1"/>
@@ -14504,22 +14498,22 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>1336</v>
+        <v>476</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>498</v>
+        <v>802</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1335</v>
+        <v>803</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>974</v>
+        <v>1111</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>843</v>
@@ -14531,139 +14525,153 @@
         <v>1101</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1" t="s">
-        <v>476</v>
+        <v>967</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>501</v>
+        <v>966</v>
       </c>
       <c r="O179" s="1" t="s">
         <v>476</v>
       </c>
       <c r="P179" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="R179" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="S179" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="T179" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="U179" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="V179" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="W179" s="1" t="s">
-        <v>1115</v>
-      </c>
+        <v>1337</v>
+      </c>
+      <c r="R179" s="1"/>
+      <c r="S179" s="1"/>
+      <c r="T179" s="1"/>
+      <c r="U179" s="1"/>
+      <c r="V179" s="1"/>
+      <c r="W179" s="1"/>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>605</v>
+        <v>1336</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>606</v>
+        <v>498</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>607</v>
+        <v>1335</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>605</v>
+        <v>476</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>608</v>
+        <v>498</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1116</v>
+        <v>974</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>561</v>
+        <v>1081</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>587</v>
+        <v>1101</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>838</v>
+        <v>1112</v>
       </c>
       <c r="K180" s="1"/>
       <c r="L180" s="1" t="s">
-        <v>605</v>
+        <v>476</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>608</v>
+        <v>500</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>645</v>
+        <v>501</v>
       </c>
       <c r="O180" s="1" t="s">
-        <v>605</v>
+        <v>476</v>
       </c>
       <c r="P180" s="1" t="s">
-        <v>606</v>
+        <v>498</v>
       </c>
       <c r="Q180" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="R180" s="1"/>
-      <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
-      <c r="U180" s="1"/>
-      <c r="V180" s="1"/>
-      <c r="W180" s="1"/>
+        <v>1113</v>
+      </c>
+      <c r="R180" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="S180" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="T180" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="U180" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="V180" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="W180" s="1" t="s">
+        <v>1115</v>
+      </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>515</v>
+        <v>605</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>516</v>
+        <v>606</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>517</v>
+        <v>607</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>515</v>
+        <v>605</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>522</v>
+        <v>608</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="J181" s="1"/>
+        <v>587</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>838</v>
+      </c>
       <c r="K181" s="1"/>
-      <c r="L181" s="1"/>
-      <c r="M181" s="1"/>
-      <c r="N181" s="1"/>
-      <c r="O181" s="1"/>
-      <c r="P181" s="1"/>
-      <c r="Q181" s="1"/>
+      <c r="L181" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="M181" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="N181" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="O181" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="P181" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q181" s="1" t="s">
+        <v>814</v>
+      </c>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -14676,32 +14684,30 @@
         <v>515</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>515</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="J182" s="1" t="s">
-        <v>953</v>
-      </c>
+      <c r="J182" s="1"/>
       <c r="K182" s="1"/>
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
@@ -14721,30 +14727,32 @@
         <v>515</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>515</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="J183" s="1"/>
+      <c r="J183" s="1" t="s">
+        <v>953</v>
+      </c>
       <c r="K183" s="1"/>
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
@@ -14764,10 +14772,10 @@
         <v>515</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>836</v>
+        <v>520</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>837</v>
+        <v>521</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>515</v>
@@ -14776,20 +14784,18 @@
         <v>524</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>1122</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="J184" s="1"/>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
@@ -14809,19 +14815,19 @@
         <v>515</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>525</v>
+        <v>836</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>526</v>
+        <v>837</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>515</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>843</v>
@@ -14830,10 +14836,10 @@
         <v>1081</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>578</v>
+        <v>1121</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
@@ -14851,33 +14857,35 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J186" s="1"/>
+        <v>578</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>1124</v>
+      </c>
       <c r="K186" s="1"/>
       <c r="L186" s="1"/>
       <c r="M186" s="1"/>
@@ -14897,28 +14905,28 @@
         <v>528</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
@@ -14937,22 +14945,22 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>909</v>
@@ -14980,138 +14988,144 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>273</v>
+        <v>536</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>270</v>
+        <v>538</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1129</v>
+        <v>560</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
-      <c r="L189" s="1" t="s">
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+      <c r="N189" s="1"/>
+      <c r="O189" s="1"/>
+      <c r="P189" s="1"/>
+      <c r="Q189" s="1"/>
+      <c r="R189" s="1"/>
+      <c r="S189" s="1"/>
+      <c r="T189" s="1"/>
+      <c r="U189" s="1"/>
+      <c r="V189" s="1"/>
+      <c r="W189" s="1"/>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A190" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="M189" s="1" t="s">
+      <c r="B190" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="N189" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="O189" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="P189" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q189" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="R189" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="S189" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="T189" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="U189" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="V189" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="W189" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>1063</v>
-      </c>
       <c r="F190" s="1" t="s">
-        <v>1332</v>
+        <v>1128</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="H190" s="1"/>
+        <v>910</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>1129</v>
+      </c>
       <c r="I190" s="1" t="s">
-        <v>1334</v>
+        <v>576</v>
       </c>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
       <c r="L190" s="1" t="s">
-        <v>1062</v>
+        <v>539</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>1063</v>
+        <v>270</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="O190" s="1"/>
-      <c r="P190" s="1"/>
-      <c r="Q190" s="1"/>
-      <c r="R190" s="1"/>
-      <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
-      <c r="U190" s="1"/>
-      <c r="V190" s="1"/>
-      <c r="W190" s="1"/>
+        <v>541</v>
+      </c>
+      <c r="O190" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="P190" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q190" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="R190" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="S190" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="T190" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="U190" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="V190" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="W190" s="1" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1" t="s">
-        <v>962</v>
+        <v>1062</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>963</v>
+        <v>1063</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="G191" s="1"/>
+        <v>1332</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>1333</v>
+      </c>
       <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
+      <c r="I191" s="1" t="s">
+        <v>1334</v>
+      </c>
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
       <c r="L191" s="1" t="s">
-        <v>962</v>
+        <v>1062</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>963</v>
+        <v>1063</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>1130</v>
+        <v>1065</v>
       </c>
       <c r="O191" s="1"/>
       <c r="P191" s="1"/>
@@ -15124,40 +15138,32 @@
       <c r="W191" s="1"/>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A192" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>545</v>
-      </c>
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
       <c r="D192" s="1" t="s">
-        <v>543</v>
+        <v>962</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>278</v>
+        <v>963</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J192" s="1" t="s">
-        <v>1132</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
       <c r="K192" s="1"/>
-      <c r="L192" s="1"/>
-      <c r="M192" s="1"/>
-      <c r="N192" s="1"/>
+      <c r="L192" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="M192" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="N192" s="1" t="s">
+        <v>1130</v>
+      </c>
       <c r="O192" s="1"/>
       <c r="P192" s="1"/>
       <c r="Q192" s="1"/>
@@ -15169,9 +15175,15 @@
       <c r="W192" s="1"/>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
+      <c r="A193" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>545</v>
+      </c>
       <c r="D193" s="1" t="s">
         <v>543</v>
       </c>
@@ -15179,7 +15191,7 @@
         <v>278</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>907</v>
@@ -15208,15 +15220,9 @@
       <c r="W193" s="1"/>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A194" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>547</v>
-      </c>
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
       <c r="D194" s="1" t="s">
         <v>543</v>
       </c>
@@ -15224,7 +15230,7 @@
         <v>278</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>907</v>
@@ -15233,9 +15239,11 @@
         <v>54</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J194" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>1132</v>
+      </c>
       <c r="K194" s="1"/>
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
@@ -15252,13 +15260,13 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>269</v>
+        <v>543</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>631</v>
+        <v>547</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>543</v>
@@ -15267,7 +15275,7 @@
         <v>278</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>907</v>
@@ -15278,9 +15286,7 @@
       <c r="I195" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="J195" s="1" t="s">
-        <v>1132</v>
-      </c>
+      <c r="J195" s="1"/>
       <c r="K195" s="1"/>
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
@@ -15297,13 +15303,13 @@
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>543</v>
+        <v>269</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>546</v>
+        <v>631</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>543</v>
@@ -15312,7 +15318,7 @@
         <v>278</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>907</v>
@@ -15345,19 +15351,19 @@
         <v>543</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>1136</v>
+        <v>546</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>543</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>871</v>
+        <v>1135</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>907</v>
@@ -15366,28 +15372,18 @@
         <v>54</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J197" s="1"/>
+        <v>579</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>1132</v>
+      </c>
       <c r="K197" s="1"/>
-      <c r="L197" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="M197" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="N197" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="O197" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="P197" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q197" s="1" t="s">
-        <v>1137</v>
-      </c>
+      <c r="L197" s="1"/>
+      <c r="M197" s="1"/>
+      <c r="N197" s="1"/>
+      <c r="O197" s="1"/>
+      <c r="P197" s="1"/>
+      <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
@@ -15397,22 +15393,22 @@
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>442</v>
+        <v>543</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>549</v>
+        <v>273</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>550</v>
+        <v>1136</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>442</v>
+        <v>543</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>1138</v>
+        <v>871</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>907</v>
@@ -15421,27 +15417,27 @@
         <v>54</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="J198" s="1"/>
       <c r="K198" s="1"/>
       <c r="L198" s="1" t="s">
-        <v>442</v>
+        <v>543</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>444</v>
+        <v>548</v>
       </c>
       <c r="O198" s="1" t="s">
-        <v>442</v>
+        <v>543</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="Q198" s="1" t="s">
-        <v>743</v>
+        <v>1137</v>
       </c>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
@@ -15455,25 +15451,25 @@
         <v>442</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>816</v>
+        <v>550</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>442</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>551</v>
+        <v>443</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>552</v>
+        <v>1138</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>592</v>
@@ -15484,14 +15480,20 @@
         <v>442</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>551</v>
+        <v>443</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="O199" s="1"/>
-      <c r="P199" s="1"/>
-      <c r="Q199" s="1"/>
+        <v>444</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="P199" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q199" s="1" t="s">
+        <v>743</v>
+      </c>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
       <c r="T199" s="1"/>
@@ -15507,22 +15509,22 @@
         <v>553</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>554</v>
+        <v>816</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>442</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1140</v>
+        <v>552</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>592</v>
@@ -15533,10 +15535,10 @@
         <v>442</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="O200" s="1"/>
       <c r="P200" s="1"/>
@@ -15549,34 +15551,44 @@
       <c r="W200" s="1"/>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A201" s="1"/>
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
+      <c r="A201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>554</v>
+      </c>
       <c r="D201" s="1" t="s">
-        <v>557</v>
+        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>1143</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="J201" s="1"/>
       <c r="K201" s="1"/>
-      <c r="L201" s="1"/>
-      <c r="M201" s="1"/>
-      <c r="N201" s="1"/>
+      <c r="L201" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="M201" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="N201" s="1" t="s">
+        <v>1141</v>
+      </c>
       <c r="O201" s="1"/>
       <c r="P201" s="1"/>
       <c r="Q201" s="1"/>
@@ -15598,7 +15610,7 @@
         <v>559</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>843</v>
@@ -15631,24 +15643,26 @@
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>569</v>
+        <v>1144</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1145</v>
+        <v>843</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1146</v>
+        <v>1081</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="J203" s="1"/>
+        <v>578</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>1143</v>
+      </c>
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
@@ -15668,13 +15682,13 @@
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>1145</v>
@@ -15705,13 +15719,13 @@
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>1145</v>
@@ -15719,7 +15733,9 @@
       <c r="H205" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="I205" s="1"/>
+      <c r="I205" s="1" t="s">
+        <v>588</v>
+      </c>
       <c r="J205" s="1"/>
       <c r="K205" s="1"/>
       <c r="L205" s="1"/>
@@ -15740,34 +15756,26 @@
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1" t="s">
-        <v>300</v>
+        <v>573</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>323</v>
+        <v>574</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1147</v>
+        <v>575</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>907</v>
+        <v>1145</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>593</v>
-      </c>
+        <v>1146</v>
+      </c>
+      <c r="I206" s="1"/>
       <c r="J206" s="1"/>
       <c r="K206" s="1"/>
-      <c r="L206" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="M206" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="N206" s="1" t="s">
-        <v>598</v>
-      </c>
+      <c r="L206" s="1"/>
+      <c r="M206" s="1"/>
+      <c r="N206" s="1"/>
       <c r="O206" s="1"/>
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
@@ -15779,38 +15787,38 @@
       <c r="W206" s="1"/>
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A207" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>617</v>
-      </c>
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
       <c r="D207" s="1" t="s">
-        <v>528</v>
+        <v>300</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>618</v>
+        <v>323</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="J207" s="1"/>
       <c r="K207" s="1"/>
-      <c r="L207" s="1"/>
-      <c r="M207" s="1"/>
-      <c r="N207" s="1"/>
+      <c r="L207" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="M207" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="N207" s="1" t="s">
+        <v>598</v>
+      </c>
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
       <c r="Q207" s="1"/>
@@ -15823,22 +15831,22 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>619</v>
+        <v>528</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>619</v>
+        <v>528</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>909</v>
@@ -15851,15 +15859,9 @@
       </c>
       <c r="J208" s="1"/>
       <c r="K208" s="1"/>
-      <c r="L208" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="M208" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="N208" s="1" t="s">
-        <v>726</v>
-      </c>
+      <c r="L208" s="1"/>
+      <c r="M208" s="1"/>
+      <c r="N208" s="1"/>
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
@@ -15872,25 +15874,25 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>560</v>
@@ -15900,9 +15902,15 @@
       </c>
       <c r="J209" s="1"/>
       <c r="K209" s="1"/>
-      <c r="L209" s="1"/>
-      <c r="M209" s="1"/>
-      <c r="N209" s="1"/>
+      <c r="L209" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="M209" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="N209" s="1" t="s">
+        <v>726</v>
+      </c>
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
       <c r="Q209" s="1"/>
@@ -15915,43 +15923,37 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>626</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>859</v>
+        <v>1150</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>560</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="J210" s="1"/>
       <c r="K210" s="1"/>
-      <c r="L210" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="M210" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="N210" s="1" t="s">
-        <v>1151</v>
-      </c>
+      <c r="L210" s="1"/>
+      <c r="M210" s="1"/>
+      <c r="N210" s="1"/>
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
       <c r="Q210" s="1"/>
@@ -15963,37 +15965,43 @@
       <c r="W210" s="1"/>
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A211" s="1"/>
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
+      <c r="A211" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>628</v>
+      </c>
       <c r="D211" s="1" t="s">
-        <v>35</v>
+        <v>626</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>934</v>
+        <v>629</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>933</v>
+        <v>859</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="J211" s="1"/>
       <c r="K211" s="1"/>
       <c r="L211" s="1" t="s">
-        <v>35</v>
+        <v>626</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>934</v>
+        <v>629</v>
       </c>
       <c r="N211" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="O211" s="1"/>
       <c r="P211" s="1"/>
@@ -16006,23 +16014,17 @@
       <c r="W211" s="1"/>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A212" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>634</v>
-      </c>
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
       <c r="D212" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>635</v>
+        <v>934</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>1153</v>
+        <v>933</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>907</v>
@@ -16039,72 +16041,78 @@
         <v>35</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>633</v>
+        <v>934</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="O212" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P212" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="Q212" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="R212" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S212" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="T212" s="1" t="s">
-        <v>1154</v>
-      </c>
+        <v>1152</v>
+      </c>
+      <c r="O212" s="1"/>
+      <c r="P212" s="1"/>
+      <c r="Q212" s="1"/>
+      <c r="R212" s="1"/>
+      <c r="S212" s="1"/>
+      <c r="T212" s="1"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
+      <c r="A213" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>634</v>
+      </c>
       <c r="D213" s="1" t="s">
-        <v>845</v>
+        <v>35</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>637</v>
+        <v>1153</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>926</v>
+        <v>576</v>
       </c>
       <c r="J213" s="1"/>
       <c r="K213" s="1"/>
       <c r="L213" s="1" t="s">
-        <v>845</v>
+        <v>35</v>
       </c>
       <c r="M213" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="O213" s="1"/>
-      <c r="P213" s="1"/>
-      <c r="Q213" s="1"/>
-      <c r="R213" s="1"/>
-      <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
+        <v>767</v>
+      </c>
+      <c r="O213" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P213" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q213" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="R213" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S213" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="T213" s="1" t="s">
+        <v>1154</v>
+      </c>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
@@ -16114,30 +16122,34 @@
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1" t="s">
-        <v>638</v>
+        <v>845</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1156</v>
+        <v>637</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J214" s="1" t="s">
-        <v>1157</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="J214" s="1"/>
       <c r="K214" s="1"/>
-      <c r="L214" s="1"/>
-      <c r="M214" s="1"/>
-      <c r="N214" s="1"/>
+      <c r="L214" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="M214" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="N214" s="1" t="s">
+        <v>1155</v>
+      </c>
       <c r="O214" s="1"/>
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
@@ -16156,10 +16168,10 @@
         <v>638</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>914</v>
@@ -16195,10 +16207,10 @@
         <v>638</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>771</v>
+        <v>640</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>914</v>
@@ -16227,35 +16239,29 @@
       <c r="W216" s="1"/>
     </row>
     <row r="217" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A217" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>643</v>
-      </c>
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
       <c r="D217" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>644</v>
+        <v>771</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>843</v>
+        <v>914</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="K217" s="1"/>
       <c r="L217" s="1"/>
@@ -16272,38 +16278,40 @@
       <c r="W217" s="1"/>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A218" s="1"/>
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
+      <c r="A218" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>643</v>
+      </c>
       <c r="D218" s="1" t="s">
-        <v>442</v>
+        <v>641</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>908</v>
+        <v>843</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>727</v>
+        <v>1081</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J218" s="1"/>
+        <v>578</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>1161</v>
+      </c>
       <c r="K218" s="1"/>
-      <c r="L218" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="M218" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="N218" s="1" t="s">
-        <v>1163</v>
-      </c>
+      <c r="L218" s="1"/>
+      <c r="M218" s="1"/>
+      <c r="N218" s="1"/>
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
       <c r="Q218" s="1"/>
@@ -16315,38 +16323,38 @@
       <c r="W218" s="1"/>
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A219" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>655</v>
-      </c>
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
       <c r="D219" s="1" t="s">
-        <v>657</v>
+        <v>442</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>54</v>
+        <v>727</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="J219" s="1"/>
       <c r="K219" s="1"/>
-      <c r="L219" s="1"/>
-      <c r="M219" s="1"/>
-      <c r="N219" s="1"/>
+      <c r="L219" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="M219" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="N219" s="1" t="s">
+        <v>1163</v>
+      </c>
       <c r="O219" s="1"/>
       <c r="P219" s="1"/>
       <c r="Q219" s="1"/>
@@ -16359,22 +16367,22 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>657</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>907</v>
@@ -16401,30 +16409,34 @@
       <c r="W220" s="1"/>
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A221" s="1"/>
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
+      <c r="A221" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>659</v>
+      </c>
       <c r="D221" s="1" t="s">
-        <v>502</v>
+        <v>657</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>503</v>
+        <v>660</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>1168</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="J221" s="1"/>
       <c r="K221" s="1"/>
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
@@ -16447,10 +16459,10 @@
         <v>502</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>508</v>
+        <v>1166</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>843</v>
@@ -16486,10 +16498,10 @@
         <v>502</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>662</v>
+        <v>508</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>662</v>
+        <v>508</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>843</v>
@@ -16525,10 +16537,10 @@
         <v>502</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>843</v>
@@ -16564,10 +16576,10 @@
         <v>502</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>843</v>
@@ -16603,10 +16615,10 @@
         <v>502</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>843</v>
@@ -16642,10 +16654,10 @@
         <v>502</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>843</v>
@@ -16681,10 +16693,10 @@
         <v>502</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>504</v>
+        <v>666</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1328</v>
+        <v>666</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>843</v>
@@ -16696,18 +16708,12 @@
         <v>1167</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>1329</v>
+        <v>1168</v>
       </c>
       <c r="K228" s="1"/>
-      <c r="L228" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="M228" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="N228" s="1" t="s">
-        <v>1169</v>
-      </c>
+      <c r="L228" s="1"/>
+      <c r="M228" s="1"/>
+      <c r="N228" s="1"/>
       <c r="O228" s="1"/>
       <c r="P228" s="1"/>
       <c r="Q228" s="1"/>
@@ -16726,10 +16732,10 @@
         <v>502</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>667</v>
+        <v>504</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>667</v>
+        <v>1328</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>843</v>
@@ -16741,12 +16747,18 @@
         <v>1167</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1168</v>
+        <v>1329</v>
       </c>
       <c r="K229" s="1"/>
-      <c r="L229" s="1"/>
-      <c r="M229" s="1"/>
-      <c r="N229" s="1"/>
+      <c r="L229" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="M229" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="N229" s="1" t="s">
+        <v>1169</v>
+      </c>
       <c r="O229" s="1"/>
       <c r="P229" s="1"/>
       <c r="Q229" s="1"/>
@@ -16765,10 +16777,10 @@
         <v>502</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>509</v>
+        <v>667</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>509</v>
+        <v>667</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>843</v>
@@ -16804,10 +16816,10 @@
         <v>502</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>843</v>
@@ -16843,10 +16855,10 @@
         <v>502</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>843</v>
@@ -16882,10 +16894,10 @@
         <v>502</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>668</v>
+        <v>511</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>668</v>
+        <v>511</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>843</v>
@@ -16921,10 +16933,10 @@
         <v>502</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>843</v>
@@ -16960,10 +16972,10 @@
         <v>502</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>843</v>
@@ -16999,10 +17011,10 @@
         <v>502</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>843</v>
@@ -17038,10 +17050,10 @@
         <v>502</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>512</v>
+        <v>661</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>512</v>
+        <v>661</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>843</v>
@@ -17077,10 +17089,10 @@
         <v>502</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>843</v>
@@ -17109,23 +17121,17 @@
       <c r="W238" s="1"/>
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A239" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>690</v>
-      </c>
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
       <c r="D239" s="1" t="s">
         <v>502</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>718</v>
+        <v>513</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1170</v>
+        <v>513</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>843</v>
@@ -17158,40 +17164,36 @@
         <v>502</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>505</v>
+        <v>689</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>506</v>
+        <v>690</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>502</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>507</v>
+        <v>718</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J240" s="1"/>
+        <v>1167</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>1168</v>
+      </c>
       <c r="K240" s="1"/>
-      <c r="L240" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="M240" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="N240" s="1" t="s">
-        <v>1172</v>
-      </c>
+      <c r="L240" s="1"/>
+      <c r="M240" s="1"/>
+      <c r="N240" s="1"/>
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
       <c r="Q240" s="1"/>
@@ -17210,7 +17212,7 @@
         <v>505</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>502</v>
@@ -17219,7 +17221,7 @@
         <v>507</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>907</v>
@@ -17239,7 +17241,7 @@
         <v>507</v>
       </c>
       <c r="N241" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="O241" s="1"/>
       <c r="P241" s="1"/>
@@ -17252,17 +17254,23 @@
       <c r="W241" s="1"/>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A242" s="1"/>
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
+      <c r="A242" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>514</v>
+      </c>
       <c r="D242" s="1" t="s">
-        <v>106</v>
+        <v>502</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>671</v>
+        <v>507</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>907</v>
@@ -17271,15 +17279,19 @@
         <v>54</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="J242" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="J242" s="1"/>
       <c r="K242" s="1"/>
-      <c r="L242" s="1"/>
-      <c r="M242" s="1"/>
-      <c r="N242" s="1"/>
+      <c r="L242" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="M242" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="N242" s="1" t="s">
+        <v>1174</v>
+      </c>
       <c r="O242" s="1"/>
       <c r="P242" s="1"/>
       <c r="Q242" s="1"/>
@@ -17295,25 +17307,25 @@
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1" t="s">
-        <v>959</v>
+        <v>106</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>960</v>
+        <v>671</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>961</v>
+        <v>1175</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>958</v>
+        <v>907</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1176</v>
+        <v>54</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>1177</v>
+        <v>579</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>957</v>
+        <v>124</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -17330,29 +17342,29 @@
       <c r="W243" s="1"/>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A244" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="D244" s="1"/>
-      <c r="E244" s="1"/>
-      <c r="F244" s="1"/>
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>961</v>
+      </c>
       <c r="G244" s="1" t="s">
-        <v>843</v>
+        <v>958</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>1081</v>
+        <v>1176</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>587</v>
+        <v>1177</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>1178</v>
+        <v>957</v>
       </c>
       <c r="K244" s="1"/>
       <c r="L244" s="1"/>
@@ -17369,36 +17381,34 @@
       <c r="W244" s="1"/>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A245" s="1"/>
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
-      <c r="D245" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E245" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F245" s="1" t="s">
-        <v>1317</v>
-      </c>
+      <c r="A245" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
       <c r="G245" s="1" t="s">
-        <v>1320</v>
-      </c>
-      <c r="H245" s="1"/>
+        <v>843</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>1081</v>
+      </c>
       <c r="I245" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J245" s="1"/>
+        <v>587</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>1178</v>
+      </c>
       <c r="K245" s="1"/>
-      <c r="L245" s="1" t="s">
-        <v>1311</v>
-      </c>
-      <c r="M245" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="N245" s="1" t="s">
-        <v>1313</v>
-      </c>
+      <c r="L245" s="1"/>
+      <c r="M245" s="1"/>
+      <c r="N245" s="1"/>
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
@@ -17417,10 +17427,10 @@
         <v>35</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>1320</v>
@@ -17435,10 +17445,10 @@
         <v>1311</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="N246" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="O246" s="1"/>
       <c r="P246" s="1"/>
@@ -17451,53 +17461,39 @@
       <c r="W246" s="1"/>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A247" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>676</v>
-      </c>
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
       <c r="D247" s="1" t="s">
-        <v>605</v>
+        <v>35</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>841</v>
+        <v>1318</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>840</v>
+        <v>1319</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1179</v>
-      </c>
-      <c r="H247" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="I247" s="1"/>
-      <c r="J247" s="1" t="s">
-        <v>839</v>
-      </c>
+        <v>1320</v>
+      </c>
+      <c r="H247" s="1"/>
+      <c r="I247" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="J247" s="1"/>
       <c r="K247" s="1"/>
       <c r="L247" s="1" t="s">
-        <v>605</v>
+        <v>1311</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>675</v>
+        <v>1314</v>
       </c>
       <c r="N247" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="O247" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="P247" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="Q247" s="1" t="s">
-        <v>1180</v>
-      </c>
+        <v>1315</v>
+      </c>
+      <c r="O247" s="1"/>
+      <c r="P247" s="1"/>
+      <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
       <c r="T247" s="1"/>
@@ -17507,40 +17503,52 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>763</v>
+        <v>676</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>679</v>
+        <v>841</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>680</v>
+        <v>840</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>919</v>
+        <v>1179</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="I248" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="J248" s="1"/>
+        <v>727</v>
+      </c>
+      <c r="I248" s="1"/>
+      <c r="J248" s="1" t="s">
+        <v>839</v>
+      </c>
       <c r="K248" s="1"/>
-      <c r="L248" s="1"/>
-      <c r="M248" s="1"/>
-      <c r="N248" s="1"/>
-      <c r="O248" s="1"/>
-      <c r="P248" s="1"/>
-      <c r="Q248" s="1"/>
+      <c r="L248" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="M248" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="N248" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="O248" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="P248" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q248" s="1" t="s">
+        <v>1180</v>
+      </c>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
       <c r="T248" s="1"/>
@@ -17550,17 +17558,23 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>543</v>
+        <v>679</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>681</v>
+        <v>626</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="D249" s="1"/>
-      <c r="E249" s="1"/>
-      <c r="F249" s="1"/>
+        <v>763</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>680</v>
+      </c>
       <c r="G249" s="1" t="s">
         <v>919</v>
       </c>
@@ -17568,7 +17582,7 @@
         <v>560</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -17586,26 +17600,26 @@
       <c r="W249" s="1"/>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A250" s="1"/>
-      <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-      <c r="D250" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>1183</v>
-      </c>
+      <c r="A250" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
       <c r="G250" s="1" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>576</v>
+        <v>1182</v>
       </c>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
@@ -17627,13 +17641,13 @@
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1" t="s">
-        <v>684</v>
+        <v>35</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>907</v>
@@ -17642,7 +17656,7 @@
         <v>54</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J251" s="1"/>
       <c r="K251" s="1"/>
@@ -17664,13 +17678,13 @@
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>907</v>
@@ -17679,7 +17693,7 @@
         <v>54</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="J252" s="1"/>
       <c r="K252" s="1"/>
@@ -17697,26 +17711,26 @@
       <c r="W252" s="1"/>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A253" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="D253" s="1"/>
-      <c r="E253" s="1"/>
-      <c r="F253" s="1"/>
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>1185</v>
+      </c>
       <c r="G253" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
@@ -17734,40 +17748,32 @@
       <c r="W253" s="1"/>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A254" s="1"/>
-      <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-      <c r="D254" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E254" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="F254" s="1" t="s">
-        <v>1186</v>
-      </c>
+      <c r="A254" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>727</v>
+        <v>561</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J254" s="1" t="s">
-        <v>846</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="J254" s="1"/>
       <c r="K254" s="1"/>
-      <c r="L254" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="M254" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="N254" s="1" t="s">
-        <v>1187</v>
-      </c>
+      <c r="L254" s="1"/>
+      <c r="M254" s="1"/>
+      <c r="N254" s="1"/>
       <c r="O254" s="1"/>
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
@@ -17783,28 +17789,36 @@
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>54</v>
+        <v>727</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="J255" s="1"/>
+      <c r="J255" s="1" t="s">
+        <v>846</v>
+      </c>
       <c r="K255" s="1"/>
-      <c r="L255" s="1"/>
-      <c r="M255" s="1"/>
-      <c r="N255" s="1"/>
+      <c r="L255" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="M255" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="N255" s="1" t="s">
+        <v>1187</v>
+      </c>
       <c r="O255" s="1"/>
       <c r="P255" s="1"/>
       <c r="Q255" s="1"/>
@@ -17816,23 +17830,17 @@
       <c r="W255" s="1"/>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A256" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>695</v>
-      </c>
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
       <c r="D256" s="1" t="s">
-        <v>693</v>
+        <v>426</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>694</v>
+        <v>429</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>907</v>
@@ -17841,7 +17849,7 @@
         <v>54</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1190</v>
+        <v>592</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -17860,25 +17868,31 @@
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="D257" s="1"/>
-      <c r="E257" s="1"/>
-      <c r="F257" s="1"/>
+        <v>695</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>1189</v>
+      </c>
       <c r="G257" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>1101</v>
+        <v>1190</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -17897,31 +17911,25 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>789</v>
+        <v>697</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E258" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="F258" s="1" t="s">
-        <v>1191</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
       <c r="G258" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>584</v>
+        <v>1101</v>
       </c>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -17939,17 +17947,23 @@
       <c r="W258" s="1"/>
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A259" s="1"/>
-      <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
+      <c r="A259" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>790</v>
+      </c>
       <c r="D259" s="1" t="s">
-        <v>143</v>
+        <v>699</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>907</v>
@@ -17958,7 +17972,7 @@
         <v>54</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
@@ -17980,13 +17994,13 @@
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1" t="s">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>907</v>
@@ -17995,7 +18009,7 @@
         <v>54</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
@@ -18017,19 +18031,19 @@
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>576</v>
@@ -18057,16 +18071,16 @@
         <v>300</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>316</v>
+        <v>703</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>576</v>
@@ -18087,23 +18101,17 @@
       <c r="W262" s="1"/>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A263" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>799</v>
-      </c>
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
       <c r="D263" s="1" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>388</v>
+        <v>316</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>907</v>
@@ -18130,26 +18138,32 @@
       <c r="W263" s="1"/>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A264" s="1"/>
-      <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
+      <c r="A264" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>799</v>
+      </c>
       <c r="D264" s="1" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>704</v>
+        <v>388</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -18174,10 +18188,10 @@
         <v>35</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>911</v>
@@ -18186,7 +18200,7 @@
         <v>561</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -18211,19 +18225,19 @@
         <v>35</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>398</v>
+        <v>705</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -18245,22 +18259,22 @@
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
       <c r="D267" s="1" t="s">
-        <v>684</v>
+        <v>35</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>706</v>
+        <v>398</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>926</v>
+        <v>579</v>
       </c>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
@@ -18282,13 +18296,13 @@
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
       <c r="D268" s="1" t="s">
-        <v>599</v>
+        <v>684</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>911</v>
@@ -18297,7 +18311,7 @@
         <v>561</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>584</v>
+        <v>926</v>
       </c>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
@@ -18322,10 +18336,10 @@
         <v>599</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>911</v>
@@ -18352,23 +18366,17 @@
       <c r="W269" s="1"/>
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A270" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>710</v>
-      </c>
+      <c r="A270" s="1"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
       <c r="D270" s="1" t="s">
-        <v>212</v>
+        <v>599</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>973</v>
+        <v>708</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>911</v>
@@ -18377,19 +18385,13 @@
         <v>561</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>1182</v>
+        <v>584</v>
       </c>
       <c r="J270" s="1"/>
       <c r="K270" s="1"/>
-      <c r="L270" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M270" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="N270" s="1" t="s">
-        <v>972</v>
-      </c>
+      <c r="L270" s="1"/>
+      <c r="M270" s="1"/>
+      <c r="N270" s="1"/>
       <c r="O270" s="1"/>
       <c r="P270" s="1"/>
       <c r="Q270" s="1"/>
@@ -18402,17 +18404,23 @@
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>638</v>
+        <v>212</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="D271" s="1"/>
-      <c r="E271" s="1"/>
-      <c r="F271" s="1"/>
+        <v>710</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>1203</v>
+      </c>
       <c r="G271" s="1" t="s">
         <v>911</v>
       </c>
@@ -18420,13 +18428,19 @@
         <v>561</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>586</v>
+        <v>1182</v>
       </c>
       <c r="J271" s="1"/>
       <c r="K271" s="1"/>
-      <c r="L271" s="1"/>
-      <c r="M271" s="1"/>
-      <c r="N271" s="1"/>
+      <c r="L271" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M271" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="N271" s="1" t="s">
+        <v>972</v>
+      </c>
       <c r="O271" s="1"/>
       <c r="P271" s="1"/>
       <c r="Q271" s="1"/>
@@ -18438,26 +18452,26 @@
       <c r="W271" s="1"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A272" s="1"/>
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
-      <c r="D272" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E272" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="F272" s="1" t="s">
-        <v>1204</v>
-      </c>
+      <c r="A272" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
       <c r="G272" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J272" s="1"/>
       <c r="K272" s="1"/>
@@ -18475,36 +18489,28 @@
       <c r="W272" s="1"/>
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A273" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>813</v>
-      </c>
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
       <c r="D273" s="1" t="s">
-        <v>605</v>
+        <v>464</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>713</v>
+        <v>469</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="J273" s="1" t="s">
-        <v>838</v>
-      </c>
+      <c r="J273" s="1"/>
       <c r="K273" s="1"/>
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
@@ -18520,28 +18526,36 @@
       <c r="W273" s="1"/>
     </row>
     <row r="274" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A274" s="1"/>
-      <c r="B274" s="1"/>
-      <c r="C274" s="1"/>
+      <c r="A274" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>813</v>
+      </c>
       <c r="D274" s="1" t="s">
         <v>605</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1207</v>
+        <v>911</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="J274" s="1"/>
+      <c r="J274" s="1" t="s">
+        <v>838</v>
+      </c>
       <c r="K274" s="1"/>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
@@ -18564,10 +18578,10 @@
         <v>605</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>1207</v>
@@ -18598,22 +18612,22 @@
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>911</v>
+        <v>1207</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
@@ -18635,22 +18649,22 @@
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1" t="s">
-        <v>722</v>
+        <v>646</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="J277" s="1"/>
       <c r="K277" s="1"/>
@@ -18672,26 +18686,24 @@
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1" t="s">
-        <v>691</v>
+        <v>722</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="J278" s="1" t="s">
-        <v>1212</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="J278" s="1"/>
       <c r="K278" s="1"/>
       <c r="L278" s="1"/>
       <c r="M278" s="1"/>
@@ -18711,36 +18723,30 @@
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1" t="s">
-        <v>724</v>
+        <v>691</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>725</v>
+        <v>692</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>843</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1190</v>
+        <v>1167</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>852</v>
+        <v>1212</v>
       </c>
       <c r="K279" s="1"/>
-      <c r="L279" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="M279" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="N279" s="1" t="s">
-        <v>863</v>
-      </c>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+      <c r="N279" s="1"/>
       <c r="O279" s="1"/>
       <c r="P279" s="1"/>
       <c r="Q279" s="1"/>
@@ -18756,28 +18762,36 @@
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1" t="s">
-        <v>570</v>
+        <v>724</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1145</v>
+        <v>843</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>1146</v>
+        <v>54</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="J280" s="1"/>
+        <v>1190</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="K280" s="1"/>
-      <c r="L280" s="1"/>
-      <c r="M280" s="1"/>
-      <c r="N280" s="1"/>
+      <c r="L280" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="M280" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="N280" s="1" t="s">
+        <v>863</v>
+      </c>
       <c r="O280" s="1"/>
       <c r="P280" s="1"/>
       <c r="Q280" s="1"/>
@@ -18793,26 +18807,24 @@
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1" t="s">
-        <v>745</v>
+        <v>570</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>930</v>
+        <v>1214</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>914</v>
+        <v>1145</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>54</v>
+        <v>1146</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J281" s="1" t="s">
-        <v>931</v>
-      </c>
+        <v>1215</v>
+      </c>
+      <c r="J281" s="1"/>
       <c r="K281" s="1"/>
       <c r="L281" s="1"/>
       <c r="M281" s="1"/>
@@ -18835,10 +18847,10 @@
         <v>745</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1216</v>
+        <v>930</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>914</v>
@@ -18847,10 +18859,10 @@
         <v>54</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>866</v>
+        <v>581</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>1217</v>
+        <v>931</v>
       </c>
       <c r="K282" s="1"/>
       <c r="L282" s="1"/>
@@ -18871,36 +18883,30 @@
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1" t="s">
-        <v>179</v>
+        <v>745</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>849</v>
+        <v>1216</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>582</v>
+        <v>866</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>830</v>
+        <v>1217</v>
       </c>
       <c r="K283" s="1"/>
-      <c r="L283" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M283" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="N283" s="1" t="s">
-        <v>848</v>
-      </c>
+      <c r="L283" s="1"/>
+      <c r="M283" s="1"/>
+      <c r="N283" s="1"/>
       <c r="O283" s="1"/>
       <c r="P283" s="1"/>
       <c r="Q283" s="1"/>
@@ -18916,13 +18922,13 @@
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>982</v>
+        <v>749</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>984</v>
+        <v>849</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>907</v>
@@ -18933,16 +18939,18 @@
       <c r="I284" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="J284" s="1"/>
+      <c r="J284" s="1" t="s">
+        <v>830</v>
+      </c>
       <c r="K284" s="1"/>
       <c r="L284" s="1" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="M284" s="1" t="s">
-        <v>982</v>
+        <v>749</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>983</v>
+        <v>848</v>
       </c>
       <c r="O284" s="1"/>
       <c r="P284" s="1"/>
@@ -18959,33 +18967,33 @@
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
       <c r="D285" s="1" t="s">
-        <v>856</v>
+        <v>49</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>270</v>
+        <v>982</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="J285" s="1"/>
       <c r="K285" s="1"/>
       <c r="L285" s="1" t="s">
-        <v>856</v>
+        <v>49</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>270</v>
+        <v>982</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>1218</v>
+        <v>983</v>
       </c>
       <c r="O285" s="1"/>
       <c r="P285" s="1"/>
@@ -18998,101 +19006,107 @@
       <c r="W285" s="1"/>
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A286" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="A286" s="1"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
       <c r="D286" s="1" t="s">
-        <v>291</v>
+        <v>856</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>755</v>
+        <v>987</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>843</v>
+        <v>909</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1081</v>
+        <v>560</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J286" s="1" t="s">
-        <v>1219</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="J286" s="1"/>
       <c r="K286" s="1"/>
       <c r="L286" s="1" t="s">
-        <v>684</v>
+        <v>856</v>
       </c>
       <c r="M286" s="1" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="O286" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="P286" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q286" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="R286" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="S286" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T286" s="1" t="s">
-        <v>906</v>
-      </c>
+        <v>1218</v>
+      </c>
+      <c r="O286" s="1"/>
+      <c r="P286" s="1"/>
+      <c r="Q286" s="1"/>
+      <c r="R286" s="1"/>
+      <c r="S286" s="1"/>
+      <c r="T286" s="1"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
     </row>
     <row r="287" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A287" s="1"/>
-      <c r="B287" s="1"/>
-      <c r="C287" s="1"/>
+      <c r="A287" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="D287" s="1" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>752</v>
+        <v>294</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1221</v>
+        <v>755</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J287" s="1"/>
+        <v>578</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>1219</v>
+      </c>
       <c r="K287" s="1"/>
-      <c r="L287" s="1"/>
-      <c r="M287" s="1"/>
-      <c r="N287" s="1"/>
-      <c r="O287" s="1"/>
-      <c r="P287" s="1"/>
-      <c r="Q287" s="1"/>
-      <c r="R287" s="1"/>
-      <c r="S287" s="1"/>
-      <c r="T287" s="1"/>
+      <c r="L287" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="M287" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N287" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="O287" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="P287" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q287" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="R287" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S287" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T287" s="1" t="s">
+        <v>906</v>
+      </c>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
@@ -19102,34 +19116,28 @@
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>331</v>
+        <v>752</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>922</v>
+        <v>54</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
-      <c r="L288" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M288" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="N288" s="1" t="s">
-        <v>1223</v>
-      </c>
+      <c r="L288" s="1"/>
+      <c r="M288" s="1"/>
+      <c r="N288" s="1"/>
       <c r="O288" s="1"/>
       <c r="P288" s="1"/>
       <c r="Q288" s="1"/>
@@ -19145,28 +19153,34 @@
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1" t="s">
-        <v>476</v>
+        <v>363</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>754</v>
+        <v>331</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>843</v>
+        <v>912</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>1081</v>
+        <v>922</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J289" s="1"/>
       <c r="K289" s="1"/>
-      <c r="L289" s="1"/>
-      <c r="M289" s="1"/>
-      <c r="N289" s="1"/>
+      <c r="L289" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M289" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="N289" s="1" t="s">
+        <v>1223</v>
+      </c>
       <c r="O289" s="1"/>
       <c r="P289" s="1"/>
       <c r="Q289" s="1"/>
@@ -19182,22 +19196,22 @@
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>443</v>
+        <v>754</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>54</v>
+        <v>1081</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="J290" s="1"/>
       <c r="K290" s="1"/>
@@ -19219,34 +19233,28 @@
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1" t="s">
-        <v>339</v>
+        <v>442</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>758</v>
+        <v>443</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>922</v>
+        <v>54</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
-      <c r="L291" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="M291" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="N291" s="1" t="s">
-        <v>1227</v>
-      </c>
+      <c r="L291" s="1"/>
+      <c r="M291" s="1"/>
+      <c r="N291" s="1"/>
       <c r="O291" s="1"/>
       <c r="P291" s="1"/>
       <c r="Q291" s="1"/>
@@ -19262,33 +19270,33 @@
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>54</v>
+        <v>922</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
       <c r="L292" s="1" t="s">
-        <v>35</v>
+        <v>339</v>
       </c>
       <c r="M292" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N292" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="O292" s="1"/>
       <c r="P292" s="1"/>
@@ -19305,30 +19313,34 @@
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
-        <v>476</v>
+        <v>35</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1231</v>
+        <v>907</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J293" s="1" t="s">
-        <v>974</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J293" s="1"/>
       <c r="K293" s="1"/>
-      <c r="L293" s="1"/>
-      <c r="M293" s="1"/>
-      <c r="N293" s="1"/>
+      <c r="L293" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M293" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="N293" s="1" t="s">
+        <v>1229</v>
+      </c>
       <c r="O293" s="1"/>
       <c r="P293" s="1"/>
       <c r="Q293" s="1"/>
@@ -19344,24 +19356,26 @@
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
       <c r="D294" s="1" t="s">
-        <v>745</v>
+        <v>476</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>907</v>
+        <v>1231</v>
       </c>
       <c r="H294" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J294" s="1"/>
+        <v>1101</v>
+      </c>
+      <c r="J294" s="1" t="s">
+        <v>974</v>
+      </c>
       <c r="K294" s="1"/>
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
@@ -19384,23 +19398,21 @@
         <v>745</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J295" s="1" t="s">
-        <v>1234</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="J295" s="1"/>
       <c r="K295" s="1"/>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
@@ -19420,24 +19432,26 @@
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
       <c r="D296" s="1" t="s">
-        <v>98</v>
+        <v>745</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H296" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J296" s="1"/>
+        <v>577</v>
+      </c>
+      <c r="J296" s="1" t="s">
+        <v>1234</v>
+      </c>
       <c r="K296" s="1"/>
       <c r="L296" s="1"/>
       <c r="M296" s="1"/>
@@ -19453,38 +19467,32 @@
       <c r="W296" s="1"/>
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A297" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>986</v>
-      </c>
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
       <c r="D297" s="1" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>985</v>
+        <v>766</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G297" s="1"/>
-      <c r="H297" s="1"/>
-      <c r="I297" s="1"/>
+        <v>1235</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="H297" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I297" s="1" t="s">
+        <v>581</v>
+      </c>
       <c r="J297" s="1"/>
       <c r="K297" s="1"/>
-      <c r="L297" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M297" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="N297" s="1" t="s">
-        <v>1237</v>
-      </c>
+      <c r="L297" s="1"/>
+      <c r="M297" s="1"/>
+      <c r="N297" s="1"/>
       <c r="O297" s="1"/>
       <c r="P297" s="1"/>
       <c r="Q297" s="1"/>
@@ -19497,39 +19505,37 @@
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>745</v>
+        <v>43</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>761</v>
+        <v>985</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>1238</v>
+        <v>986</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>745</v>
+        <v>43</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>932</v>
+        <v>985</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>914</v>
-      </c>
-      <c r="H298" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I298" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="J298" s="1" t="s">
-        <v>1240</v>
-      </c>
+        <v>1236</v>
+      </c>
+      <c r="G298" s="1"/>
+      <c r="H298" s="1"/>
+      <c r="I298" s="1"/>
+      <c r="J298" s="1"/>
       <c r="K298" s="1"/>
-      <c r="L298" s="1"/>
-      <c r="M298" s="1"/>
-      <c r="N298" s="1"/>
+      <c r="L298" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M298" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="N298" s="1" t="s">
+        <v>1237</v>
+      </c>
       <c r="O298" s="1"/>
       <c r="P298" s="1"/>
       <c r="Q298" s="1"/>
@@ -19541,28 +19547,36 @@
       <c r="W298" s="1"/>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A299" s="1"/>
-      <c r="B299" s="1"/>
-      <c r="C299" s="1"/>
+      <c r="A299" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>1238</v>
+      </c>
       <c r="D299" s="1" t="s">
-        <v>696</v>
+        <v>745</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>768</v>
+        <v>932</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>561</v>
+        <v>54</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J299" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="J299" s="1" t="s">
+        <v>1240</v>
+      </c>
       <c r="K299" s="1"/>
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
@@ -19582,22 +19596,22 @@
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
       <c r="D300" s="1" t="s">
-        <v>769</v>
+        <v>696</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>576</v>
+        <v>1101</v>
       </c>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
@@ -19619,21 +19633,23 @@
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
       <c r="D301" s="1" t="s">
-        <v>212</v>
+        <v>769</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>772</v>
+        <v>1242</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="I301" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I301" s="1" t="s">
+        <v>576</v>
+      </c>
       <c r="J301" s="1"/>
       <c r="K301" s="1"/>
       <c r="L301" s="1"/>
@@ -19650,36 +19666,26 @@
       <c r="W301" s="1"/>
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A302" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>774</v>
-      </c>
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
       <c r="D302" s="1" t="s">
-        <v>300</v>
+        <v>212</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>335</v>
+        <v>772</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1243</v>
+        <v>772</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I302" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J302" s="1" t="s">
-        <v>338</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="I302" s="1"/>
+      <c r="J302" s="1"/>
       <c r="K302" s="1"/>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
@@ -19696,43 +19702,39 @@
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>391</v>
+        <v>774</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>67</v>
+        <v>335</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>922</v>
+        <v>54</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="J303" s="1"/>
+      <c r="J303" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="K303" s="1"/>
-      <c r="L303" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="M303" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N303" s="1" t="s">
-        <v>941</v>
-      </c>
+      <c r="L303" s="1"/>
+      <c r="M303" s="1"/>
+      <c r="N303" s="1"/>
       <c r="O303" s="1"/>
       <c r="P303" s="1"/>
       <c r="Q303" s="1"/>
@@ -19745,39 +19747,43 @@
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>49</v>
+        <v>390</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>784</v>
+        <v>65</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>785</v>
+        <v>391</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>49</v>
+        <v>390</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>765</v>
+        <v>67</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>914</v>
+        <v>843</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>54</v>
+        <v>922</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="J304" s="1" t="s">
-        <v>1246</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="J304" s="1"/>
       <c r="K304" s="1"/>
-      <c r="L304" s="1"/>
-      <c r="M304" s="1"/>
-      <c r="N304" s="1"/>
+      <c r="L304" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="M304" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N304" s="1" t="s">
+        <v>941</v>
+      </c>
       <c r="O304" s="1"/>
       <c r="P304" s="1"/>
       <c r="Q304" s="1"/>
@@ -19790,43 +19796,39 @@
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>788</v>
+        <v>765</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="H305" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J305" s="1"/>
+        <v>581</v>
+      </c>
+      <c r="J305" s="1" t="s">
+        <v>1246</v>
+      </c>
       <c r="K305" s="1"/>
-      <c r="L305" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M305" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="N305" s="1" t="s">
-        <v>1248</v>
-      </c>
+      <c r="L305" s="1"/>
+      <c r="M305" s="1"/>
+      <c r="N305" s="1"/>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
@@ -19838,32 +19840,44 @@
       <c r="W305" s="1"/>
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A306" s="1"/>
-      <c r="B306" s="1"/>
-      <c r="C306" s="1"/>
+      <c r="A306" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>787</v>
+      </c>
       <c r="D306" s="1" t="s">
-        <v>502</v>
+        <v>57</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>817</v>
+        <v>788</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>817</v>
+        <v>1247</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>1081</v>
+        <v>54</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>1167</v>
+        <v>582</v>
       </c>
       <c r="J306" s="1"/>
       <c r="K306" s="1"/>
-      <c r="L306" s="1"/>
-      <c r="M306" s="1"/>
-      <c r="N306" s="1"/>
+      <c r="L306" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M306" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="N306" s="1" t="s">
+        <v>1248</v>
+      </c>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
@@ -19879,36 +19893,28 @@
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>897</v>
+        <v>817</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1307</v>
+        <v>817</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>561</v>
+        <v>1081</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J307" s="1" t="s">
-        <v>838</v>
-      </c>
+        <v>1167</v>
+      </c>
+      <c r="J307" s="1"/>
       <c r="K307" s="1"/>
-      <c r="L307" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="M307" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="N307" s="1" t="s">
-        <v>898</v>
-      </c>
+      <c r="L307" s="1"/>
+      <c r="M307" s="1"/>
+      <c r="N307" s="1"/>
       <c r="O307" s="1"/>
       <c r="P307" s="1"/>
       <c r="Q307" s="1"/>
@@ -19927,10 +19933,10 @@
         <v>605</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>818</v>
+        <v>897</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1295</v>
+        <v>1307</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>911</v>
@@ -19949,10 +19955,10 @@
         <v>605</v>
       </c>
       <c r="M308" s="1" t="s">
-        <v>818</v>
+        <v>897</v>
       </c>
       <c r="N308" s="1" t="s">
-        <v>1249</v>
+        <v>898</v>
       </c>
       <c r="O308" s="1"/>
       <c r="P308" s="1"/>
@@ -19969,26 +19975,36 @@
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1" t="s">
-        <v>819</v>
+        <v>605</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1250</v>
+        <v>1295</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1145</v>
+        <v>911</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I309" s="1"/>
-      <c r="J309" s="1"/>
+        <v>561</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="J309" s="1" t="s">
+        <v>838</v>
+      </c>
       <c r="K309" s="1"/>
-      <c r="L309" s="1"/>
-      <c r="M309" s="1"/>
-      <c r="N309" s="1"/>
+      <c r="L309" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="M309" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="N309" s="1" t="s">
+        <v>1249</v>
+      </c>
       <c r="O309" s="1"/>
       <c r="P309" s="1"/>
       <c r="Q309" s="1"/>
@@ -20007,10 +20023,10 @@
         <v>819</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>1145</v>
@@ -20034,37 +20050,31 @@
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
     </row>
-    <row r="311" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
-      <c r="D311" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E311" s="5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="F311" s="5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G311" s="5" t="s">
-        <v>907</v>
-      </c>
-      <c r="H311" s="1"/>
-      <c r="I311" s="1" t="s">
-        <v>576</v>
-      </c>
+      <c r="D311" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="F311" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H311" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I311" s="1"/>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
-      <c r="L311" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="M311" s="5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="N311" s="5" t="s">
-        <v>1310</v>
-      </c>
+      <c r="L311" s="1"/>
+      <c r="M311" s="1"/>
+      <c r="N311" s="1"/>
       <c r="O311" s="1"/>
       <c r="P311" s="1"/>
       <c r="Q311" s="1"/>
@@ -20075,31 +20085,37 @@
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
-      <c r="D312" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E312" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="F312" s="1" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G312" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H312" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I312" s="1"/>
+      <c r="D312" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E312" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F312" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G312" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="H312" s="1"/>
+      <c r="I312" s="1" t="s">
+        <v>576</v>
+      </c>
       <c r="J312" s="1"/>
       <c r="K312" s="1"/>
-      <c r="L312" s="1"/>
-      <c r="M312" s="1"/>
-      <c r="N312" s="1"/>
+      <c r="L312" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="M312" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="N312" s="5" t="s">
+        <v>1310</v>
+      </c>
       <c r="O312" s="1"/>
       <c r="P312" s="1"/>
       <c r="Q312" s="1"/>
@@ -20115,26 +20131,22 @@
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1" t="s">
-        <v>515</v>
+        <v>1252</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>843</v>
+        <v>1145</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="I313" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="J313" s="1" t="s">
-        <v>1255</v>
-      </c>
+        <v>1146</v>
+      </c>
+      <c r="I313" s="1"/>
+      <c r="J313" s="1"/>
       <c r="K313" s="1"/>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
@@ -20154,24 +20166,26 @@
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1" t="s">
-        <v>684</v>
+        <v>515</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1256</v>
+        <v>823</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>561</v>
+        <v>1081</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="J314" s="1"/>
+        <v>877</v>
+      </c>
+      <c r="J314" s="1" t="s">
+        <v>1255</v>
+      </c>
       <c r="K314" s="1"/>
       <c r="L314" s="1"/>
       <c r="M314" s="1"/>
@@ -20191,13 +20205,13 @@
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1" t="s">
-        <v>106</v>
+        <v>684</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>114</v>
+        <v>1256</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>911</v>
@@ -20206,19 +20220,13 @@
         <v>561</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>586</v>
+        <v>926</v>
       </c>
       <c r="J315" s="1"/>
       <c r="K315" s="1"/>
-      <c r="L315" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M315" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N315" s="1" t="s">
-        <v>1259</v>
-      </c>
+      <c r="L315" s="1"/>
+      <c r="M315" s="1"/>
+      <c r="N315" s="1"/>
       <c r="O315" s="1"/>
       <c r="P315" s="1"/>
       <c r="Q315" s="1"/>
@@ -20234,30 +20242,34 @@
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>826</v>
+        <v>114</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J316" s="1" t="s">
-        <v>1261</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="J316" s="1"/>
       <c r="K316" s="1"/>
-      <c r="L316" s="1"/>
-      <c r="M316" s="1"/>
-      <c r="N316" s="1"/>
+      <c r="L316" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M316" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N316" s="1" t="s">
+        <v>1259</v>
+      </c>
       <c r="O316" s="1"/>
       <c r="P316" s="1"/>
       <c r="Q316" s="1"/>
@@ -20273,25 +20285,25 @@
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
       <c r="D317" s="1" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>180</v>
+        <v>826</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H317" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J317" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="K317" s="1"/>
       <c r="L317" s="1"/>
@@ -20312,34 +20324,30 @@
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
       <c r="D318" s="1" t="s">
-        <v>831</v>
+        <v>179</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>832</v>
+        <v>180</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J318" s="1"/>
+        <v>581</v>
+      </c>
+      <c r="J318" s="1" t="s">
+        <v>1263</v>
+      </c>
       <c r="K318" s="1"/>
-      <c r="L318" s="1" t="s">
-        <v>1265</v>
-      </c>
-      <c r="M318" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="N318" s="1" t="s">
-        <v>1266</v>
-      </c>
+      <c r="L318" s="1"/>
+      <c r="M318" s="1"/>
+      <c r="N318" s="1"/>
       <c r="O318" s="1"/>
       <c r="P318" s="1"/>
       <c r="Q318" s="1"/>
@@ -20355,13 +20363,13 @@
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>909</v>
@@ -20374,9 +20382,15 @@
       </c>
       <c r="J319" s="1"/>
       <c r="K319" s="1"/>
-      <c r="L319" s="1"/>
-      <c r="M319" s="1"/>
-      <c r="N319" s="1"/>
+      <c r="L319" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="M319" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="N319" s="1" t="s">
+        <v>1266</v>
+      </c>
       <c r="O319" s="1"/>
       <c r="P319" s="1"/>
       <c r="Q319" s="1"/>
@@ -20392,26 +20406,24 @@
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
       <c r="D320" s="1" t="s">
-        <v>421</v>
+        <v>834</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>424</v>
+        <v>835</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>842</v>
+        <v>1267</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>843</v>
+        <v>909</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J320" s="1" t="s">
-        <v>844</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="J320" s="1"/>
       <c r="K320" s="1"/>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
@@ -20427,34 +20439,30 @@
       <c r="W320" s="1"/>
     </row>
     <row r="321" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A321" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B321" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>825</v>
-      </c>
+      <c r="A321" s="1"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
       <c r="D321" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>847</v>
+        <v>424</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>908</v>
+        <v>843</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>727</v>
+        <v>54</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="J321" s="1"/>
+        <v>578</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>844</v>
+      </c>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
@@ -20471,31 +20479,31 @@
     </row>
     <row r="322" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>35</v>
+        <v>433</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>410</v>
+        <v>847</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>410</v>
+        <v>847</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>411</v>
+        <v>846</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>54</v>
+        <v>727</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="J322" s="1"/>
       <c r="K322" s="1"/>
@@ -20513,26 +20521,32 @@
       <c r="W322" s="1"/>
     </row>
     <row r="323" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A323" s="1"/>
-      <c r="B323" s="1"/>
-      <c r="C323" s="1"/>
+      <c r="A323" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>850</v>
+      </c>
       <c r="D323" s="1" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>564</v>
+        <v>410</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>792</v>
+        <v>411</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J323" s="1"/>
       <c r="K323" s="1"/>
@@ -20550,36 +20564,28 @@
       <c r="W323" s="1"/>
     </row>
     <row r="324" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A324" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>854</v>
-      </c>
+      <c r="A324" s="1"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
       <c r="D324" s="1" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>855</v>
+        <v>564</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1268</v>
+        <v>792</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="H324" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J324" s="1" t="s">
-        <v>1269</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="J324" s="1"/>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
@@ -20595,17 +20601,23 @@
       <c r="W324" s="1"/>
     </row>
     <row r="325" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A325" s="1"/>
-      <c r="B325" s="1"/>
-      <c r="C325" s="1"/>
+      <c r="A325" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>854</v>
+      </c>
       <c r="D325" s="1" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>865</v>
+        <v>1268</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>914</v>
@@ -20614,10 +20626,10 @@
         <v>54</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>866</v>
+        <v>577</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>867</v>
+        <v>1269</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -20638,25 +20650,25 @@
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
       <c r="D326" s="1" t="s">
-        <v>381</v>
+        <v>143</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>69</v>
+        <v>864</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>924</v>
+        <v>865</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H326" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>582</v>
+        <v>866</v>
       </c>
       <c r="J326" s="1" t="s">
-        <v>905</v>
+        <v>867</v>
       </c>
       <c r="K326" s="1"/>
       <c r="L326" s="1"/>
@@ -20683,10 +20695,10 @@
         <v>69</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1270</v>
+        <v>924</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="H327" s="1" t="s">
         <v>54</v>
@@ -20694,7 +20706,9 @@
       <c r="I327" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="J327" s="1"/>
+      <c r="J327" s="1" t="s">
+        <v>905</v>
+      </c>
       <c r="K327" s="1"/>
       <c r="L327" s="1"/>
       <c r="M327" s="1"/>
@@ -20714,22 +20728,22 @@
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
       <c r="D328" s="1" t="s">
-        <v>623</v>
+        <v>381</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>872</v>
+        <v>69</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>873</v>
+        <v>1270</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>874</v>
+        <v>582</v>
       </c>
       <c r="J328" s="1"/>
       <c r="K328" s="1"/>
@@ -20751,26 +20765,24 @@
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
       <c r="D329" s="1" t="s">
-        <v>515</v>
+        <v>623</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="J329" s="1" t="s">
-        <v>878</v>
-      </c>
+        <v>874</v>
+      </c>
+      <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
       <c r="M329" s="1"/>
@@ -20786,46 +20798,34 @@
       <c r="W329" s="1"/>
     </row>
     <row r="330" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A330" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>950</v>
-      </c>
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
       <c r="D330" s="1" t="s">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1271</v>
+        <v>876</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1272</v>
+        <v>913</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>727</v>
+        <v>561</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>587</v>
+        <v>877</v>
       </c>
       <c r="J330" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="K330" s="1"/>
-      <c r="L330" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M330" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="N330" s="1" t="s">
-        <v>1273</v>
-      </c>
+      <c r="L330" s="1"/>
+      <c r="M330" s="1"/>
+      <c r="N330" s="1"/>
       <c r="O330" s="1"/>
       <c r="P330" s="1"/>
       <c r="Q330" s="1"/>
@@ -20837,37 +20837,45 @@
       <c r="W330" s="1"/>
     </row>
     <row r="331" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A331" s="1"/>
-      <c r="B331" s="1"/>
-      <c r="C331" s="1"/>
+      <c r="A331" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>950</v>
+      </c>
       <c r="D331" s="1" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>923</v>
+        <v>879</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>843</v>
+        <v>1272</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>922</v>
+        <v>727</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J331" s="1"/>
+        <v>587</v>
+      </c>
+      <c r="J331" s="1" t="s">
+        <v>880</v>
+      </c>
       <c r="K331" s="1"/>
       <c r="L331" s="1" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="M331" s="1" t="s">
-        <v>923</v>
+        <v>879</v>
       </c>
       <c r="N331" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="O331" s="1"/>
       <c r="P331" s="1"/>
@@ -20880,35 +20888,38 @@
       <c r="W331" s="1"/>
     </row>
     <row r="332" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A332" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>1277</v>
-      </c>
+      <c r="A332" s="1"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
       <c r="D332" s="1" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>62</v>
+        <v>923</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>561</v>
+        <v>922</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
+      <c r="L332" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M332" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="N332" s="1" t="s">
+        <v>1275</v>
+      </c>
       <c r="O332" s="1"/>
       <c r="P332" s="1"/>
       <c r="Q332" s="1"/>
@@ -20920,49 +20931,38 @@
       <c r="W332" s="1"/>
     </row>
     <row r="333" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A333" s="1"/>
-      <c r="B333" s="1"/>
-      <c r="C333" s="1"/>
+      <c r="A333" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>1277</v>
+      </c>
       <c r="D333" s="1" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>410</v>
+        <v>62</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>927</v>
+        <v>1276</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J333" s="1" t="s">
-        <v>850</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="J333" s="1"/>
       <c r="K333" s="1"/>
-      <c r="L333" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M333" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="N333" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="O333" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P333" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q333" s="1" t="s">
-        <v>594</v>
-      </c>
+      <c r="O333" s="1"/>
+      <c r="P333" s="1"/>
+      <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
       <c r="T333" s="1"/>
@@ -20971,41 +20971,49 @@
       <c r="W333" s="1"/>
     </row>
     <row r="334" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A334" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>881</v>
-      </c>
+      <c r="A334" s="1"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
       <c r="D334" s="1" t="s">
-        <v>464</v>
+        <v>35</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>882</v>
+        <v>410</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>880</v>
+        <v>927</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>1272</v>
+        <v>914</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>727</v>
+        <v>54</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="J334" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="J334" s="1" t="s">
+        <v>850</v>
+      </c>
       <c r="K334" s="1"/>
-      <c r="L334" s="1"/>
-      <c r="M334" s="1"/>
-      <c r="N334" s="1"/>
-      <c r="O334" s="1"/>
-      <c r="P334" s="1"/>
-      <c r="Q334" s="1"/>
+      <c r="L334" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M334" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N334" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="O334" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P334" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q334" s="1" t="s">
+        <v>594</v>
+      </c>
       <c r="R334" s="1"/>
       <c r="S334" s="1"/>
       <c r="T334" s="1"/>
@@ -21014,26 +21022,32 @@
       <c r="W334" s="1"/>
     </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A335" s="1"/>
-      <c r="B335" s="1"/>
-      <c r="C335" s="1"/>
+      <c r="A335" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>881</v>
+      </c>
       <c r="D335" s="1" t="s">
-        <v>684</v>
+        <v>464</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>706</v>
+        <v>882</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>925</v>
+        <v>880</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>911</v>
+        <v>1272</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>561</v>
+        <v>727</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>926</v>
+        <v>587</v>
       </c>
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
@@ -21051,85 +21065,85 @@
       <c r="W335" s="1"/>
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1" t="s">
-        <v>476</v>
+        <v>684</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>482</v>
+        <v>706</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>851</v>
+        <v>925</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>1283</v>
+        <v>911</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>54</v>
+        <v>561</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="J336" s="1" t="s">
-        <v>1092</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="J336" s="1"/>
+      <c r="K336" s="1"/>
+      <c r="L336" s="1"/>
+      <c r="M336" s="1"/>
+      <c r="N336" s="1"/>
+      <c r="O336" s="1"/>
+      <c r="P336" s="1"/>
+      <c r="Q336" s="1"/>
+      <c r="R336" s="1"/>
+      <c r="S336" s="1"/>
+      <c r="T336" s="1"/>
+      <c r="U336" s="1"/>
+      <c r="V336" s="1"/>
+      <c r="W336" s="1"/>
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1" t="s">
-        <v>834</v>
+        <v>476</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>884</v>
+        <v>482</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>920</v>
+        <v>851</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>910</v>
+        <v>1283</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>1129</v>
+        <v>54</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="J337" s="1"/>
-      <c r="K337" s="1"/>
-      <c r="L337" s="1"/>
-      <c r="M337" s="1"/>
-      <c r="N337" s="1"/>
-      <c r="O337" s="1"/>
-      <c r="P337" s="1"/>
-      <c r="Q337" s="1"/>
-      <c r="R337" s="1"/>
-      <c r="S337" s="1"/>
-      <c r="T337" s="1"/>
-      <c r="U337" s="1"/>
-      <c r="V337" s="1"/>
-      <c r="W337" s="1"/>
+        <v>1082</v>
+      </c>
+      <c r="J337" s="1" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="338" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1" t="s">
-        <v>883</v>
+        <v>834</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>886</v>
+        <v>920</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>560</v>
+        <v>1129</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>576</v>
@@ -21154,22 +21168,22 @@
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1" t="s">
-        <v>722</v>
+        <v>883</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
@@ -21191,13 +21205,13 @@
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1" t="s">
-        <v>890</v>
+        <v>722</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>907</v>
@@ -21206,7 +21220,7 @@
         <v>54</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
@@ -21234,7 +21248,7 @@
         <v>891</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>907</v>
@@ -21265,32 +21279,28 @@
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
       <c r="D342" s="1" t="s">
-        <v>567</v>
+        <v>890</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>567</v>
+        <v>891</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>567</v>
+        <v>892</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1145</v>
+        <v>907</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I342" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>587</v>
+      </c>
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
-      <c r="L342" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="M342" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="N342" s="1" t="s">
-        <v>894</v>
-      </c>
+      <c r="L342" s="1"/>
+      <c r="M342" s="1"/>
+      <c r="N342" s="1"/>
       <c r="O342" s="1"/>
       <c r="P342" s="1"/>
       <c r="Q342" s="1"/>
@@ -21306,13 +21316,13 @@
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
       <c r="D343" s="1" t="s">
-        <v>893</v>
+        <v>567</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>893</v>
+        <v>567</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>893</v>
+        <v>567</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>1145</v>
@@ -21324,13 +21334,13 @@
       <c r="J343" s="1"/>
       <c r="K343" s="1"/>
       <c r="L343" s="1" t="s">
-        <v>893</v>
+        <v>567</v>
       </c>
       <c r="M343" s="1" t="s">
-        <v>893</v>
+        <v>567</v>
       </c>
       <c r="N343" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O343" s="1"/>
       <c r="P343" s="1"/>
@@ -21347,13 +21357,13 @@
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
       <c r="D344" s="1" t="s">
-        <v>570</v>
+        <v>893</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>570</v>
+        <v>893</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>570</v>
+        <v>893</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>1145</v>
@@ -21365,13 +21375,13 @@
       <c r="J344" s="1"/>
       <c r="K344" s="1"/>
       <c r="L344" s="1" t="s">
-        <v>570</v>
+        <v>893</v>
       </c>
       <c r="M344" s="1" t="s">
-        <v>570</v>
+        <v>893</v>
       </c>
       <c r="N344" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="O344" s="1"/>
       <c r="P344" s="1"/>
@@ -21388,16 +21398,16 @@
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
       <c r="D345" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1278</v>
+        <v>1145</v>
       </c>
       <c r="H345" s="1" t="s">
         <v>1146</v>
@@ -21406,13 +21416,13 @@
       <c r="J345" s="1"/>
       <c r="K345" s="1"/>
       <c r="L345" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M345" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="N345" s="1" t="s">
-        <v>575</v>
+        <v>896</v>
       </c>
       <c r="O345" s="1"/>
       <c r="P345" s="1"/>
@@ -21424,175 +21434,216 @@
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
     </row>
+    <row r="346" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A346" s="1"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="F346" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G346" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H346" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I346" s="1"/>
+      <c r="J346" s="1"/>
+      <c r="K346" s="1"/>
+      <c r="L346" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="M346" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="N346" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="O346" s="1"/>
+      <c r="P346" s="1"/>
+      <c r="Q346" s="1"/>
+      <c r="R346" s="1"/>
+      <c r="S346" s="1"/>
+      <c r="T346" s="1"/>
+      <c r="U346" s="1"/>
+      <c r="V346" s="1"/>
+      <c r="W346" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F311">
-    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="191"/>
+  <conditionalFormatting sqref="F312">
+    <cfRule type="duplicateValues" dxfId="160" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="189"/>
     <cfRule type="duplicateValues" dxfId="133" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="215"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N311">
-    <cfRule type="duplicateValues" dxfId="107" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="160"/>
+  <conditionalFormatting sqref="N312">
+    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="162"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T152">
+  <conditionalFormatting sqref="T153">
     <cfRule type="duplicateValues" dxfId="54" priority="1"/>
     <cfRule type="duplicateValues" dxfId="53" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
     <cfRule type="duplicateValues" dxfId="26" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0427\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF77E877-F35C-49A0-B8E2-B1C9B1A8993B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E263861-8618-42B0-BF89-2BCBD1B0A745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1349">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4071,9 +4071,6 @@
     <t>SC4643VB-Q-DF-03AK-FFH-L43</t>
   </si>
   <si>
-    <t>SC4643VB-Q-DG-03AR-FFH-L43</t>
-  </si>
-  <si>
     <t>STC9D03G</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4120,6 +4117,13 @@
   </si>
   <si>
     <t>SC4643VB-P-Q-DE-43AR-4643</t>
+  </si>
+  <si>
+    <t>SC4643VB-Q-DG-03AR-FFH-L43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643VB-Q-DE-40CR-FFH-L43</t>
   </si>
 </sst>
 </file>
@@ -14375,17 +14379,17 @@
         <v>752</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1" t="s">
         <v>1097</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
@@ -14412,13 +14416,13 @@
         <v>1323</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>496</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>839</v>
@@ -14575,13 +14579,13 @@
         <v>801</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>499</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1333</v>
+        <v>1347</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>839</v>
@@ -14597,7 +14601,7 @@
       </c>
       <c r="K180" s="1"/>
       <c r="L180" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="M180" s="1" t="s">
         <v>499</v>
@@ -14606,7 +14610,7 @@
         <v>1106</v>
       </c>
       <c r="O180" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="P180" s="1" t="s">
         <v>499</v>
@@ -14615,17 +14619,23 @@
         <v>962</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="S180" s="1" t="s">
         <v>499</v>
       </c>
       <c r="T180" s="1" t="s">
-        <v>1337</v>
-      </c>
-      <c r="U180" s="1"/>
-      <c r="V180" s="1"/>
-      <c r="W180" s="1"/>
+        <v>1336</v>
+      </c>
+      <c r="U180" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="V180" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="W180" s="1" t="s">
+        <v>1348</v>
+      </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
@@ -14638,17 +14648,17 @@
         <v>499</v>
       </c>
       <c r="F181" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G181" s="1" t="s">
         <v>1344</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>1345</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1" t="s">
         <v>1097</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="K181" s="1"/>
       <c r="L181" s="1"/>
@@ -14669,20 +14679,20 @@
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>498</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>907</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
@@ -14693,16 +14703,16 @@
         <v>498</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="O182" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="P182" s="1" t="s">
         <v>498</v>
       </c>
       <c r="Q182" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
@@ -14713,7 +14723,7 @@
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>498</v>
@@ -14722,13 +14732,13 @@
         <v>970</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>498</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>839</v>
@@ -14740,7 +14750,7 @@
         <v>1097</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="K183" s="1"/>
       <c r="L183" s="1" t="s">
@@ -14762,7 +14772,7 @@
         <v>1107</v>
       </c>
       <c r="R183" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="S183" s="1" t="s">
         <v>498</v>
@@ -14777,7 +14787,7 @@
         <v>498</v>
       </c>
       <c r="W183" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.2">
@@ -19372,7 +19382,7 @@
         <v>576</v>
       </c>
       <c r="J293" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="K293" s="1"/>
       <c r="L293" s="1"/>
@@ -19534,7 +19544,7 @@
         <v>1097</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0501\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307A01DE-3095-487B-98B8-40AE3E685D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D51E0B-D80C-4844-BFEA-32333A77F807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0501\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D51E0B-D80C-4844-BFEA-32333A77F807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977E13E-04CB-43BA-9B71-076C854A15B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="1365">
   <si>
     <t>替代规格2</t>
   </si>
@@ -3148,9 +3148,6 @@
     <t>SC2432SO-Q-CM-10CR-NM</t>
   </si>
   <si>
-    <t>SC2432SO-Q-CM-10AR-2432</t>
-  </si>
-  <si>
     <t>SC2434SO-CM-10AR-2434</t>
   </si>
   <si>
@@ -3187,9 +3184,6 @@
     <t>SC2442SO-CR-10CR-2442</t>
   </si>
   <si>
-    <t>SC2443UA-Q-CW-10HK-2443</t>
-  </si>
-  <si>
     <t>SC2443UA-Q-CW-10AK-2443</t>
   </si>
   <si>
@@ -3668,9 +3662,6 @@
   </si>
   <si>
     <t>NF.SC1445A2-713B</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-GC-00NR-NM</t>
   </si>
   <si>
     <t>NF.SC2546VB-AB-CH-2546</t>
@@ -4055,9 +4046,6 @@
     <t>SC4933SO-N-TR</t>
   </si>
   <si>
-    <t>SC4933SO-N-CD-00AR-4933</t>
-  </si>
-  <si>
     <t>SC4933SO-N-CD-00NR-4933</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4168,6 +4156,32 @@
   </si>
   <si>
     <t>SC69401DC-Q-HD-4XCR-69401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245C2-CD-90AK-41F</t>
+  </si>
+  <si>
+    <t>SC1245UA-CD-90HK-41F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245C2-BK</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-GC-00NR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10AR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛扬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4933SO-N-CD-00AR-4933</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4265,7 +4279,1837 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="459">
+  <dxfs count="642">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -9239,7 +11083,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -9248,7 +11092,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>902</v>
@@ -9417,29 +11261,29 @@
     </row>
     <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1280</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>902</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="5" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -9503,7 +11347,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -9603,10 +11447,10 @@
         <v>179</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -9643,7 +11487,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>902</v>
@@ -9688,7 +11532,7 @@
         <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>902</v>
@@ -9733,7 +11577,7 @@
         <v>123</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>902</v>
@@ -9874,7 +11718,7 @@
         <v>40</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
@@ -10055,7 +11899,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>902</v>
@@ -10093,17 +11937,17 @@
         <v>49</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -10111,10 +11955,10 @@
         <v>49</v>
       </c>
       <c r="M20" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>1347</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>1351</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -10258,10 +12102,10 @@
         <v>880</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
@@ -10270,13 +12114,13 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="5" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>880</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -11288,7 +13132,7 @@
         <v>123</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -11339,7 +13183,7 @@
         <v>123</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -11390,7 +13234,7 @@
         <v>123</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -11413,7 +13257,7 @@
         <v>123</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>902</v>
@@ -11435,7 +13279,7 @@
         <v>123</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -11486,7 +13330,7 @@
         <v>123</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -11537,7 +13381,7 @@
         <v>123</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -12121,10 +13965,10 @@
         <v>143</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>909</v>
@@ -12184,10 +14028,10 @@
         <v>143</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>909</v>
@@ -13012,7 +14856,7 @@
         <v>230</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>229</v>
@@ -14535,13 +16379,13 @@
         <v>304</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="S115" s="1" t="s">
         <v>303</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="U115" s="1" t="s">
         <v>617</v>
@@ -14550,7 +16394,7 @@
         <v>303</v>
       </c>
       <c r="W115" s="1" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.2">
@@ -15353,22 +17197,28 @@
         <v>607</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1035</v>
+        <v>608</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>917</v>
+        <v>559</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>574</v>
       </c>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
-      <c r="L133" s="1"/>
-      <c r="M133" s="1"/>
-      <c r="N133" s="1"/>
+      <c r="L133" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="M133" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="N133" s="1" t="s">
+        <v>1362</v>
+      </c>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
@@ -15387,21 +17237,23 @@
         <v>363</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>607</v>
+        <v>372</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>608</v>
+        <v>373</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>559</v>
+        <v>54</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="J134" s="1"/>
+      <c r="J134" s="1" t="s">
+        <v>940</v>
+      </c>
       <c r="K134" s="1"/>
       <c r="L134" s="1"/>
       <c r="M134" s="1"/>
@@ -15424,23 +17276,21 @@
         <v>363</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>372</v>
+        <v>717</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>373</v>
+        <v>718</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>54</v>
+        <v>559</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="J135" s="1" t="s">
-        <v>940</v>
-      </c>
+      <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
@@ -15460,28 +17310,32 @@
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1" t="s">
-        <v>363</v>
+        <v>28</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>717</v>
+        <v>1324</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>718</v>
+        <v>1325</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>559</v>
-      </c>
+        <v>902</v>
+      </c>
+      <c r="H136" s="1"/>
       <c r="I136" s="1" t="s">
         <v>574</v>
       </c>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
-      <c r="L136" s="1"/>
-      <c r="M136" s="1"/>
-      <c r="N136" s="1"/>
+      <c r="L136" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>1364</v>
+      </c>
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
@@ -15493,35 +17347,43 @@
       <c r="W136" s="1"/>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
+      <c r="A137" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>369</v>
+      </c>
       <c r="D137" s="1" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1327</v>
+        <v>370</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1328</v>
+        <v>371</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="H137" s="1"/>
+        <v>906</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>559</v>
+      </c>
       <c r="I137" s="1" t="s">
         <v>574</v>
       </c>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>1327</v>
+        <v>370</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>1329</v>
+        <v>1035</v>
       </c>
       <c r="O137" s="1"/>
       <c r="P137" s="1"/>
@@ -15538,25 +17400,25 @@
         <v>363</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>371</v>
+        <v>1036</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>906</v>
+        <v>838</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>559</v>
+        <v>917</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>574</v>
@@ -15567,10 +17429,10 @@
         <v>363</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
@@ -15587,22 +17449,22 @@
         <v>363</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>320</v>
+        <v>750</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>838</v>
+        <v>907</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>917</v>
@@ -15616,10 +17478,10 @@
         <v>363</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>320</v>
+        <v>750</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
@@ -15633,22 +17495,22 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>750</v>
+        <v>379</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>907</v>
@@ -15662,13 +17524,13 @@
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>750</v>
+        <v>379</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>1040</v>
+        <v>380</v>
       </c>
       <c r="O140" s="1"/>
       <c r="P140" s="1"/>
@@ -15682,28 +17544,28 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>377</v>
+        <v>60</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>379</v>
+        <v>62</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>1041</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>917</v>
+        <v>559</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>574</v>
@@ -15711,17 +17573,23 @@
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>379</v>
+        <v>60</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="O141" s="1"/>
-      <c r="P141" s="1"/>
-      <c r="Q141" s="1"/>
+        <v>779</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="P141" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q141" s="1" t="s">
+        <v>1042</v>
+      </c>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
@@ -15734,49 +17602,37 @@
         <v>381</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>60</v>
+        <v>386</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>62</v>
+        <v>388</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1042</v>
+        <v>389</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>559</v>
+        <v>54</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
-      <c r="L142" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="M142" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="N142" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="O142" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="P142" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q142" s="1" t="s">
-        <v>1043</v>
-      </c>
+      <c r="L142" s="1"/>
+      <c r="M142" s="1"/>
+      <c r="N142" s="1"/>
+      <c r="O142" s="1"/>
+      <c r="P142" s="1"/>
+      <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
@@ -15789,34 +17645,40 @@
         <v>381</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>389</v>
+        <v>1043</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>902</v>
+        <v>838</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>54</v>
+        <v>917</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
-      <c r="L143" s="1"/>
-      <c r="M143" s="1"/>
-      <c r="N143" s="1"/>
+      <c r="L143" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="M143" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="N143" s="1" t="s">
+        <v>1044</v>
+      </c>
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
@@ -15828,23 +17690,17 @@
       <c r="W143" s="1"/>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A144" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>385</v>
-      </c>
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
       <c r="D144" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>838</v>
@@ -15858,17 +17714,23 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
+        <v>773</v>
+      </c>
+      <c r="O144" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="P144" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q144" s="1" t="s">
+        <v>1046</v>
+      </c>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
@@ -15877,46 +17739,52 @@
       <c r="W144" s="1"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
+      <c r="A145" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="D145" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1046</v>
+        <v>399</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>838</v>
+        <v>906</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>917</v>
+        <v>559</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>773</v>
+        <v>400</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>1047</v>
+        <v>401</v>
       </c>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
@@ -15926,23 +17794,17 @@
       <c r="W145" s="1"/>
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A146" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>397</v>
-      </c>
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
       <c r="D146" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>906</v>
@@ -15951,28 +17813,16 @@
         <v>559</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
-      <c r="L146" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M146" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="N146" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="O146" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="P146" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q146" s="1" t="s">
-        <v>401</v>
-      </c>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
+      <c r="N146" s="1"/>
+      <c r="O146" s="1"/>
+      <c r="P146" s="1"/>
+      <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -15988,10 +17838,10 @@
         <v>402</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>906</v>
@@ -16004,9 +17854,15 @@
       </c>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
-      <c r="L147" s="1"/>
-      <c r="M147" s="1"/>
-      <c r="N147" s="1"/>
+      <c r="L147" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M147" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="N147" s="1" t="s">
+        <v>593</v>
+      </c>
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
@@ -16018,127 +17874,129 @@
       <c r="W147" s="1"/>
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
+      <c r="A148" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="D148" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>935</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>906</v>
+        <v>1363</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>559</v>
+        <v>54</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="J148" s="1"/>
+        <v>580</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N148" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="O148" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M148" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="N148" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1"/>
-      <c r="Q148" s="1"/>
-      <c r="R148" s="1"/>
-      <c r="S148" s="1"/>
-      <c r="T148" s="1"/>
-      <c r="U148" s="1"/>
-      <c r="V148" s="1"/>
-      <c r="W148" s="1"/>
+      <c r="P148" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q148" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="R148" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S148" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="T148" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="U148" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="V148" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="W148" s="1" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>1048</v>
+        <v>415</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>411</v>
+        <v>1049</v>
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O149" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P149" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q149" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="R149" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S149" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="T149" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="U149" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="V149" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="W149" s="1" t="s">
-        <v>935</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O149" s="1"/>
+      <c r="P149" s="1"/>
+      <c r="Q149" s="1"/>
+      <c r="R149" s="1"/>
+      <c r="S149" s="1"/>
+      <c r="T149" s="1"/>
+      <c r="U149" s="1"/>
+      <c r="V149" s="1"/>
+      <c r="W149" s="1"/>
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A150" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>414</v>
-      </c>
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
       <c r="D150" s="1" t="s">
         <v>412</v>
       </c>
@@ -16146,19 +18004,19 @@
         <v>415</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>417</v>
+        <v>1284</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>902</v>
+        <v>1285</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>54</v>
+        <v>724</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>590</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
@@ -16168,7 +18026,7 @@
         <v>415</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>416</v>
+        <v>739</v>
       </c>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
@@ -16180,40 +18038,34 @@
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
-      <c r="D151" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>1287</v>
+      <c r="D151" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>1358</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>1051</v>
-      </c>
+        <v>1285</v>
+      </c>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
       <c r="K151" s="1"/>
-      <c r="L151" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="M151" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="N151" s="1" t="s">
-        <v>739</v>
+      <c r="L151" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="M151" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="N151" s="5" t="s">
+        <v>1359</v>
       </c>
       <c r="O151" s="1"/>
       <c r="P151" s="1"/>
@@ -16315,7 +18167,7 @@
         <v>436</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>433</v>
@@ -16344,7 +18196,7 @@
         <v>52</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>909</v>
@@ -16383,7 +18235,7 @@
         <v>159</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>909</v>
@@ -16405,7 +18257,7 @@
         <v>159</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
@@ -16419,25 +18271,25 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="D156" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="G156" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>1061</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>558</v>
@@ -16475,7 +18327,7 @@
         <v>438</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>911</v>
@@ -16500,13 +18352,13 @@
         <v>439</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>438</v>
       </c>
       <c r="Q157" s="1" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="R157" s="5" t="s">
         <v>426</v>
@@ -16515,7 +18367,7 @@
         <v>438</v>
       </c>
       <c r="T157" s="5" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
@@ -16538,7 +18390,7 @@
         <v>448</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>913</v>
@@ -16550,7 +18402,7 @@
         <v>576</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1" t="s">
@@ -16560,7 +18412,7 @@
         <v>448</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
@@ -16589,7 +18441,7 @@
         <v>451</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>913</v>
@@ -16601,7 +18453,7 @@
         <v>576</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
@@ -16611,7 +18463,7 @@
         <v>451</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
@@ -16640,7 +18492,7 @@
         <v>454</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>913</v>
@@ -16652,7 +18504,7 @@
         <v>576</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="K160" s="1"/>
       <c r="L160" s="1" t="s">
@@ -16662,7 +18514,7 @@
         <v>454</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
@@ -16691,7 +18543,7 @@
         <v>649</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>913</v>
@@ -16703,7 +18555,7 @@
         <v>576</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
@@ -16713,7 +18565,7 @@
         <v>649</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="O161" s="1"/>
       <c r="P161" s="1"/>
@@ -16742,7 +18594,7 @@
         <v>457</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>906</v>
@@ -16787,7 +18639,7 @@
         <v>458</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>913</v>
@@ -16799,7 +18651,7 @@
         <v>576</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="K163" s="1"/>
       <c r="L163" s="1" t="s">
@@ -16809,7 +18661,7 @@
         <v>458</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="O163" s="1"/>
       <c r="P163" s="1"/>
@@ -16838,10 +18690,10 @@
         <v>459</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>558</v>
@@ -16850,7 +18702,7 @@
         <v>576</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="1" t="s">
@@ -16889,19 +18741,19 @@
         <v>467</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H165" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="J165" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
@@ -16934,7 +18786,7 @@
         <v>468</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>902</v>
@@ -16983,7 +18835,7 @@
         <v>469</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>902</v>
@@ -17032,19 +18884,19 @@
         <v>469</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="K168" s="1"/>
       <c r="L168" s="1" t="s">
@@ -17083,19 +18935,19 @@
         <v>475</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="K169" s="1"/>
       <c r="L169" s="1" t="s">
@@ -17134,7 +18986,7 @@
         <v>479</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>902</v>
@@ -17143,7 +18995,7 @@
         <v>54</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
@@ -17183,7 +19035,7 @@
         <v>482</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>824</v>
@@ -17192,10 +19044,10 @@
         <v>54</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="K171" s="1"/>
       <c r="L171" s="1" t="s">
@@ -17234,7 +19086,7 @@
         <v>482</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>906</v>
@@ -17243,7 +19095,7 @@
         <v>559</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
@@ -17277,7 +19129,7 @@
         <v>488</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>902</v>
@@ -17286,7 +19138,7 @@
         <v>54</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -17311,7 +19163,7 @@
         <v>489</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>962</v>
@@ -17320,7 +19172,7 @@
         <v>489</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>906</v>
@@ -17329,7 +19181,7 @@
         <v>559</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
@@ -17357,19 +19209,19 @@
         <v>491</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
@@ -17402,19 +19254,19 @@
         <v>491</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
@@ -17447,19 +19299,19 @@
         <v>494</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -17483,7 +19335,7 @@
         <v>495</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>476</v>
@@ -17492,7 +19344,7 @@
         <v>495</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>906</v>
@@ -17501,7 +19353,7 @@
         <v>559</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
@@ -17529,19 +19381,19 @@
         <v>751</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
@@ -17568,17 +19420,17 @@
         <v>751</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
@@ -17596,34 +19448,34 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>496</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="K181" s="1"/>
       <c r="L181" s="1" t="s">
@@ -17633,7 +19485,7 @@
         <v>496</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="O181" s="1" t="s">
         <v>476</v>
@@ -17651,7 +19503,7 @@
         <v>496</v>
       </c>
       <c r="T181" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="U181" s="1" t="s">
         <v>476</v>
@@ -17671,7 +19523,7 @@
         <v>498</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>476</v>
@@ -17680,7 +19532,7 @@
         <v>498</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>906</v>
@@ -17689,7 +19541,7 @@
         <v>559</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
@@ -17723,19 +19575,19 @@
         <v>498</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="K183" s="1"/>
       <c r="L183" s="1" t="s">
@@ -17745,7 +19597,7 @@
         <v>498</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
@@ -17768,38 +19620,38 @@
         <v>800</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="O184" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="P184" s="1" t="s">
         <v>499</v>
@@ -17808,22 +19660,22 @@
         <v>961</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="S184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="T184" s="1" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="U184" s="1" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="V184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="W184" s="1" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.2">
@@ -17837,17 +19689,17 @@
         <v>499</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
@@ -17868,20 +19720,20 @@
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>498</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>906</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -17892,16 +19744,16 @@
         <v>498</v>
       </c>
       <c r="N186" s="1" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="P186" s="1" t="s">
         <v>498</v>
       </c>
       <c r="Q186" s="1" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
@@ -17912,7 +19764,7 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>498</v>
@@ -17921,25 +19773,25 @@
         <v>969</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>498</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="K187" s="1"/>
       <c r="L187" s="1" t="s">
@@ -17949,7 +19801,7 @@
         <v>498</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="O187" s="1" t="s">
         <v>476</v>
@@ -17958,16 +19810,16 @@
         <v>498</v>
       </c>
       <c r="Q187" s="1" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="R187" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="S187" s="1" t="s">
         <v>498</v>
       </c>
       <c r="T187" s="1" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="U187" s="1" t="s">
         <v>962</v>
@@ -17976,7 +19828,7 @@
         <v>498</v>
       </c>
       <c r="W187" s="1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.2">
@@ -17996,7 +19848,7 @@
         <v>606</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>906</v>
@@ -18018,7 +19870,7 @@
         <v>606</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>603</v>
@@ -18053,7 +19905,7 @@
         <v>520</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>902</v>
@@ -18096,13 +19948,13 @@
         <v>521</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>872</v>
@@ -18141,7 +19993,7 @@
         <v>522</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>902</v>
@@ -18184,19 +20036,19 @@
         <v>522</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
@@ -18229,19 +20081,19 @@
         <v>525</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="K193" s="1"/>
       <c r="L193" s="1"/>
@@ -18274,7 +20126,7 @@
         <v>529</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>902</v>
@@ -18317,7 +20169,7 @@
         <v>532</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>904</v>
@@ -18360,7 +20212,7 @@
         <v>536</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>904</v>
@@ -18403,13 +20255,13 @@
         <v>270</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>905</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>574</v>
@@ -18458,31 +20310,31 @@
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="H198" s="1"/>
       <c r="I198" s="1" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="J198" s="1"/>
       <c r="K198" s="1"/>
       <c r="L198" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="M198" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="N198" s="1" t="s">
         <v>1058</v>
-      </c>
-      <c r="N198" s="1" t="s">
-        <v>1060</v>
       </c>
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
@@ -18519,7 +20371,7 @@
         <v>958</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -18548,7 +20400,7 @@
         <v>278</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>902</v>
@@ -18560,7 +20412,7 @@
         <v>580</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
@@ -18587,7 +20439,7 @@
         <v>278</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>902</v>
@@ -18599,7 +20451,7 @@
         <v>580</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
@@ -18632,7 +20484,7 @@
         <v>278</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>902</v>
@@ -18675,7 +20527,7 @@
         <v>278</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>902</v>
@@ -18687,7 +20539,7 @@
         <v>577</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
@@ -18720,7 +20572,7 @@
         <v>278</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>902</v>
@@ -18732,7 +20584,7 @@
         <v>577</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
@@ -18756,7 +20608,7 @@
         <v>273</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>541</v>
@@ -18794,7 +20646,7 @@
         <v>270</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
@@ -18820,7 +20672,7 @@
         <v>443</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>902</v>
@@ -18895,7 +20747,7 @@
         <v>549</v>
       </c>
       <c r="N207" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
@@ -18924,7 +20776,7 @@
         <v>553</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>902</v>
@@ -18944,7 +20796,7 @@
         <v>553</v>
       </c>
       <c r="N208" s="1" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
@@ -18967,19 +20819,19 @@
         <v>557</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
@@ -19006,19 +20858,19 @@
         <v>557</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
@@ -19048,10 +20900,10 @@
         <v>567</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>586</v>
@@ -19085,10 +20937,10 @@
         <v>570</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>586</v>
@@ -19122,10 +20974,10 @@
         <v>573</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I213" s="1"/>
       <c r="J213" s="1"/>
@@ -19154,7 +21006,7 @@
         <v>323</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>902</v>
@@ -19203,7 +21055,7 @@
         <v>616</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>904</v>
@@ -19246,7 +21098,7 @@
         <v>620</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>904</v>
@@ -19295,7 +21147,7 @@
         <v>622</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>914</v>
@@ -19358,7 +21210,7 @@
         <v>627</v>
       </c>
       <c r="N218" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
@@ -19401,7 +21253,7 @@
         <v>929</v>
       </c>
       <c r="N219" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="O219" s="1"/>
       <c r="P219" s="1"/>
@@ -19430,7 +21282,7 @@
         <v>633</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>902</v>
@@ -19468,7 +21320,7 @@
         <v>633</v>
       </c>
       <c r="T220" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
@@ -19505,7 +21357,7 @@
         <v>634</v>
       </c>
       <c r="N221" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="O221" s="1"/>
       <c r="P221" s="1"/>
@@ -19528,7 +21380,7 @@
         <v>637</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>909</v>
@@ -19540,7 +21392,7 @@
         <v>575</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
@@ -19567,7 +21419,7 @@
         <v>638</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>909</v>
@@ -19579,7 +21431,7 @@
         <v>575</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -19606,7 +21458,7 @@
         <v>768</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>909</v>
@@ -19618,7 +21470,7 @@
         <v>575</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
@@ -19651,19 +21503,19 @@
         <v>642</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
@@ -19690,7 +21542,7 @@
         <v>646</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>903</v>
@@ -19710,7 +21562,7 @@
         <v>646</v>
       </c>
       <c r="N226" s="1" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="O226" s="1"/>
       <c r="P226" s="1"/>
@@ -19739,7 +21591,7 @@
         <v>653</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>902</v>
@@ -19782,7 +21634,7 @@
         <v>657</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>902</v>
@@ -19819,19 +21671,19 @@
         <v>501</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -19864,13 +21716,13 @@
         <v>838</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
@@ -19903,13 +21755,13 @@
         <v>838</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
@@ -19942,13 +21794,13 @@
         <v>838</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -19981,13 +21833,13 @@
         <v>838</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
@@ -20020,13 +21872,13 @@
         <v>838</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
@@ -20059,13 +21911,13 @@
         <v>838</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -20092,19 +21944,19 @@
         <v>502</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="K236" s="1"/>
       <c r="L236" s="1" t="s">
@@ -20114,7 +21966,7 @@
         <v>502</v>
       </c>
       <c r="N236" s="1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
@@ -20143,13 +21995,13 @@
         <v>838</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
@@ -20182,13 +22034,13 @@
         <v>838</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
@@ -20221,13 +22073,13 @@
         <v>838</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
@@ -20260,13 +22112,13 @@
         <v>838</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K240" s="1"/>
       <c r="L240" s="1"/>
@@ -20299,13 +22151,13 @@
         <v>838</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K241" s="1"/>
       <c r="L241" s="1"/>
@@ -20338,13 +22190,13 @@
         <v>838</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
@@ -20377,13 +22229,13 @@
         <v>838</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -20416,13 +22268,13 @@
         <v>838</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K244" s="1"/>
       <c r="L244" s="1"/>
@@ -20455,13 +22307,13 @@
         <v>838</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K245" s="1"/>
       <c r="L245" s="1"/>
@@ -20494,13 +22346,13 @@
         <v>838</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K246" s="1"/>
       <c r="L246" s="1"/>
@@ -20533,19 +22385,19 @@
         <v>715</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="K247" s="1"/>
       <c r="L247" s="1"/>
@@ -20578,7 +22430,7 @@
         <v>505</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>902</v>
@@ -20598,7 +22450,7 @@
         <v>505</v>
       </c>
       <c r="N248" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="O248" s="1"/>
       <c r="P248" s="1"/>
@@ -20627,7 +22479,7 @@
         <v>505</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>902</v>
@@ -20647,7 +22499,7 @@
         <v>505</v>
       </c>
       <c r="N249" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="O249" s="1"/>
       <c r="P249" s="1"/>
@@ -20670,7 +22522,7 @@
         <v>668</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>902</v>
@@ -20715,10 +22567,10 @@
         <v>953</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>952</v>
@@ -20754,13 +22606,13 @@
         <v>838</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>585</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="K252" s="1"/>
       <c r="L252" s="1"/>
@@ -20784,13 +22636,13 @@
         <v>35</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="F253" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G253" s="1" t="s">
         <v>1308</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>1311</v>
       </c>
       <c r="H253" s="1"/>
       <c r="I253" s="1" t="s">
@@ -20799,13 +22651,13 @@
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
       <c r="L253" s="1" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="N253" s="1" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
@@ -20825,13 +22677,13 @@
         <v>35</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="H254" s="1"/>
       <c r="I254" s="1" t="s">
@@ -20840,13 +22692,13 @@
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
       <c r="L254" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="M254" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="M254" s="1" t="s">
-        <v>1305</v>
-      </c>
       <c r="N254" s="1" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="O254" s="1"/>
       <c r="P254" s="1"/>
@@ -20878,7 +22730,7 @@
         <v>835</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>724</v>
@@ -20904,7 +22756,7 @@
         <v>822</v>
       </c>
       <c r="Q255" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
@@ -20939,7 +22791,7 @@
         <v>558</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -20976,7 +22828,7 @@
         <v>558</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -21004,7 +22856,7 @@
         <v>680</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>902</v>
@@ -21041,7 +22893,7 @@
         <v>682</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>902</v>
@@ -21078,7 +22930,7 @@
         <v>684</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>902</v>
@@ -21152,7 +23004,7 @@
         <v>436</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>903</v>
@@ -21174,7 +23026,7 @@
         <v>436</v>
       </c>
       <c r="N262" s="1" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="O262" s="1"/>
       <c r="P262" s="1"/>
@@ -21197,7 +23049,7 @@
         <v>429</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>902</v>
@@ -21240,7 +23092,7 @@
         <v>691</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>902</v>
@@ -21249,7 +23101,7 @@
         <v>54</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -21286,7 +23138,7 @@
         <v>559</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -21320,7 +23172,7 @@
         <v>697</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>902</v>
@@ -21357,7 +23209,7 @@
         <v>698</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>902</v>
@@ -21394,7 +23246,7 @@
         <v>699</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>902</v>
@@ -21431,7 +23283,7 @@
         <v>700</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>906</v>
@@ -21468,7 +23320,7 @@
         <v>316</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>902</v>
@@ -21511,7 +23363,7 @@
         <v>388</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>902</v>
@@ -21548,7 +23400,7 @@
         <v>701</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>906</v>
@@ -21585,7 +23437,7 @@
         <v>702</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>906</v>
@@ -21622,7 +23474,7 @@
         <v>398</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>902</v>
@@ -21659,7 +23511,7 @@
         <v>703</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>906</v>
@@ -21696,7 +23548,7 @@
         <v>704</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>906</v>
@@ -21733,7 +23585,7 @@
         <v>705</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>906</v>
@@ -21776,7 +23628,7 @@
         <v>968</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>906</v>
@@ -21785,7 +23637,7 @@
         <v>559</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="J278" s="1"/>
       <c r="K278" s="1"/>
@@ -21856,7 +23708,7 @@
         <v>469</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>902</v>
@@ -21899,7 +23751,7 @@
         <v>710</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>906</v>
@@ -21938,10 +23790,10 @@
         <v>711</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="H282" s="1" t="s">
         <v>558</v>
@@ -21975,10 +23827,10 @@
         <v>712</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>558</v>
@@ -22012,7 +23864,7 @@
         <v>713</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>906</v>
@@ -22049,7 +23901,7 @@
         <v>720</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>902</v>
@@ -22086,19 +23938,19 @@
         <v>689</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="K286" s="1"/>
       <c r="L286" s="1"/>
@@ -22125,7 +23977,7 @@
         <v>722</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>838</v>
@@ -22134,7 +23986,7 @@
         <v>54</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>847</v>
@@ -22170,16 +24022,16 @@
         <v>741</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
@@ -22246,7 +24098,7 @@
         <v>743</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>909</v>
@@ -22258,7 +24110,7 @@
         <v>861</v>
       </c>
       <c r="J290" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
@@ -22373,7 +24225,7 @@
         <v>270</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>982</v>
+        <v>1361</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>904</v>
@@ -22393,7 +24245,7 @@
         <v>270</v>
       </c>
       <c r="N293" s="1" t="s">
-        <v>1209</v>
+        <v>982</v>
       </c>
       <c r="O293" s="1"/>
       <c r="P293" s="1"/>
@@ -22428,13 +24280,13 @@
         <v>838</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J294" s="1" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="K294" s="1"/>
       <c r="L294" s="1" t="s">
@@ -22444,7 +24296,7 @@
         <v>294</v>
       </c>
       <c r="N294" s="1" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="O294" s="1" t="s">
         <v>681</v>
@@ -22479,7 +24331,7 @@
         <v>749</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>902</v>
@@ -22516,7 +24368,7 @@
         <v>331</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>907</v>
@@ -22536,7 +24388,7 @@
         <v>331</v>
       </c>
       <c r="N296" s="1" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
@@ -22559,19 +24411,19 @@
         <v>751</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
@@ -22598,7 +24450,7 @@
         <v>443</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>902</v>
@@ -22635,7 +24487,7 @@
         <v>755</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>838</v>
@@ -22655,7 +24507,7 @@
         <v>755</v>
       </c>
       <c r="N299" s="1" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="O299" s="1"/>
       <c r="P299" s="1"/>
@@ -22678,7 +24530,7 @@
         <v>756</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>902</v>
@@ -22698,7 +24550,7 @@
         <v>756</v>
       </c>
       <c r="N300" s="1" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="O300" s="1"/>
       <c r="P300" s="1"/>
@@ -22721,19 +24573,19 @@
         <v>757</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="K301" s="1"/>
       <c r="L301" s="1" t="s">
@@ -22743,7 +24595,7 @@
         <v>757</v>
       </c>
       <c r="N301" s="1" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="O301" s="1"/>
       <c r="P301" s="1"/>
@@ -22766,7 +24618,7 @@
         <v>758</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>902</v>
@@ -22803,7 +24655,7 @@
         <v>759</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>909</v>
@@ -22815,7 +24667,7 @@
         <v>575</v>
       </c>
       <c r="J303" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
@@ -22842,7 +24694,7 @@
         <v>763</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>910</v>
@@ -22885,7 +24737,7 @@
         <v>980</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
@@ -22899,7 +24751,7 @@
         <v>980</v>
       </c>
       <c r="N305" s="1" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
@@ -22919,7 +24771,7 @@
         <v>758</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>742</v>
@@ -22928,7 +24780,7 @@
         <v>927</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>909</v>
@@ -22940,7 +24792,7 @@
         <v>582</v>
       </c>
       <c r="J306" s="1" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="K306" s="1"/>
       <c r="L306" s="1"/>
@@ -22967,7 +24819,7 @@
         <v>765</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>906</v>
@@ -22976,7 +24828,7 @@
         <v>559</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J307" s="1"/>
       <c r="K307" s="1"/>
@@ -23004,7 +24856,7 @@
         <v>767</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>902</v>
@@ -23082,7 +24934,7 @@
         <v>335</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>902</v>
@@ -23127,7 +24979,7 @@
         <v>67</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>838</v>
@@ -23176,7 +25028,7 @@
         <v>762</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>909</v>
@@ -23188,7 +25040,7 @@
         <v>579</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
@@ -23221,7 +25073,7 @@
         <v>785</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>902</v>
@@ -23241,7 +25093,7 @@
         <v>785</v>
       </c>
       <c r="N313" s="1" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="O313" s="1"/>
       <c r="P313" s="1"/>
@@ -23270,10 +25122,10 @@
         <v>838</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
@@ -23301,7 +25153,7 @@
         <v>892</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>906</v>
@@ -23346,7 +25198,7 @@
         <v>813</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>906</v>
@@ -23368,7 +25220,7 @@
         <v>813</v>
       </c>
       <c r="N316" s="1" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="O316" s="1"/>
       <c r="P316" s="1"/>
@@ -23391,13 +25243,13 @@
         <v>815</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -23426,13 +25278,13 @@
         <v>816</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -23458,10 +25310,10 @@
         <v>291</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="G319" s="5" t="s">
         <v>902</v>
@@ -23476,10 +25328,10 @@
         <v>291</v>
       </c>
       <c r="M319" s="5" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="N319" s="5" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="O319" s="1"/>
       <c r="P319" s="1"/>
@@ -23496,19 +25348,19 @@
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
       <c r="D320" s="1" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>817</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
@@ -23537,19 +25389,19 @@
         <v>818</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>872</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
@@ -23573,10 +25425,10 @@
         <v>681</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>906</v>
@@ -23613,7 +25465,7 @@
         <v>114</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>906</v>
@@ -23633,7 +25485,7 @@
         <v>114</v>
       </c>
       <c r="N323" s="1" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="O323" s="1"/>
       <c r="P323" s="1"/>
@@ -23656,7 +25508,7 @@
         <v>821</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>910</v>
@@ -23668,7 +25520,7 @@
         <v>575</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
@@ -23695,7 +25547,7 @@
         <v>180</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>909</v>
@@ -23707,7 +25559,7 @@
         <v>579</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -23734,7 +25586,7 @@
         <v>827</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>904</v>
@@ -23748,13 +25600,13 @@
       <c r="J326" s="1"/>
       <c r="K326" s="1"/>
       <c r="L326" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="M326" s="1" t="s">
         <v>827</v>
       </c>
       <c r="N326" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
@@ -23777,7 +25629,7 @@
         <v>830</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>904</v>
@@ -23982,7 +25834,7 @@
         <v>850</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>909</v>
@@ -23994,7 +25846,7 @@
         <v>575</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="K332" s="1"/>
       <c r="L332" s="1"/>
@@ -24088,7 +25940,7 @@
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -24099,7 +25951,7 @@
         <v>69</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>902</v>
@@ -24112,9 +25964,15 @@
       </c>
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
-      <c r="L335" s="1"/>
-      <c r="M335" s="1"/>
-      <c r="N335" s="1"/>
+      <c r="L335" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="M335" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N335" s="5" t="s">
+        <v>919</v>
+      </c>
       <c r="O335" s="1"/>
       <c r="P335" s="1"/>
       <c r="Q335" s="1"/>
@@ -24218,10 +26076,10 @@
         <v>874</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="H338" s="1" t="s">
         <v>724</v>
@@ -24240,7 +26098,7 @@
         <v>874</v>
       </c>
       <c r="N338" s="1" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
@@ -24263,7 +26121,7 @@
         <v>918</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>838</v>
@@ -24283,7 +26141,7 @@
         <v>918</v>
       </c>
       <c r="N339" s="1" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
@@ -24303,7 +26161,7 @@
         <v>62</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>381</v>
@@ -24312,7 +26170,7 @@
         <v>62</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>906</v>
@@ -24406,7 +26264,7 @@
         <v>875</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>724</v>
@@ -24479,16 +26337,16 @@
         <v>846</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="H344" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="J344" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.2">
@@ -24508,7 +26366,7 @@
         <v>905</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>574</v>
@@ -24690,10 +26548,10 @@
         <v>565</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I350" s="1"/>
       <c r="J350" s="1"/>
@@ -24731,10 +26589,10 @@
         <v>888</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I351" s="1"/>
       <c r="J351" s="1"/>
@@ -24772,10 +26630,10 @@
         <v>568</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
@@ -24813,10 +26671,10 @@
         <v>571</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
@@ -24844,479 +26702,668 @@
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="458" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="457" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="456" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="455" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="453" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="452" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="451" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="449" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="448" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="447" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="446" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="445" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="444" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="443" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="441" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="440" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="439" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="438" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="436" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="435" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="433" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="432" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="431" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="429" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="428" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="427" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="426" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="425" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="424" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="423" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="422" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="421" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="420" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="417" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="416" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="415" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="414" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="413" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="412" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="410" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="409" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="408" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="407" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="405" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="404" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="403" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="402" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="401" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="400" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="399" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="398" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="397" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="396" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="395" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="392" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="391" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="389" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="387" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="385" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="380" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="377" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="371" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="369" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="368" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="367" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="363" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="356" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="349" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="347" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="345" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="344" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="342" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="341" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="433"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F151">
+    <cfRule type="duplicateValues" dxfId="522" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F319">
-    <cfRule type="duplicateValues" dxfId="339" priority="498"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="470"/>
-    <cfRule type="duplicateValues" dxfId="337" priority="513"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="461"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="462"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="463"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="464"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="465"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="466"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="467"/>
-    <cfRule type="duplicateValues" dxfId="329" priority="468"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="469"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="471"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="472"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="473"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="322" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="314" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="485"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="491"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="497"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="505"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="511"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="694"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="duplicateValues" dxfId="286" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="351"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19">
-    <cfRule type="duplicateValues" dxfId="226" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="duplicateValues" dxfId="166" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="373"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N151">
+    <cfRule type="duplicateValues" dxfId="229" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N319">
-    <cfRule type="duplicateValues" dxfId="107" priority="459"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="460"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="409"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="411"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="412"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="414"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="417"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="421"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="422"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="423"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="429"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="430"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="431"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="432"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="433"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="434"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="435"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="436"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="438"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="442"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="445"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="457"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="601"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="602"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="626"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="623"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N335">
+    <cfRule type="duplicateValues" dxfId="115" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T157">
-    <cfRule type="duplicateValues" dxfId="54" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="351"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="343"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="337"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="327"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="326"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="325"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="319"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="318"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="316"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="315"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="482"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977E13E-04CB-43BA-9B71-076C854A15B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D15BF9-E891-4ADA-8A22-9BB1D2880014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4173,15 +4173,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SC2432SO-Q-CM-10AR-2432</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>赛扬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SC4933SO-N-CD-00AR-4933</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10AR-2432</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17197,7 +17197,7 @@
         <v>607</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>608</v>
+        <v>1364</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>906</v>
@@ -17217,7 +17217,7 @@
         <v>607</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>1362</v>
+        <v>608</v>
       </c>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
@@ -17334,7 +17334,7 @@
         <v>1324</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
@@ -17893,7 +17893,7 @@
         <v>935</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>54</v>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D15BF9-E891-4ADA-8A22-9BB1D2880014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717D004D-8151-4529-A493-46E9E98FADD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="1365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1367">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4182,6 +4182,14 @@
   </si>
   <si>
     <t>SC2432SO-Q-CM-10AR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4688SA-Q-DC-40AK-888K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4688SA-Q-DC-40AK-4688</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -18756,9 +18764,15 @@
         <v>1076</v>
       </c>
       <c r="K165" s="1"/>
-      <c r="L165" s="1"/>
-      <c r="M165" s="1"/>
-      <c r="N165" s="1"/>
+      <c r="L165" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="M165" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="N165" s="1" t="s">
+        <v>1365</v>
+      </c>
       <c r="O165" s="1"/>
       <c r="P165" s="1"/>
       <c r="Q165" s="1"/>
@@ -18908,9 +18922,15 @@
       <c r="N168" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="O168" s="1"/>
-      <c r="P168" s="1"/>
-      <c r="Q168" s="1"/>
+      <c r="O168" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="P168" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q168" s="1" t="s">
+        <v>1366</v>
+      </c>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0508\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717D004D-8151-4529-A493-46E9E98FADD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CC4D59-3640-46A8-A67B-CFB0D1A72701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0508\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CC4D59-3640-46A8-A67B-CFB0D1A72701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A403A-7961-4B81-A507-BE4AE653977C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1368">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4191,6 +4191,9 @@
   <si>
     <t>SC4688SA-Q-DC-40AK-4688</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA.SC4643VB-Q-DG-XXAK</t>
   </si>
 </sst>
 </file>
@@ -19607,7 +19610,7 @@
         <v>1094</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>1102</v>
+        <v>1367</v>
       </c>
       <c r="K183" s="1"/>
       <c r="L183" s="1" t="s">
@@ -19619,9 +19622,15 @@
       <c r="N183" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="O183" s="1"/>
-      <c r="P183" s="1"/>
-      <c r="Q183" s="1"/>
+      <c r="O183" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="P183" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q183" s="1" t="s">
+        <v>1103</v>
+      </c>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
@@ -19658,17 +19667,17 @@
         <v>1094</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>1102</v>
+        <v>1367</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>1103</v>
+        <v>961</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>1329</v>
@@ -19677,26 +19686,20 @@
         <v>499</v>
       </c>
       <c r="Q184" s="1" t="s">
-        <v>961</v>
+        <v>1330</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="S184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="T184" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="U184" s="1" t="s">
-        <v>1328</v>
-      </c>
-      <c r="V184" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="W184" s="1" t="s">
         <v>1342</v>
       </c>
+      <c r="U184" s="1"/>
+      <c r="V184" s="1"/>
+      <c r="W184" s="1"/>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0510\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A403A-7961-4B81-A507-BE4AE653977C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F81E11-984A-4A91-BAE2-F2BBBD30977C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0510\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F81E11-984A-4A91-BAE2-F2BBBD30977C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5459AF06-EEE2-4065-9D0F-99A5BD5C0F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0510\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0508\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5459AF06-EEE2-4065-9D0F-99A5BD5C0F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CC4D59-3640-46A8-A67B-CFB0D1A72701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1367">
   <si>
     <t>替代规格2</t>
   </si>
@@ -4191,9 +4191,6 @@
   <si>
     <t>SC4688SA-Q-DC-40AK-4688</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA.SC4643VB-Q-DG-XXAK</t>
   </si>
 </sst>
 </file>
@@ -19610,7 +19607,7 @@
         <v>1094</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>1367</v>
+        <v>1102</v>
       </c>
       <c r="K183" s="1"/>
       <c r="L183" s="1" t="s">
@@ -19622,15 +19619,9 @@
       <c r="N183" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="O183" s="1" t="s">
-        <v>1328</v>
-      </c>
-      <c r="P183" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q183" s="1" t="s">
-        <v>1103</v>
-      </c>
+      <c r="O183" s="1"/>
+      <c r="P183" s="1"/>
+      <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
       <c r="T183" s="1"/>
@@ -19667,17 +19658,17 @@
         <v>1094</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>1367</v>
+        <v>1102</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>961</v>
+        <v>1103</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>1329</v>
@@ -19686,20 +19677,26 @@
         <v>499</v>
       </c>
       <c r="Q184" s="1" t="s">
-        <v>1330</v>
+        <v>961</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="S184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="T184" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="U184" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="V184" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="W184" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="U184" s="1"/>
-      <c r="V184" s="1"/>
-      <c r="W184" s="1"/>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0508\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0501\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CC4D59-3640-46A8-A67B-CFB0D1A72701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D51E0B-D80C-4844-BFEA-32333A77F807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1362">
   <si>
     <t>替代规格2</t>
   </si>
@@ -3148,6 +3148,9 @@
     <t>SC2432SO-Q-CM-10CR-NM</t>
   </si>
   <si>
+    <t>SC2432SO-Q-CM-10AR-2432</t>
+  </si>
+  <si>
     <t>SC2434SO-CM-10AR-2434</t>
   </si>
   <si>
@@ -3184,6 +3187,9 @@
     <t>SC2442SO-CR-10CR-2442</t>
   </si>
   <si>
+    <t>SC2443UA-Q-CW-10HK-2443</t>
+  </si>
+  <si>
     <t>SC2443UA-Q-CW-10AK-2443</t>
   </si>
   <si>
@@ -3662,6 +3668,9 @@
   </si>
   <si>
     <t>NF.SC1445A2-713B</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-GC-00NR-NM</t>
   </si>
   <si>
     <t>NF.SC2546VB-AB-CH-2546</t>
@@ -4046,6 +4055,9 @@
     <t>SC4933SO-N-TR</t>
   </si>
   <si>
+    <t>SC4933SO-N-CD-00AR-4933</t>
+  </si>
+  <si>
     <t>SC4933SO-N-CD-00NR-4933</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4156,40 +4168,6 @@
   </si>
   <si>
     <t>SC69401DC-Q-HD-4XCR-69401</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1245C2-CD-90AK-41F</t>
-  </si>
-  <si>
-    <t>SC1245UA-CD-90HK-41F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1245C2-BK</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-GC-00NR-NM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赛扬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4933SO-N-CD-00AR-4933</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-Q-CM-10AR-2432</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4688SA-Q-DC-40AK-888K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4688SA-Q-DC-40AK-4688</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4287,1837 +4265,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="642">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="459">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -11091,7 +9239,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -11100,7 +9248,7 @@
         <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>902</v>
@@ -11269,29 +9417,29 @@
     </row>
     <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="B6" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C6" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>1275</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>902</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="5" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -11355,7 +9503,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
@@ -11455,10 +9603,10 @@
         <v>179</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -11495,7 +9643,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>902</v>
@@ -11540,7 +9688,7 @@
         <v>123</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>902</v>
@@ -11585,7 +9733,7 @@
         <v>123</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>902</v>
@@ -11726,7 +9874,7 @@
         <v>40</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
@@ -11907,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>902</v>
@@ -11945,17 +10093,17 @@
         <v>49</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -11963,10 +10111,10 @@
         <v>49</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -12110,10 +10258,10 @@
         <v>880</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
@@ -12122,13 +10270,13 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="5" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>880</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -13140,7 +11288,7 @@
         <v>123</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -13191,7 +11339,7 @@
         <v>123</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -13242,7 +11390,7 @@
         <v>123</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -13265,7 +11413,7 @@
         <v>123</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>902</v>
@@ -13287,7 +11435,7 @@
         <v>123</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -13338,7 +11486,7 @@
         <v>123</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -13389,7 +11537,7 @@
         <v>123</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -13973,10 +12121,10 @@
         <v>143</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>909</v>
@@ -14036,10 +12184,10 @@
         <v>143</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>909</v>
@@ -14864,7 +13012,7 @@
         <v>230</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>229</v>
@@ -16387,13 +14535,13 @@
         <v>304</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="S115" s="1" t="s">
         <v>303</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="U115" s="1" t="s">
         <v>617</v>
@@ -16402,7 +14550,7 @@
         <v>303</v>
       </c>
       <c r="W115" s="1" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.2">
@@ -17205,28 +15353,22 @@
         <v>607</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1364</v>
+        <v>1035</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>559</v>
+        <v>917</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>574</v>
       </c>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
-      <c r="L133" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M133" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="N133" s="1" t="s">
-        <v>608</v>
-      </c>
+      <c r="L133" s="1"/>
+      <c r="M133" s="1"/>
+      <c r="N133" s="1"/>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
@@ -17245,23 +15387,21 @@
         <v>363</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>372</v>
+        <v>607</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>373</v>
+        <v>608</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>54</v>
+        <v>559</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>940</v>
-      </c>
+      <c r="J134" s="1"/>
       <c r="K134" s="1"/>
       <c r="L134" s="1"/>
       <c r="M134" s="1"/>
@@ -17284,21 +15424,23 @@
         <v>363</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>717</v>
+        <v>372</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>718</v>
+        <v>373</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>559</v>
+        <v>54</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="J135" s="1"/>
+      <c r="J135" s="1" t="s">
+        <v>940</v>
+      </c>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
@@ -17318,32 +15460,28 @@
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>1324</v>
+        <v>717</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1325</v>
+        <v>718</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="H136" s="1"/>
+        <v>906</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>559</v>
+      </c>
       <c r="I136" s="1" t="s">
         <v>574</v>
       </c>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
-      <c r="L136" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>1363</v>
-      </c>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1"/>
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
@@ -17355,43 +15493,35 @@
       <c r="W136" s="1"/>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A137" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
       <c r="D137" s="1" t="s">
-        <v>363</v>
+        <v>28</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>370</v>
+        <v>1327</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>371</v>
+        <v>1328</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>559</v>
-      </c>
+        <v>902</v>
+      </c>
+      <c r="H137" s="1"/>
       <c r="I137" s="1" t="s">
         <v>574</v>
       </c>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
       <c r="L137" s="1" t="s">
-        <v>363</v>
+        <v>28</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>370</v>
+        <v>1327</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>1035</v>
+        <v>1329</v>
       </c>
       <c r="O137" s="1"/>
       <c r="P137" s="1"/>
@@ -17408,25 +15538,25 @@
         <v>363</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1036</v>
+        <v>371</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>838</v>
+        <v>906</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>917</v>
+        <v>559</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>574</v>
@@ -17437,10 +15567,10 @@
         <v>363</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
@@ -17457,22 +15587,22 @@
         <v>363</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>363</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>750</v>
+        <v>320</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>907</v>
+        <v>838</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>917</v>
@@ -17486,10 +15616,10 @@
         <v>363</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>750</v>
+        <v>320</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
@@ -17503,22 +15633,22 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>379</v>
+        <v>750</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>907</v>
@@ -17532,13 +15662,13 @@
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
       <c r="L140" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>379</v>
+        <v>750</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>380</v>
+        <v>1040</v>
       </c>
       <c r="O140" s="1"/>
       <c r="P140" s="1"/>
@@ -17552,28 +15682,28 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>60</v>
+        <v>377</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>1041</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>559</v>
+        <v>917</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>574</v>
@@ -17581,23 +15711,17 @@
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>60</v>
+        <v>379</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="O141" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="P141" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q141" s="1" t="s">
-        <v>1042</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="O141" s="1"/>
+      <c r="P141" s="1"/>
+      <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
@@ -17610,37 +15734,49 @@
         <v>381</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>386</v>
+        <v>60</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>388</v>
+        <v>62</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>389</v>
+        <v>1042</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>54</v>
+        <v>559</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
-      <c r="L142" s="1"/>
-      <c r="M142" s="1"/>
-      <c r="N142" s="1"/>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1"/>
-      <c r="Q142" s="1"/>
+      <c r="L142" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="M142" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="P142" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q142" s="1" t="s">
+        <v>1043</v>
+      </c>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
       <c r="T142" s="1"/>
@@ -17653,40 +15789,34 @@
         <v>381</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>381</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1043</v>
+        <v>389</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>838</v>
+        <v>902</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>917</v>
+        <v>54</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
-      <c r="L143" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="M143" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="N143" s="1" t="s">
-        <v>1044</v>
-      </c>
+      <c r="L143" s="1"/>
+      <c r="M143" s="1"/>
+      <c r="N143" s="1"/>
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
@@ -17698,17 +15828,23 @@
       <c r="W143" s="1"/>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
+      <c r="A144" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="D144" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>838</v>
@@ -17722,23 +15858,17 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="O144" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="P144" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q144" s="1" t="s">
-        <v>1046</v>
-      </c>
+        <v>1045</v>
+      </c>
+      <c r="O144" s="1"/>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
       <c r="T144" s="1"/>
@@ -17747,52 +15877,46 @@
       <c r="W144" s="1"/>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A145" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>397</v>
-      </c>
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
       <c r="D145" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>399</v>
+        <v>1046</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>906</v>
+        <v>838</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>559</v>
+        <v>917</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>400</v>
+        <v>773</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>401</v>
+        <v>1047</v>
       </c>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
@@ -17802,17 +15926,23 @@
       <c r="W145" s="1"/>
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
+      <c r="A146" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="D146" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>906</v>
@@ -17821,16 +15951,28 @@
         <v>559</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
-      <c r="L146" s="1"/>
-      <c r="M146" s="1"/>
-      <c r="N146" s="1"/>
-      <c r="O146" s="1"/>
-      <c r="P146" s="1"/>
-      <c r="Q146" s="1"/>
+      <c r="L146" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="P146" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q146" s="1" t="s">
+        <v>401</v>
+      </c>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
       <c r="T146" s="1"/>
@@ -17846,10 +15988,10 @@
         <v>402</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>906</v>
@@ -17862,15 +16004,9 @@
       </c>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
-      <c r="L147" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M147" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="N147" s="1" t="s">
-        <v>593</v>
-      </c>
+      <c r="L147" s="1"/>
+      <c r="M147" s="1"/>
+      <c r="N147" s="1"/>
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
@@ -17882,129 +16018,127 @@
       <c r="W147" s="1"/>
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A148" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>409</v>
-      </c>
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
       <c r="D148" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>935</v>
+        <v>405</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1362</v>
+        <v>906</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>54</v>
+        <v>559</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>411</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="J148" s="1"/>
       <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
-        <v>407</v>
+        <v>35</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="O148" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P148" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q148" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="R148" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S148" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="T148" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="U148" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="V148" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="W148" s="1" t="s">
-        <v>935</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="O148" s="1"/>
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1"/>
+      <c r="R148" s="1"/>
+      <c r="S148" s="1"/>
+      <c r="T148" s="1"/>
+      <c r="U148" s="1"/>
+      <c r="V148" s="1"/>
+      <c r="W148" s="1"/>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>417</v>
+        <v>410</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>1048</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1049</v>
+        <v>411</v>
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q149" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="R149" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S149" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="T149" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="U149" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="V149" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="W149" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="M149" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="N149" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
-      <c r="Q149" s="1"/>
-      <c r="R149" s="1"/>
-      <c r="S149" s="1"/>
-      <c r="T149" s="1"/>
-      <c r="U149" s="1"/>
-      <c r="V149" s="1"/>
-      <c r="W149" s="1"/>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A150" s="1"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
+      <c r="B150" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>414</v>
+      </c>
       <c r="D150" s="1" t="s">
         <v>412</v>
       </c>
@@ -18012,19 +16146,19 @@
         <v>415</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1284</v>
+        <v>417</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1285</v>
+        <v>902</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>724</v>
+        <v>54</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>590</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="1" t="s">
@@ -18034,7 +16168,7 @@
         <v>415</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>739</v>
+        <v>416</v>
       </c>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
@@ -18046,34 +16180,40 @@
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
     </row>
-    <row r="151" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
-      <c r="D151" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>1360</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>1358</v>
+      <c r="D151" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>1287</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="1"/>
+        <v>1288</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>1051</v>
+      </c>
       <c r="K151" s="1"/>
-      <c r="L151" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="M151" s="5" t="s">
-        <v>895</v>
-      </c>
-      <c r="N151" s="5" t="s">
-        <v>1359</v>
+      <c r="L151" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>739</v>
       </c>
       <c r="O151" s="1"/>
       <c r="P151" s="1"/>
@@ -18175,7 +16315,7 @@
         <v>436</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>433</v>
@@ -18204,7 +16344,7 @@
         <v>52</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>909</v>
@@ -18243,7 +16383,7 @@
         <v>159</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>909</v>
@@ -18265,7 +16405,7 @@
         <v>159</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
@@ -18279,25 +16419,25 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>1055</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>558</v>
@@ -18335,7 +16475,7 @@
         <v>438</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>911</v>
@@ -18360,13 +16500,13 @@
         <v>439</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>438</v>
       </c>
       <c r="Q157" s="1" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="R157" s="5" t="s">
         <v>426</v>
@@ -18375,7 +16515,7 @@
         <v>438</v>
       </c>
       <c r="T157" s="5" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
@@ -18398,7 +16538,7 @@
         <v>448</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>913</v>
@@ -18410,7 +16550,7 @@
         <v>576</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1" t="s">
@@ -18420,7 +16560,7 @@
         <v>448</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
@@ -18449,7 +16589,7 @@
         <v>451</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>913</v>
@@ -18461,7 +16601,7 @@
         <v>576</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="1" t="s">
@@ -18471,7 +16611,7 @@
         <v>451</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
@@ -18500,7 +16640,7 @@
         <v>454</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>913</v>
@@ -18512,7 +16652,7 @@
         <v>576</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K160" s="1"/>
       <c r="L160" s="1" t="s">
@@ -18522,7 +16662,7 @@
         <v>454</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
@@ -18551,7 +16691,7 @@
         <v>649</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>913</v>
@@ -18563,7 +16703,7 @@
         <v>576</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1" t="s">
@@ -18573,7 +16713,7 @@
         <v>649</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="O161" s="1"/>
       <c r="P161" s="1"/>
@@ -18602,7 +16742,7 @@
         <v>457</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>906</v>
@@ -18647,7 +16787,7 @@
         <v>458</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>913</v>
@@ -18659,7 +16799,7 @@
         <v>576</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="K163" s="1"/>
       <c r="L163" s="1" t="s">
@@ -18669,7 +16809,7 @@
         <v>458</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="O163" s="1"/>
       <c r="P163" s="1"/>
@@ -18698,10 +16838,10 @@
         <v>459</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>558</v>
@@ -18710,7 +16850,7 @@
         <v>576</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="1" t="s">
@@ -18749,30 +16889,24 @@
         <v>467</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="K165" s="1"/>
-      <c r="L165" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="M165" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="N165" s="1" t="s">
-        <v>1365</v>
-      </c>
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+      <c r="N165" s="1"/>
       <c r="O165" s="1"/>
       <c r="P165" s="1"/>
       <c r="Q165" s="1"/>
@@ -18800,7 +16934,7 @@
         <v>468</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>902</v>
@@ -18849,7 +16983,7 @@
         <v>469</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>902</v>
@@ -18898,19 +17032,19 @@
         <v>469</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="K168" s="1"/>
       <c r="L168" s="1" t="s">
@@ -18922,15 +17056,9 @@
       <c r="N168" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="O168" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="P168" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q168" s="1" t="s">
-        <v>1366</v>
-      </c>
+      <c r="O168" s="1"/>
+      <c r="P168" s="1"/>
+      <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
@@ -18955,19 +17083,19 @@
         <v>475</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="K169" s="1"/>
       <c r="L169" s="1" t="s">
@@ -19006,7 +17134,7 @@
         <v>479</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>902</v>
@@ -19015,7 +17143,7 @@
         <v>54</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
@@ -19055,7 +17183,7 @@
         <v>482</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>824</v>
@@ -19064,10 +17192,10 @@
         <v>54</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="K171" s="1"/>
       <c r="L171" s="1" t="s">
@@ -19106,7 +17234,7 @@
         <v>482</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>906</v>
@@ -19115,7 +17243,7 @@
         <v>559</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
@@ -19149,7 +17277,7 @@
         <v>488</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>902</v>
@@ -19158,7 +17286,7 @@
         <v>54</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -19183,7 +17311,7 @@
         <v>489</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>962</v>
@@ -19192,7 +17320,7 @@
         <v>489</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>906</v>
@@ -19201,7 +17329,7 @@
         <v>559</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
@@ -19229,19 +17357,19 @@
         <v>491</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
@@ -19274,19 +17402,19 @@
         <v>491</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
@@ -19319,19 +17447,19 @@
         <v>494</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -19355,7 +17483,7 @@
         <v>495</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>476</v>
@@ -19364,7 +17492,7 @@
         <v>495</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>906</v>
@@ -19373,7 +17501,7 @@
         <v>559</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
@@ -19401,19 +17529,19 @@
         <v>751</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
@@ -19440,17 +17568,17 @@
         <v>751</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="K180" s="1"/>
       <c r="L180" s="1"/>
@@ -19468,34 +17596,34 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>496</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="K181" s="1"/>
       <c r="L181" s="1" t="s">
@@ -19505,7 +17633,7 @@
         <v>496</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="O181" s="1" t="s">
         <v>476</v>
@@ -19523,7 +17651,7 @@
         <v>496</v>
       </c>
       <c r="T181" s="1" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="U181" s="1" t="s">
         <v>476</v>
@@ -19543,7 +17671,7 @@
         <v>498</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>476</v>
@@ -19552,7 +17680,7 @@
         <v>498</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>906</v>
@@ -19561,7 +17689,7 @@
         <v>559</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
@@ -19595,19 +17723,19 @@
         <v>498</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="K183" s="1"/>
       <c r="L183" s="1" t="s">
@@ -19617,7 +17745,7 @@
         <v>498</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
@@ -19640,38 +17768,38 @@
         <v>800</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="O184" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="P184" s="1" t="s">
         <v>499</v>
@@ -19680,22 +17808,22 @@
         <v>961</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="S184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="T184" s="1" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="U184" s="1" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="V184" s="1" t="s">
         <v>499</v>
       </c>
       <c r="W184" s="1" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.2">
@@ -19709,17 +17837,17 @@
         <v>499</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="K185" s="1"/>
       <c r="L185" s="1"/>
@@ -19740,20 +17868,20 @@
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>498</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>906</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -19764,16 +17892,16 @@
         <v>498</v>
       </c>
       <c r="N186" s="1" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="P186" s="1" t="s">
         <v>498</v>
       </c>
       <c r="Q186" s="1" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
@@ -19784,7 +17912,7 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>498</v>
@@ -19793,25 +17921,25 @@
         <v>969</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>498</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="K187" s="1"/>
       <c r="L187" s="1" t="s">
@@ -19821,7 +17949,7 @@
         <v>498</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="O187" s="1" t="s">
         <v>476</v>
@@ -19830,16 +17958,16 @@
         <v>498</v>
       </c>
       <c r="Q187" s="1" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="R187" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="S187" s="1" t="s">
         <v>498</v>
       </c>
       <c r="T187" s="1" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="U187" s="1" t="s">
         <v>962</v>
@@ -19848,7 +17976,7 @@
         <v>498</v>
       </c>
       <c r="W187" s="1" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.2">
@@ -19868,7 +17996,7 @@
         <v>606</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>906</v>
@@ -19890,7 +18018,7 @@
         <v>606</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>603</v>
@@ -19925,7 +18053,7 @@
         <v>520</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>902</v>
@@ -19968,13 +18096,13 @@
         <v>521</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>872</v>
@@ -20013,7 +18141,7 @@
         <v>522</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>902</v>
@@ -20056,19 +18184,19 @@
         <v>522</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="K192" s="1"/>
       <c r="L192" s="1"/>
@@ -20101,19 +18229,19 @@
         <v>525</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="K193" s="1"/>
       <c r="L193" s="1"/>
@@ -20146,7 +18274,7 @@
         <v>529</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>902</v>
@@ -20189,7 +18317,7 @@
         <v>532</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>904</v>
@@ -20232,7 +18360,7 @@
         <v>536</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>904</v>
@@ -20275,13 +18403,13 @@
         <v>270</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>905</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>574</v>
@@ -20330,31 +18458,31 @@
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="H198" s="1"/>
       <c r="I198" s="1" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="J198" s="1"/>
       <c r="K198" s="1"/>
       <c r="L198" s="1" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
@@ -20391,7 +18519,7 @@
         <v>958</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -20420,7 +18548,7 @@
         <v>278</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>902</v>
@@ -20432,7 +18560,7 @@
         <v>580</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="K200" s="1"/>
       <c r="L200" s="1"/>
@@ -20459,7 +18587,7 @@
         <v>278</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>902</v>
@@ -20471,7 +18599,7 @@
         <v>580</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="K201" s="1"/>
       <c r="L201" s="1"/>
@@ -20504,7 +18632,7 @@
         <v>278</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>902</v>
@@ -20547,7 +18675,7 @@
         <v>278</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>902</v>
@@ -20559,7 +18687,7 @@
         <v>577</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="K203" s="1"/>
       <c r="L203" s="1"/>
@@ -20592,7 +18720,7 @@
         <v>278</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>902</v>
@@ -20604,7 +18732,7 @@
         <v>577</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="K204" s="1"/>
       <c r="L204" s="1"/>
@@ -20628,7 +18756,7 @@
         <v>273</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>541</v>
@@ -20666,7 +18794,7 @@
         <v>270</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
@@ -20692,7 +18820,7 @@
         <v>443</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>902</v>
@@ -20767,7 +18895,7 @@
         <v>549</v>
       </c>
       <c r="N207" s="1" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
@@ -20796,7 +18924,7 @@
         <v>553</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>902</v>
@@ -20816,7 +18944,7 @@
         <v>553</v>
       </c>
       <c r="N208" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
@@ -20839,19 +18967,19 @@
         <v>557</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
@@ -20878,19 +19006,19 @@
         <v>557</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="K210" s="1"/>
       <c r="L210" s="1"/>
@@ -20920,10 +19048,10 @@
         <v>567</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>586</v>
@@ -20957,10 +19085,10 @@
         <v>570</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>586</v>
@@ -20994,10 +19122,10 @@
         <v>573</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I213" s="1"/>
       <c r="J213" s="1"/>
@@ -21026,7 +19154,7 @@
         <v>323</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>902</v>
@@ -21075,7 +19203,7 @@
         <v>616</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>904</v>
@@ -21118,7 +19246,7 @@
         <v>620</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>904</v>
@@ -21167,7 +19295,7 @@
         <v>622</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>914</v>
@@ -21230,7 +19358,7 @@
         <v>627</v>
       </c>
       <c r="N218" s="1" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
@@ -21273,7 +19401,7 @@
         <v>929</v>
       </c>
       <c r="N219" s="1" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="O219" s="1"/>
       <c r="P219" s="1"/>
@@ -21302,7 +19430,7 @@
         <v>633</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>902</v>
@@ -21340,7 +19468,7 @@
         <v>633</v>
       </c>
       <c r="T220" s="1" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
@@ -21377,7 +19505,7 @@
         <v>634</v>
       </c>
       <c r="N221" s="1" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="O221" s="1"/>
       <c r="P221" s="1"/>
@@ -21400,7 +19528,7 @@
         <v>637</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>909</v>
@@ -21412,7 +19540,7 @@
         <v>575</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
@@ -21439,7 +19567,7 @@
         <v>638</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>909</v>
@@ -21451,7 +19579,7 @@
         <v>575</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -21478,7 +19606,7 @@
         <v>768</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>909</v>
@@ -21490,7 +19618,7 @@
         <v>575</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K224" s="1"/>
       <c r="L224" s="1"/>
@@ -21523,19 +19651,19 @@
         <v>642</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="K225" s="1"/>
       <c r="L225" s="1"/>
@@ -21562,7 +19690,7 @@
         <v>646</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>903</v>
@@ -21582,7 +19710,7 @@
         <v>646</v>
       </c>
       <c r="N226" s="1" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="O226" s="1"/>
       <c r="P226" s="1"/>
@@ -21611,7 +19739,7 @@
         <v>653</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>902</v>
@@ -21654,7 +19782,7 @@
         <v>657</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>902</v>
@@ -21691,19 +19819,19 @@
         <v>501</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -21736,13 +19864,13 @@
         <v>838</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K230" s="1"/>
       <c r="L230" s="1"/>
@@ -21775,13 +19903,13 @@
         <v>838</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K231" s="1"/>
       <c r="L231" s="1"/>
@@ -21814,13 +19942,13 @@
         <v>838</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K232" s="1"/>
       <c r="L232" s="1"/>
@@ -21853,13 +19981,13 @@
         <v>838</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
@@ -21892,13 +20020,13 @@
         <v>838</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K234" s="1"/>
       <c r="L234" s="1"/>
@@ -21931,13 +20059,13 @@
         <v>838</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -21964,19 +20092,19 @@
         <v>502</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="K236" s="1"/>
       <c r="L236" s="1" t="s">
@@ -21986,7 +20114,7 @@
         <v>502</v>
       </c>
       <c r="N236" s="1" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
@@ -22015,13 +20143,13 @@
         <v>838</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
@@ -22054,13 +20182,13 @@
         <v>838</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
@@ -22093,13 +20221,13 @@
         <v>838</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
@@ -22132,13 +20260,13 @@
         <v>838</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K240" s="1"/>
       <c r="L240" s="1"/>
@@ -22171,13 +20299,13 @@
         <v>838</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K241" s="1"/>
       <c r="L241" s="1"/>
@@ -22210,13 +20338,13 @@
         <v>838</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K242" s="1"/>
       <c r="L242" s="1"/>
@@ -22249,13 +20377,13 @@
         <v>838</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K243" s="1"/>
       <c r="L243" s="1"/>
@@ -22288,13 +20416,13 @@
         <v>838</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K244" s="1"/>
       <c r="L244" s="1"/>
@@ -22327,13 +20455,13 @@
         <v>838</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K245" s="1"/>
       <c r="L245" s="1"/>
@@ -22366,13 +20494,13 @@
         <v>838</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K246" s="1"/>
       <c r="L246" s="1"/>
@@ -22405,19 +20533,19 @@
         <v>715</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="K247" s="1"/>
       <c r="L247" s="1"/>
@@ -22450,7 +20578,7 @@
         <v>505</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>902</v>
@@ -22470,7 +20598,7 @@
         <v>505</v>
       </c>
       <c r="N248" s="1" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="O248" s="1"/>
       <c r="P248" s="1"/>
@@ -22499,7 +20627,7 @@
         <v>505</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>902</v>
@@ -22519,7 +20647,7 @@
         <v>505</v>
       </c>
       <c r="N249" s="1" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="O249" s="1"/>
       <c r="P249" s="1"/>
@@ -22542,7 +20670,7 @@
         <v>668</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>902</v>
@@ -22587,10 +20715,10 @@
         <v>953</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>952</v>
@@ -22626,13 +20754,13 @@
         <v>838</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>585</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="K252" s="1"/>
       <c r="L252" s="1"/>
@@ -22656,13 +20784,13 @@
         <v>35</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="H253" s="1"/>
       <c r="I253" s="1" t="s">
@@ -22671,13 +20799,13 @@
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
       <c r="L253" s="1" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="N253" s="1" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
@@ -22697,13 +20825,13 @@
         <v>35</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="H254" s="1"/>
       <c r="I254" s="1" t="s">
@@ -22712,13 +20840,13 @@
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
       <c r="L254" s="1" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="M254" s="1" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="N254" s="1" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="O254" s="1"/>
       <c r="P254" s="1"/>
@@ -22750,7 +20878,7 @@
         <v>835</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>724</v>
@@ -22776,7 +20904,7 @@
         <v>822</v>
       </c>
       <c r="Q255" s="1" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
@@ -22811,7 +20939,7 @@
         <v>558</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -22848,7 +20976,7 @@
         <v>558</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -22876,7 +21004,7 @@
         <v>680</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>902</v>
@@ -22913,7 +21041,7 @@
         <v>682</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>902</v>
@@ -22950,7 +21078,7 @@
         <v>684</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>902</v>
@@ -23024,7 +21152,7 @@
         <v>436</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>903</v>
@@ -23046,7 +21174,7 @@
         <v>436</v>
       </c>
       <c r="N262" s="1" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="O262" s="1"/>
       <c r="P262" s="1"/>
@@ -23069,7 +21197,7 @@
         <v>429</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>902</v>
@@ -23112,7 +21240,7 @@
         <v>691</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>902</v>
@@ -23121,7 +21249,7 @@
         <v>54</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -23158,7 +21286,7 @@
         <v>559</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -23192,7 +21320,7 @@
         <v>697</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>902</v>
@@ -23229,7 +21357,7 @@
         <v>698</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>902</v>
@@ -23266,7 +21394,7 @@
         <v>699</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>902</v>
@@ -23303,7 +21431,7 @@
         <v>700</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>906</v>
@@ -23340,7 +21468,7 @@
         <v>316</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>902</v>
@@ -23383,7 +21511,7 @@
         <v>388</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>902</v>
@@ -23420,7 +21548,7 @@
         <v>701</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>906</v>
@@ -23457,7 +21585,7 @@
         <v>702</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>906</v>
@@ -23494,7 +21622,7 @@
         <v>398</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>902</v>
@@ -23531,7 +21659,7 @@
         <v>703</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>906</v>
@@ -23568,7 +21696,7 @@
         <v>704</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>906</v>
@@ -23605,7 +21733,7 @@
         <v>705</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>906</v>
@@ -23648,7 +21776,7 @@
         <v>968</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>906</v>
@@ -23657,7 +21785,7 @@
         <v>559</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="J278" s="1"/>
       <c r="K278" s="1"/>
@@ -23728,7 +21856,7 @@
         <v>469</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>902</v>
@@ -23771,7 +21899,7 @@
         <v>710</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>906</v>
@@ -23810,10 +21938,10 @@
         <v>711</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="H282" s="1" t="s">
         <v>558</v>
@@ -23847,10 +21975,10 @@
         <v>712</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>558</v>
@@ -23884,7 +22012,7 @@
         <v>713</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>906</v>
@@ -23921,7 +22049,7 @@
         <v>720</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>902</v>
@@ -23958,19 +22086,19 @@
         <v>689</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="K286" s="1"/>
       <c r="L286" s="1"/>
@@ -23997,7 +22125,7 @@
         <v>722</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>838</v>
@@ -24006,7 +22134,7 @@
         <v>54</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>847</v>
@@ -24042,16 +22170,16 @@
         <v>741</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
@@ -24118,7 +22246,7 @@
         <v>743</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>909</v>
@@ -24130,7 +22258,7 @@
         <v>861</v>
       </c>
       <c r="J290" s="1" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="K290" s="1"/>
       <c r="L290" s="1"/>
@@ -24245,7 +22373,7 @@
         <v>270</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1361</v>
+        <v>982</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>904</v>
@@ -24265,7 +22393,7 @@
         <v>270</v>
       </c>
       <c r="N293" s="1" t="s">
-        <v>982</v>
+        <v>1209</v>
       </c>
       <c r="O293" s="1"/>
       <c r="P293" s="1"/>
@@ -24300,13 +22428,13 @@
         <v>838</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J294" s="1" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="K294" s="1"/>
       <c r="L294" s="1" t="s">
@@ -24316,7 +22444,7 @@
         <v>294</v>
       </c>
       <c r="N294" s="1" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="O294" s="1" t="s">
         <v>681</v>
@@ -24351,7 +22479,7 @@
         <v>749</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>902</v>
@@ -24388,7 +22516,7 @@
         <v>331</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>907</v>
@@ -24408,7 +22536,7 @@
         <v>331</v>
       </c>
       <c r="N296" s="1" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
@@ -24431,19 +22559,19 @@
         <v>751</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>576</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="K297" s="1"/>
       <c r="L297" s="1"/>
@@ -24470,7 +22598,7 @@
         <v>443</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>902</v>
@@ -24507,7 +22635,7 @@
         <v>755</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>838</v>
@@ -24527,7 +22655,7 @@
         <v>755</v>
       </c>
       <c r="N299" s="1" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="O299" s="1"/>
       <c r="P299" s="1"/>
@@ -24550,7 +22678,7 @@
         <v>756</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>902</v>
@@ -24570,7 +22698,7 @@
         <v>756</v>
       </c>
       <c r="N300" s="1" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="O300" s="1"/>
       <c r="P300" s="1"/>
@@ -24593,19 +22721,19 @@
         <v>757</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="K301" s="1"/>
       <c r="L301" s="1" t="s">
@@ -24615,7 +22743,7 @@
         <v>757</v>
       </c>
       <c r="N301" s="1" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="O301" s="1"/>
       <c r="P301" s="1"/>
@@ -24638,7 +22766,7 @@
         <v>758</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>902</v>
@@ -24675,7 +22803,7 @@
         <v>759</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>909</v>
@@ -24687,7 +22815,7 @@
         <v>575</v>
       </c>
       <c r="J303" s="1" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="K303" s="1"/>
       <c r="L303" s="1"/>
@@ -24714,7 +22842,7 @@
         <v>763</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>910</v>
@@ -24757,7 +22885,7 @@
         <v>980</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
@@ -24771,7 +22899,7 @@
         <v>980</v>
       </c>
       <c r="N305" s="1" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
@@ -24791,7 +22919,7 @@
         <v>758</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>742</v>
@@ -24800,7 +22928,7 @@
         <v>927</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>909</v>
@@ -24812,7 +22940,7 @@
         <v>582</v>
       </c>
       <c r="J306" s="1" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="K306" s="1"/>
       <c r="L306" s="1"/>
@@ -24839,7 +22967,7 @@
         <v>765</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>906</v>
@@ -24848,7 +22976,7 @@
         <v>559</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="J307" s="1"/>
       <c r="K307" s="1"/>
@@ -24876,7 +23004,7 @@
         <v>767</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>902</v>
@@ -24954,7 +23082,7 @@
         <v>335</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>902</v>
@@ -24999,7 +23127,7 @@
         <v>67</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>838</v>
@@ -25048,7 +23176,7 @@
         <v>762</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>909</v>
@@ -25060,7 +23188,7 @@
         <v>579</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="K312" s="1"/>
       <c r="L312" s="1"/>
@@ -25093,7 +23221,7 @@
         <v>785</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>902</v>
@@ -25113,7 +23241,7 @@
         <v>785</v>
       </c>
       <c r="N313" s="1" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="O313" s="1"/>
       <c r="P313" s="1"/>
@@ -25142,10 +23270,10 @@
         <v>838</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
@@ -25173,7 +23301,7 @@
         <v>892</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>906</v>
@@ -25218,7 +23346,7 @@
         <v>813</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>906</v>
@@ -25240,7 +23368,7 @@
         <v>813</v>
       </c>
       <c r="N316" s="1" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="O316" s="1"/>
       <c r="P316" s="1"/>
@@ -25263,13 +23391,13 @@
         <v>815</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -25298,13 +23426,13 @@
         <v>816</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -25330,10 +23458,10 @@
         <v>291</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="G319" s="5" t="s">
         <v>902</v>
@@ -25348,10 +23476,10 @@
         <v>291</v>
       </c>
       <c r="M319" s="5" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="N319" s="5" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="O319" s="1"/>
       <c r="P319" s="1"/>
@@ -25368,19 +23496,19 @@
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
       <c r="D320" s="1" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>817</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
@@ -25409,19 +23537,19 @@
         <v>818</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>838</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>872</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="K321" s="1"/>
       <c r="L321" s="1"/>
@@ -25445,10 +23573,10 @@
         <v>681</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>906</v>
@@ -25485,7 +23613,7 @@
         <v>114</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>906</v>
@@ -25505,7 +23633,7 @@
         <v>114</v>
       </c>
       <c r="N323" s="1" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="O323" s="1"/>
       <c r="P323" s="1"/>
@@ -25528,7 +23656,7 @@
         <v>821</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>910</v>
@@ -25540,7 +23668,7 @@
         <v>575</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="K324" s="1"/>
       <c r="L324" s="1"/>
@@ -25567,7 +23695,7 @@
         <v>180</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>909</v>
@@ -25579,7 +23707,7 @@
         <v>579</v>
       </c>
       <c r="J325" s="1" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -25606,7 +23734,7 @@
         <v>827</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>904</v>
@@ -25620,13 +23748,13 @@
       <c r="J326" s="1"/>
       <c r="K326" s="1"/>
       <c r="L326" s="1" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="M326" s="1" t="s">
         <v>827</v>
       </c>
       <c r="N326" s="1" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
@@ -25649,7 +23777,7 @@
         <v>830</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>904</v>
@@ -25854,7 +23982,7 @@
         <v>850</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>909</v>
@@ -25866,7 +23994,7 @@
         <v>575</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="K332" s="1"/>
       <c r="L332" s="1"/>
@@ -25960,7 +24088,7 @@
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
     </row>
-    <row r="335" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -25971,7 +24099,7 @@
         <v>69</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>902</v>
@@ -25984,15 +24112,9 @@
       </c>
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
-      <c r="L335" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="M335" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="N335" s="5" t="s">
-        <v>919</v>
-      </c>
+      <c r="L335" s="1"/>
+      <c r="M335" s="1"/>
+      <c r="N335" s="1"/>
       <c r="O335" s="1"/>
       <c r="P335" s="1"/>
       <c r="Q335" s="1"/>
@@ -26096,10 +24218,10 @@
         <v>874</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="H338" s="1" t="s">
         <v>724</v>
@@ -26118,7 +24240,7 @@
         <v>874</v>
       </c>
       <c r="N338" s="1" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
@@ -26141,7 +24263,7 @@
         <v>918</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>838</v>
@@ -26161,7 +24283,7 @@
         <v>918</v>
       </c>
       <c r="N339" s="1" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
@@ -26181,7 +24303,7 @@
         <v>62</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>381</v>
@@ -26190,7 +24312,7 @@
         <v>62</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>906</v>
@@ -26284,7 +24406,7 @@
         <v>875</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>724</v>
@@ -26357,16 +24479,16 @@
         <v>846</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="H344" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J344" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.2">
@@ -26386,7 +24508,7 @@
         <v>905</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>574</v>
@@ -26568,10 +24690,10 @@
         <v>565</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I350" s="1"/>
       <c r="J350" s="1"/>
@@ -26609,10 +24731,10 @@
         <v>888</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I351" s="1"/>
       <c r="J351" s="1"/>
@@ -26650,10 +24772,10 @@
         <v>568</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
@@ -26691,10 +24813,10 @@
         <v>571</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
@@ -26722,668 +24844,479 @@
   <autoFilter ref="A1:W1" xr:uid="{10C74089-6144-4719-863A-8F7B0AC96662}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="641" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="640" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="639" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="638" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="637" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="636" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="635" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="634" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="633" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="632" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="631" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="630" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="629" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="628" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="627" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="626" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="625" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="624" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="623" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="622" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="621" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="620" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="619" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="618" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="617" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="616" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="615" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="614" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="613" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="612" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="611" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="610" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="609" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="608" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="607" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="606" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="605" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="604" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="603" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="602" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="601" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="600" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="599" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="598" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="597" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="596" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="595" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="594" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="593" priority="291"/>
-    <cfRule type="duplicateValues" dxfId="592" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="591" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="590" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="589" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="588" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="587" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="586" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="585" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="584" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="583" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="582" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="581" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="580" priority="432"/>
-    <cfRule type="duplicateValues" dxfId="579" priority="431"/>
-    <cfRule type="duplicateValues" dxfId="578" priority="430"/>
-    <cfRule type="duplicateValues" dxfId="577" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="576" priority="429"/>
-    <cfRule type="duplicateValues" dxfId="575" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="574" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="573" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="572" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="571" priority="423"/>
-    <cfRule type="duplicateValues" dxfId="570" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="569" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="568" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="567" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="566" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="565" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="564" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="563" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="562" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="561" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="560" priority="473"/>
-    <cfRule type="duplicateValues" dxfId="559" priority="472"/>
-    <cfRule type="duplicateValues" dxfId="558" priority="471"/>
-    <cfRule type="duplicateValues" dxfId="557" priority="470"/>
-    <cfRule type="duplicateValues" dxfId="556" priority="469"/>
-    <cfRule type="duplicateValues" dxfId="555" priority="468"/>
-    <cfRule type="duplicateValues" dxfId="554" priority="467"/>
-    <cfRule type="duplicateValues" dxfId="553" priority="466"/>
-    <cfRule type="duplicateValues" dxfId="552" priority="465"/>
-    <cfRule type="duplicateValues" dxfId="551" priority="463"/>
-    <cfRule type="duplicateValues" dxfId="550" priority="462"/>
-    <cfRule type="duplicateValues" dxfId="549" priority="461"/>
-    <cfRule type="duplicateValues" dxfId="548" priority="460"/>
-    <cfRule type="duplicateValues" dxfId="547" priority="459"/>
-    <cfRule type="duplicateValues" dxfId="546" priority="458"/>
-    <cfRule type="duplicateValues" dxfId="545" priority="457"/>
-    <cfRule type="duplicateValues" dxfId="544" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="543" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="542" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="541" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="540" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="539" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="538" priority="464"/>
-    <cfRule type="duplicateValues" dxfId="537" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="536" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="535" priority="445"/>
-    <cfRule type="duplicateValues" dxfId="534" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="533" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="532" priority="442"/>
-    <cfRule type="duplicateValues" dxfId="531" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="530" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="529" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="528" priority="438"/>
-    <cfRule type="duplicateValues" dxfId="527" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="526" priority="436"/>
-    <cfRule type="duplicateValues" dxfId="525" priority="435"/>
-    <cfRule type="duplicateValues" dxfId="524" priority="434"/>
-    <cfRule type="duplicateValues" dxfId="523" priority="433"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F151">
-    <cfRule type="duplicateValues" dxfId="522" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="521" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="520" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="519" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="518" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="517" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="516" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="515" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="514" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="513" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="512" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="511" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="510" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="509" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="508" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="507" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="506" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="505" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="504" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="503" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="502" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="501" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="500" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="499" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="498" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="497" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="496" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="495" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="494" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="493" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="492" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="491" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="490" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="489" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="488" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="487" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="486" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="485" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="484" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="483" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="482" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="481" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="480" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="479" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="478" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="477" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="476" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="475" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="474" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="473" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="472" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="471" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="470" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="469" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="468" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="467" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="466" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="465" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="464" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="463" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="462" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F319">
-    <cfRule type="duplicateValues" dxfId="461" priority="681"/>
-    <cfRule type="duplicateValues" dxfId="460" priority="645"/>
-    <cfRule type="duplicateValues" dxfId="459" priority="644"/>
-    <cfRule type="duplicateValues" dxfId="458" priority="696"/>
-    <cfRule type="duplicateValues" dxfId="457" priority="695"/>
-    <cfRule type="duplicateValues" dxfId="456" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="455" priority="652"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="646"/>
-    <cfRule type="duplicateValues" dxfId="453" priority="647"/>
-    <cfRule type="duplicateValues" dxfId="452" priority="648"/>
-    <cfRule type="duplicateValues" dxfId="451" priority="649"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="650"/>
-    <cfRule type="duplicateValues" dxfId="449" priority="651"/>
-    <cfRule type="duplicateValues" dxfId="448" priority="653"/>
-    <cfRule type="duplicateValues" dxfId="447" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="446" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="445" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="444" priority="657"/>
-    <cfRule type="duplicateValues" dxfId="443" priority="658"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="659"/>
-    <cfRule type="duplicateValues" dxfId="441" priority="660"/>
-    <cfRule type="duplicateValues" dxfId="440" priority="661"/>
-    <cfRule type="duplicateValues" dxfId="439" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="438" priority="663"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="664"/>
-    <cfRule type="duplicateValues" dxfId="436" priority="665"/>
-    <cfRule type="duplicateValues" dxfId="435" priority="667"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="668"/>
-    <cfRule type="duplicateValues" dxfId="433" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="432" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="431" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="672"/>
-    <cfRule type="duplicateValues" dxfId="429" priority="673"/>
-    <cfRule type="duplicateValues" dxfId="428" priority="674"/>
-    <cfRule type="duplicateValues" dxfId="427" priority="675"/>
-    <cfRule type="duplicateValues" dxfId="426" priority="676"/>
-    <cfRule type="duplicateValues" dxfId="425" priority="677"/>
-    <cfRule type="duplicateValues" dxfId="424" priority="678"/>
-    <cfRule type="duplicateValues" dxfId="423" priority="679"/>
-    <cfRule type="duplicateValues" dxfId="422" priority="680"/>
-    <cfRule type="duplicateValues" dxfId="421" priority="682"/>
-    <cfRule type="duplicateValues" dxfId="420" priority="683"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="684"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="685"/>
-    <cfRule type="duplicateValues" dxfId="417" priority="686"/>
-    <cfRule type="duplicateValues" dxfId="416" priority="687"/>
-    <cfRule type="duplicateValues" dxfId="415" priority="688"/>
-    <cfRule type="duplicateValues" dxfId="414" priority="689"/>
-    <cfRule type="duplicateValues" dxfId="413" priority="690"/>
-    <cfRule type="duplicateValues" dxfId="412" priority="691"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="692"/>
-    <cfRule type="duplicateValues" dxfId="410" priority="693"/>
-    <cfRule type="duplicateValues" dxfId="409" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="duplicateValues" dxfId="408" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="407" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="405" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="404" priority="326"/>
-    <cfRule type="duplicateValues" dxfId="403" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="402" priority="325"/>
-    <cfRule type="duplicateValues" dxfId="401" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="400" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="399" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="398" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="397" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="396" priority="356"/>
-    <cfRule type="duplicateValues" dxfId="395" priority="355"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="392" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="391" priority="327"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="389" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="387" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="385" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="343"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="363"/>
-    <cfRule type="duplicateValues" dxfId="380" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="377" priority="359"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="371" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="369" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="368" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="367" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="315"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="316"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="363" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="318"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="319"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="356" priority="337"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="349" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19">
-    <cfRule type="duplicateValues" dxfId="348" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="347" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="345" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="344" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="342" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="341" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="337" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="329" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="322" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="314" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="duplicateValues" dxfId="288" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="376"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="377"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="379"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="380"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="381"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="421"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="422"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="417"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="414"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="412"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="411"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="409"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="407"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="406"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="405"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="404"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="403"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="402"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="401"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="390"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="400"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="399"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="398"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="392"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="388"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="385"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="384"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="365"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="368"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="369"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="372"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="373"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N151">
-    <cfRule type="duplicateValues" dxfId="229" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N319">
-    <cfRule type="duplicateValues" dxfId="168" priority="622"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="621"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="619"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="618"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="617"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="616"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="614"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="613"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="591"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="592"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="594"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="595"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="596"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="597"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="598"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="599"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="600"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="601"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="612"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="602"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="603"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="604"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="605"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="606"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="607"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="608"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="609"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="610"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="611"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="643"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="642"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="641"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="640"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="639"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="638"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="637"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="636"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="635"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="634"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="633"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="632"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="631"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="630"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="629"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="628"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="627"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="626"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="625"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="624"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="623"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N335">
-    <cfRule type="duplicateValues" dxfId="115" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T157">
-    <cfRule type="duplicateValues" dxfId="54" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="485"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="491"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="497"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="498"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="505"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="516"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="515"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="513"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="512"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="511"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="536"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="535"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="534"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="533"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="532"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="530"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="529"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="528"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="527"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="526"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="525"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="524"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="523"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="522"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="521"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="519"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="518"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="517"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="345"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
